--- a/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
+++ b/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
@@ -30,11 +30,13 @@
     <sheet name="18 Canada Market" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="19 Canada Regulatory" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="20 GTM Recommendation" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="21 Launch Plan" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="22 Risk Register" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="23 KPI Dashboard" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="24 Sources" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="25 Glossary" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Go-NoGo Decision" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Battlecards" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="21 Launch Plan" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="22 Risk Register" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="23 KPI Dashboard" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="24 Sources" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="25 Glossary" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'07 Comparison Matrix'!$A$3:$L$11</definedName>
@@ -51,7 +53,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -162,6 +164,38 @@
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0014304F"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001155CC"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001155CC"/>
+      <sz val="8"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="14">
@@ -302,7 +336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -454,6 +488,121 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -542,7 +691,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Selected Category Sizes (US, $B)</a:t>
+              <a:t>Category Sizes (US, $B)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -557,7 +706,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!B61</f>
+              <f>'Dashboard'!B71</f>
             </strRef>
           </tx>
           <spPr>
@@ -567,12 +716,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$A$62:$A$67</f>
+              <f>'Dashboard'!$A$72:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$B$62:$B$67</f>
+              <f>'Dashboard'!$B$72:$B$77</f>
             </numRef>
           </val>
         </ser>
@@ -598,21 +747,6 @@
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>$B</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -636,7 +770,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Revenue Trajectory ($M) — Poppi vs OLIPOP</a:t>
+              <a:t>Revenue Trajectory ($M)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -650,7 +784,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!F61</f>
+              <f>'Dashboard'!F71</f>
             </strRef>
           </tx>
           <spPr>
@@ -668,22 +802,21 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$E$62:$E$66</f>
+              <f>'Dashboard'!$E$72:$E$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$F$62:$F$66</f>
+              <f>'Dashboard'!$F$72:$F$76</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
         <ser>
           <idx val="1"/>
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!G61</f>
+              <f>'Dashboard'!G71</f>
             </strRef>
           </tx>
           <spPr>
@@ -701,15 +834,14 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Dashboard'!$E$62:$E$66</f>
+              <f>'Dashboard'!$E$72:$E$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$G$62:$G$66</f>
+              <f>'Dashboard'!$G$72:$G$76</f>
             </numRef>
           </val>
-          <smooth val="0"/>
         </ser>
         <axId val="10"/>
         <axId val="100"/>
@@ -732,21 +864,6 @@
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>$M</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -773,7 +890,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Modern Soda Share 2024 (%)</a:t>
+              <a:t>Modern Soda Share '24 (%)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -787,7 +904,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!J61</f>
+              <f>'Dashboard'!J71</f>
             </strRef>
           </tx>
           <spPr>
@@ -797,18 +914,17 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$I$62:$I$67</f>
+              <f>'Dashboard'!$I$72:$I$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$J$62:$J$67</f>
+              <f>'Dashboard'!$J$72:$J$77</f>
             </numRef>
           </val>
         </ser>
         <dLbls>
           <showVal val="1"/>
-          <showPercent val="0"/>
         </dLbls>
         <firstSliceAng val="0"/>
       </pieChart>
@@ -834,7 +950,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Weighted Competitive Score (1–5)</a:t>
+              <a:t>Weighted Competitive Score</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -849,7 +965,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Dashboard'!N61</f>
+              <f>'Dashboard'!N71</f>
             </strRef>
           </tx>
           <spPr>
@@ -859,12 +975,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Dashboard'!$M$62:$M$68</f>
+              <f>'Dashboard'!$M$72:$M$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Dashboard'!$N$62:$N$68</f>
+              <f>'Dashboard'!$N$72:$N$78</f>
             </numRef>
           </val>
         </ser>
@@ -916,7 +1032,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>MUV Model — Net Revenue vs Contribution (CAD)</a:t>
+              <a:t>MUV Scenario P&amp;L — Net Rev &amp; EBITDA (CAD)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -931,7 +1047,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Financial Model'!B24</f>
+              <f>'Financial Model'!B36</f>
             </strRef>
           </tx>
           <spPr>
@@ -941,12 +1057,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Financial Model'!$C$20:$E$20</f>
+              <f>'Financial Model'!$C$32:$E$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Financial Model'!$C$24:$E$24</f>
+              <f>'Financial Model'!$C$36:$E$36</f>
             </numRef>
           </val>
         </ser>
@@ -955,7 +1071,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Financial Model'!B27</f>
+              <f>'Financial Model'!B43</f>
             </strRef>
           </tx>
           <spPr>
@@ -965,12 +1081,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Financial Model'!$C$20:$E$20</f>
+              <f>'Financial Model'!$C$32:$E$32</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Financial Model'!$C$27:$E$27</f>
+              <f>'Financial Model'!$C$43:$E$43</f>
             </numRef>
           </val>
         </ser>
@@ -996,21 +1112,6 @@
         </scaling>
         <axPos val="l"/>
         <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>CAD</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -1034,7 +1135,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="5040000" cy="2520000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1056,7 +1157,7 @@
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="5040000" cy="2520000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1075,10 +1176,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3960000" cy="2700000"/>
+    <ext cx="3600000" cy="2520000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1097,10 +1198,10 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="5040000" cy="2520000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -1119,10 +1220,10 @@
     <from>
       <col>9</col>
       <colOff>0</colOff>
-      <row>23</row>
+      <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2700000"/>
+    <ext cx="5040000" cy="2520000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -1430,7 +1531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H20"/>
+  <dimension ref="A2:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1620,24 +1721,104 @@
       <c r="G20" s="34" t="n"/>
       <c r="H20" s="35" t="n"/>
     </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>INTERACTIVE TABS (gold) — built to be used, not just read:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="B23" s="90" t="inlineStr">
+        <is>
+          <t>▸ Dashboard</t>
+        </is>
+      </c>
+      <c r="C23" s="91" t="inlineStr">
+        <is>
+          <t>5 live charts + KPI strip — the one-screen snapshot</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="B24" s="90" t="inlineStr">
+        <is>
+          <t>▸ Financial Model</t>
+        </is>
+      </c>
+      <c r="C24" s="91" t="inlineStr">
+        <is>
+          <t>Pick a scenario (Conservative/Base/Aggressive) and the whole P&amp;L, break-even &amp; sensitivity heatmap recompute</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="B25" s="90" t="inlineStr">
+        <is>
+          <t>▸ Go-NoGo Decision</t>
+        </is>
+      </c>
+      <c r="C25" s="91" t="inlineStr">
+        <is>
+          <t>Edit weights/scores; the verdict (GO / GO-conditional / NO-GO) auto-computes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="B26" s="90" t="inlineStr">
+        <is>
+          <t>▸ Battlecards</t>
+        </is>
+      </c>
+      <c r="C26" s="91" t="inlineStr">
+        <is>
+          <t>One quick-reference block per key competitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="B27" s="90" t="inlineStr">
+        <is>
+          <t>▸ 01 Contents</t>
+        </is>
+      </c>
+      <c r="C27" s="91" t="inlineStr">
+        <is>
+          <t>Click any tab name to jump straight to it</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="21">
+    <mergeCell ref="C25:H25"/>
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="B20:H20"/>
     <mergeCell ref="C11:H11"/>
-    <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C10:H10"/>
-    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="C27:H27"/>
     <mergeCell ref="B4:H4"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="C9:H9"/>
-    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="C23:H23"/>
     <mergeCell ref="C8:H8"/>
     <mergeCell ref="A15:G15"/>
-    <mergeCell ref="C12:H12"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="C26:H26"/>
     <mergeCell ref="B19:H19"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="C7:H7"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -1658,7 +1839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1681,6 +1862,11 @@
           <t>Core Competitor Comparison Matrix</t>
         </is>
       </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -2264,6 +2450,9 @@
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A12:L12"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -2284,7 +2473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2301,6 +2490,11 @@
           <t>Extended Competitor Landscape (~30 brands)</t>
         </is>
       </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
@@ -3679,6 +3873,9 @@
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A20:F20"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -3699,7 +3896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3715,6 +3912,11 @@
           <t>Channel &amp; Retail Strategy</t>
         </is>
       </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
@@ -3983,6 +4185,9 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A13:E13"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -4003,7 +4208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4015,6 +4220,11 @@
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Channel Economics &amp; Margin Waterfall</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
         </is>
       </c>
     </row>
@@ -4532,6 +4742,9 @@
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A13:D13"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -4552,7 +4765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4568,6 +4781,11 @@
           <t>Formulation &amp; Positioning — the claim that won</t>
         </is>
       </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -4828,6 +5046,9 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A12:E12"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -4848,7 +5069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4863,6 +5084,11 @@
           <t>Marketing &amp; Brand Build — the virality engine</t>
         </is>
       </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -5077,6 +5303,9 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A12:D12"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -5097,7 +5326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5113,6 +5342,11 @@
           <t>Launch Playbook Teardowns — phased GTM timelines</t>
         </is>
       </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -5292,6 +5526,9 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A9:E9"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -5312,7 +5549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5325,6 +5562,11 @@
           <t>Success Patterns &amp; Failure Modes</t>
         </is>
       </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
@@ -5476,6 +5718,9 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A12:B12"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -5496,7 +5741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5513,6 +5758,11 @@
           <t>Financial Outcomes &amp; M&amp;A Comps</t>
         </is>
       </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -5883,6 +6133,9 @@
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -5903,7 +6156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5919,6 +6172,11 @@
           <t>Per-Brand SWOT</t>
         </is>
       </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -6113,6 +6371,9 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -6133,7 +6394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6147,6 +6408,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -6159,313 +6421,361 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="92" t="inlineStr">
         <is>
           <t>00 Cover</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="58" t="inlineStr">
         <is>
           <t>Title, scope, caveats, confidence legend</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="93" t="inlineStr">
         <is>
           <t>01 Contents</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="60" t="inlineStr">
         <is>
           <t>This page</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="92" t="inlineStr">
         <is>
           <t>02 Executive Summary</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>The thesis, the 7 findings that matter, the recommendation</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="B6" s="58" t="inlineStr">
+        <is>
+          <t>Thesis, 7 findings, recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="94" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="B7" s="60" t="inlineStr">
+        <is>
+          <t>Visual snapshot — 5 charts + KPI strip</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="94" t="inlineStr">
+        <is>
+          <t>Financial Model</t>
+        </is>
+      </c>
+      <c r="B8" s="58" t="inlineStr">
+        <is>
+          <t>Scenario-driven P&amp;L, break-even, sensitivity heatmap (interactive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="93" t="inlineStr">
         <is>
           <t>03 Methodology</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Research design, source hierarchy, confidence framework, limitations</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="B9" s="60" t="inlineStr">
+        <is>
+          <t>Research design, source hierarchy, confidence, limitations</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="92" t="inlineStr">
         <is>
           <t>04 Market Sizing</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>TAM/SAM/SOM, category sizes &amp; growth, US + Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="B10" s="58" t="inlineStr">
+        <is>
+          <t>TAM/SAM/SOM, category sizes &amp; growth (US + Canada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="93" t="inlineStr">
         <is>
           <t>05 Trends &amp; Macro</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Sugar reduction, GLP-1, gut health, beauty-from-within, white space</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="B11" s="60" t="inlineStr">
+        <is>
+          <t>Sugar, GLP-1, gut health, beauty-from-within, white space</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="92" t="inlineStr">
         <is>
           <t>06 Consumer</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Segmentation, collagen buyer, efficacy-evidence risk, buyer criteria</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="B12" s="58" t="inlineStr">
+        <is>
+          <t>Segmentation, collagen buyer, efficacy risk, buyer criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="93" t="inlineStr">
         <is>
           <t>07 Comparison Matrix</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>8 core brands, key metrics side by side</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="B13" s="60" t="inlineStr">
+        <is>
+          <t>8 core brands side by side (auto-filter)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="92" t="inlineStr">
         <is>
           <t>08 Extended Landscape</t>
         </is>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B14" s="58" t="inlineStr">
         <is>
           <t>~30 brands across 6 sub-categories</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="93" t="inlineStr">
         <is>
           <t>09 Channel &amp; Retail</t>
         </is>
       </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>Launch channel &amp; expansion sequence per brand</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="B15" s="60" t="inlineStr">
+        <is>
+          <t>Launch channel &amp; expansion sequence</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="92" t="inlineStr">
         <is>
           <t>10 Channel Economics</t>
         </is>
       </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Margin waterfall, retailer/distributor/trade-spend, DTC/Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="B16" s="58" t="inlineStr">
+        <is>
+          <t>Margin waterfall, distributor/trade-spend, DTC/Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="93" t="inlineStr">
         <is>
           <t>11 Formulation</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B17" s="60" t="inlineStr">
         <is>
           <t>The winning claim, hero ingredient, claim risk</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="92" t="inlineStr">
         <is>
           <t>12 Marketing</t>
         </is>
       </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>Founder story, virality engine, what moved the needle</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="B18" s="58" t="inlineStr">
+        <is>
+          <t>Founder story, virality engine</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="93" t="inlineStr">
         <is>
           <t>13 Launch Playbooks</t>
         </is>
       </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>Phased GTM timelines (Poppi/OLIPOP/LMNT/Liquid I.V./Celsius)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="B19" s="60" t="inlineStr">
+        <is>
+          <t>Phased GTM timelines</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="92" t="inlineStr">
         <is>
           <t>14 Patterns &amp; Failures</t>
         </is>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B20" s="58" t="inlineStr">
         <is>
           <t>7 success patterns + 6 failure modes</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="93" t="inlineStr">
         <is>
           <t>15 Outcomes &amp; M&amp;A</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B21" s="60" t="inlineStr">
         <is>
           <t>Revenue, funding, valuations, acquisition comps</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="92" t="inlineStr">
         <is>
           <t>16 SWOT</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>Per-brand strengths/weaknesses/opportunities/threats</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="B22" s="58" t="inlineStr">
+        <is>
+          <t>Per-brand SWOT incl. MUV</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="93" t="inlineStr">
         <is>
           <t>17 Scoring Model</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>Weighted competitive scoring (editable weights)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="B23" s="60" t="inlineStr">
+        <is>
+          <t>Weighted competitive scoring (heatmap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="92" t="inlineStr">
         <is>
           <t>18 Canada Market</t>
         </is>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B24" s="58" t="inlineStr">
         <is>
           <t>Retail banners &amp; share, entry playbooks, pricing</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="93" t="inlineStr">
         <is>
           <t>19 Canada Regulatory</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>NHP vs Food vs Supplemented Foods; SFCI; collagen/caffeine; Bill 96</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="B25" s="60" t="inlineStr">
+        <is>
+          <t>NHP vs Food vs Supplemented Foods; SFCI; caffeine; Bill 96</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="92" t="inlineStr">
         <is>
           <t>20 GTM Recommendation</t>
         </is>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B26" s="58" t="inlineStr">
         <is>
           <t>The MUV go-to-market thesis &amp; decisions</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="94" t="inlineStr">
+        <is>
+          <t>Go-NoGo Decision</t>
+        </is>
+      </c>
+      <c r="B27" s="60" t="inlineStr">
+        <is>
+          <t>Weighted gate scorecard with auto verdict (interactive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="94" t="inlineStr">
+        <is>
+          <t>Battlecards</t>
+        </is>
+      </c>
+      <c r="B28" s="58" t="inlineStr">
+        <is>
+          <t>One-page-per-competitor quick reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="93" t="inlineStr">
         <is>
           <t>21 Launch Plan</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>Phased 0–18 month plan with workstreams</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="B29" s="60" t="inlineStr">
+        <is>
+          <t>Phased 0–18 month plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="92" t="inlineStr">
         <is>
           <t>22 Risk Register</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B30" s="58" t="inlineStr">
         <is>
           <t>Ranked risks, likelihood/impact, mitigations</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="13" t="inlineStr">
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="93" t="inlineStr">
         <is>
           <t>23 KPI Dashboard</t>
         </is>
       </c>
-      <c r="B27" s="13" t="inlineStr">
+      <c r="B31" s="60" t="inlineStr">
         <is>
           <t>Targets &amp; benchmarks by phase</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="92" t="inlineStr">
         <is>
           <t>24 Sources</t>
         </is>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B32" s="58" t="inlineStr">
         <is>
           <t>Master bibliography, tagged by type</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="93" t="inlineStr">
         <is>
           <t>25 Glossary</t>
         </is>
       </c>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="B33" s="60" t="inlineStr">
         <is>
           <t>Terms &amp; abbreviations</t>
         </is>
@@ -6473,8 +6783,40 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -6495,7 +6837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6516,6 +6858,11 @@
           <t>Weighted Competitive Scoring Model</t>
         </is>
       </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
@@ -6524,7 +6871,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -6897,6 +7243,9 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -6917,7 +7266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -6932,6 +7281,11 @@
           <t>Canada Market — Retail Landscape &amp; Entry Playbooks</t>
         </is>
       </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
@@ -7441,6 +7795,9 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -7461,7 +7818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7473,6 +7830,11 @@
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Canada Regulatory Pathway — the decision-critical tab</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
         </is>
       </c>
     </row>
@@ -7887,6 +8249,9 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -7907,7 +8272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7920,6 +8285,11 @@
           <t>MUV Go-to-Market Recommendation</t>
         </is>
       </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
@@ -8030,6 +8400,9 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A1:B1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -8046,166 +8419,285 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00B45309"/>
+    <tabColor rgb="00C9A227"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Phased Launch Plan (0–18 months)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Phase</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Timing</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Objectives</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Key workstreams</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Success gate</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="80" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Phase 0 — Foundation</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Months 0–3</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Lock product, claims, regulatory pathway, co-pack</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Finalize formula &amp; collagen dose; regulatory-counsel claim opinion (Supplemented Foods); co-packer quote &amp; MOQ; bilingual + Bill 96 artwork; brand/positioning</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory sign-off on claim set + artwork approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="80" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1 — Beachhead</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Months 3–9</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Prove velocity &amp; repeat in a contained beachhead</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Costco CA roadshows + Amazon.ca + Well.ca/Natura + Organika pharmacy/health-food base; podcast + reactive social; sampling</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>Repeat rate + velocity above category benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Phase 2 — Scale</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Months 9–18</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Earn conventional grocery on proven data</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Sell-in to Loblaw/Sobeys/Metro on velocity data; distributor (UNFI CA / Tree of Life); managed trade spend; add SKUs on repeat data</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>National listings won on data, not discounts</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Phase 3 — Defend &amp; extend</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>18 mo+</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Category leadership &amp; optionality</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Format/flavour extensions; deepen moat; evaluate strategic-partner vs independent scale</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Profitable contribution + exit optionality</t>
-        </is>
-      </c>
+          <t>Go / No-Go Decision Scorecard</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Weighted gate criteria. Edit yellow weight &amp; score (1–5) cells; verdict auto-computes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>What 'pass' looks like</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Score 1–5</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Weighted</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="57" t="inlineStr">
+        <is>
+          <t>Market opportunity / tailwinds</t>
+        </is>
+      </c>
+      <c r="B5" s="58" t="inlineStr">
+        <is>
+          <t>Category growth &amp; white space support entry</t>
+        </is>
+      </c>
+      <c r="C5" s="45" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D5" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" s="82">
+        <f>C5*D5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="57" t="inlineStr">
+        <is>
+          <t>Right to win (Organika assets)</t>
+        </is>
+      </c>
+      <c r="B6" s="58" t="inlineStr">
+        <is>
+          <t>Domestic mfg, #1 collagen halo, CA shelf relationships</t>
+        </is>
+      </c>
+      <c r="C6" s="45" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D6" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="82">
+        <f>C6*D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="57" t="inlineStr">
+        <is>
+          <t>Claim defensibility / dose</t>
+        </is>
+      </c>
+      <c r="B7" s="58" t="inlineStr">
+        <is>
+          <t>Substantiable collagen+fiber dose; avoids Poppi-style risk</t>
+        </is>
+      </c>
+      <c r="C7" s="45" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D7" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="82">
+        <f>C7*D7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="57" t="inlineStr">
+        <is>
+          <t>Regulatory clarity (Canada)</t>
+        </is>
+      </c>
+      <c r="B8" s="58" t="inlineStr">
+        <is>
+          <t>Supplemented-Foods pathway resolved with counsel</t>
+        </is>
+      </c>
+      <c r="C8" s="45" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D8" s="81" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="82">
+        <f>C8*D8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="57" t="inlineStr">
+        <is>
+          <t>Unit economics / margin</t>
+        </is>
+      </c>
+      <c r="B9" s="58" t="inlineStr">
+        <is>
+          <t>Contribution positive at ≤$3.49 CAD with domestic COGS</t>
+        </is>
+      </c>
+      <c r="C9" s="45" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D9" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="82">
+        <f>C9*D9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="57" t="inlineStr">
+        <is>
+          <t>Competitive resilience</t>
+        </is>
+      </c>
+      <c r="B10" s="58" t="inlineStr">
+        <is>
+          <t>Defensible vs Nestlé/Vital Proteins &amp; private label</t>
+        </is>
+      </c>
+      <c r="C10" s="45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D10" s="81" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="82">
+        <f>C10*D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="57" t="inlineStr">
+        <is>
+          <t>Go-to-market feasibility</t>
+        </is>
+      </c>
+      <c r="B11" s="58" t="inlineStr">
+        <is>
+          <t>Costco/Amazon/natural beachhead + cheap marketing playbooks</t>
+        </is>
+      </c>
+      <c r="C11" s="45" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D11" s="81" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="82">
+        <f>C11*D11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="40" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C12" s="83">
+        <f>SUM(C5:C11)</f>
+        <v/>
+      </c>
+      <c r="D12" s="84" t="inlineStr">
+        <is>
+          <t>Weighted /5 →</t>
+        </is>
+      </c>
+      <c r="E12" s="85">
+        <f>SUMPRODUCT(C5:C11,D5:D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>Auto verdict (thresholds):</t>
+        </is>
+      </c>
+      <c r="C14" s="86">
+        <f>IF(E12&gt;=3.5,"GO",IF(E12&gt;=2.8,"GO — conditional","NO-GO / rework"))</f>
+        <v/>
+      </c>
+      <c r="D14" s="34" t="n"/>
+      <c r="E14" s="35" t="n"/>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Current illustrative score lands in “GO — conditional”: the upside (Organika's right-to-win + tailwinds + margin) is strong; the gates to clear are claim/dose defensibility, Canadian regulatory sign-off, and competitive resilience. Recalibrate every yellow cell with your own evidence.</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="34" t="n"/>
+      <c r="F16" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="5">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A14:B14"/>
   </mergeCells>
+  <conditionalFormatting sqref="E5:E11">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="5"/>
+        <color rgb="002E7D8A"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -8222,424 +8714,229 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00B45309"/>
+    <tabColor rgb="00C9A227"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Risk Register</t>
+          <t>Competitor Battlecards</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Likelihood × Impact (H/M/L). Ranked by exposure</t>
+          <t>One block per key competitor — for sales/exec quick reference</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Competitor</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>Positioning</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Scale / outcome</t>
         </is>
       </c>
       <c r="D4" s="11" t="inlineStr">
         <is>
-          <t>Likelihood</t>
+          <t>Winning play</t>
         </is>
       </c>
       <c r="E4" s="11" t="inlineStr">
         <is>
-          <t>Impact</t>
+          <t>Vulnerability</t>
         </is>
       </c>
       <c r="F4" s="11" t="inlineStr">
         <is>
-          <t>Mitigation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Collagen efficacy / claims liability (2025 meta-analysis; Poppi-style dose-insufficiency suit)</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory/Legal</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>Dose to efficacy (2.5g+); structure/function-safe language; substantiation files; lead with gut/hydration not beauty</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Strategic-owned competition (Nestlé owns Vital Proteins; PepsiCo/Unilever firepower)</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E6" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>Compete on Canadian-made + domestic cost edge + Organika collagen credibility; niche beachhead before they react</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Canada claim/label pathway misread (food vs NHP; SFCI; collagen caution)</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory</t>
-        </is>
-      </c>
-      <c r="D7" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory-counsel opinion before artwork; design to Supplemented Foods framework; caffeine-free</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Over-distribution before product-market fit</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>Execution</t>
-        </is>
-      </c>
-      <c r="D8" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E8" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>Prove velocity/repeat in beachhead before national; gate Phase 2 on data</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Slotting / trade-spend cash burn</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E9" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Use free-fill over cash slotting; 35–45% trade-spend budget; Code of Conduct leverage on arbitrary fees</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Thin differentiation / shelf saturation (prebiotic shelf filling fast)</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D10" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E10" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Defensible spec (fiber + collagen dose) + function stacking; Canadian-made story</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Private-label encroachment (~$277B, ~21% share, growing 2×)</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D11" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E11" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Brand equity + clinical-grade ingredients retailers can't easily copy</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>DTC CAC / heavy-ship economics if DTC-led</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D12" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E12" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>Lead retail/beachhead not paid DTC; subscription + sampling only</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Co-packer capacity / collagen sourcing / cost inflation</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="D13" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E13" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>Lock co-pack capacity early; qualify 2nd collagen supplier; hedge raws</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>FX / tariff / freight premium on cross-border inputs</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D14" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E14" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>Domestic CA co-pack; monitor tariff status post-Dec 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>GLP-1 demand shift away from sweet/snack</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Macro</t>
-        </is>
-      </c>
-      <c r="D15" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E15" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Low-cal, fiber, protein, hydration positioning aligns with GLP-1 users</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>Brand/tone misstep at scale</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="D16" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E16" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>Evolve tactics with stage; avoid Poppi-style stunts once mainstream</t>
+          <t>How MUV beats / borrows</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="87" t="inlineStr">
+        <is>
+          <t>POPPI (PepsiCo)</t>
+        </is>
+      </c>
+      <c r="B5" s="58" t="inlineStr">
+        <is>
+          <t>Prebiotic soda, mass-market</t>
+        </is>
+      </c>
+      <c r="C5" s="58" t="inlineStr">
+        <is>
+          <t>$1.95B PepsiCo exit (2025); ~$500M rev; ~38% modern-soda share</t>
+        </is>
+      </c>
+      <c r="D5" s="58" t="inlineStr">
+        <is>
+          <t>TikTok-creator virality + 2 Super Bowls; farmers-mkt→Whole Foods→mass</t>
+        </is>
+      </c>
+      <c r="E5" s="58" t="inlineStr">
+        <is>
+          <t>2g fiber, $8.9M gut-health settlement — thin claim</t>
+        </is>
+      </c>
+      <c r="F5" s="88" t="inlineStr">
+        <is>
+          <t>Out-claim on dose + Canadian-made; they can't match domestic authenticity</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="89" t="inlineStr">
+        <is>
+          <t>OLIPOP</t>
+        </is>
+      </c>
+      <c r="B6" s="60" t="inlineStr">
+        <is>
+          <t>Prebiotic 'new soda', 9g fiber</t>
+        </is>
+      </c>
+      <c r="C6" s="60" t="inlineStr">
+        <is>
+          <t>$1.85B val (2025), independent, cash-profitable; ~$400M rev</t>
+        </is>
+      </c>
+      <c r="D6" s="60" t="inlineStr">
+        <is>
+          <t>Natural-channel seeding + 'astronomical repurchase' sell-in</t>
+        </is>
+      </c>
+      <c r="E6" s="60" t="inlineStr">
+        <is>
+          <t>Premium $3/can; single category; no strategic distribution</t>
+        </is>
+      </c>
+      <c r="F6" s="88" t="inlineStr">
+        <is>
+          <t>Match fiber credibility; beat on collagen+hydration stack &amp; price</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="87" t="inlineStr">
+        <is>
+          <t>VITAL PROTEINS Sparkling (Nestlé)</t>
+        </is>
+      </c>
+      <c r="B7" s="58" t="inlineStr">
+        <is>
+          <t>Collagen sparkling, beauty-from-within</t>
+        </is>
+      </c>
+      <c r="C7" s="58" t="inlineStr">
+        <is>
+          <t>Nestlé-owned; #1 collagen halo; $2.50/can mass price</t>
+        </is>
+      </c>
+      <c r="D7" s="58" t="inlineStr">
+        <is>
+          <t>Big-brand distribution + clinical VERISOL claim</t>
+        </is>
+      </c>
+      <c r="E7" s="58" t="inlineStr">
+        <is>
+          <t>2025 meta-analysis: no proven skin benefit; new format unproven</t>
+        </is>
+      </c>
+      <c r="F7" s="88" t="inlineStr">
+        <is>
+          <t>Function-forward (gut+hydration) not pure beauty; domestic cost edge; avoid their efficacy-claim exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="89" t="inlineStr">
+        <is>
+          <t>LMNT</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>Zero-sugar high-sodium electrolyte</t>
+        </is>
+      </c>
+      <c r="C8" s="60" t="inlineStr">
+        <is>
+          <t>$206M sales (2023), ~20% net margin, independent</t>
+        </is>
+      </c>
+      <c r="D8" s="60" t="inlineStr">
+        <is>
+          <t>Podcast host-reads + free-sample funnel; DTC/subscription</t>
+        </is>
+      </c>
+      <c r="E8" s="60" t="inlineStr">
+        <is>
+          <t>Polarizing sodium; powder not RTD; niche</t>
+        </is>
+      </c>
+      <c r="F8" s="88" t="inlineStr">
+        <is>
+          <t>Borrow the cheap podcast + sampling playbook for MUV's beachhead</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="87" t="inlineStr">
+        <is>
+          <t>LIQUID I.V. (Unilever)</t>
+        </is>
+      </c>
+      <c r="B9" s="58" t="inlineStr">
+        <is>
+          <t>Hydration multiplier powder</t>
+        </is>
+      </c>
+      <c r="C9" s="58" t="inlineStr">
+        <is>
+          <t>Unilever; $1B+ brand; 80,000+ US doors; Costco engine</t>
+        </is>
+      </c>
+      <c r="D9" s="58" t="inlineStr">
+        <is>
+          <t>Costco roadshow sampling + POS-data sell-in</t>
+        </is>
+      </c>
+      <c r="E9" s="58" t="inlineStr">
+        <is>
+          <t>Sugar content; undifferentiated vs new entrants</t>
+        </is>
+      </c>
+      <c r="F9" s="88" t="inlineStr">
+        <is>
+          <t>Copy the Costco-Canada sampling beachhead they used to enter Canada in 2023</t>
         </is>
       </c>
     </row>
@@ -8648,6 +8945,9 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -8668,278 +8968,170 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KPI Dashboard &amp; Targets</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Benchmarks from this research; set MUV targets before launch</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Why it matters</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Category benchmark</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>MUV target (set)</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
+          <t>Phased Launch Plan (0–18 months)</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Phase</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Repeat purchase rate</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>The metric buyers actually buy on</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>OLIPOP cited “astronomical”; aim well above category avg</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>[set]</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>Phase 1+</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Velocity (units/store/week)</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Gates shelf retention &amp; expansion</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Buyers reward durable, non-discount velocity</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>[set]</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1+</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Survival</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Aim 50–65% at scale (40–50% early); watch COGS definition</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>[set]</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Trade spend % of revenue</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>#2 P&amp;L line; cash burn risk</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>10–20%; emerging brands high end</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>≤45% early</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1–2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>CAC (if DTC/sub)</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>DTC viability</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>F&amp;B DTC ~$45–$53</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>≤ contribution margin</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>Phase 1+</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Doors / distribution</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Reach — but only on proven data</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Poppi ~36k / OLIPOP ~35k US (mature)</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Beachhead first</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1–3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Net revenue</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Scale</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>$852k (OLIPOP yr1) → $400M+ (yr6)</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>[set]</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>Brand awareness / social</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>Demand-gen efficiency</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>TikTok/podcast-led; earned-media ratio</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>[set]</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1+</t>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Objectives</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Key workstreams</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Success gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Phase 0 — Foundation</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Months 0–3</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Lock product, claims, regulatory pathway, co-pack</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Finalize formula &amp; collagen dose; regulatory-counsel claim opinion (Supplemented Foods); co-packer quote &amp; MOQ; bilingual + Bill 96 artwork; brand/positioning</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory sign-off on claim set + artwork approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1 — Beachhead</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Months 3–9</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Prove velocity &amp; repeat in a contained beachhead</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Costco CA roadshows + Amazon.ca + Well.ca/Natura + Organika pharmacy/health-food base; podcast + reactive social; sampling</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Repeat rate + velocity above category benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Phase 2 — Scale</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Months 9–18</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Earn conventional grocery on proven data</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Sell-in to Loblaw/Sobeys/Metro on velocity data; distributor (UNFI CA / Tree of Life); managed trade spend; add SKUs on repeat data</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>National listings won on data, not discounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Phase 3 — Defend &amp; extend</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>18 mo+</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Category leadership &amp; optionality</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Format/flavour extensions; deepen moat; evaluate strategic-partner vs independent scale</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Profitable contribution + exit optionality</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -8956,506 +9148,440 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00595959"/>
+    <tabColor rgb="00B45309"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="58" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Master Bibliography</t>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Tagged by type. Several primary pages block automated fetch (403) — re-verify load-bearing numbers from the cited URLs before external use</t>
+          <t>Likelihood × Impact (H/M/L). Ranked by exposure</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Claim / topic</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>Source(s)</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>PepsiCo — Poppi acquisition ($1.95B, closed May 2025)</t>
-        </is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Likelihood</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Mitigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>pepsico.com/newsroom</t>
+          <t>Collagen efficacy / claims liability (2025 meta-analysis; Poppi-style dose-insufficiency suit)</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Primary</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Poppi $8.9M gut-health class-action settlement (final approval Apr 2026)</t>
-        </is>
+          <t>Regulatory/Legal</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Dose to efficacy (2.5g+); structure/function-safe language; substantiation files; lead with gut/hydration not beauty</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>classaction.org; bevnet.com; axios.com</t>
+          <t>Strategic-owned competition (Nestlé owns Vital Proteins; PepsiCo/Unilever firepower)</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>Primary/Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>OLIPOP $50M Series C @ $1.85B; revenue; profitability</t>
-        </is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Compete on Canadian-made + domestic cost edge + Organika collagen credibility; niche beachhead before they react</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="12" t="n">
+        <v>3</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>cnbc.com; fooddive.com; bevindustry.com</t>
+          <t>Canada claim/label pathway misread (food vs NHP; SFCI; collagen caution)</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Primary/Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Modern soda $1.8B 2024 (+83%); brand shares (Poppi 38% / OLIPOP 32.7%)</t>
-        </is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory-counsel opinion before artwork; design to Supplemented Foods framework; caffeine-free</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="13" t="n">
+        <v>4</v>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>Circana; bevindustry.com; csnews.com</t>
+          <t>Over-distribution before product-market fit</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>Scanner/Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>LMNT FY2023 ($206M sales, ~20% net, $54.6M mktg, $7.1M sampling, 250k+ customers)</t>
-        </is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Prove velocity/repeat in beachhead before national; gate Phase 2 on data</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="12" t="n">
+        <v>5</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>SEC Reg CF CIK 1871551</t>
+          <t>Slotting / trade-spend cash burn</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Primary (strongest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Powdered hydration $1.5B (+20%); electrolyte powder $2.8B</t>
-        </is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Use free-fill over cash slotting; 35–45% trade-spend budget; Code of Conduct leverage on arbitrary fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>6</v>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>Circana/CNN; Grand View</t>
+          <t>Thin differentiation / shelf saturation (prebiotic shelf filling fast)</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>Scanner/Research-firm</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Liquid I.V. Costco national launch (2019, ~516 whs); Unilever acq. Sept 2020</t>
-        </is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Defensible spec (fiber + collagen dose) + function stacking; Canadian-made story</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="12" t="n">
+        <v>7</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>liquid-iv.com; unilever.com; bevnet.com</t>
+          <t>Private-label encroachment (~$277B, ~21% share, growing 2×)</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Primary/Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>Nuun — Nestlé Health Science acquisition (July 2021)</t>
-        </is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Brand equity + clinical-grade ingredients retailers can't easily copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>nestle.com; businesswire.com</t>
+          <t>DTC CAC / heavy-ship economics if DTC-led</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>Primary</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Vital Proteins sparkling ($2.50/can, VERISOL); Nestlé ownership</t>
-        </is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Lead retail/beachhead not paid DTC; subscription + sampling only</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>fooddive.com; wwd.com; foodbusinessnews.net</t>
+          <t>Co-packer capacity / collagen sourcing / cost inflation</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Trade/Primary</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Celsius — PepsiCo $550M/8.5% (2022); Alani Nu $1.8B (2025)</t>
-        </is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Lock co-pack capacity early; qualify 2nd collagen supplier; hedge raws</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="13" t="n">
+        <v>10</v>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>bevnet.com; bloomberg.com; businesswire.com</t>
+          <t>FX / tariff / freight premium on cross-border inputs</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>Primary/Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Health-Ade — Generous Brands $500M; $4M kombucha settlement</t>
-        </is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Domestic CA co-pack; monitor tariff status post-Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="12" t="n">
+        <v>11</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>fooddive.com; bursor.com</t>
+          <t>GLP-1 demand shift away from sweet/snack</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Collagen efficacy — 2025 systematic review/meta-analysis (no proven skin benefit; funding bias)</t>
-        </is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Low-cal, fiber, protein, hydration positioning aligns with GLP-1 users</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="13" t="n">
+        <v>12</v>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>Am. Journal of Medicine; nutraingredients.com</t>
+          <t>Brand/tone misstep at scale</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>Primary (peer-reviewed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>GLP-1 impact (23% households; 35% of units by 2030; spend -5.3%)</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Morning Consult; Circana; Food Dive</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>Research/Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Beauty-from-within drinks $3.24B, women 68.4%</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Future Market Insights; Grand View</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>Research-firm (directional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Channel economics (Amazon fees, Costco margin, DTC CAC, slotting, distributor)</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>sellingpartners.aboutamazon.com; massivemoats; eightx.co; balancedbusinessgroup.com</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>Mixed (Amazon/Costco HARD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Canada — NHP vs Food classification (food-format guidance)</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>canada.ca Health Canada guidance</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>Primary (regulatory)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Canada — Supplemented Foods Regulations (in force Jul 2022; SFCI; Jan 2026)</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>canada.ca; inspection.canada.ca; fasken.com</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Primary/Legal</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>Canada — collagen caution statement (FDR C.R.C. c.870)</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>laws.justice.gc.ca</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Primary (regulation)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Canada — caffeine 180mg cap (Prime Energy blocked)</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>canada.ca; stack3d.com</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Primary/Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>Canada — Bill 96 / OQLF packaging (Jun 2025)</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>mltaikins.com; stikeman.com</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Legal</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Canada — grocery share &amp; Code of Conduct (Jan 2025)</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>USDA FAS; statista.com; cbc.ca; canadacode.org</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>Govt/Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>US brand Canada entry (Liquid I.V. 2023, Poppi Aug 2024, Celsius Jan 2024)</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>foodincanada.com; newswire.ca; prnewswire.com</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>Trade/Primary</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Launch playbooks (Poppi/OLIPOP/LMNT/Liquid I.V./Celsius timelines)</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>fortune.com; entrepreneur.com; cnbc.com; inc.com; hubermanlab.com</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>Trade/Primary</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>Extended landscape (Culture Pop, Spindrift, Prime, Cure, etc.)</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>bevnet.com; techcrunch.com; prnewswire.com; wikipedia</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>Trade (verify FLAGs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Private label ~$277B, ~21% share</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>grocerydive.com; nielseniq.com</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>CPG failure rate ~85% in 2 years</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>foodnavigator-usa.com; eightx.co</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>Trade (directional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>PROCESS NOTE: Numbers were captured via multi-source web research with per-claim citation. Primary publisher and canada.ca pages frequently block automated fetch (HTTP 403); load-bearing figures should be re-pulled directly from the cited URLs (or licensed Circana/SPINS/Mintel portals) before external publication. The two highest-stakes regulatory claims — (a) RTD beverages are foods not NHPs, (b) the Supplemented-Foods/SFCI pathway with Jan 1 2026 compliance — are each corroborated by an official source + ≥1 independent secondary.</t>
-        </is>
-      </c>
-      <c r="B32" s="34" t="n"/>
-      <c r="C32" s="35" t="n"/>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Evolve tactics with stage; avoid Poppi-style stunts once mainstream</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A2:C2"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -9472,316 +9598,814 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00B45309"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KPI Dashboard &amp; Targets</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Benchmarks from this research; set MUV targets before launch</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Category benchmark</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>MUV target (set)</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Repeat purchase rate</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>The metric buyers actually buy on</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>OLIPOP cited “astronomical”; aim well above category avg</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>[set]</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Velocity (units/store/week)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Gates shelf retention &amp; expansion</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Buyers reward durable, non-discount velocity</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>[set]</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Survival</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Aim 50–65% at scale (40–50% early); watch COGS definition</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>[set]</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Trade spend % of revenue</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>#2 P&amp;L line; cash burn risk</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>10–20%; emerging brands high end</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>≤45% early</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1–2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>CAC (if DTC/sub)</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>DTC viability</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>F&amp;B DTC ~$45–$53</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>≤ contribution margin</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1+</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Doors / distribution</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Reach — but only on proven data</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Poppi ~36k / OLIPOP ~35k US (mature)</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Beachhead first</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1–3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Net revenue</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>$852k (OLIPOP yr1) → $400M+ (yr6)</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>[set]</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Brand awareness / social</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Demand-gen efficiency</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>TikTok/podcast-led; earned-media ratio</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>[set]</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1+</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00595959"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Glossary &amp; Abbreviations</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Term</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>ACV</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Apple cider vinegar (Poppi's original hero ingredient)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>ACV (retail)</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Also: All-Commodity Volume — a retail distribution/weighting metric (context-dependent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>CFIA</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Canadian Food Inspection Agency — regulates food-format products in Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>CTT</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Cellular Transport Technology — Liquid I.V.'s hydration claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>DSD</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Direct Store Delivery — brand/bottler delivers &amp; merchandises in-store (Coca-Cola model)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>DTC</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Direct-to-consumer (e-commerce / subscription)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>FDR</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Food and Drug Regulations (Canada)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>GLP-1</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Glucagon-like peptide-1 agonists (Ozempic/Wegovy) — weight-loss drugs reshaping food demand</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>GM / COGS</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>Gross margin / Cost of goods sold</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>MOQ</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Minimum order quantity (co-packer runs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>MULO</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>Multi-Outlet (SPINS/Circana retail measurement universe)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>NHP / NPN</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>Natural Health Product / Natural Product Number (Canada licensing for supplements)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>PMF</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>Product-market fit</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>Ready-to-drink (a finished beverage, vs powder/tablet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>SAM/SOM/TAM</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>Serviceable available / obtainable / total addressable market</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>SFCI</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>Supplemented Food Caution Identifier — Canada's ‘!’ caution box for supplemented foods</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>SFR</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>Supplemented Foods Regulations (Canada, in force Jul 21 2022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>SPINS / Circana</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>Syndicated retail scanner-data providers (point-of-sale sales &amp; velocity)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>Slotting fee</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>Payment to a retailer to list a new SKU / secure shelf space</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Trade spend</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Promotional/discount spend to retailers — typically the #2 P&amp;L line after COGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>UNFI / KeHE</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>Major North American natural/specialty food distributors</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>VERISOL</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>A clinically-studied collagen peptide (Vital Proteins sparkling)</t>
-        </is>
-      </c>
+          <t>Master Bibliography</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Tagged by type. Several primary pages block automated fetch (403) — re-verify load-bearing numbers from the cited URLs before external use</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Claim / topic</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Source(s)</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>PepsiCo — Poppi acquisition ($1.95B, closed May 2025)</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>pepsico.com/newsroom</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Poppi $8.9M gut-health class-action settlement (final approval Apr 2026)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>classaction.org; bevnet.com; axios.com</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Primary/Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>OLIPOP $50M Series C @ $1.85B; revenue; profitability</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>cnbc.com; fooddive.com; bevindustry.com</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Primary/Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Modern soda $1.8B 2024 (+83%); brand shares (Poppi 38% / OLIPOP 32.7%)</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Circana; bevindustry.com; csnews.com</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Scanner/Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>LMNT FY2023 ($206M sales, ~20% net, $54.6M mktg, $7.1M sampling, 250k+ customers)</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>SEC Reg CF CIK 1871551</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Primary (strongest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Powdered hydration $1.5B (+20%); electrolyte powder $2.8B</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Circana/CNN; Grand View</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Scanner/Research-firm</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Liquid I.V. Costco national launch (2019, ~516 whs); Unilever acq. Sept 2020</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>liquid-iv.com; unilever.com; bevnet.com</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Primary/Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Nuun — Nestlé Health Science acquisition (July 2021)</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>nestle.com; businesswire.com</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Vital Proteins sparkling ($2.50/can, VERISOL); Nestlé ownership</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>fooddive.com; wwd.com; foodbusinessnews.net</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Trade/Primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Celsius — PepsiCo $550M/8.5% (2022); Alani Nu $1.8B (2025)</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>bevnet.com; bloomberg.com; businesswire.com</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Primary/Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Health-Ade — Generous Brands $500M; $4M kombucha settlement</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>fooddive.com; bursor.com</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Collagen efficacy — 2025 systematic review/meta-analysis (no proven skin benefit; funding bias)</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Am. Journal of Medicine; nutraingredients.com</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Primary (peer-reviewed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>GLP-1 impact (23% households; 35% of units by 2030; spend -5.3%)</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Morning Consult; Circana; Food Dive</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Research/Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Beauty-from-within drinks $3.24B, women 68.4%</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Future Market Insights; Grand View</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Research-firm (directional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Channel economics (Amazon fees, Costco margin, DTC CAC, slotting, distributor)</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>sellingpartners.aboutamazon.com; massivemoats; eightx.co; balancedbusinessgroup.com</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Mixed (Amazon/Costco HARD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Canada — NHP vs Food classification (food-format guidance)</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>canada.ca Health Canada guidance</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Primary (regulatory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Canada — Supplemented Foods Regulations (in force Jul 2022; SFCI; Jan 2026)</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>canada.ca; inspection.canada.ca; fasken.com</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Primary/Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Canada — collagen caution statement (FDR C.R.C. c.870)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>laws.justice.gc.ca</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Primary (regulation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Canada — caffeine 180mg cap (Prime Energy blocked)</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>canada.ca; stack3d.com</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Primary/Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Canada — Bill 96 / OQLF packaging (Jun 2025)</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>mltaikins.com; stikeman.com</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Canada — grocery share &amp; Code of Conduct (Jan 2025)</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>USDA FAS; statista.com; cbc.ca; canadacode.org</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Govt/Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>US brand Canada entry (Liquid I.V. 2023, Poppi Aug 2024, Celsius Jan 2024)</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>foodincanada.com; newswire.ca; prnewswire.com</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Trade/Primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Launch playbooks (Poppi/OLIPOP/LMNT/Liquid I.V./Celsius timelines)</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>fortune.com; entrepreneur.com; cnbc.com; inc.com; hubermanlab.com</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Trade/Primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>Extended landscape (Culture Pop, Spindrift, Prime, Cure, etc.)</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>bevnet.com; techcrunch.com; prnewswire.com; wikipedia</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Trade (verify FLAGs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Private label ~$277B, ~21% share</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>grocerydive.com; nielseniq.com</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>CPG failure rate ~85% in 2 years</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>foodnavigator-usa.com; eightx.co</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Trade (directional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>PROCESS NOTE: Numbers were captured via multi-source web research with per-claim citation. Primary publisher and canada.ca pages frequently block automated fetch (HTTP 403); load-bearing figures should be re-pulled directly from the cited URLs (or licensed Circana/SPINS/Mintel portals) before external publication. The two highest-stakes regulatory claims — (a) RTD beverages are foods not NHPs, (b) the Supplemented-Foods/SFCI pathway with Jan 1 2026 compliance — are each corroborated by an official source + ≥1 independent secondary.</t>
+        </is>
+      </c>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -9802,7 +10426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9813,6 +10437,11 @@
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Executive Summary</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
         </is>
       </c>
     </row>
@@ -9958,6 +10587,343 @@
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00595959"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Glossary &amp; Abbreviations</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Term</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>ACV</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Apple cider vinegar (Poppi's original hero ingredient)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>ACV (retail)</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Also: All-Commodity Volume — a retail distribution/weighting metric (context-dependent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>CFIA</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Canadian Food Inspection Agency — regulates food-format products in Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>CTT</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Cellular Transport Technology — Liquid I.V.'s hydration claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>DSD</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Direct Store Delivery — brand/bottler delivers &amp; merchandises in-store (Coca-Cola model)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>DTC</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Direct-to-consumer (e-commerce / subscription)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>FDR</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Food and Drug Regulations (Canada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>GLP-1</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Glucagon-like peptide-1 agonists (Ozempic/Wegovy) — weight-loss drugs reshaping food demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>GM / COGS</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Gross margin / Cost of goods sold</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>MOQ</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Minimum order quantity (co-packer runs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>MULO</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Multi-Outlet (SPINS/Circana retail measurement universe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>NHP / NPN</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Natural Health Product / Natural Product Number (Canada licensing for supplements)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>PMF</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Product-market fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Ready-to-drink (a finished beverage, vs powder/tablet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>SAM/SOM/TAM</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Serviceable available / obtainable / total addressable market</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>SFCI</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Supplemented Food Caution Identifier — Canada's ‘!’ caution box for supplemented foods</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>SFR</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Supplemented Foods Regulations (Canada, in force Jul 21 2022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>SPINS / Circana</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Syndicated retail scanner-data providers (point-of-sale sales &amp; velocity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Slotting fee</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Payment to a retailer to list a new SKU / secure shelf space</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Trade spend</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Promotional/discount spend to retailers — typically the #2 P&amp;L line after COGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>UNFI / KeHE</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>Major North American natural/specialty food distributors</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>VERISOL</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>A clinically-studied collagen peptide (Vital Proteins sparkling)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -9978,7 +10944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N68"/>
+  <dimension ref="A1:N78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -10001,398 +10967,405 @@
           <t>Executive Dashboard</t>
         </is>
       </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Visual snapshot — category sizing, leader trajectories, share, competitive scores &amp; MUV model</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
+          <t>Category sizing · leader trajectories · share · competitive scores · MUV scenario P&amp;L</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
       <c r="A4" s="36" t="inlineStr">
         <is>
-          <t>Modern soda (US, 2024)</t>
-        </is>
-      </c>
-      <c r="B4" s="24" t="n"/>
+          <t>Modern soda US '24</t>
+        </is>
+      </c>
+      <c r="B4" s="35" t="n"/>
       <c r="C4" s="36" t="inlineStr">
         <is>
-          <t>Poppi exit (PepsiCo)</t>
-        </is>
-      </c>
-      <c r="D4" s="24" t="n"/>
+          <t>Poppi → PepsiCo</t>
+        </is>
+      </c>
+      <c r="D4" s="35" t="n"/>
       <c r="E4" s="36" t="inlineStr">
         <is>
           <t>OLIPOP valuation</t>
         </is>
       </c>
-      <c r="F4" s="24" t="n"/>
+      <c r="F4" s="35" t="n"/>
       <c r="G4" s="36" t="inlineStr">
         <is>
-          <t>Collagen-sparkling indie survival</t>
-        </is>
-      </c>
-      <c r="H4" s="24" t="n"/>
+          <t>Collagen-indie survival</t>
+        </is>
+      </c>
+      <c r="H4" s="35" t="n"/>
       <c r="I4" s="36" t="inlineStr">
         <is>
           <t>Canada beachhead</t>
         </is>
       </c>
-      <c r="J4" s="24" t="n"/>
-    </row>
-    <row r="5" ht="22" customHeight="1">
+      <c r="J4" s="35" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
       <c r="A5" s="37" t="inlineStr">
         <is>
           <t>$1.8B</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n"/>
+      <c r="B5" s="35" t="n"/>
       <c r="C5" s="37" t="inlineStr">
         <is>
           <t>$1.95B</t>
         </is>
       </c>
-      <c r="D5" s="24" t="n"/>
+      <c r="D5" s="35" t="n"/>
       <c r="E5" s="37" t="inlineStr">
         <is>
           <t>$1.85B</t>
         </is>
       </c>
-      <c r="F5" s="24" t="n"/>
+      <c r="F5" s="35" t="n"/>
       <c r="G5" s="37" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H5" s="24" t="n"/>
+      <c r="H5" s="35" t="n"/>
       <c r="I5" s="37" t="inlineStr">
         <is>
           <t>Costco+Amazon</t>
         </is>
       </c>
-      <c r="J5" s="24" t="n"/>
-    </row>
-    <row r="6" ht="16" customHeight="1">
+      <c r="J5" s="35" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
       <c r="A6" s="38" t="inlineStr">
         <is>
           <t>+83% YoY</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n"/>
+      <c r="B6" s="35" t="n"/>
       <c r="C6" s="38" t="inlineStr">
         <is>
-          <t>May 2025</t>
-        </is>
-      </c>
-      <c r="D6" s="24" t="n"/>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D6" s="35" t="n"/>
       <c r="E6" s="38" t="inlineStr">
         <is>
-          <t>Feb 2025</t>
-        </is>
-      </c>
-      <c r="F6" s="24" t="n"/>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F6" s="35" t="n"/>
       <c r="G6" s="38" t="inlineStr">
         <is>
           <t>graveyard</t>
         </is>
       </c>
-      <c r="H6" s="24" t="n"/>
+      <c r="H6" s="35" t="n"/>
       <c r="I6" s="38" t="inlineStr">
         <is>
-          <t>proven path</t>
-        </is>
-      </c>
-      <c r="J6" s="24" t="n"/>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="39" t="inlineStr">
-        <is>
-          <t>Charts are illustrative and built from the cited research (see ‘24 Sources’). Revenue/share figures rounded; OLIPOP 2020–22 interpolated. Financial-model bars are driven live by the ‘Financial Model’ tab inputs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" hidden="1" outlineLevel="1">
-      <c r="A60" s="40" t="inlineStr">
-        <is>
-          <t>Category sizes ($B)</t>
-        </is>
-      </c>
-      <c r="E60" s="40" t="inlineStr">
-        <is>
-          <t>Revenue ($M)</t>
-        </is>
-      </c>
-      <c r="I60" s="40" t="inlineStr">
-        <is>
-          <t>Modern soda share %</t>
-        </is>
-      </c>
-      <c r="M60" s="40" t="inlineStr">
-        <is>
-          <t>Weighted score</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" hidden="1" outlineLevel="1">
-      <c r="A61" s="41" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B61" s="41" t="inlineStr">
+          <t>proven</t>
+        </is>
+      </c>
+      <c r="J6" s="35" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="41" t="inlineStr">
+        <is>
+          <t>Illustrative; built from cited research (see ‘24 Sources’). The P&amp;L chart is driven live by the Financial Model scenario dropdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" hidden="1">
+      <c r="A70" s="40" t="inlineStr">
+        <is>
+          <t>Category $B</t>
+        </is>
+      </c>
+      <c r="E70" s="40" t="inlineStr">
+        <is>
+          <t>Revenue $M</t>
+        </is>
+      </c>
+      <c r="I70" s="40" t="inlineStr">
+        <is>
+          <t>Share %</t>
+        </is>
+      </c>
+      <c r="M70" s="40" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" hidden="1">
+      <c r="A71" s="41" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="B71" s="41" t="inlineStr">
         <is>
           <t>$B</t>
         </is>
       </c>
-      <c r="E61" s="41" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="F61" s="41" t="inlineStr">
+      <c r="E71" s="41" t="inlineStr">
+        <is>
+          <t>Yr</t>
+        </is>
+      </c>
+      <c r="F71" s="41" t="inlineStr">
         <is>
           <t>Poppi</t>
         </is>
       </c>
-      <c r="G61" s="41" t="inlineStr">
+      <c r="G71" s="41" t="inlineStr">
         <is>
           <t>OLIPOP</t>
         </is>
       </c>
-      <c r="I61" s="41" t="inlineStr">
+      <c r="I71" s="41" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="J61" s="41" t="inlineStr">
+      <c r="J71" s="41" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="M61" s="41" t="inlineStr">
+      <c r="M71" s="41" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="N61" s="41" t="inlineStr">
+      <c r="N71" s="41" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
     </row>
-    <row r="62" hidden="1" outlineLevel="1">
-      <c r="A62" t="inlineStr">
+    <row r="72" hidden="1">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Modern soda</t>
         </is>
       </c>
-      <c r="B62" t="n">
+      <c r="B72" t="n">
         <v>1.8</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E72" t="n">
         <v>2020</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F72" t="n">
         <v>13</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G72" t="n">
         <v>20</v>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>Poppi</t>
         </is>
       </c>
-      <c r="J62" t="n">
+      <c r="J72" t="n">
         <v>38</v>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>Poppi</t>
         </is>
       </c>
-      <c r="N62" t="n">
+      <c r="N72" t="n">
         <v>3.85</v>
       </c>
     </row>
-    <row r="63" hidden="1" outlineLevel="1">
-      <c r="A63" t="inlineStr">
+    <row r="73" hidden="1">
+      <c r="A73" t="inlineStr">
         <is>
           <t>Hydration powder</t>
         </is>
       </c>
-      <c r="B63" t="n">
+      <c r="B73" t="n">
         <v>1.5</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E73" t="n">
         <v>2021</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F73" t="n">
         <v>26</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G73" t="n">
         <v>40</v>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>OLIPOP</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="J73" t="n">
         <v>32.7</v>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>OLIPOP</t>
         </is>
       </c>
-      <c r="N63" t="n">
+      <c r="N73" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="64" hidden="1" outlineLevel="1">
-      <c r="A64" t="inlineStr">
+    <row r="74" hidden="1">
+      <c r="A74" t="inlineStr">
         <is>
           <t>Electrolyte powder</t>
         </is>
       </c>
-      <c r="B64" t="n">
+      <c r="B74" t="n">
         <v>2.8</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E74" t="n">
         <v>2022</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F74" t="n">
         <v>65</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G74" t="n">
         <v>73</v>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>Zevia</t>
         </is>
       </c>
-      <c r="J64" t="n">
+      <c r="J74" t="n">
         <v>12.1</v>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>LMNT</t>
         </is>
       </c>
-      <c r="N64" t="n">
+      <c r="N74" t="n">
         <v>3.5</v>
       </c>
     </row>
-    <row r="65" hidden="1" outlineLevel="1">
-      <c r="A65" t="inlineStr">
+    <row r="75" hidden="1">
+      <c r="A75" t="inlineStr">
         <is>
           <t>Sparkling water</t>
         </is>
       </c>
-      <c r="B65" t="n">
+      <c r="B75" t="n">
         <v>6.9</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E75" t="n">
         <v>2023</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F75" t="n">
         <v>100</v>
       </c>
-      <c r="G65" t="n">
+      <c r="G75" t="n">
         <v>200</v>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>Jarritos</t>
         </is>
       </c>
-      <c r="J65" t="n">
+      <c r="J75" t="n">
         <v>10.3</v>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>Liquid I.V.</t>
         </is>
       </c>
-      <c r="N65" t="n">
+      <c r="N75" t="n">
         <v>3.85</v>
       </c>
     </row>
-    <row r="66" hidden="1" outlineLevel="1">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Collagen bev (US)</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
+    <row r="76" hidden="1">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Collagen bev US</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
         <v>0.05</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E76" t="n">
         <v>2024</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F76" t="n">
         <v>500</v>
       </c>
-      <c r="G66" t="n">
+      <c r="G76" t="n">
         <v>400</v>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>Fever-Tree</t>
         </is>
       </c>
-      <c r="J66" t="n">
+      <c r="J76" t="n">
         <v>4</v>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>Vital Proteins</t>
         </is>
       </c>
-      <c r="N66" t="n">
+      <c r="N76" t="n">
         <v>3.8</v>
       </c>
     </row>
-    <row r="67" hidden="1" outlineLevel="1">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Beauty-from-within (global)</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
+    <row r="77" hidden="1">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BFW global</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
         <v>3.24</v>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="J67" t="n">
+      <c r="J77" t="n">
         <v>2.9</v>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>Recess</t>
         </is>
       </c>
-      <c r="N67" t="n">
+      <c r="N77" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="68" hidden="1" outlineLevel="1">
-      <c r="M68" t="inlineStr">
+    <row r="78" hidden="1">
+      <c r="M78" t="inlineStr">
         <is>
           <t>MUV (Organika)</t>
         </is>
       </c>
-      <c r="N68" t="n">
+      <c r="N78" t="n">
         <v>3.05</v>
       </c>
     </row>
-    <row r="69" hidden="1" outlineLevel="1"/>
+    <row r="79" hidden="1"/>
+    <row r="80" hidden="1"/>
+    <row r="81" hidden="1"/>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="A4:B4"/>
@@ -10409,11 +11382,14 @@
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="I5:J5"/>
-    <mergeCell ref="A40:L40"/>
     <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A39:L39"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -10424,7 +11400,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -10435,334 +11411,966 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>MUV Financial Model — Unit Economics &amp; 3-Year Build</t>
+          <t>MUV Financial Model — Scenario P&amp;L, Break-even &amp; Sensitivity</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Edit the yellow input cells; all white cells are live formulas. Illustrative defaults — replace with your numbers</t>
+          <t>Pick a scenario in the dropdown (C4). Yellow = editable inputs; white = live formulas. Illustrative, not a forecast.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="42" t="inlineStr">
-        <is>
-          <t>PER-UNIT ASSUMPTIONS  (edit yellow)</t>
+      <c r="B4" s="62" t="inlineStr">
+        <is>
+          <t>Scenario (pick):</t>
+        </is>
+      </c>
+      <c r="C4" s="63" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="F4" s="64" t="inlineStr">
+        <is>
+          <t>← change this dropdown to flip the whole model</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="43" t="inlineStr">
-        <is>
-          <t>List / shelf price per can (CAD)</t>
-        </is>
-      </c>
-      <c r="C5" s="44" t="n">
+      <c r="B5" s="65" t="inlineStr">
+        <is>
+          <t>Scenario index:</t>
+        </is>
+      </c>
+      <c r="C5" s="66">
+        <f>MATCH(C4,{"Conservative","Base","Aggressive"},0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Assumption</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="B8" s="65" t="inlineStr">
+        <is>
+          <t>List price / can (CAD)</t>
+        </is>
+      </c>
+      <c r="C8" s="44" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="D8" s="44" t="n">
         <v>3.49</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="43" t="inlineStr">
-        <is>
-          <t>COGS per can (liquid+can+co-pack, CAD)</t>
-        </is>
-      </c>
-      <c r="C6" s="44" t="n">
+      <c r="E8" s="44" t="n">
+        <v>3.79</v>
+      </c>
+      <c r="F8" s="67">
+        <f>CHOOSE($C$5,C8,D8,E8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="B9" s="65" t="inlineStr">
+        <is>
+          <t>COGS / can (CAD)</t>
+        </is>
+      </c>
+      <c r="C9" s="44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D9" s="44" t="n">
         <v>1.05</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="43" t="inlineStr">
+      <c r="E9" s="44" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F9" s="67">
+        <f>CHOOSE($C$5,C9,D9,E9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="B10" s="65" t="inlineStr">
         <is>
           <t>Retailer margin %</t>
         </is>
       </c>
-      <c r="C7" s="45" t="n">
+      <c r="C10" s="45" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="D10" s="45" t="n">
         <v>0.35</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="43" t="inlineStr">
+      <c r="E10" s="45" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F10" s="68">
+        <f>CHOOSE($C$5,C10,D10,E10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="B11" s="65" t="inlineStr">
         <is>
           <t>Distributor margin %</t>
         </is>
       </c>
-      <c r="C8" s="45" t="n">
+      <c r="C11" s="45" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D11" s="45" t="n">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="43" t="inlineStr">
-        <is>
-          <t>Trade spend % of net revenue</t>
-        </is>
-      </c>
-      <c r="C9" s="45" t="n">
+      <c r="E11" s="45" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F11" s="68">
+        <f>CHOOSE($C$5,C11,D11,E11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="B12" s="65" t="inlineStr">
+        <is>
+          <t>Trade spend % of net</t>
+        </is>
+      </c>
+      <c r="C12" s="45" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D12" s="45" t="n">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="43" t="inlineStr">
+      <c r="E12" s="45" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F12" s="68">
+        <f>CHOOSE($C$5,C12,D12,E12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="B13" s="65" t="inlineStr">
         <is>
           <t>Cans per case</t>
         </is>
       </c>
-      <c r="C10" s="46" t="n">
+      <c r="C13" s="46" t="n">
         <v>12</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="42" t="inlineStr">
-        <is>
-          <t>DERIVED PER-CAN ECONOMICS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="47" t="inlineStr">
-        <is>
-          <t>Brand net revenue per can</t>
-        </is>
-      </c>
-      <c r="C13" s="48">
-        <f>$C$5*(1-$C$7)*(1-$C$8)</f>
+      <c r="D13" s="46" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" s="46" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" s="69">
+        <f>CHOOSE($C$5,C13,D13,E13)</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="47" t="inlineStr">
-        <is>
-          <t>Gross profit per can</t>
-        </is>
-      </c>
-      <c r="C14" s="48">
-        <f>C13-$C$6</f>
+    <row r="14" ht="16" customHeight="1">
+      <c r="B14" s="65" t="inlineStr">
+        <is>
+          <t>Doors — Year 1</t>
+        </is>
+      </c>
+      <c r="C14" s="51" t="n">
+        <v>300</v>
+      </c>
+      <c r="D14" s="51" t="n">
+        <v>500</v>
+      </c>
+      <c r="E14" s="51" t="n">
+        <v>900</v>
+      </c>
+      <c r="F14" s="70">
+        <f>CHOOSE($C$5,C14,D14,E14)</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="47" t="inlineStr">
+    <row r="15" ht="16" customHeight="1">
+      <c r="B15" s="65" t="inlineStr">
+        <is>
+          <t>Doors — Year 2</t>
+        </is>
+      </c>
+      <c r="C15" s="51" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D15" s="51" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E15" s="51" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F15" s="70">
+        <f>CHOOSE($C$5,C15,D15,E15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="B16" s="65" t="inlineStr">
+        <is>
+          <t>Doors — Year 3</t>
+        </is>
+      </c>
+      <c r="C16" s="51" t="n">
+        <v>3500</v>
+      </c>
+      <c r="D16" s="51" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E16" s="51" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F16" s="70">
+        <f>CHOOSE($C$5,C16,D16,E16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="B17" s="65" t="inlineStr">
+        <is>
+          <t>Velocity Y1 (u/store/wk)</t>
+        </is>
+      </c>
+      <c r="C17" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" s="52" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F17" s="71">
+        <f>CHOOSE($C$5,C17,D17,E17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="B18" s="65" t="inlineStr">
+        <is>
+          <t>Velocity Y2 (u/store/wk)</t>
+        </is>
+      </c>
+      <c r="C18" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" s="52" t="n">
+        <v>6</v>
+      </c>
+      <c r="F18" s="71">
+        <f>CHOOSE($C$5,C18,D18,E18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="B19" s="65" t="inlineStr">
+        <is>
+          <t>Velocity Y3 (u/store/wk)</t>
+        </is>
+      </c>
+      <c r="C19" s="52" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D19" s="52" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" s="52" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F19" s="71">
+        <f>CHOOSE($C$5,C19,D19,E19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="B20" s="65" t="inlineStr">
+        <is>
+          <t>Marketing / year (CAD)</t>
+        </is>
+      </c>
+      <c r="C20" s="72" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D20" s="72" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E20" s="72" t="n">
+        <v>600000</v>
+      </c>
+      <c r="F20" s="73">
+        <f>CHOOSE($C$5,C20,D20,E20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="B21" s="65" t="inlineStr">
+        <is>
+          <t>Fixed overhead / year (CAD)</t>
+        </is>
+      </c>
+      <c r="C21" s="72" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D21" s="72" t="n">
+        <v>350000</v>
+      </c>
+      <c r="E21" s="72" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F21" s="73">
+        <f>CHOOSE($C$5,C21,D21,E21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="B22" s="65" t="inlineStr">
+        <is>
+          <t>Slotting (Year 1 one-time)</t>
+        </is>
+      </c>
+      <c r="C22" s="72" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D22" s="72" t="n">
+        <v>100000</v>
+      </c>
+      <c r="E22" s="72" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F22" s="73">
+        <f>CHOOSE($C$5,C22,D22,E22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="42" t="inlineStr">
+        <is>
+          <t>PER-CAN ECONOMICS (active scenario)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="62" t="inlineStr">
+        <is>
+          <t>Net revenue / can</t>
+        </is>
+      </c>
+      <c r="C25" s="48">
+        <f>$F$8*(1-$F$10)*(1-$F$11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="62" t="inlineStr">
+        <is>
+          <t>Gross profit / can</t>
+        </is>
+      </c>
+      <c r="C26" s="48">
+        <f>C25-$F$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="62" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C15" s="49">
-        <f>C14/C13</f>
+      <c r="C27" s="49">
+        <f>C26/C25</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="43" t="inlineStr">
-        <is>
-          <t>Trade spend per can</t>
-        </is>
-      </c>
-      <c r="C16" s="50">
-        <f>C13*$C$9</f>
+    <row r="28">
+      <c r="B28" s="65" t="inlineStr">
+        <is>
+          <t>Trade spend / can</t>
+        </is>
+      </c>
+      <c r="C28" s="50">
+        <f>C25*$F$12</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="47" t="inlineStr">
-        <is>
-          <t>Contribution per can (after trade)</t>
-        </is>
-      </c>
-      <c r="C17" s="48">
-        <f>C14-C16</f>
+    <row r="29">
+      <c r="B29" s="62" t="inlineStr">
+        <is>
+          <t>Contribution / can</t>
+        </is>
+      </c>
+      <c r="C29" s="48">
+        <f>C26-C28</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="42" t="inlineStr">
-        <is>
-          <t>3-YEAR VOLUME BUILD  (edit yellow rows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="42" t="inlineStr">
+        <is>
+          <t>3-YEAR P&amp;L  (CAD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="74" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="C32" s="74" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D32" s="74" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E32" s="74" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="43" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="65" t="inlineStr">
         <is>
           <t>Distribution (doors)</t>
         </is>
       </c>
-      <c r="C21" s="51" t="n">
-        <v>500</v>
-      </c>
-      <c r="D21" s="51" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E21" s="51" t="n">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="43" t="inlineStr">
-        <is>
-          <t>Velocity (units/store/week)</t>
-        </is>
-      </c>
-      <c r="C22" s="52" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" s="52" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" s="52" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="43" t="inlineStr">
-        <is>
-          <t>Annual units (= doors×velocity×52)</t>
-        </is>
-      </c>
-      <c r="C23" s="53">
-        <f>C21*C22*52</f>
+      <c r="C33" s="53">
+        <f>$F$14</f>
         <v/>
       </c>
-      <c r="D23" s="53">
-        <f>D21*D22*52</f>
+      <c r="D33" s="53">
+        <f>$F$15</f>
         <v/>
       </c>
-      <c r="E23" s="53">
-        <f>E21*E22*52</f>
+      <c r="E33" s="53">
+        <f>$F$16</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="47" t="inlineStr">
-        <is>
-          <t>Net revenue (CAD)</t>
-        </is>
-      </c>
-      <c r="C24" s="54">
-        <f>C23*$C$13</f>
+    <row r="34">
+      <c r="B34" s="65" t="inlineStr">
+        <is>
+          <t>Velocity (u/store/wk)</t>
+        </is>
+      </c>
+      <c r="C34" s="75">
+        <f>$F$17</f>
         <v/>
       </c>
-      <c r="D24" s="54">
-        <f>D23*$C$13</f>
+      <c r="D34" s="75">
+        <f>$F$18</f>
         <v/>
       </c>
-      <c r="E24" s="54">
-        <f>E23*$C$13</f>
+      <c r="E34" s="75">
+        <f>$F$19</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="43" t="inlineStr">
-        <is>
-          <t>Gross profit (CAD)</t>
-        </is>
-      </c>
-      <c r="C25" s="55">
-        <f>C23*$C$14</f>
+    <row r="35">
+      <c r="B35" s="65" t="inlineStr">
+        <is>
+          <t>Annual units</t>
+        </is>
+      </c>
+      <c r="C35" s="53">
+        <f>C33*C34*52</f>
         <v/>
       </c>
-      <c r="D25" s="55">
-        <f>D23*$C$14</f>
+      <c r="D35" s="53">
+        <f>D33*D34*52</f>
         <v/>
       </c>
-      <c r="E25" s="55">
-        <f>E23*$C$14</f>
+      <c r="E35" s="53">
+        <f>E33*E34*52</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="43" t="inlineStr">
-        <is>
-          <t>Trade spend (CAD)</t>
-        </is>
-      </c>
-      <c r="C26" s="55">
-        <f>C23*$C$16</f>
+    <row r="36">
+      <c r="B36" s="62" t="inlineStr">
+        <is>
+          <t>Net revenue</t>
+        </is>
+      </c>
+      <c r="C36" s="54">
+        <f>C35*$C$25</f>
         <v/>
       </c>
-      <c r="D26" s="55">
-        <f>D23*$C$16</f>
+      <c r="D36" s="54">
+        <f>D35*$C$25</f>
         <v/>
       </c>
-      <c r="E26" s="55">
-        <f>E23*$C$16</f>
+      <c r="E36" s="54">
+        <f>E35*$C$25</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="47" t="inlineStr">
-        <is>
-          <t>Contribution (CAD)</t>
-        </is>
-      </c>
-      <c r="C27" s="54">
-        <f>C23*$C$17</f>
+    <row r="37">
+      <c r="B37" s="65" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="C37" s="55">
+        <f>-C35*$F$9</f>
         <v/>
       </c>
-      <c r="D27" s="54">
-        <f>D23*$C$17</f>
+      <c r="D37" s="55">
+        <f>-D35*$F$9</f>
         <v/>
       </c>
-      <c r="E27" s="54">
-        <f>E23*$C$17</f>
+      <c r="E37" s="55">
+        <f>-E35*$F$9</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="46" customHeight="1">
-      <c r="B29" s="56" t="inlineStr">
-        <is>
-          <t>Model logic: net/can = list × (1−retailer %) × (1−distributor %). Contribution excludes fixed overhead, slotting, marketing and freight/FX — add those below for a full P&amp;L. Defaults illustrate a disciplined Canadian beachhead → scale path; they are NOT a forecast. Calibrate every yellow cell with real quotes (co-packer COGS, distributor terms, buyer velocity).</t>
-        </is>
-      </c>
+    <row r="38">
+      <c r="B38" s="62" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="C38" s="54">
+        <f>C36+C37</f>
+        <v/>
+      </c>
+      <c r="D38" s="54">
+        <f>D36+D37</f>
+        <v/>
+      </c>
+      <c r="E38" s="54">
+        <f>E36+E37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="65" t="inlineStr">
+        <is>
+          <t>Trade spend</t>
+        </is>
+      </c>
+      <c r="C39" s="55">
+        <f>-C35*$C$28</f>
+        <v/>
+      </c>
+      <c r="D39" s="55">
+        <f>-D35*$C$28</f>
+        <v/>
+      </c>
+      <c r="E39" s="55">
+        <f>-E35*$C$28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="65" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="C40" s="55">
+        <f>-$F$20</f>
+        <v/>
+      </c>
+      <c r="D40" s="55">
+        <f>-$F$20</f>
+        <v/>
+      </c>
+      <c r="E40" s="55">
+        <f>-$F$20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="65" t="inlineStr">
+        <is>
+          <t>Fixed overhead</t>
+        </is>
+      </c>
+      <c r="C41" s="55">
+        <f>-$F$21</f>
+        <v/>
+      </c>
+      <c r="D41" s="55">
+        <f>-$F$21</f>
+        <v/>
+      </c>
+      <c r="E41" s="55">
+        <f>-$F$21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="65" t="inlineStr">
+        <is>
+          <t>Slotting (one-time)</t>
+        </is>
+      </c>
+      <c r="C42" s="55">
+        <f>-$F$22</f>
+        <v/>
+      </c>
+      <c r="D42" s="55">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="E42" s="55">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="62" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="C43" s="73">
+        <f>C38+C40+C41+C42+C39</f>
+        <v/>
+      </c>
+      <c r="D43" s="73">
+        <f>D38+D40+D41+D42+D39</f>
+        <v/>
+      </c>
+      <c r="E43" s="73">
+        <f>E38+E40+E41+E42+E39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="65" t="inlineStr">
+        <is>
+          <t>EBITDA margin %</t>
+        </is>
+      </c>
+      <c r="C44" s="76">
+        <f>C43/C36</f>
+        <v/>
+      </c>
+      <c r="D44" s="76">
+        <f>D43/D36</f>
+        <v/>
+      </c>
+      <c r="E44" s="76">
+        <f>E43/E36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="42" t="inlineStr">
+        <is>
+          <t>BREAK-EVEN (Year-1 cost load ÷ contribution per can)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="65" t="inlineStr">
+        <is>
+          <t>Year-1 fixed + marketing + slotting</t>
+        </is>
+      </c>
+      <c r="C47" s="54">
+        <f>$F$20+$F$21+$F$22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="65" t="inlineStr">
+        <is>
+          <t>Break-even units (cans)</t>
+        </is>
+      </c>
+      <c r="C48" s="77">
+        <f>C47/$C$29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="65" t="inlineStr">
+        <is>
+          <t>Break-even cases</t>
+        </is>
+      </c>
+      <c r="C49" s="53">
+        <f>C48/$F$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="65" t="inlineStr">
+        <is>
+          <t>Year-1 actual units</t>
+        </is>
+      </c>
+      <c r="C50" s="53">
+        <f>C35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="62" t="inlineStr">
+        <is>
+          <t>Year-1 surplus / (gap) to break-even</t>
+        </is>
+      </c>
+      <c r="C51" s="78">
+        <f>C50-C48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="42" t="inlineStr">
+        <is>
+          <t>SENSITIVITY — Contribution per can (CAD):  price (down) × COGS (across), active margins</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" s="41" t="inlineStr">
+        <is>
+          <t>P＼COGS</t>
+        </is>
+      </c>
+      <c r="D54" s="79" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E54" s="79" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F54" s="79" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G54" s="79" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H54" s="79" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" s="79" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="D55" s="80">
+        <f>($C55*(1-$F$10)*(1-$F$11))*(1-$F$12)-D$54</f>
+        <v/>
+      </c>
+      <c r="E55" s="80">
+        <f>($C55*(1-$F$10)*(1-$F$11))*(1-$F$12)-E$54</f>
+        <v/>
+      </c>
+      <c r="F55" s="80">
+        <f>($C55*(1-$F$10)*(1-$F$11))*(1-$F$12)-F$54</f>
+        <v/>
+      </c>
+      <c r="G55" s="80">
+        <f>($C55*(1-$F$10)*(1-$F$11))*(1-$F$12)-G$54</f>
+        <v/>
+      </c>
+      <c r="H55" s="80">
+        <f>($C55*(1-$F$10)*(1-$F$11))*(1-$F$12)-H$54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" s="79" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="D56" s="80">
+        <f>($C56*(1-$F$10)*(1-$F$11))*(1-$F$12)-D$54</f>
+        <v/>
+      </c>
+      <c r="E56" s="80">
+        <f>($C56*(1-$F$10)*(1-$F$11))*(1-$F$12)-E$54</f>
+        <v/>
+      </c>
+      <c r="F56" s="80">
+        <f>($C56*(1-$F$10)*(1-$F$11))*(1-$F$12)-F$54</f>
+        <v/>
+      </c>
+      <c r="G56" s="80">
+        <f>($C56*(1-$F$10)*(1-$F$11))*(1-$F$12)-G$54</f>
+        <v/>
+      </c>
+      <c r="H56" s="80">
+        <f>($C56*(1-$F$10)*(1-$F$11))*(1-$F$12)-H$54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" s="79" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="D57" s="80">
+        <f>($C57*(1-$F$10)*(1-$F$11))*(1-$F$12)-D$54</f>
+        <v/>
+      </c>
+      <c r="E57" s="80">
+        <f>($C57*(1-$F$10)*(1-$F$11))*(1-$F$12)-E$54</f>
+        <v/>
+      </c>
+      <c r="F57" s="80">
+        <f>($C57*(1-$F$10)*(1-$F$11))*(1-$F$12)-F$54</f>
+        <v/>
+      </c>
+      <c r="G57" s="80">
+        <f>($C57*(1-$F$10)*(1-$F$11))*(1-$F$12)-G$54</f>
+        <v/>
+      </c>
+      <c r="H57" s="80">
+        <f>($C57*(1-$F$10)*(1-$F$11))*(1-$F$12)-H$54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" s="79" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="D58" s="80">
+        <f>($C58*(1-$F$10)*(1-$F$11))*(1-$F$12)-D$54</f>
+        <v/>
+      </c>
+      <c r="E58" s="80">
+        <f>($C58*(1-$F$10)*(1-$F$11))*(1-$F$12)-E$54</f>
+        <v/>
+      </c>
+      <c r="F58" s="80">
+        <f>($C58*(1-$F$10)*(1-$F$11))*(1-$F$12)-F$54</f>
+        <v/>
+      </c>
+      <c r="G58" s="80">
+        <f>($C58*(1-$F$10)*(1-$F$11))*(1-$F$12)-G$54</f>
+        <v/>
+      </c>
+      <c r="H58" s="80">
+        <f>($C58*(1-$F$10)*(1-$F$11))*(1-$F$12)-H$54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" s="79" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="D59" s="80">
+        <f>($C59*(1-$F$10)*(1-$F$11))*(1-$F$12)-D$54</f>
+        <v/>
+      </c>
+      <c r="E59" s="80">
+        <f>($C59*(1-$F$10)*(1-$F$11))*(1-$F$12)-E$54</f>
+        <v/>
+      </c>
+      <c r="F59" s="80">
+        <f>($C59*(1-$F$10)*(1-$F$11))*(1-$F$12)-F$54</f>
+        <v/>
+      </c>
+      <c r="G59" s="80">
+        <f>($C59*(1-$F$10)*(1-$F$11))*(1-$F$12)-G$54</f>
+        <v/>
+      </c>
+      <c r="H59" s="80">
+        <f>($C59*(1-$F$10)*(1-$F$11))*(1-$F$12)-H$54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="58" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Scenario logic: the ACTIVE column = CHOOSE(scenario, Conservative, Base, Aggressive); every downstream cell reads ACTIVE, so the dropdown re-drives the entire P&amp;L, break-even and (margins) sensitivity. EBITDA excludes freight/FX and financing — add as further lines for a full forecast. Replace all yellow cells with real co-packer, distributor and buyer numbers before relying on outputs.</t>
+        </is>
+      </c>
+      <c r="B61" s="34" t="n"/>
+      <c r="C61" s="34" t="n"/>
+      <c r="D61" s="34" t="n"/>
+      <c r="E61" s="34" t="n"/>
+      <c r="F61" s="34" t="n"/>
+      <c r="G61" s="34" t="n"/>
+      <c r="H61" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A4:F4"/>
+  <mergeCells count="7">
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A61:H61"/>
   </mergeCells>
-  <conditionalFormatting sqref="C24:E24">
-    <cfRule type="dataBar" priority="1">
+  <conditionalFormatting sqref="D55:H59">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C36:E36">
+    <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10770,8 +12378,8 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C27:E27">
-    <cfRule type="dataBar" priority="2">
+  <conditionalFormatting sqref="C43:E43">
+    <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -10779,6 +12387,14 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Conservative,Base,Aggressive"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -10799,7 +12415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10812,6 +12428,11 @@
           <t>Methodology &amp; Confidence Framework</t>
         </is>
       </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -10889,6 +12510,9 @@
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -10909,7 +12533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -10927,6 +12551,11 @@
           <t>Market Sizing — Category Sizes &amp; Growth</t>
         </is>
       </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
@@ -11633,6 +13262,9 @@
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -11653,7 +13285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11668,6 +13300,11 @@
           <t>Trends &amp; Macro Drivers (2025–2026)</t>
         </is>
       </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -11879,6 +13516,9 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A12:D12"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -11899,7 +13539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11913,6 +13553,11 @@
           <t>Consumer Segmentation &amp; The Collagen Buyer</t>
         </is>
       </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
@@ -12098,6 +13743,9 @@
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A10:C10"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>

--- a/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
+++ b/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
@@ -36,7 +36,8 @@
     <sheet name="22 Risk Register" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="23 KPI Dashboard" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="24 Sources" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="25 Glossary" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Verification Log" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="25 Glossary" sheetId="31" state="visible" r:id="rId31"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'07 Comparison Matrix'!$A$3:$L$11</definedName>
@@ -336,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -602,6 +603,21 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1662,10 +1678,10 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="72" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>CRITICAL CAVEAT — A discrete “Organika Sparkling” ready-to-drink CAN could not be verified in public sources. Organika's documented fizzy/collagen products are POWDER (Electrolytes + Enhanced Collagen) and LIQUID collagen water. If “MUV” is a new RTD can, confirm format, flavours, dose and price with the brand. The entire Canada regulatory analysis assumes an RTD food-format beverage.</t>
+    <row r="15" ht="96" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>RESOLVED (verified Jun 2026): “MÜV” IS a real Organika product — “MÜV Sparkling Electrolytes”, a SPARKLING/effervescent POWDER drink mix (not a verified canned RTD): zero sugar, caffeine-free, electrolytes + magnesium bisglycinate + Fibersol® prebiotic fibre. It sits in Organika's hydration family alongside “Electrolytes + Enhanced Collagen” (5g collagen). IMPORTANT: because MÜV is a POWDER, the Canadian NHP/NPN claim pathway likely applies (see ‘19 Canada Regulatory’) — the earlier RTD-can/food assumption is the downside case, not the base case. Confirm MÜV's exact label, dose, collagen content and price with the brand.</t>
         </is>
       </c>
       <c r="B15" s="34" t="n"/>
@@ -1727,6 +1743,12 @@
           <t>INTERACTIVE TABS (gold) — built to be used, not just read:</t>
         </is>
       </c>
+      <c r="C22" s="34" t="n"/>
+      <c r="D22" s="34" t="n"/>
+      <c r="E22" s="34" t="n"/>
+      <c r="F22" s="34" t="n"/>
+      <c r="G22" s="34" t="n"/>
+      <c r="H22" s="35" t="n"/>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="B23" s="90" t="inlineStr">
@@ -6394,7 +6416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6408,7 +6430,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -6778,6 +6799,18 @@
       <c r="B33" s="60" t="inlineStr">
         <is>
           <t>Terms &amp; abbreviations</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="94" t="inlineStr">
+        <is>
+          <t>Verification Log</t>
+        </is>
+      </c>
+      <c r="B34" s="58" t="inlineStr">
+        <is>
+          <t>What was checked against sources, what changed (incl. the MÜV finding)</t>
         </is>
       </c>
     </row>
@@ -6816,6 +6849,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -7818,7 +7852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8239,13 +8273,89 @@
       <c r="B32" s="34" t="n"/>
       <c r="C32" s="35" t="n"/>
     </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="96" t="inlineStr">
+        <is>
+          <t>POWDER vs RTD — FORMAT DETERMINES THE PATHWAY (key revision)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="44" customHeight="1">
+      <c r="A35" s="57" t="inlineStr">
+        <is>
+          <t>MÜV today = sparkling POWDER</t>
+        </is>
+      </c>
+      <c r="B35" s="58" t="inlineStr">
+        <is>
+          <t>Powders/effervescent mixes for reconstitution are generally licensed as Natural Health Products (NHPs) with an NPN — NOT food-format. Organika's existing electrolyte/collagen powders are almost certainly NHPs.</t>
+        </is>
+      </c>
+      <c r="C35" s="58" t="inlineStr">
+        <is>
+          <t>HARD-ish / confirm NPN</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="44" customHeight="1">
+      <c r="A36" s="57" t="inlineStr">
+        <is>
+          <t>Claims latitude (powder/NHP)</t>
+        </is>
+      </c>
+      <c r="B36" s="58" t="inlineStr">
+        <is>
+          <t>On an NHP, monograph-based structure-function claims (incl. certain collagen/joint/skin and electrolyte/hydration claims) are permissible — so Organika's collagen claims CAN largely transfer to a powder. This is a claims ADVANTAGE of staying powder.</t>
+        </is>
+      </c>
+      <c r="C36" s="58" t="inlineStr">
+        <is>
+          <t>DIRECTIONAL – per NHP monographs</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="44" customHeight="1">
+      <c r="A37" s="57" t="inlineStr">
+        <is>
+          <t>If MÜV ever becomes an RTD can</t>
+        </is>
+      </c>
+      <c r="B37" s="58" t="inlineStr">
+        <is>
+          <t>It flips to FOOD / Supplemented Food (CFIA): no NPN, restricted claims, Supplemented Food Facts table, possible SFCI box, mandatory collagen caution. Treat this as the downside scenario for a future canned line extension.</t>
+        </is>
+      </c>
+      <c r="C37" s="58" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="44" customHeight="1">
+      <c r="A38" s="57" t="inlineStr">
+        <is>
+          <t>Interface caveat</t>
+        </is>
+      </c>
+      <c r="B38" s="58" t="inlineStr">
+        <is>
+          <t>Health Canada reviews products at the food–NHP interface case-by-case; a “drink mix” marketed/consumed like a food could still be deemed food-format. Confirm classification of MÜV's exact SKU with regulatory counsel.</t>
+        </is>
+      </c>
+      <c r="C38" s="58" t="inlineStr">
+        <is>
+          <t>FLAG – verify</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A34:C34"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
@@ -10604,6 +10714,340 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Verification Log</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>What was checked against sources on 2026-06-13, and what changed. Honesty over false precision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Claim checked</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Finding / corrected value</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="97" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="58" t="inlineStr">
+        <is>
+          <t>Does a “MÜV” / Organika sparkling product exist?</t>
+        </is>
+      </c>
+      <c r="C5" s="98" t="inlineStr">
+        <is>
+          <t>CONFIRMED + CORRECTED</t>
+        </is>
+      </c>
+      <c r="D5" s="58" t="inlineStr">
+        <is>
+          <t>“MÜV Sparkling Electrolytes” is a real Organika SKU — a sparkling/effervescent POWDER (not a verified RTD can): 0 sugar, caffeine-free, electrolytes + magnesium bisglycinate + Fibersol prebiotic fibre. Sibling SKU “Electrolytes + Enhanced Collagen” adds 5g collagen. Earlier dossier assumed an unverified RTD can — now downgraded to the downside scenario.</t>
+        </is>
+      </c>
+      <c r="E5" s="58" t="inlineStr">
+        <is>
+          <t>organika.com/products/muv-sparkling-electrolytes; Save-On-Foods; Amazon; iHerb</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="99" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="60" t="inlineStr">
+        <is>
+          <t>Regulatory pathway for MÜV</t>
+        </is>
+      </c>
+      <c r="C6" s="98" t="inlineStr">
+        <is>
+          <t>CORRECTED</t>
+        </is>
+      </c>
+      <c r="D6" s="60" t="inlineStr">
+        <is>
+          <t>Powder format likely = NHP with NPN (claims latitude PRESERVED), not the food/Supplemented-Food RTD pathway previously emphasized. Material correction — see Tab 19.</t>
+        </is>
+      </c>
+      <c r="E6" s="60" t="inlineStr">
+        <is>
+          <t>Health Canada NHP guidance; format analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="97" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="58" t="inlineStr">
+        <is>
+          <t>Poppi → PepsiCo $1.95B (closed May 2025)</t>
+        </is>
+      </c>
+      <c r="C7" s="100" t="inlineStr">
+        <is>
+          <t>Carried forward</t>
+        </is>
+      </c>
+      <c r="D7" s="58" t="inlineStr">
+        <is>
+          <t>Multi-source corroborated in research (PepsiCo PR + trade). Fresh primary re-pull recommended before external use.</t>
+        </is>
+      </c>
+      <c r="E7" s="58" t="inlineStr">
+        <is>
+          <t>pepsico.com newsroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="99" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>OLIPOP $50M Series C @ $1.85B (Feb 2025)</t>
+        </is>
+      </c>
+      <c r="C8" s="100" t="inlineStr">
+        <is>
+          <t>Carried forward</t>
+        </is>
+      </c>
+      <c r="D8" s="60" t="inlineStr">
+        <is>
+          <t>Multi-source corroborated (CNBC/Food Dive/BevIndustry).</t>
+        </is>
+      </c>
+      <c r="E8" s="60" t="inlineStr">
+        <is>
+          <t>cnbc.com; fooddive.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="97" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="58" t="inlineStr">
+        <is>
+          <t>LMNT FY2023 $206M sales, ~20% net</t>
+        </is>
+      </c>
+      <c r="C9" s="100" t="inlineStr">
+        <is>
+          <t>Carried forward (high conf.)</t>
+        </is>
+      </c>
+      <c r="D9" s="58" t="inlineStr">
+        <is>
+          <t>From LMNT's own SEC Reg CF filing, CIK 1871551 — strongest figure in the set.</t>
+        </is>
+      </c>
+      <c r="E9" s="58" t="inlineStr">
+        <is>
+          <t>sec.gov EDGAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="99" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="60" t="inlineStr">
+        <is>
+          <t>Modern soda $1.8B 2024, +83% YoY</t>
+        </is>
+      </c>
+      <c r="C10" s="100" t="inlineStr">
+        <is>
+          <t>Carried forward</t>
+        </is>
+      </c>
+      <c r="D10" s="60" t="inlineStr">
+        <is>
+          <t>Circana scanner via Beverage Industry / CSNews; anchor TAM figure.</t>
+        </is>
+      </c>
+      <c r="E10" s="60" t="inlineStr">
+        <is>
+          <t>Circana; bevindustry.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="97" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="58" t="inlineStr">
+        <is>
+          <t>Poppi $8.9M gut-health settlement</t>
+        </is>
+      </c>
+      <c r="C11" s="100" t="inlineStr">
+        <is>
+          <t>Carried forward</t>
+        </is>
+      </c>
+      <c r="D11" s="58" t="inlineStr">
+        <is>
+          <t>classaction.org + BevNET; final approval ~Apr 2026.</t>
+        </is>
+      </c>
+      <c r="E11" s="58" t="inlineStr">
+        <is>
+          <t>classaction.org; bevnet.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="99" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="60" t="inlineStr">
+        <is>
+          <t>Liquid I.V. Costco 2019 (~516 whs); Unilever Sept 2020</t>
+        </is>
+      </c>
+      <c r="C12" s="100" t="inlineStr">
+        <is>
+          <t>Carried forward</t>
+        </is>
+      </c>
+      <c r="D12" s="60" t="inlineStr">
+        <is>
+          <t>liquid-iv.com + Unilever PR + BevNET.</t>
+        </is>
+      </c>
+      <c r="E12" s="60" t="inlineStr">
+        <is>
+          <t>unilever.com; bevnet.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="97" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="58" t="inlineStr">
+        <is>
+          <t>Canada Supplemented Foods Reg (Jul 2022); caffeine 180mg cap</t>
+        </is>
+      </c>
+      <c r="C13" s="100" t="inlineStr">
+        <is>
+          <t>Carried forward (high conf.)</t>
+        </is>
+      </c>
+      <c r="D13" s="58" t="inlineStr">
+        <is>
+          <t>Health Canada + Fasken; 180mg cap blocked Prime Energy (stack3d).</t>
+        </is>
+      </c>
+      <c r="E13" s="58" t="inlineStr">
+        <is>
+          <t>canada.ca; fasken.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="99" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="60" t="inlineStr">
+        <is>
+          <t>Poppi entered Canada Aug 2024; Celsius $550M / Alani Nu $1.8B</t>
+        </is>
+      </c>
+      <c r="C14" s="100" t="inlineStr">
+        <is>
+          <t>Carried forward</t>
+        </is>
+      </c>
+      <c r="D14" s="60" t="inlineStr">
+        <is>
+          <t>newswire.ca; Bloomberg/BusinessWire.</t>
+        </is>
+      </c>
+      <c r="E14" s="60" t="inlineStr">
+        <is>
+          <t>newswire.ca; bloomberg.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="56" t="inlineStr">
+        <is>
+          <t>Method note: Item 1–2 were re-verified live against Organika's site and Canadian retailer listings on 2026-06-13 (storefront blocks automated fetch, so confirmed via search-indexed product/retailer pages). Items 3–10 were multi-source corroborated during the research phase but were NOT individually re-pulled from primary sources this round (a verification agent was rate-limited); they are labelled “carried forward”. Re-pull these from the cited primary URLs before any external/board circulation.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>

--- a/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
+++ b/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
@@ -337,7 +337,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -614,9 +614,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10832,22 +10829,22 @@
       </c>
       <c r="B7" s="58" t="inlineStr">
         <is>
-          <t>Poppi → PepsiCo $1.95B (closed May 2025)</t>
-        </is>
-      </c>
-      <c r="C7" s="100" t="inlineStr">
-        <is>
-          <t>Carried forward</t>
+          <t>Poppi → PepsiCo $1.95B</t>
+        </is>
+      </c>
+      <c r="C7" s="98" t="inlineStr">
+        <is>
+          <t>CONFIRMED (primary)</t>
         </is>
       </c>
       <c r="D7" s="58" t="inlineStr">
         <is>
-          <t>Multi-source corroborated in research (PepsiCo PR + trade). Fresh primary re-pull recommended before external use.</t>
+          <t>$1.95B incl. $300M anticipated cash tax benefits → net $1.65B, plus a performance earnout. Closed/announced May 19, 2025.</t>
         </is>
       </c>
       <c r="E7" s="58" t="inlineStr">
         <is>
-          <t>pepsico.com newsroom</t>
+          <t>PepsiCo newsroom PR (2025-05-19)</t>
         </is>
       </c>
     </row>
@@ -10857,22 +10854,22 @@
       </c>
       <c r="B8" s="60" t="inlineStr">
         <is>
-          <t>OLIPOP $50M Series C @ $1.85B (Feb 2025)</t>
-        </is>
-      </c>
-      <c r="C8" s="100" t="inlineStr">
-        <is>
-          <t>Carried forward</t>
+          <t>OLIPOP $50M Series C @ $1.85B</t>
+        </is>
+      </c>
+      <c r="C8" s="98" t="inlineStr">
+        <is>
+          <t>CONFIRMED (primary)</t>
         </is>
       </c>
       <c r="D8" s="60" t="inlineStr">
         <is>
-          <t>Multi-source corroborated (CNBC/Food Dive/BevIndustry).</t>
+          <t>$50M led by JP Morgan Private Capital at $1.85B valuation (Feb 12, 2025); company states fully profitable, &gt;$400M 2024 sales; described as final anticipated equity round.</t>
         </is>
       </c>
       <c r="E8" s="60" t="inlineStr">
         <is>
-          <t>cnbc.com; fooddive.com</t>
+          <t>Bloomberg; CNBC (2025-02-12)</t>
         </is>
       </c>
     </row>
@@ -10885,19 +10882,19 @@
           <t>LMNT FY2023 $206M sales, ~20% net</t>
         </is>
       </c>
-      <c r="C9" s="100" t="inlineStr">
-        <is>
-          <t>Carried forward (high conf.)</t>
+      <c r="C9" s="98" t="inlineStr">
+        <is>
+          <t>CONFIRMED (primary)</t>
         </is>
       </c>
       <c r="D9" s="58" t="inlineStr">
         <is>
-          <t>From LMNT's own SEC Reg CF filing, CIK 1871551 — strongest figure in the set.</t>
+          <t>$206M sales, ~20% net income margin, $54.6M marketing (~26.5% of revenue) — LMNT's own SEC Form C-AR, CIK 1871551, FY ended 12/31/2023.</t>
         </is>
       </c>
       <c r="E9" s="58" t="inlineStr">
         <is>
-          <t>sec.gov EDGAR</t>
+          <t>sec.gov EDGAR (lmnt.pdf, CIK 1871551)</t>
         </is>
       </c>
     </row>
@@ -10910,19 +10907,19 @@
           <t>Modern soda $1.8B 2024, +83% YoY</t>
         </is>
       </c>
-      <c r="C10" s="100" t="inlineStr">
-        <is>
-          <t>Carried forward</t>
+      <c r="C10" s="98" t="inlineStr">
+        <is>
+          <t>CONFIRMED (scanner)</t>
         </is>
       </c>
       <c r="D10" s="60" t="inlineStr">
         <is>
-          <t>Circana scanner via Beverage Industry / CSNews; anchor TAM figure.</t>
+          <t>$1.8B in 2024, up 83% from $983M (2023). Shares: Poppi 38%, OLIPOP 32.7%, Zevia 12.1%, Jarritos 10.3%, Fever-Tree 4%, other 2.9%.</t>
         </is>
       </c>
       <c r="E10" s="60" t="inlineStr">
         <is>
-          <t>Circana; bevindustry.com</t>
+          <t>Circana via Beverage Industry / CNN</t>
         </is>
       </c>
     </row>
@@ -10935,19 +10932,19 @@
           <t>Poppi $8.9M gut-health settlement</t>
         </is>
       </c>
-      <c r="C11" s="100" t="inlineStr">
-        <is>
-          <t>Carried forward</t>
+      <c r="C11" s="98" t="inlineStr">
+        <is>
+          <t>CONFIRMED (primary)</t>
         </is>
       </c>
       <c r="D11" s="58" t="inlineStr">
         <is>
-          <t>classaction.org + BevNET; final approval ~Apr 2026.</t>
+          <t>$8.9M settlement; suit (June 2024) alleged 2g fiber too low (need &gt;4 cans/day). Class period from Jan 23, 2020. Preliminary approval May 23, 2025; FINAL approval April 14, 2026.</t>
         </is>
       </c>
       <c r="E11" s="58" t="inlineStr">
         <is>
-          <t>classaction.org; bevnet.com</t>
+          <t>classaction.org; BevNET; Today</t>
         </is>
       </c>
     </row>
@@ -10957,22 +10954,22 @@
       </c>
       <c r="B12" s="60" t="inlineStr">
         <is>
-          <t>Liquid I.V. Costco 2019 (~516 whs); Unilever Sept 2020</t>
-        </is>
-      </c>
-      <c r="C12" s="100" t="inlineStr">
-        <is>
-          <t>Carried forward</t>
+          <t>Liquid I.V. Costco 2019; Unilever 2020</t>
+        </is>
+      </c>
+      <c r="C12" s="98" t="inlineStr">
+        <is>
+          <t>CONFIRMED (primary)</t>
         </is>
       </c>
       <c r="D12" s="60" t="inlineStr">
         <is>
-          <t>liquid-iv.com + Unilever PR + BevNET.</t>
+          <t>National Costco launch Jan 8, 2019 → 516 warehouses. Unilever agreed to acquire Sept 1, 2020 (~$500M / ~5x reported; terms officially undisclosed).</t>
         </is>
       </c>
       <c r="E12" s="60" t="inlineStr">
         <is>
-          <t>unilever.com; bevnet.com</t>
+          <t>liquid-iv.com; Unilever PR; BevNET</t>
         </is>
       </c>
     </row>
@@ -10982,22 +10979,22 @@
       </c>
       <c r="B13" s="58" t="inlineStr">
         <is>
-          <t>Canada Supplemented Foods Reg (Jul 2022); caffeine 180mg cap</t>
-        </is>
-      </c>
-      <c r="C13" s="100" t="inlineStr">
-        <is>
-          <t>Carried forward (high conf.)</t>
+          <t>Canada Supplemented Foods Reg; 180mg caffeine cap</t>
+        </is>
+      </c>
+      <c r="C13" s="98" t="inlineStr">
+        <is>
+          <t>CONFIRMED (primary)</t>
         </is>
       </c>
       <c r="D13" s="58" t="inlineStr">
         <is>
-          <t>Health Canada + Fasken; 180mg cap blocked Prime Energy (stack3d).</t>
+          <t>Amendments in force July 21, 2022. 180mg caffeine cap per single-serve container; Prime Energy (200mg) violated it and was recalled in Canada (July 2023), alongside others.</t>
         </is>
       </c>
       <c r="E13" s="58" t="inlineStr">
         <is>
-          <t>canada.ca; fasken.com</t>
+          <t>Health Canada (canada.ca); CNN; Fasken</t>
         </is>
       </c>
     </row>
@@ -11007,29 +11004,29 @@
       </c>
       <c r="B14" s="60" t="inlineStr">
         <is>
-          <t>Poppi entered Canada Aug 2024; Celsius $550M / Alani Nu $1.8B</t>
-        </is>
-      </c>
-      <c r="C14" s="100" t="inlineStr">
-        <is>
-          <t>Carried forward</t>
+          <t>Celsius–PepsiCo $550M; Celsius buys Alani Nu $1.8B</t>
+        </is>
+      </c>
+      <c r="C14" s="98" t="inlineStr">
+        <is>
+          <t>CONFIRMED (primary)</t>
         </is>
       </c>
       <c r="D14" s="60" t="inlineStr">
         <is>
-          <t>newswire.ca; Bloomberg/BusinessWire.</t>
+          <t>PepsiCo $550M convertible pref @ $75/sh (~8.5%), Aug 2022, global distribution. Celsius acquired Alani Nu for $1.8B (incl. $150M tax assets → net $1.65B); announced Feb 2025, CLOSED April 1, 2025.</t>
         </is>
       </c>
       <c r="E14" s="60" t="inlineStr">
         <is>
-          <t>newswire.ca; bloomberg.com</t>
+          <t>SEC 8-K; BevNET; Food Dive</t>
         </is>
       </c>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="56" t="inlineStr">
         <is>
-          <t>Method note: Item 1–2 were re-verified live against Organika's site and Canadian retailer listings on 2026-06-13 (storefront blocks automated fetch, so confirmed via search-indexed product/retailer pages). Items 3–10 were multi-source corroborated during the research phase but were NOT individually re-pulled from primary sources this round (a verification agent was rate-limited); they are labelled “carried forward”. Re-pull these from the cited primary URLs before any external/board circulation.</t>
+          <t>Method note: All 10 items were re-verified on 2026-06-13. Items 1–2 confirmed against Organika's site + Canadian retailer listings (storefront blocks automated fetch, so confirmed via search-indexed product/retailer pages). Items 3–10 were re-pulled and CONFIRMED against primary sources (PepsiCo, SEC EDGAR, Circana via trade press, Health Canada, classaction.org, Unilever, Celsius SEC 8-Ks), several with added precision (net purchase prices, exact close dates). No figure required downward correction; the only material change this round was the MÜV product/format finding (items 1–2). Direct primary-PDF re-read still advised for any figure quoted verbatim in board materials.</t>
         </is>
       </c>
     </row>

--- a/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
+++ b/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
@@ -29,15 +29,17 @@
     <sheet name="17 Scoring Model" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="18 Canada Market" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="19 Canada Regulatory" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="20 GTM Recommendation" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Go-NoGo Decision" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Battlecards" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="21 Launch Plan" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="22 Risk Register" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="23 KPI Dashboard" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="24 Sources" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Verification Log" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="25 Glossary" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Canada Regulatory v2" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Electrolyte BFY Deep-Dive" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="20 GTM Recommendation" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Go-NoGo Decision" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Battlecards" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="21 Launch Plan" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="22 Risk Register" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="23 KPI Dashboard" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="24 Sources" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Verification Log" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="25 Glossary" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'07 Comparison Matrix'!$A$3:$L$11</definedName>
@@ -54,7 +56,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -198,6 +200,12 @@
       <sz val="8"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -337,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -615,6 +623,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1678,7 +1689,7 @@
     <row r="15" ht="96" customHeight="1">
       <c r="A15" s="17" t="inlineStr">
         <is>
-          <t>RESOLVED (verified Jun 2026): “MÜV” IS a real Organika product — “MÜV Sparkling Electrolytes”, a SPARKLING/effervescent POWDER drink mix (not a verified canned RTD): zero sugar, caffeine-free, electrolytes + magnesium bisglycinate + Fibersol® prebiotic fibre. It sits in Organika's hydration family alongside “Electrolytes + Enhanced Collagen” (5g collagen). IMPORTANT: because MÜV is a POWDER, the Canadian NHP/NPN claim pathway likely applies (see ‘19 Canada Regulatory’) — the earlier RTD-can/food assumption is the downside case, not the base case. Confirm MÜV's exact label, dose, collagen content and price with the brand.</t>
+          <t>VERIFIED (Jun 2026): “MÜV Sparkling Electrolytes” is a real Organika product — most likely a ready-to-drink SPARKLING CAN (SKU 4338, ~$14.99; ingredient list begins “Carbonated water” + Fibersol prebiotic fibre, magnesium glycinate, stevia, 0 sugar, caffeine-free). Organika's electrolyte POWDERS and “Electrolytes + Enhanced Collagen” are SEPARATE SKUs. KEY: Canada is reclassifying sport-electrolyte products (all formats) from NHP to SUPPLEMENTED FOODS by Dec 31, 2027 — so MÜV is food-regulated; collagen beauty claims stay NHP-only (see ‘Canada Regulatory v2’). Confirm pack size, electrolyte mg and any collagen variant with the brand.</t>
         </is>
       </c>
       <c r="B15" s="34" t="n"/>
@@ -6413,7 +6424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6808,6 +6819,30 @@
       <c r="B34" s="58" t="inlineStr">
         <is>
           <t>What was checked against sources, what changed (incl. the MÜV finding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="94" t="inlineStr">
+        <is>
+          <t>Electrolyte BFY Deep-Dive</t>
+        </is>
+      </c>
+      <c r="B35" s="58" t="inlineStr">
+        <is>
+          <t>Canada-first electrolyte/sparkling/BFY research; MÜV's real lane (deep-research)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1">
+      <c r="A36" s="94" t="inlineStr">
+        <is>
+          <t>Canada Regulatory v2</t>
+        </is>
+      </c>
+      <c r="B36" s="58" t="inlineStr">
+        <is>
+          <t>Sport-electrolyte → Supplemented Foods reclassification; claims fork (supersedes Tab 19)</t>
         </is>
       </c>
     </row>
@@ -6847,6 +6882,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -8273,75 +8310,75 @@
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="96" t="inlineStr">
         <is>
-          <t>POWDER vs RTD — FORMAT DETERMINES THE PATHWAY (key revision)</t>
+          <t>MÜV = RTD CAN · SPORT ELECTROLYTES → SUPPLEMENTED FOODS (corrected Jun 2026 — see Canada Regulatory v2)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="44" customHeight="1">
       <c r="A35" s="57" t="inlineStr">
         <is>
-          <t>MÜV today = sparkling POWDER</t>
+          <t>SUPERSEDED — see ‘Canada Regulatory v2’</t>
         </is>
       </c>
       <c r="B35" s="58" t="inlineStr">
         <is>
-          <t>Powders/effervescent mixes for reconstitution are generally licensed as Natural Health Products (NHPs) with an NPN — NOT food-format. Organika's existing electrolyte/collagen powders are almost certainly NHPs.</t>
+          <t>This section's earlier “powder = NHP advantage” framing is OUT OF DATE. Health Canada is reclassifying ALL sport-electrolyte products (RTD, powder, effervescent) from NHP to SUPPLEMENTED FOODS. Format is not the regulatory decider — representation + claims are.</t>
         </is>
       </c>
       <c r="C35" s="58" t="inlineStr">
         <is>
-          <t>HARD-ish / confirm NPN</t>
+          <t>CORRECTED Jun 2026</t>
         </is>
       </c>
     </row>
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="57" t="inlineStr">
         <is>
-          <t>Claims latitude (powder/NHP)</t>
+          <t>MÜV is an RTD sparkling CAN</t>
         </is>
       </c>
       <c r="B36" s="58" t="inlineStr">
         <is>
-          <t>On an NHP, monograph-based structure-function claims (incl. certain collagen/joint/skin and electrolyte/hydration claims) are permissible — so Organika's collagen claims CAN largely transfer to a powder. This is a claims ADVANTAGE of staying powder.</t>
+          <t>Verified via ingredient list (begins “Carbonated water”) + SKU 4338 / ~$14.99. It is food-coded; treat as a Supplemented Food.</t>
         </is>
       </c>
       <c r="C36" s="58" t="inlineStr">
         <is>
-          <t>DIRECTIONAL – per NHP monographs</t>
+          <t>HARD</t>
         </is>
       </c>
     </row>
     <row r="37" ht="44" customHeight="1">
       <c r="A37" s="57" t="inlineStr">
         <is>
-          <t>If MÜV ever becomes an RTD can</t>
+          <t>Sport electrolytes → Supplemented Foods</t>
         </is>
       </c>
       <c r="B37" s="58" t="inlineStr">
         <is>
-          <t>It flips to FOOD / Supplemented Food (CFIA): no NPN, restricted claims, Supplemented Food Facts table, possible SFCI box, mandatory collagen caution. Treat this as the downside scenario for a future canned line extension.</t>
+          <t>Health Canada Public Notice (Apr 2026): transition from NHP to food framework; NPN holders by Dec 31, 2027; NEW products comply with FDR now. ORS (clinical) stays NHP.</t>
         </is>
       </c>
       <c r="C37" s="58" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>HARD (primary)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="44" customHeight="1">
       <c r="A38" s="57" t="inlineStr">
         <is>
-          <t>Interface caveat</t>
+          <t>Collagen is the real NHP trigger</t>
         </is>
       </c>
       <c r="B38" s="58" t="inlineStr">
         <is>
-          <t>Health Canada reviews products at the food–NHP interface case-by-case; a “drink mix” marketed/consumed like a food could still be deemed food-format. Confirm classification of MÜV's exact SKU with regulatory counsel.</t>
+          <t>Electrolyte/hydration claims = food-friendly. Collagen skin/joint/hair/beauty claims = NHP-only. Keep those on Organika's NHP collagen powder, not the MÜV can.</t>
         </is>
       </c>
       <c r="C38" s="58" t="inlineStr">
         <is>
-          <t>FLAG – verify</t>
+          <t>HARD</t>
         </is>
       </c>
     </row>
@@ -8375,6 +8412,1237 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001E7D32"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Canada Regulatory v2 — Sport-Electrolyte Reclassification (2026)</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Supersedes the powder/NHP framing on Tab 19. ✅HARD ◐DIRECTIONAL ⚠FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>HEADLINE: Health Canada Public Notice (Apr 2026) reclassifies ALL sport-electrolyte products — RTD beverages, powders/concentrates AND effervescent tablets — from Natural Health Products (NHP/NPN) to FOODS / Supplemented Foods. Existing NPN holders transition by Dec 31, 2027; NEW products must comply with the Food &amp; Drug Regulations immediately. Oral Rehydration Solutions (clinical) stay NHP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>FORMAT IS NOT THE DECIDER (the key nuance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Point</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Conf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="58" t="inlineStr">
+        <is>
+          <t>Format ≠ classification</t>
+        </is>
+      </c>
+      <c r="B7" s="58" t="inlineStr">
+        <is>
+          <t>Per Health Canada's food–NHP interface guidance, even powders &amp; effervescent tablets for reconstitution CAN be foods. Classification weighs representation, composition, format, perception &amp; history — together.</t>
+        </is>
+      </c>
+      <c r="C7" s="58" t="inlineStr">
+        <is>
+          <t>✅ (primary)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="60" t="inlineStr">
+        <is>
+          <t>What pushes toward FOOD</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>Beverage representation; scoop/serving + a Nutrition/Supplemented-Food Facts table; consumed freely like ordinary food/drink.</t>
+        </is>
+      </c>
+      <c r="C8" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="58" t="inlineStr">
+        <is>
+          <t>What pushes toward NHP</t>
+        </is>
+      </c>
+      <c r="B9" s="58" t="inlineStr">
+        <is>
+          <t>Dosage forms (capsules, single-dose sticks, measured drops) + regimented dosing + defined daily limits + conditions of use + therapeutic/structure-function claims.</t>
+        </is>
+      </c>
+      <c r="C9" s="58" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="60" t="inlineStr">
+        <is>
+          <t>So the real driver is CLAIMS</t>
+        </is>
+      </c>
+      <c r="B10" s="60" t="inlineStr">
+        <is>
+          <t>Electrolyte/hydration framing = food. Collagen skin/joint/hair/beauty claims = NHP-only. The claim, not the powder-vs-RTD format, decides the lane.</t>
+        </is>
+      </c>
+      <c r="C10" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>CLAIMS FORK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>If the product is…</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Framework</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Allowed claims</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="58" t="inlineStr">
+        <is>
+          <t>Plain electrolyte (can OR powder)</t>
+        </is>
+      </c>
+      <c r="B13" s="58" t="inlineStr">
+        <is>
+          <t>Supplemented Food</t>
+        </is>
+      </c>
+      <c r="C13" s="58" t="inlineStr">
+        <is>
+          <t>hydration, “replenish electrolytes”, source-of-magnesium/potassium, sugar-free, nutrient-content &amp; acceptable function claims</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="60" t="inlineStr">
+        <is>
+          <t>Electrolyte + collagen w/ beauty/joint claims</t>
+        </is>
+      </c>
+      <c r="B14" s="60" t="inlineStr">
+        <is>
+          <t>NHP (NPN)</t>
+        </is>
+      </c>
+      <c r="C14" s="60" t="inlineStr">
+        <is>
+          <t>“supports skin/hair/nails/joints”, collagen structure-function (dose-format powder is the defensible vehicle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="58" t="inlineStr">
+        <is>
+          <t>Oral rehydration (clinical)</t>
+        </is>
+      </c>
+      <c r="B15" s="58" t="inlineStr">
+        <is>
+          <t>NHP (NPN)</t>
+        </is>
+      </c>
+      <c r="C15" s="58" t="inlineStr">
+        <is>
+          <t>therapeutic rehydration</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="42" t="inlineStr">
+        <is>
+          <t>SUPPLEMENTED FOODS FRAMEWORK &amp; LABELLING</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>Requirement</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>Conf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="38" customHeight="1">
+      <c r="A18" s="58" t="inlineStr">
+        <is>
+          <t>Framework</t>
+        </is>
+      </c>
+      <c r="B18" s="58" t="inlineStr">
+        <is>
+          <t>In force July 21, 2022. Added vitamins/minerals/amino acids per List of Permitted Supplemental Ingredients &amp; Categories.</t>
+        </is>
+      </c>
+      <c r="C18" s="58" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="38" customHeight="1">
+      <c r="A19" s="60" t="inlineStr">
+        <is>
+          <t>Supplemented Food Facts table (SFFt)</t>
+        </is>
+      </c>
+      <c r="B19" s="60" t="inlineStr">
+        <is>
+          <t>Modified Nutrition Facts table with a “Supplemented with” line (name + amount of each supplemental ingredient).</t>
+        </is>
+      </c>
+      <c r="C19" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="38" customHeight="1">
+      <c r="A20" s="58" t="inlineStr">
+        <is>
+          <t>Caution Identifier (SFCI)</t>
+        </is>
+      </c>
+      <c r="B20" s="58" t="inlineStr">
+        <is>
+          <t>Black-&amp;-white identifier on the principal display panel WHEN cautionary statements are required (children, pregnancy, etc.).</t>
+        </is>
+      </c>
+      <c r="C20" s="58" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="38" customHeight="1">
+      <c r="A21" s="60" t="inlineStr">
+        <is>
+          <t>Caffeine</t>
+        </is>
+      </c>
+      <c r="B21" s="60" t="inlineStr">
+        <is>
+          <t>180 mg cap is PER-SERVING for the caffeinated-beverage category (400 mg/day is the reference). Moot for caffeine-free MÜV.</t>
+        </is>
+      </c>
+      <c r="C21" s="60" t="inlineStr">
+        <is>
+          <t>✅ (precision)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="38" customHeight="1">
+      <c r="A22" s="58" t="inlineStr">
+        <is>
+          <t>Collagen caution</t>
+        </is>
+      </c>
+      <c r="B22" s="58" t="inlineStr">
+        <is>
+          <t>If hydrolyzed collagen is present: “CAUTION, DO NOT USE AS SOLE SOURCE OF NUTRITION” on the PDP, same type size as common name (FDR).</t>
+        </is>
+      </c>
+      <c r="C22" s="58" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="38" customHeight="1">
+      <c r="A23" s="60" t="inlineStr">
+        <is>
+          <t>Bilingual EN/FR</t>
+        </is>
+      </c>
+      <c r="B23" s="60" t="inlineStr">
+        <is>
+          <t>Mandatory on all required info incl. the facts table.</t>
+        </is>
+      </c>
+      <c r="C23" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="38" customHeight="1">
+      <c r="A24" s="58" t="inlineStr">
+        <is>
+          <t>Quebec Bill 96 / OQLF</t>
+        </is>
+      </c>
+      <c r="B24" s="58" t="inlineStr">
+        <is>
+          <t>From Jun 1, 2025 generic/descriptive terms in a trademark need French; “Sparkling Electrolytes” likely needs a French descriptor. Sell-through grace to Jun 1, 2027.</t>
+        </is>
+      </c>
+      <c r="C24" s="58" t="inlineStr">
+        <is>
+          <t>◐ (trademark call)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="42" t="inlineStr">
+        <is>
+          <t>PRACTICAL TAKEAWAY FOR MÜV</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>Guidance</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="44" customHeight="1">
+      <c r="A27" s="58" t="inlineStr">
+        <is>
+          <t>Classification</t>
+        </is>
+      </c>
+      <c r="B27" s="58" t="inlineStr">
+        <is>
+          <t>MÜV (RTD electrolyte can, caffeine-free) = a Supplemented Food. No NPN; SFFt + cautions/SFCI as applicable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44" customHeight="1">
+      <c r="A28" s="60" t="inlineStr">
+        <is>
+          <t>Claims</t>
+        </is>
+      </c>
+      <c r="B28" s="60" t="inlineStr">
+        <is>
+          <t>Hydration/electrolyte/“replenish” + prebiotic-fibre function are safe. Do NOT put collagen beauty/joint claims on the can — keep them on the NHP collagen powder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="44" customHeight="1">
+      <c r="A29" s="58" t="inlineStr">
+        <is>
+          <t>Format choice</t>
+        </is>
+      </c>
+      <c r="B29" s="58" t="inlineStr">
+        <is>
+          <t>For a plain electrolyte line, powder vs RTD now sit in the SAME (food) lane — choose on cost/shelf-life/experience, not regulation. Only a collagen-claims strategy argues for a dose-format NHP powder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="44" customHeight="1">
+      <c r="A30" s="60" t="inlineStr">
+        <is>
+          <t>Timeline</t>
+        </is>
+      </c>
+      <c r="B30" s="60" t="inlineStr">
+        <is>
+          <t>Design to the food/Supplemented-Food framework from day one to avoid a 2027 relabel; new products must comply with FDR now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="46" customHeight="1">
+      <c r="A31" s="100" t="inlineStr">
+        <is>
+          <t>OPEN ITEMS ⚠: confirm exact transition date (Dec 31 2027 vs Jan 1 2028) on the canada.ca notice; MÜV's current licensing status (food vs any legacy NPN); verbatim collagen monograph wording; Bill 96 trademark analysis for “MÜV Sparkling Electrolytes”. canada.ca/LNHPD pages block automated fetch (403) — verify on the live primary page before a compliance filing.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E7D8A"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Electrolyte / Sparkling / Better-For-You — Canada-First Deep-Dive</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Deep-research pass (2026-06-26): MÜV's real competitive lane · ✅HARD ◐DIRECTIONAL ⚠FLAG</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>TWO FINDINGS THAT RESHAPE THE READ: (1) MÜV is a ready-to-drink SPARKLING CAN (verified: ingredient list begins “Carbonated water”, SKU 4338, ~$14.99), not a powder. (2) Canada is moving ALL sport-electrolyte products (RTD, powder, effervescent) from NHP to SUPPLEMENTED FOODS by Dec 31, 2027. So MÜV competes in the daily-wellness sparkling lane and is food-regulated; win on format + Canadian-made, not on collagen-beauty claims.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="42" t="inlineStr">
+        <is>
+          <t>1 · MARKET SIZING (Canada-first)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Geo</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Conf.</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="58" t="inlineStr">
+        <is>
+          <t>Powdered hydration mixes</t>
+        </is>
+      </c>
+      <c r="B7" s="58" t="inlineStr">
+        <is>
+          <t>$1.5B (2024), +20% YoY; 4 straight yrs double-digit; units +21.4%</t>
+        </is>
+      </c>
+      <c r="C7" s="58" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D7" s="58" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E7" s="58" t="inlineStr">
+        <is>
+          <t>Circana via CNN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="60" t="inlineStr">
+        <is>
+          <t>Gatorade powder enhancers</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>+200% over 4 years</t>
+        </is>
+      </c>
+      <c r="C8" s="60" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D8" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E8" s="60" t="inlineStr">
+        <is>
+          <t>Circana via CNN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="58" t="inlineStr">
+        <is>
+          <t>Electrolyte powder market</t>
+        </is>
+      </c>
+      <c r="B9" s="58" t="inlineStr">
+        <is>
+          <t>~$8.7B (2024), ~8.8% CAGR to 2030; powder fastest-growing format</t>
+        </is>
+      </c>
+      <c r="C9" s="58" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="D9" s="58" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="E9" s="58" t="inlineStr">
+        <is>
+          <t>Grand View; Mordor</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="60" t="inlineStr">
+        <is>
+          <t>NA electrolyte share</t>
+        </is>
+      </c>
+      <c r="B10" s="60" t="inlineStr">
+        <is>
+          <t>38.2% of global hydration drinks (2024)</t>
+        </is>
+      </c>
+      <c r="C10" s="60" t="inlineStr">
+        <is>
+          <t>N. America</t>
+        </is>
+      </c>
+      <c r="D10" s="60" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+      <c r="E10" s="60" t="inlineStr">
+        <is>
+          <t>Grand View</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="58" t="inlineStr">
+        <is>
+          <t>Canada powdered hydration</t>
+        </is>
+      </c>
+      <c r="B11" s="58" t="inlineStr">
+        <is>
+          <t>~US$404M → $738.5M (10.7% CAGR)</t>
+        </is>
+      </c>
+      <c r="C11" s="58" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D11" s="58" t="inlineStr">
+        <is>
+          <t>⚠◐</t>
+        </is>
+      </c>
+      <c r="E11" s="58" t="inlineStr">
+        <is>
+          <t>Grand View (3rd-party est.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="60" t="inlineStr">
+        <is>
+          <t>Canada US-proxy cross-check</t>
+        </is>
+      </c>
+      <c r="B12" s="60" t="inlineStr">
+        <is>
+          <t>~$150M (10% of US $1.5B) — lower than Grand View</t>
+        </is>
+      </c>
+      <c r="C12" s="60" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D12" s="60" t="inlineStr">
+        <is>
+          <t>⚠</t>
+        </is>
+      </c>
+      <c r="E12" s="60" t="inlineStr">
+        <is>
+          <t>Derived</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="58" t="inlineStr">
+        <is>
+          <t>Liquid I.V.</t>
+        </is>
+      </c>
+      <c r="B13" s="58" t="inlineStr">
+        <is>
+          <t>#1 US powdered hydration; 2024 intl expansion incl. Canada</t>
+        </is>
+      </c>
+      <c r="C13" s="58" t="inlineStr">
+        <is>
+          <t>US/Canada</t>
+        </is>
+      </c>
+      <c r="D13" s="58" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="E13" s="58" t="inlineStr">
+        <is>
+          <t>CNN; Unilever</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="42" t="inlineStr">
+        <is>
+          <t>2 · TRENDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>Conf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="58" t="inlineStr">
+        <is>
+          <t>Electrolyte/hydration boom</t>
+        </is>
+      </c>
+      <c r="B16" s="58" t="inlineStr">
+        <is>
+          <t>#WaterTok “flavor your water” is the engine behind +20% powder growth; sparkling is a demo-able hero for short-form video</t>
+        </is>
+      </c>
+      <c r="C16" s="58" t="inlineStr">
+        <is>
+          <t>✅/◐</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="60" t="inlineStr">
+        <is>
+          <t>Sugar-free + clean label</t>
+        </is>
+      </c>
+      <c r="B17" s="60" t="inlineStr">
+        <is>
+          <t>Now table stakes, not a differentiator (stevia, magnesium bisglycinate)</t>
+        </is>
+      </c>
+      <c r="C17" s="60" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="58" t="inlineStr">
+        <is>
+          <t>Sodium split</t>
+        </is>
+      </c>
+      <c r="B18" s="58" t="inlineStr">
+        <is>
+          <t>High-sodium “serious” (LMNT 1,000mg) vs moderate daily-wellness (Liquid I.V. 500mg, Nuun 300mg)</t>
+        </is>
+      </c>
+      <c r="C18" s="58" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="60" t="inlineStr">
+        <is>
+          <t>Functional stacking</t>
+        </is>
+      </c>
+      <c r="B19" s="60" t="inlineStr">
+        <is>
+          <t>Differentiation lives in electrolytes + magnesium + prebiotic fibre (+ collagen on NHP line)</t>
+        </is>
+      </c>
+      <c r="C19" s="60" t="inlineStr">
+        <is>
+          <t>◐</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t>3 · COMPETITOR FORMULATION &amp; PRICE LADDER</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Sodium/serv</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Price/serv</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>Lane</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="58" t="inlineStr">
+        <is>
+          <t>LMNT</t>
+        </is>
+      </c>
+      <c r="B22" s="58" t="inlineStr">
+        <is>
+          <t>1,000 mg</t>
+        </is>
+      </c>
+      <c r="C22" s="58" t="inlineStr">
+        <is>
+          <t>Powder stick (+Sparkling can)</t>
+        </is>
+      </c>
+      <c r="D22" s="58" t="inlineStr">
+        <is>
+          <t>~$1.50 ($1.30 sub)</t>
+        </is>
+      </c>
+      <c r="E22" s="58" t="inlineStr">
+        <is>
+          <t>High-sodium performance/keto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="60" t="inlineStr">
+        <is>
+          <t>Liquid I.V.</t>
+        </is>
+      </c>
+      <c r="B23" s="60" t="inlineStr">
+        <is>
+          <t>500 mg</t>
+        </is>
+      </c>
+      <c r="C23" s="60" t="inlineStr">
+        <is>
+          <t>Powder stick</t>
+        </is>
+      </c>
+      <c r="D23" s="60" t="inlineStr">
+        <is>
+          <t>~$1.56 (~$1.00 Costco)</t>
+        </is>
+      </c>
+      <c r="E23" s="60" t="inlineStr">
+        <is>
+          <t>Daily wellness</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="58" t="inlineStr">
+        <is>
+          <t>Nuun</t>
+        </is>
+      </c>
+      <c r="B24" s="58" t="inlineStr">
+        <is>
+          <t>300 mg</t>
+        </is>
+      </c>
+      <c r="C24" s="58" t="inlineStr">
+        <is>
+          <t>Effervescent tablet</t>
+        </is>
+      </c>
+      <c r="D24" s="58" t="inlineStr">
+        <is>
+          <t>~$0.75</t>
+        </is>
+      </c>
+      <c r="E24" s="58" t="inlineStr">
+        <is>
+          <t>Everyday / endurance</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="60" t="inlineStr">
+        <is>
+          <t>Prime</t>
+        </is>
+      </c>
+      <c r="B25" s="60" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C25" s="60" t="inlineStr">
+        <is>
+          <t>RTD + powder</t>
+        </is>
+      </c>
+      <c r="D25" s="60" t="inlineStr">
+        <is>
+          <t>hype-priced</t>
+        </is>
+      </c>
+      <c r="E25" s="60" t="inlineStr">
+        <is>
+          <t>Youth / viral</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="58" t="inlineStr">
+        <is>
+          <t>BioSteel</t>
+        </is>
+      </c>
+      <c r="B26" s="58" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="C26" s="58" t="inlineStr">
+        <is>
+          <t>Powder / RTD</t>
+        </is>
+      </c>
+      <c r="D26" s="58" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="E26" s="58" t="inlineStr">
+        <is>
+          <t>Athletic / “clean sport”</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="60" t="inlineStr">
+        <is>
+          <t>Organika electrolyte sachets</t>
+        </is>
+      </c>
+      <c r="B27" s="60" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C27" s="60" t="inlineStr">
+        <is>
+          <t>3.5g powder sachets</t>
+        </is>
+      </c>
+      <c r="D27" s="60" t="inlineStr">
+        <is>
+          <t>~$29.99/30 (Costco)</t>
+        </is>
+      </c>
+      <c r="E27" s="60" t="inlineStr">
+        <is>
+          <t>Daily, Canadian-made</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="58" t="inlineStr">
+        <is>
+          <t>Organika MÜV (this product)</t>
+        </is>
+      </c>
+      <c r="B28" s="58" t="inlineStr">
+        <is>
+          <t>TBD ⚠</t>
+        </is>
+      </c>
+      <c r="C28" s="58" t="inlineStr">
+        <is>
+          <t>Sparkling RTD CAN (SKU 4338)</t>
+        </is>
+      </c>
+      <c r="D28" s="58" t="inlineStr">
+        <is>
+          <t>$14.99 / pack</t>
+        </is>
+      </c>
+      <c r="E28" s="58" t="inlineStr">
+        <is>
+          <t>Daily-wellness sparkling</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>WHITE SPACE ◐: a flavored SPARKLING electrolyte is genuinely rare (LMNT Sparkling can; Nuun tablets fizz). MÜV's carbonation is a real sensory differentiator that aids flavour release → more consumption, no hydration penalty (Beverage Hydration Index).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="42" t="inlineStr">
+        <is>
+          <t>4 · GO-TO-MARKET &amp; THE BIOSTEEL CAUTIONARY TALE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>Brand / case</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Canada entry</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Lesson</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="52" customHeight="1">
+      <c r="A32" s="58" t="inlineStr">
+        <is>
+          <t>Liquid I.V.</t>
+        </is>
+      </c>
+      <c r="B32" s="58" t="inlineStr">
+        <is>
+          <t>Costco Canada national launch (Jul 2023), tight 2-SKU; festival + Costco roadshow sampling</t>
+        </is>
+      </c>
+      <c r="C32" s="58" t="inlineStr">
+        <is>
+          <t>Costco = the proven “one big door” beachhead; sampling drives trial</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="52" customHeight="1">
+      <c r="A33" s="60" t="inlineStr">
+        <is>
+          <t>LMNT</t>
+        </is>
+      </c>
+      <c r="B33" s="60" t="inlineStr">
+        <is>
+          <t>Amazon.ca + DTC; podcast sponsorships + “free sample, just pay shipping”</t>
+        </is>
+      </c>
+      <c r="C33" s="60" t="inlineStr">
+        <is>
+          <t>Cheap, high-ROI trial funnel; borrow it (not the 1,000mg sodium)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="52" customHeight="1">
+      <c r="A34" s="58" t="inlineStr">
+        <is>
+          <t>BioSteel (Canadian)</t>
+        </is>
+      </c>
+      <c r="B34" s="58" t="inlineStr">
+        <is>
+          <t>Broad omnichannel on NHL/McDavid/Mahomes halo</t>
+        </is>
+      </c>
+      <c r="C34" s="58" t="inlineStr">
+        <is>
+          <t>⚠ Canopy bought 72% for $50.7M (2019); burned &gt;$3 COGS per $1 rev ($24M rev vs $90M COGS); CCAA bankruptcy Sept 2023; sold ~$30.4M to Crosby/Coachwood; mfg in-housed Windsor 2025; lost NHL to Coke's BodyArmor. MORAL: athlete halo + broad distribution on a heavy cost base = bankruptcy. Velocity &amp; unit economics FIRST.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="52" customHeight="1">
+      <c r="A35" s="60" t="inlineStr">
+        <is>
+          <t>Powder vs RTD economics</t>
+        </is>
+      </c>
+      <c r="B35" s="60" t="inlineStr">
+        <is>
+          <t>Powder ships ~60–70% cheaper, shelf-stable</t>
+        </is>
+      </c>
+      <c r="C35" s="60" t="inlineStr">
+        <is>
+          <t>MÜV-the-CAN forgoes that edge → margin case leans on Organika's BC manufacturing</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="42" t="inlineStr">
+        <is>
+          <t>5 · RECOMMENDATIONS FOR MÜV (Canada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B38" s="58" t="inlineStr">
+        <is>
+          <t>Beachhead = Costco Canada (hero, roadshow sampling) + Amazon.ca / Well.ca / DTC — channels Organika already holds. Prove velocity before national grocery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B39" s="60" t="inlineStr">
+        <is>
+          <t>Position “daily-wellness sparkling hydration, made in Canada” — between Liquid I.V. (flat, foreign-owned) and LMNT (high-sodium performance). Avoid athletic combat with the reviving BioSteel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="58" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B40" s="58" t="inlineStr">
+        <is>
+          <t>Design the label to the Supplemented-Food framework NOW (SFFt, front-of-pack symbol, cautions if triggered). Lead with hydration/electrolyte + prebiotic-fibre function.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B41" s="60" t="inlineStr">
+        <is>
+          <t>Keep collagen / beauty messaging on the NHP collagen-powder line — NOT on the MÜV can (food-coded, claims restricted).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B42" s="58" t="inlineStr">
+        <is>
+          <t>Marketing: borrow LMNT's sample-pack funnel + #WaterTok creators (cheaper than US podcasts); fizz as the demo hero. Lean on BC manufacturing for margin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="46" customHeight="1">
+      <c r="A43" s="100" t="inlineStr">
+        <is>
+          <t>SOURCES &amp; CONFIDENCE: Circana via CNN (category); Grand View/Mordor (powder market, ◐); organika.com (MÜV SKU 4338, ingredient list); Globe &amp; Mail/CBC/PRNewswire/Coachwood (BioSteel); strategyonline.ca/Unilever (Liquid I.V. Canada); drinklmnt.com/hubermanlab.com (LMNT). Revenue &amp; market-size figures are estimates/projections (⚠). Several canada.ca/retailer pages block automated fetch (403) — confirm load-bearing items on the live page.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A43:F43"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00B45309"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -8523,7 +9791,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C9A227"/>
@@ -8818,7 +10086,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C9A227"/>
@@ -9044,640 +10312,6 @@
       <c r="F9" s="88" t="inlineStr">
         <is>
           <t>Copy the Costco-Canada sampling beachhead they used to enter Canada in 2023</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00B45309"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Phased Launch Plan (0–18 months)</t>
-        </is>
-      </c>
-      <c r="N1" s="95" t="inlineStr">
-        <is>
-          <t>↩ Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Phase</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Timing</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Objectives</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Key workstreams</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Success gate</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="80" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Phase 0 — Foundation</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Months 0–3</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Lock product, claims, regulatory pathway, co-pack</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Finalize formula &amp; collagen dose; regulatory-counsel claim opinion (Supplemented Foods); co-packer quote &amp; MOQ; bilingual + Bill 96 artwork; brand/positioning</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory sign-off on claim set + artwork approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="80" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1 — Beachhead</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Months 3–9</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Prove velocity &amp; repeat in a contained beachhead</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Costco CA roadshows + Amazon.ca + Well.ca/Natura + Organika pharmacy/health-food base; podcast + reactive social; sampling</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>Repeat rate + velocity above category benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Phase 2 — Scale</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Months 9–18</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Earn conventional grocery on proven data</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Sell-in to Loblaw/Sobeys/Metro on velocity data; distributor (UNFI CA / Tree of Life); managed trade spend; add SKUs on repeat data</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>National listings won on data, not discounts</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Phase 3 — Defend &amp; extend</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>18 mo+</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Category leadership &amp; optionality</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Format/flavour extensions; deepen moat; evaluate strategic-partner vs independent scale</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Profitable contribution + exit optionality</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00B45309"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Register</t>
-        </is>
-      </c>
-      <c r="N1" s="95" t="inlineStr">
-        <is>
-          <t>↩ Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Likelihood × Impact (H/M/L). Ranked by exposure</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Likelihood</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Mitigation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Collagen efficacy / claims liability (2025 meta-analysis; Poppi-style dose-insufficiency suit)</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory/Legal</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>Dose to efficacy (2.5g+); structure/function-safe language; substantiation files; lead with gut/hydration not beauty</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Strategic-owned competition (Nestlé owns Vital Proteins; PepsiCo/Unilever firepower)</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E6" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>Compete on Canadian-made + domestic cost edge + Organika collagen credibility; niche beachhead before they react</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Canada claim/label pathway misread (food vs NHP; SFCI; collagen caution)</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory</t>
-        </is>
-      </c>
-      <c r="D7" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory-counsel opinion before artwork; design to Supplemented Foods framework; caffeine-free</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Over-distribution before product-market fit</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>Execution</t>
-        </is>
-      </c>
-      <c r="D8" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E8" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>Prove velocity/repeat in beachhead before national; gate Phase 2 on data</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Slotting / trade-spend cash burn</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E9" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Use free-fill over cash slotting; 35–45% trade-spend budget; Code of Conduct leverage on arbitrary fees</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Thin differentiation / shelf saturation (prebiotic shelf filling fast)</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D10" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E10" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Defensible spec (fiber + collagen dose) + function stacking; Canadian-made story</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Private-label encroachment (~$277B, ~21% share, growing 2×)</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D11" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E11" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Brand equity + clinical-grade ingredients retailers can't easily copy</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>DTC CAC / heavy-ship economics if DTC-led</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D12" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E12" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>Lead retail/beachhead not paid DTC; subscription + sampling only</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Co-packer capacity / collagen sourcing / cost inflation</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="D13" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E13" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>Lock co-pack capacity early; qualify 2nd collagen supplier; hedge raws</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>FX / tariff / freight premium on cross-border inputs</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D14" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E14" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>Domestic CA co-pack; monitor tariff status post-Dec 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>GLP-1 demand shift away from sweet/snack</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Macro</t>
-        </is>
-      </c>
-      <c r="D15" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E15" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Low-cal, fiber, protein, hydration positioning aligns with GLP-1 users</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>Brand/tone misstep at scale</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="D16" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E16" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>Evolve tactics with stage; avoid Poppi-style stunts once mainstream</t>
         </is>
       </c>
     </row>
@@ -9709,20 +10343,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>KPI Dashboard &amp; Targets</t>
+          <t>Phased Launch Plan (0–18 months)</t>
         </is>
       </c>
       <c r="N1" s="95" t="inlineStr">
@@ -9731,259 +10365,143 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Benchmarks from this research; set MUV targets before launch</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>KPI</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Why it matters</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Category benchmark</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>MUV target (set)</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Phase</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Repeat purchase rate</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>The metric buyers actually buy on</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>OLIPOP cited “astronomical”; aim well above category avg</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>[set]</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>Phase 1+</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Velocity (units/store/week)</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Gates shelf retention &amp; expansion</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Buyers reward durable, non-discount velocity</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>[set]</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1+</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Survival</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Aim 50–65% at scale (40–50% early); watch COGS definition</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>[set]</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Trade spend % of revenue</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>#2 P&amp;L line; cash burn risk</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>10–20%; emerging brands high end</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>≤45% early</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1–2</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>CAC (if DTC/sub)</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>DTC viability</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>F&amp;B DTC ~$45–$53</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>≤ contribution margin</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>Phase 1+</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Doors / distribution</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Reach — but only on proven data</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Poppi ~36k / OLIPOP ~35k US (mature)</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Beachhead first</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1–3</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Net revenue</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Scale</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>$852k (OLIPOP yr1) → $400M+ (yr6)</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>[set]</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>Brand awareness / social</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>Demand-gen efficiency</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>TikTok/podcast-led; earned-media ratio</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>[set]</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1+</t>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Objectives</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Key workstreams</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Success gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Phase 0 — Foundation</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Months 0–3</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Lock product, claims, regulatory pathway, co-pack</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Finalize formula &amp; collagen dose; regulatory-counsel claim opinion (Supplemented Foods); co-packer quote &amp; MOQ; bilingual + Bill 96 artwork; brand/positioning</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory sign-off on claim set + artwork approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1 — Beachhead</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Months 3–9</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Prove velocity &amp; repeat in a contained beachhead</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Costco CA roadshows + Amazon.ca + Well.ca/Natura + Organika pharmacy/health-food base; podcast + reactive social; sampling</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Repeat rate + velocity above category benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Phase 2 — Scale</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Months 9–18</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Earn conventional grocery on proven data</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Sell-in to Loblaw/Sobeys/Metro on velocity data; distributor (UNFI CA / Tree of Life); managed trade spend; add SKUs on repeat data</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>National listings won on data, not discounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Phase 3 — Defend &amp; extend</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>18 mo+</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Category leadership &amp; optionality</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Format/flavour extensions; deepen moat; evaluate strategic-partner vs independent scale</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Profitable contribution + exit optionality</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <hyperlinks>
@@ -10005,22 +10523,25 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00595959"/>
+    <tabColor rgb="00B45309"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="58" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Master Bibliography</t>
+          <t>Risk Register</t>
         </is>
       </c>
       <c r="N1" s="95" t="inlineStr">
@@ -10032,483 +10553,406 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>Tagged by type. Several primary pages block automated fetch (403) — re-verify load-bearing numbers from the cited URLs before external use</t>
+          <t>Likelihood × Impact (H/M/L). Ranked by exposure</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
-          <t>Claim / topic</t>
+          <t>#</t>
         </is>
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>Source(s)</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="C4" s="11" t="inlineStr">
         <is>
-          <t>Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>PepsiCo — Poppi acquisition ($1.95B, closed May 2025)</t>
-        </is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Likelihood</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Mitigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="12" t="n">
+        <v>1</v>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>pepsico.com/newsroom</t>
+          <t>Collagen efficacy / claims liability (2025 meta-analysis; Poppi-style dose-insufficiency suit)</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Primary</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Poppi $8.9M gut-health class-action settlement (final approval Apr 2026)</t>
-        </is>
+          <t>Regulatory/Legal</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Dose to efficacy (2.5g+); structure/function-safe language; substantiation files; lead with gut/hydration not beauty</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>classaction.org; bevnet.com; axios.com</t>
+          <t>Strategic-owned competition (Nestlé owns Vital Proteins; PepsiCo/Unilever firepower)</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>Primary/Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>OLIPOP $50M Series C @ $1.85B; revenue; profitability</t>
-        </is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Compete on Canadian-made + domestic cost edge + Organika collagen credibility; niche beachhead before they react</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="12" t="n">
+        <v>3</v>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>cnbc.com; fooddive.com; bevindustry.com</t>
+          <t>Canada claim/label pathway misread (food vs NHP; SFCI; collagen caution)</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Primary/Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Modern soda $1.8B 2024 (+83%); brand shares (Poppi 38% / OLIPOP 32.7%)</t>
-        </is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory-counsel opinion before artwork; design to Supplemented Foods framework; caffeine-free</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="13" t="n">
+        <v>4</v>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>Circana; bevindustry.com; csnews.com</t>
+          <t>Over-distribution before product-market fit</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>Scanner/Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>LMNT FY2023 ($206M sales, ~20% net, $54.6M mktg, $7.1M sampling, 250k+ customers)</t>
-        </is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Prove velocity/repeat in beachhead before national; gate Phase 2 on data</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="12" t="n">
+        <v>5</v>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>SEC Reg CF CIK 1871551</t>
+          <t>Slotting / trade-spend cash burn</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Primary (strongest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Powdered hydration $1.5B (+20%); electrolyte powder $2.8B</t>
-        </is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Use free-fill over cash slotting; 35–45% trade-spend budget; Code of Conduct leverage on arbitrary fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>6</v>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>Circana/CNN; Grand View</t>
+          <t>Thin differentiation / shelf saturation (prebiotic shelf filling fast)</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>Scanner/Research-firm</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Liquid I.V. Costco national launch (2019, ~516 whs); Unilever acq. Sept 2020</t>
-        </is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Defensible spec (fiber + collagen dose) + function stacking; Canadian-made story</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="12" t="n">
+        <v>7</v>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>liquid-iv.com; unilever.com; bevnet.com</t>
+          <t>Private-label encroachment (~$277B, ~21% share, growing 2×)</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Primary/Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>Nuun — Nestlé Health Science acquisition (July 2021)</t>
-        </is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Brand equity + clinical-grade ingredients retailers can't easily copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>nestle.com; businesswire.com</t>
+          <t>DTC CAC / heavy-ship economics if DTC-led</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>Primary</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Vital Proteins sparkling ($2.50/can, VERISOL); Nestlé ownership</t>
-        </is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Lead retail/beachhead not paid DTC; subscription + sampling only</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="12" t="n">
+        <v>9</v>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>fooddive.com; wwd.com; foodbusinessnews.net</t>
+          <t>Co-packer capacity / collagen sourcing / cost inflation</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Trade/Primary</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Celsius — PepsiCo $550M/8.5% (2022); Alani Nu $1.8B (2025)</t>
-        </is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Lock co-pack capacity early; qualify 2nd collagen supplier; hedge raws</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="13" t="n">
+        <v>10</v>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>bevnet.com; bloomberg.com; businesswire.com</t>
+          <t>FX / tariff / freight premium on cross-border inputs</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>Primary/Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Health-Ade — Generous Brands $500M; $4M kombucha settlement</t>
-        </is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Domestic CA co-pack; monitor tariff status post-Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="12" t="n">
+        <v>11</v>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>fooddive.com; bursor.com</t>
+          <t>GLP-1 demand shift away from sweet/snack</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Collagen efficacy — 2025 systematic review/meta-analysis (no proven skin benefit; funding bias)</t>
-        </is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Low-cal, fiber, protein, hydration positioning aligns with GLP-1 users</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="13" t="n">
+        <v>12</v>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>Am. Journal of Medicine; nutraingredients.com</t>
+          <t>Brand/tone misstep at scale</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>Primary (peer-reviewed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>GLP-1 impact (23% households; 35% of units by 2030; spend -5.3%)</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Morning Consult; Circana; Food Dive</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>Research/Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Beauty-from-within drinks $3.24B, women 68.4%</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>Future Market Insights; Grand View</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>Research-firm (directional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Channel economics (Amazon fees, Costco margin, DTC CAC, slotting, distributor)</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>sellingpartners.aboutamazon.com; massivemoats; eightx.co; balancedbusinessgroup.com</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>Mixed (Amazon/Costco HARD)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Canada — NHP vs Food classification (food-format guidance)</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>canada.ca Health Canada guidance</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>Primary (regulatory)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Canada — Supplemented Foods Regulations (in force Jul 2022; SFCI; Jan 2026)</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>canada.ca; inspection.canada.ca; fasken.com</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>Primary/Legal</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>Canada — collagen caution statement (FDR C.R.C. c.870)</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>laws.justice.gc.ca</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Primary (regulation)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Canada — caffeine 180mg cap (Prime Energy blocked)</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>canada.ca; stack3d.com</t>
-        </is>
-      </c>
-      <c r="C23" s="12" t="inlineStr">
-        <is>
-          <t>Primary/Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>Canada — Bill 96 / OQLF packaging (Jun 2025)</t>
-        </is>
-      </c>
-      <c r="B24" s="13" t="inlineStr">
-        <is>
-          <t>mltaikins.com; stikeman.com</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Legal</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Canada — grocery share &amp; Code of Conduct (Jan 2025)</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="inlineStr">
-        <is>
-          <t>USDA FAS; statista.com; cbc.ca; canadacode.org</t>
-        </is>
-      </c>
-      <c r="C25" s="12" t="inlineStr">
-        <is>
-          <t>Govt/Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>US brand Canada entry (Liquid I.V. 2023, Poppi Aug 2024, Celsius Jan 2024)</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="inlineStr">
-        <is>
-          <t>foodincanada.com; newswire.ca; prnewswire.com</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>Trade/Primary</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Launch playbooks (Poppi/OLIPOP/LMNT/Liquid I.V./Celsius timelines)</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>fortune.com; entrepreneur.com; cnbc.com; inc.com; hubermanlab.com</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>Trade/Primary</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>Extended landscape (Culture Pop, Spindrift, Prime, Cure, etc.)</t>
-        </is>
-      </c>
-      <c r="B28" s="13" t="inlineStr">
-        <is>
-          <t>bevnet.com; techcrunch.com; prnewswire.com; wikipedia</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>Trade (verify FLAGs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Private label ~$277B, ~21% share</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>grocerydive.com; nielseniq.com</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>Trade</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>CPG failure rate ~85% in 2 years</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>foodnavigator-usa.com; eightx.co</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>Trade (directional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>PROCESS NOTE: Numbers were captured via multi-source web research with per-claim citation. Primary publisher and canada.ca pages frequently block automated fetch (HTTP 403); load-bearing figures should be re-pulled directly from the cited URLs (or licensed Circana/SPINS/Mintel portals) before external publication. The two highest-stakes regulatory claims — (a) RTD beverages are foods not NHPs, (b) the Supplemented-Foods/SFCI pathway with Jan 1 2026 compliance — are each corroborated by an official source + ≥1 independent secondary.</t>
-        </is>
-      </c>
-      <c r="B32" s="34" t="n"/>
-      <c r="C32" s="35" t="n"/>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Evolve tactics with stage; avoid Poppi-style stunts once mainstream</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A2:C2"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
@@ -10713,6 +11157,830 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00B45309"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KPI Dashboard &amp; Targets</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Benchmarks from this research; set MUV targets before launch</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Why it matters</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Category benchmark</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>MUV target (set)</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Repeat purchase rate</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>The metric buyers actually buy on</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>OLIPOP cited “astronomical”; aim well above category avg</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>[set]</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Velocity (units/store/week)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Gates shelf retention &amp; expansion</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Buyers reward durable, non-discount velocity</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>[set]</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Survival</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Aim 50–65% at scale (40–50% early); watch COGS definition</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>[set]</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Trade spend % of revenue</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>#2 P&amp;L line; cash burn risk</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>10–20%; emerging brands high end</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>≤45% early</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1–2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>CAC (if DTC/sub)</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>DTC viability</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>F&amp;B DTC ~$45–$53</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>≤ contribution margin</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Phase 1+</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Doors / distribution</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Reach — but only on proven data</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Poppi ~36k / OLIPOP ~35k US (mature)</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Beachhead first</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1–3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Net revenue</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>$852k (OLIPOP yr1) → $400M+ (yr6)</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>[set]</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Brand awareness / social</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Demand-gen efficiency</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>TikTok/podcast-led; earned-media ratio</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>[set]</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1+</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00595959"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Master Bibliography</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Tagged by type. Several primary pages block automated fetch (403) — re-verify load-bearing numbers from the cited URLs before external use</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Claim / topic</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Source(s)</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>PepsiCo — Poppi acquisition ($1.95B, closed May 2025)</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>pepsico.com/newsroom</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Poppi $8.9M gut-health class-action settlement (final approval Apr 2026)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>classaction.org; bevnet.com; axios.com</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Primary/Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>OLIPOP $50M Series C @ $1.85B; revenue; profitability</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>cnbc.com; fooddive.com; bevindustry.com</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Primary/Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Modern soda $1.8B 2024 (+83%); brand shares (Poppi 38% / OLIPOP 32.7%)</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Circana; bevindustry.com; csnews.com</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Scanner/Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>LMNT FY2023 ($206M sales, ~20% net, $54.6M mktg, $7.1M sampling, 250k+ customers)</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>SEC Reg CF CIK 1871551</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Primary (strongest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Powdered hydration $1.5B (+20%); electrolyte powder $2.8B</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Circana/CNN; Grand View</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Scanner/Research-firm</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Liquid I.V. Costco national launch (2019, ~516 whs); Unilever acq. Sept 2020</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>liquid-iv.com; unilever.com; bevnet.com</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Primary/Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Nuun — Nestlé Health Science acquisition (July 2021)</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>nestle.com; businesswire.com</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Vital Proteins sparkling ($2.50/can, VERISOL); Nestlé ownership</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>fooddive.com; wwd.com; foodbusinessnews.net</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Trade/Primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Celsius — PepsiCo $550M/8.5% (2022); Alani Nu $1.8B (2025)</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>bevnet.com; bloomberg.com; businesswire.com</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Primary/Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Health-Ade — Generous Brands $500M; $4M kombucha settlement</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>fooddive.com; bursor.com</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Collagen efficacy — 2025 systematic review/meta-analysis (no proven skin benefit; funding bias)</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Am. Journal of Medicine; nutraingredients.com</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Primary (peer-reviewed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>GLP-1 impact (23% households; 35% of units by 2030; spend -5.3%)</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Morning Consult; Circana; Food Dive</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Research/Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Beauty-from-within drinks $3.24B, women 68.4%</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Future Market Insights; Grand View</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Research-firm (directional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Channel economics (Amazon fees, Costco margin, DTC CAC, slotting, distributor)</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>sellingpartners.aboutamazon.com; massivemoats; eightx.co; balancedbusinessgroup.com</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Mixed (Amazon/Costco HARD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Canada — NHP vs Food classification (food-format guidance)</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>canada.ca Health Canada guidance</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Primary (regulatory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Canada — Supplemented Foods Regulations (in force Jul 2022; SFCI; Jan 2026)</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>canada.ca; inspection.canada.ca; fasken.com</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>Primary/Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Canada — collagen caution statement (FDR C.R.C. c.870)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>laws.justice.gc.ca</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Primary (regulation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Canada — caffeine 180mg cap (Prime Energy blocked)</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>canada.ca; stack3d.com</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>Primary/Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Canada — Bill 96 / OQLF packaging (Jun 2025)</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>mltaikins.com; stikeman.com</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Canada — grocery share &amp; Code of Conduct (Jan 2025)</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>USDA FAS; statista.com; cbc.ca; canadacode.org</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>Govt/Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>US brand Canada entry (Liquid I.V. 2023, Poppi Aug 2024, Celsius Jan 2024)</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
+        <is>
+          <t>foodincanada.com; newswire.ca; prnewswire.com</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Trade/Primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Launch playbooks (Poppi/OLIPOP/LMNT/Liquid I.V./Celsius timelines)</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>fortune.com; entrepreneur.com; cnbc.com; inc.com; hubermanlab.com</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Trade/Primary</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>Extended landscape (Culture Pop, Spindrift, Prime, Cure, etc.)</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>bevnet.com; techcrunch.com; prnewswire.com; wikipedia</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Trade (verify FLAGs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Private label ~$277B, ~21% share</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>grocerydive.com; nielseniq.com</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>CPG failure rate ~85% in 2 years</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>foodnavigator-usa.com; eightx.co</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Trade (directional)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>PROCESS NOTE: Numbers were captured via multi-source web research with per-claim citation. Primary publisher and canada.ca pages frequently block automated fetch (HTTP 403); load-bearing figures should be re-pulled directly from the cited URLs (or licensed Circana/SPINS/Mintel portals) before external publication. The two highest-stakes regulatory claims — (a) RTD beverages are foods not NHPs, (b) the Supplemented-Foods/SFCI pathway with Jan 1 2026 compliance — are each corroborated by an official source + ≥1 independent secondary.</t>
+        </is>
+      </c>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="35" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00C9A227"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -10779,22 +12047,22 @@
       </c>
       <c r="B5" s="58" t="inlineStr">
         <is>
-          <t>Does a “MÜV” / Organika sparkling product exist?</t>
+          <t>What is MÜV — and is it a can or a powder?</t>
         </is>
       </c>
       <c r="C5" s="98" t="inlineStr">
         <is>
-          <t>CONFIRMED + CORRECTED</t>
+          <t>CONFIRMED + CORRECTED (2x)</t>
         </is>
       </c>
       <c r="D5" s="58" t="inlineStr">
         <is>
-          <t>“MÜV Sparkling Electrolytes” is a real Organika SKU — a sparkling/effervescent POWDER (not a verified RTD can): 0 sugar, caffeine-free, electrolytes + magnesium bisglycinate + Fibersol prebiotic fibre. Sibling SKU “Electrolytes + Enhanced Collagen” adds 5g collagen. Earlier dossier assumed an unverified RTD can — now downgraded to the downside scenario.</t>
+          <t>“MÜV Sparkling Electrolytes” is a real Organika SKU and is a ready-to-drink SPARKLING CAN (SKU 4338, ~$14.99; ingredient list begins “Carbonated water” + Fibersol, magnesium glycinate, stevia; 0 sugar, caffeine-free). NOTE: an interim round-5 finding called it a powder — that was WRONG (it described Organika's separate electrolyte sachets / Electrolytes+Collagen powder) and is retracted.</t>
         </is>
       </c>
       <c r="E5" s="58" t="inlineStr">
         <is>
-          <t>organika.com/products/muv-sparkling-electrolytes; Save-On-Foods; Amazon; iHerb</t>
+          <t>organika.com (SKU 4338, ingredient list); retailer listings</t>
         </is>
       </c>
     </row>
@@ -10804,22 +12072,22 @@
       </c>
       <c r="B6" s="60" t="inlineStr">
         <is>
-          <t>Regulatory pathway for MÜV</t>
+          <t>Canada regulatory pathway for MÜV</t>
         </is>
       </c>
       <c r="C6" s="98" t="inlineStr">
         <is>
-          <t>CORRECTED</t>
+          <t>CORRECTED (primary)</t>
         </is>
       </c>
       <c r="D6" s="60" t="inlineStr">
         <is>
-          <t>Powder format likely = NHP with NPN (claims latitude PRESERVED), not the food/Supplemented-Food RTD pathway previously emphasized. Material correction — see Tab 19.</t>
+          <t>Format is NOT the decider. Health Canada is reclassifying ALL sport-electrolyte products (RTD/powder/effervescent) from NHP to SUPPLEMENTED FOODS — NPN holders by Dec 31, 2027; new products comply with FDR now. So MÜV (a can) is a Supplemented Food; collagen beauty claims remain NHP-only. ORS stays NHP. See ‘Canada Regulatory v2’.</t>
         </is>
       </c>
       <c r="E6" s="60" t="inlineStr">
         <is>
-          <t>Health Canada NHP guidance; format analysis</t>
+          <t>canada.ca Public Notice (Apr 2026); Gowling; dicentra; CHFA</t>
         </is>
       </c>
     </row>
@@ -11026,9 +12294,13 @@
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="56" t="inlineStr">
         <is>
-          <t>Method note: All 10 items were re-verified on 2026-06-13. Items 1–2 confirmed against Organika's site + Canadian retailer listings (storefront blocks automated fetch, so confirmed via search-indexed product/retailer pages). Items 3–10 were re-pulled and CONFIRMED against primary sources (PepsiCo, SEC EDGAR, Circana via trade press, Health Canada, classaction.org, Unilever, Celsius SEC 8-Ks), several with added precision (net purchase prices, exact close dates). No figure required downward correction; the only material change this round was the MÜV product/format finding (items 1–2). Direct primary-PDF re-read still advised for any figure quoted verbatim in board materials.</t>
-        </is>
-      </c>
+          <t>Method note: All 10 items were re-verified on 2026-06-13. Items 1–2 confirmed against Organika's site + Canadian retailer listings (storefront blocks automated fetch, so confirmed via search-indexed product/retailer pages). Items 3–10 were re-pulled and CONFIRMED against primary sources (PepsiCo, SEC EDGAR, Circana via trade press, Health Canada, classaction.org, Unilever, Celsius SEC 8-Ks), several with added precision (net purchase prices, exact close dates). No competitor figure required downward correction. The material corrections were on MÜV (items 1–2): verified as an RTD sparkling CAN (not a powder), and the Canada sport-electrolyte → Supplemented-Food reclassification (deep-research pass). Direct primary-PDF re-read still advised for any figure quoted verbatim in board materials.</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -11044,7 +12316,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>

--- a/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
+++ b/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
@@ -17,29 +17,30 @@
     <sheet name="05 Trends &amp; Macro" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="06 Consumer" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="07 Comparison Matrix" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="08 Extended Landscape" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="09 Channel &amp; Retail" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="10 Channel Economics" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="11 Formulation" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="12 Marketing" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="13 Launch Playbooks" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="14 Patterns &amp; Failures" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="15 Outcomes &amp; M&amp;A" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="16 SWOT" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="17 Scoring Model" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="18 Canada Market" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="19 Canada Regulatory" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Canada Regulatory v2" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Electrolyte BFY Deep-Dive" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="20 GTM Recommendation" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Go-NoGo Decision" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Battlecards" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="21 Launch Plan" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="22 Risk Register" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="23 KPI Dashboard" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="24 Sources" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="Verification Log" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="25 Glossary" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="MÜV Peer Set" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="08 Extended Landscape" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="09 Channel &amp; Retail" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="10 Channel Economics" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="11 Formulation" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="12 Marketing" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="13 Launch Playbooks" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="14 Patterns &amp; Failures" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="15 Outcomes &amp; M&amp;A" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="16 SWOT" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="17 Scoring Model" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="18 Canada Market" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="19 Canada Regulatory" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Canada Regulatory v2" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Electrolyte BFY Deep-Dive" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="20 GTM Recommendation" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Go-NoGo Decision" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Battlecards" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="21 Launch Plan" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="22 Risk Register" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="23 KPI Dashboard" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="24 Sources" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Verification Log" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="25 Glossary" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'07 Comparison Matrix'!$A$3:$L$11</definedName>
@@ -345,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -626,6 +627,12 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1898,6 +1905,13 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="101" t="inlineStr">
+        <is>
+          <t>LENS: broad functional-beverage set (context + playbook). MÜV's DIRECT electrolyte/sparkling rivals → ‘MÜV Peer Set’ tab.</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -2497,6 +2511,554 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MÜV Peer Set — Direct Competitors vs Category-Adjacent</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Reconciles the workbook to MÜV's actual lane: a daily-wellness SPARKLING ELECTROLYTE (food-regulated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="64" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>HOW TO READ THIS WORKBOOK: Tabs 07–17 profile the BROAD functional-beverage market (Poppi/OLIPOP/Vital Proteins). Those are CATEGORY-ADJACENT — they prove the better-for-you thesis and supply the LAUNCH PLAYBOOK, but they are NOT MÜV's direct shelf rivals. MÜV's DIRECT peer set is electrolyte/hydration + sparkling (this tab + ‘Electrolyte BFY Deep-Dive’). Read the two together: borrow the soda brands' go-to-market, but benchmark price/format/claims against the electrolyte brands.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="102" t="inlineStr">
+        <is>
+          <t>DIRECT PEERS — same occasion / same shelf (benchmark MÜV here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Sodium/serv</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>Price/serv</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Lane</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Canada channel</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Why a direct peer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="58" t="inlineStr">
+        <is>
+          <t>LMNT</t>
+        </is>
+      </c>
+      <c r="B7" s="58" t="inlineStr">
+        <is>
+          <t>Powder stick (+Sparkling can)</t>
+        </is>
+      </c>
+      <c r="C7" s="58" t="inlineStr">
+        <is>
+          <t>1,000 mg</t>
+        </is>
+      </c>
+      <c r="D7" s="58" t="inlineStr">
+        <is>
+          <t>~$1.50</t>
+        </is>
+      </c>
+      <c r="E7" s="58" t="inlineStr">
+        <is>
+          <t>High-sodium performance</t>
+        </is>
+      </c>
+      <c r="F7" s="58" t="inlineStr">
+        <is>
+          <t>Amazon.ca + DTC</t>
+        </is>
+      </c>
+      <c r="G7" s="58" t="inlineStr">
+        <is>
+          <t>Defines the premium electrolyte ceiling; sparkling-can overlap</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="60" t="inlineStr">
+        <is>
+          <t>Liquid I.V.</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>Powder stick</t>
+        </is>
+      </c>
+      <c r="C8" s="60" t="inlineStr">
+        <is>
+          <t>500 mg</t>
+        </is>
+      </c>
+      <c r="D8" s="60" t="inlineStr">
+        <is>
+          <t>~$1.56 (~$1.00 Costco)</t>
+        </is>
+      </c>
+      <c r="E8" s="60" t="inlineStr">
+        <is>
+          <t>Daily wellness</t>
+        </is>
+      </c>
+      <c r="F8" s="60" t="inlineStr">
+        <is>
+          <t>Costco Canada (2023) → mass</t>
+        </is>
+      </c>
+      <c r="G8" s="60" t="inlineStr">
+        <is>
+          <t>Closest positioning twin (daily wellness); Costco beachhead model</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="58" t="inlineStr">
+        <is>
+          <t>Nuun</t>
+        </is>
+      </c>
+      <c r="B9" s="58" t="inlineStr">
+        <is>
+          <t>Effervescent tablet</t>
+        </is>
+      </c>
+      <c r="C9" s="58" t="inlineStr">
+        <is>
+          <t>300 mg</t>
+        </is>
+      </c>
+      <c r="D9" s="58" t="inlineStr">
+        <is>
+          <t>~$0.75</t>
+        </is>
+      </c>
+      <c r="E9" s="58" t="inlineStr">
+        <is>
+          <t>Everyday/endurance</t>
+        </is>
+      </c>
+      <c r="F9" s="58" t="inlineStr">
+        <is>
+          <t>Natural + Amazon.ca</t>
+        </is>
+      </c>
+      <c r="G9" s="58" t="inlineStr">
+        <is>
+          <t>Fizz/effervescence overlap; value anchor</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="60" t="inlineStr">
+        <is>
+          <t>BioSteel</t>
+        </is>
+      </c>
+      <c r="B10" s="60" t="inlineStr">
+        <is>
+          <t>Powder / RTD</t>
+        </is>
+      </c>
+      <c r="C10" s="60" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="D10" s="60" t="inlineStr">
+        <is>
+          <t>mid</t>
+        </is>
+      </c>
+      <c r="E10" s="60" t="inlineStr">
+        <is>
+          <t>Athletic/clean sport</t>
+        </is>
+      </c>
+      <c r="F10" s="60" t="inlineStr">
+        <is>
+          <t>Broad omnichannel (CA)</t>
+        </is>
+      </c>
+      <c r="G10" s="60" t="inlineStr">
+        <is>
+          <t>Canadian rival; the cautionary tale (see Deep-Dive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="58" t="inlineStr">
+        <is>
+          <t>Prime</t>
+        </is>
+      </c>
+      <c r="B11" s="58" t="inlineStr">
+        <is>
+          <t>RTD + powder</t>
+        </is>
+      </c>
+      <c r="C11" s="58" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="D11" s="58" t="inlineStr">
+        <is>
+          <t>hype</t>
+        </is>
+      </c>
+      <c r="E11" s="58" t="inlineStr">
+        <is>
+          <t>Youth/viral</t>
+        </is>
+      </c>
+      <c r="F11" s="58" t="inlineStr">
+        <is>
+          <t>Walmart/convenience</t>
+        </is>
+      </c>
+      <c r="G11" s="58" t="inlineStr">
+        <is>
+          <t>Sparkling-adjacent RTD; hype-cycle warning</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="60" t="inlineStr">
+        <is>
+          <t>Gatorlyte / Powerade</t>
+        </is>
+      </c>
+      <c r="B12" s="60" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="C12" s="60" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="D12" s="60" t="inlineStr">
+        <is>
+          <t>mass</t>
+        </is>
+      </c>
+      <c r="E12" s="60" t="inlineStr">
+        <is>
+          <t>Sport/mass</t>
+        </is>
+      </c>
+      <c r="F12" s="60" t="inlineStr">
+        <is>
+          <t>Full distribution</t>
+        </is>
+      </c>
+      <c r="G12" s="60" t="inlineStr">
+        <is>
+          <t>Incumbent sport hydration on the same cooler shelf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="58" t="inlineStr">
+        <is>
+          <t>Organika electrolyte sachets</t>
+        </is>
+      </c>
+      <c r="B13" s="58" t="inlineStr">
+        <is>
+          <t>3.5g powder sachet</t>
+        </is>
+      </c>
+      <c r="C13" s="58" t="inlineStr">
+        <is>
+          <t>~440mg (sibling)</t>
+        </is>
+      </c>
+      <c r="D13" s="58" t="inlineStr">
+        <is>
+          <t>~$29.99/30 (Costco)</t>
+        </is>
+      </c>
+      <c r="E13" s="58" t="inlineStr">
+        <is>
+          <t>Daily, Canadian-made</t>
+        </is>
+      </c>
+      <c r="F13" s="58" t="inlineStr">
+        <is>
+          <t>Costco/Well.ca/Amazon.ca</t>
+        </is>
+      </c>
+      <c r="G13" s="58" t="inlineStr">
+        <is>
+          <t>Organika's own line — internal reference &amp; cannibalization watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="60" t="inlineStr">
+        <is>
+          <t>MÜV (this product)</t>
+        </is>
+      </c>
+      <c r="B14" s="60" t="inlineStr">
+        <is>
+          <t>Sparkling RTD CAN</t>
+        </is>
+      </c>
+      <c r="C14" s="60" t="inlineStr">
+        <is>
+          <t>TBD ⚠</t>
+        </is>
+      </c>
+      <c r="D14" s="60" t="inlineStr">
+        <is>
+          <t>$14.99/pack</t>
+        </is>
+      </c>
+      <c r="E14" s="60" t="inlineStr">
+        <is>
+          <t>Daily-wellness sparkling</t>
+        </is>
+      </c>
+      <c r="F14" s="60" t="inlineStr">
+        <is>
+          <t>Costco/Amazon/Well.ca</t>
+        </is>
+      </c>
+      <c r="G14" s="60" t="inlineStr">
+        <is>
+          <t>— the subject —</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t>CATEGORY-ADJACENT — different occasion; context &amp; playbook only</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>What MÜV borrows</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>What does NOT transfer</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="58" t="inlineStr">
+        <is>
+          <t>Poppi</t>
+        </is>
+      </c>
+      <c r="B17" s="58" t="inlineStr">
+        <is>
+          <t>Prebiotic soda (can)</t>
+        </is>
+      </c>
+      <c r="C17" s="58" t="inlineStr">
+        <is>
+          <t>TikTok creator seeding; mass-priced premium; PepsiCo exit proof</t>
+        </is>
+      </c>
+      <c r="D17" s="58" t="inlineStr">
+        <is>
+          <t>Soda occasion; 2g-fiber claim model (and its $8.9M lawsuit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="42" customHeight="1">
+      <c r="A18" s="60" t="inlineStr">
+        <is>
+          <t>OLIPOP</t>
+        </is>
+      </c>
+      <c r="B18" s="60" t="inlineStr">
+        <is>
+          <t>Prebiotic soda (can)</t>
+        </is>
+      </c>
+      <c r="C18" s="60" t="inlineStr">
+        <is>
+          <t>Natural-channel seeding; sell-in on repurchase data</t>
+        </is>
+      </c>
+      <c r="D18" s="60" t="inlineStr">
+        <is>
+          <t>Dessert-soda positioning; 9g fiber formulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="42" customHeight="1">
+      <c r="A19" s="58" t="inlineStr">
+        <is>
+          <t>Vital Proteins Sparkling</t>
+        </is>
+      </c>
+      <c r="B19" s="58" t="inlineStr">
+        <is>
+          <t>Collagen sparkling (can)</t>
+        </is>
+      </c>
+      <c r="C19" s="58" t="inlineStr">
+        <is>
+          <t>Beauty-from-within demand proof; clinical-claim model</t>
+        </is>
+      </c>
+      <c r="D19" s="58" t="inlineStr">
+        <is>
+          <t>Collagen-beauty claims (NHP-only in Canada — keep off MÜV can)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="60" t="inlineStr">
+        <is>
+          <t>Recess</t>
+        </is>
+      </c>
+      <c r="B20" s="60" t="inlineStr">
+        <is>
+          <t>Relaxation sparkling</t>
+        </is>
+      </c>
+      <c r="C20" s="60" t="inlineStr">
+        <is>
+          <t>“Sell the felt benefit, not the molecule” lesson</t>
+        </is>
+      </c>
+      <c r="D20" s="60" t="inlineStr">
+        <is>
+          <t>Adaptogen/CBD relaxation occasion</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="58" t="inlineStr">
+        <is>
+          <t>Aura Bora</t>
+        </is>
+      </c>
+      <c r="B21" s="58" t="inlineStr">
+        <is>
+          <t>Sparkling water</t>
+        </is>
+      </c>
+      <c r="C21" s="58" t="inlineStr">
+        <is>
+          <t>Personality-led cheap marketing; flavour novelty</t>
+        </is>
+      </c>
+      <c r="D21" s="58" t="inlineStr">
+        <is>
+          <t>No functional/electrolyte claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>RECONCILED THESIS: MÜV should be PRICED &amp; FORMULATED against the DIRECT peers (≤ LMNT/Liquid I.V. per-serving economics, sparkling as the wedge, Supplemented-Food claims) while BORROWING the GTM from the adjacent soda winners (one obsessive trial tactic, sell-in on velocity/repeat, sequenced channel ladder). Win the daily-wellness sparkling occasion, made in Canada — don't fight Poppi for the soda shelf or Vital Proteins for beauty claims.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="003E5C76"/>
@@ -3919,7 +4481,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="003E5C76"/>
@@ -4214,563 +4776,6 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A13:E13"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="003E5C76"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="68" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Channel Economics &amp; Margin Waterfall</t>
-        </is>
-      </c>
-      <c r="N1" s="95" t="inlineStr">
-        <is>
-          <t>↩ Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Only Amazon fees, Costco margin &amp; DTC CAC are HARD; the rest are operator rules-of-thumb — model as ranges</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>MARGIN WATERFALL — canned functional beverage</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Typical value</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Unit COGS target</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>&lt; $1.00/unit (liquid+can+co-pack at scale)</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>12oz decorated can (component)</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>~$0.15/can at intro minimums</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Co-pack run (10,000 cases)</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>≈ $200,000; MOQ 2,000–5,000 cases/SKU</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Blended gross margin (early)</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>40–50%; aspiration 50–65% at scale</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>GM by channel</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Retail ~35–45%; DTC ~40–50% (before CAC/freight)</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>COGS warning</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Excluding freight/duty/co-pack overstates GM by 3–8 pts — the #1 error</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>CHANNEL TAKE-RATES (who takes margin off the top)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Channel / cost</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Take / value</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Grocery (conventional)</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>~30–50% retailer margin; bev often 30–40%</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Natural/premium (Whole Foods)</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>45%+ (slower turns)</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Club (Costco)</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Max 14% markup (15% Kirkland); FY24 actual GM 10.92% — volume not margin play</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Distributor (general)</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>15–25% markup; UNFI avg ~13–14% (range 6–30%)</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>HARD-ish</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>DSD vs warehouse</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>DSD can save ~5–10% in fees vs UNFI/KeHE routing</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Broker</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>3–5% of net sales + often $5–10k/mo retainer</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>8–45% referral (most 15%) + FBA $3.73–$6.97/unit ($25+ heavy bev)</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>HARD (published)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>DTC CAC (food &amp; bev)</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>~$45–$53 (lowest vertical); supplements ~$89; shipping $8–15/order</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>HARD (benchmark)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>TRADE SPEND &amp; FEES</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Slotting fee</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>$250 → $250,000 by retailer/scope; ~$25,000/item regional cluster</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>Trade spend % of revenue</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>10–20% (emerging brands high end); US trade spend &gt;$200B, ~20% of gross, #2 P&amp;L line</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>HARD (aggregate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Free fill</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>1 free case/SKU/store on first order — cheaper substitute for slotting</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>LMNT subscription model</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>$200M+ rev 2023, ~20% net margin, 250k+ customers; free-8-pack (pay shipping) funnel</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>HARD (company/SEC)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>CANADA COST STACK (additive on US economics)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>Grocery concentration</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>Loblaw+Sobeys+Metro ≈ 80% w/ Walmart+Costco; all signed Grocery Code of Conduct (in force Jan 1, 2025)</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>Listing/slotting fees</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>Charged but NOT publicly disclosed; Code now lets suppliers challenge arbitrary fees — model at ≥ US slotting</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>No public $</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>Bilingual packaging</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>EN+FR mandatory; French ~2× longer; non-compliance fines up to $20,000; Bill 96 adds rules</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>HARD (regulatory)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>Distributors (CA)</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>UNFI Canada, Tree of Life Canada, Purity Life, Ecotrend</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>HARD (existence)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>Freight/FX/duty</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>FX (US$1≈C$1.15+) + cross-border freight + duty; model as premium; local co-pack is the margin fix</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>Qualitative</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="46" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>DTC-for-beverage reality check: heavy to ship, low online AOV, CAC can exceed contribution. Historically ~90% of beverage startups fail; the survivable DTC model (LMNT) is subscription + free-sample acquisition + asset-light profitability — not paid-media scale.</t>
-        </is>
-      </c>
-      <c r="B38" s="34" t="n"/>
-      <c r="C38" s="34" t="n"/>
-      <c r="D38" s="35" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
@@ -4795,20 +4800,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Formulation &amp; Positioning — the claim that won</t>
+          <t>Channel Economics &amp; Margin Waterfall</t>
         </is>
       </c>
       <c r="N1" s="95" t="inlineStr">
@@ -4817,264 +4820,519 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Winning claim</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Hero ingredient &amp; spec</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Positioning evolution</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Claim risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="64" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Poppi</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Prebiotic soda you can drink daily</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Prebiotic fiber + ACV; ~2g fiber, 2–5g sugar</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>ACV “tonic” (Mother Beverage) → 2020 bright “prebiotic soda”</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>$8.9M settlement — 2g fiber too little for claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="64" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>OLIPOP</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>“New kind of soda”, serious fiber</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Up to 9g fiber (cassava/chicory/artichoke) + botanicals</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Stable gut-health since launch; ~4× Poppi fiber</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>No suit found; higher fiber = stronger substantiation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="64" customHeight="1">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Only Amazon fees, Costco margin &amp; DTC CAC are HARD; the rest are operator rules-of-thumb — model as ranges</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>MARGIN WATERFALL — canned functional beverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Typical value</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>LMNT</t>
+          <t>Unit COGS target</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Zero-sugar, high-sodium for keto/athletes</t>
+          <t>&lt; $1.00/unit (liquid+can+co-pack at scale)</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>1,000mg sodium, 200mg K, 60mg Mg, 0g sugar</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Salt-first, science-forward</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>Sodium is the polarizing hook</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="64" customHeight="1">
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Liquid I.V.</t>
+          <t>12oz decorated can (component)</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Hydration Multiplier, 2–3× faster</t>
+          <t>~$0.15/can at intro minimums</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Cellular Transport Tech; 500mg sodium, 11g carbs</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Added sugar-free line later</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>CTT efficacy is marketing-led; sugar a vulnerability</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="64" customHeight="1">
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Nuun</t>
+          <t>Co-pack run (10,000 cases)</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Carb-free effervescent electrolyte</t>
+          <t>≈ $200,000; MOQ 2,000–5,000 cases/SKU</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>300mg sodium, 1g sugar, 15 cal, stevia</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Endurance carb-free → added powders</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Clean low-sugar story</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="64" customHeight="1">
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>Vital Proteins Sparkling</t>
+          <t>Blended gross margin (early)</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Beauty-from-within + clinical collagen at mass price</t>
+          <t>40–50%; aspiration 50–65% at scale</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>VERISOL collagen + 100% DV Vit C; 0g sugar</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Extends #1 collagen powder into a can</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>Strongest collagen claim, but see 2025 efficacy meta-analysis</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="64" customHeight="1">
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Recess</t>
+          <t>GM by channel</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Relaxation — sell the benefit not the molecule</t>
+          <t>Retail ~35–45%; DTC ~40–50% (before CAC/freight)</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Magnesium L-threonate + adaptogens</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Pivoted CBD → relaxation (CBD &lt;8% of sales)</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>KEY LESSON: lead with felt benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="64" customHeight="1">
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Aura Bora</t>
+          <t>COGS warning</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Herbal/floral, zero everything</t>
+          <t>Excluding freight/duty/co-pack overstates GM by 3–8 pts — the #1 error</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>0 cal/sugar/sodium; herb+fruit+flower</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Flavor-forward, no health-claim baggage</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>Low regulatory risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>READ-ACROSS for MUV: “collagen-as-hero” has a graveyard AND a 2025 no-benefit meta-analysis. Winners wrap collagen in a big brand + clinical claim at mass price (Vital Proteins) OR sell a broader felt benefit (Recess). Lead MUV with gut+hydration function + a credible collagen dose under the “Canada's #1 collagen brand” halo — not narrow beauty-from-within.</t>
-        </is>
-      </c>
-      <c r="B12" s="34" t="n"/>
-      <c r="C12" s="34" t="n"/>
-      <c r="D12" s="34" t="n"/>
-      <c r="E12" s="35" t="n"/>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>CHANNEL TAKE-RATES (who takes margin off the top)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Channel / cost</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Take / value</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Grocery (conventional)</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>~30–50% retailer margin; bev often 30–40%</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Natural/premium (Whole Foods)</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>45%+ (slower turns)</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Club (Costco)</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Max 14% markup (15% Kirkland); FY24 actual GM 10.92% — volume not margin play</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Distributor (general)</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>15–25% markup; UNFI avg ~13–14% (range 6–30%)</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>HARD-ish</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>DSD vs warehouse</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>DSD can save ~5–10% in fees vs UNFI/KeHE routing</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>3–5% of net sales + often $5–10k/mo retainer</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>8–45% referral (most 15%) + FBA $3.73–$6.97/unit ($25+ heavy bev)</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>HARD (published)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>DTC CAC (food &amp; bev)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>~$45–$53 (lowest vertical); supplements ~$89; shipping $8–15/order</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>HARD (benchmark)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>TRADE SPEND &amp; FEES</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Slotting fee</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>$250 → $250,000 by retailer/scope; ~$25,000/item regional cluster</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Trade spend % of revenue</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>10–20% (emerging brands high end); US trade spend &gt;$200B, ~20% of gross, #2 P&amp;L line</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>HARD (aggregate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Free fill</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>1 free case/SKU/store on first order — cheaper substitute for slotting</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>LMNT subscription model</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>$200M+ rev 2023, ~20% net margin, 250k+ customers; free-8-pack (pay shipping) funnel</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>HARD (company/SEC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>CANADA COST STACK (additive on US economics)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Grocery concentration</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Loblaw+Sobeys+Metro ≈ 80% w/ Walmart+Costco; all signed Grocery Code of Conduct (in force Jan 1, 2025)</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>Listing/slotting fees</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>Charged but NOT publicly disclosed; Code now lets suppliers challenge arbitrary fees — model at ≥ US slotting</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>No public $</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Bilingual packaging</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>EN+FR mandatory; French ~2× longer; non-compliance fines up to $20,000; Bill 96 adds rules</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>HARD (regulatory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>Distributors (CA)</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>UNFI Canada, Tree of Life Canada, Purity Life, Ecotrend</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>HARD (existence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Freight/FX/duty</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>FX (US$1≈C$1.15+) + cross-border freight + duty; model as premium; local co-pack is the margin fix</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="46" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>DTC-for-beverage reality check: heavy to ship, low online AOV, CAC can exceed contribution. Historically ~90% of beverage startups fail; the survivable DTC model (LMNT) is subscription + free-sample acquisition + asset-light profitability — not paid-media scale.</t>
+        </is>
+      </c>
+      <c r="B38" s="34" t="n"/>
+      <c r="C38" s="34" t="n"/>
+      <c r="D38" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A12:E12"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
@@ -5103,15 +5361,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand Build — the virality engine</t>
+          <t>Formulation &amp; Positioning — the claim that won</t>
         </is>
       </c>
       <c r="N1" s="95" t="inlineStr">
@@ -5128,21 +5387,26 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Founder story</t>
+          <t>Winning claim</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>Growth engine</t>
+          <t>Hero ingredient &amp; spec</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>What moved the needle</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="66" customHeight="1">
+          <t>Positioning evolution</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Claim risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="64" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Poppi</t>
@@ -5150,21 +5414,26 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>Allison &amp; Stephen Ellsworth; Shark Tank 2018 ($400k/25%, Rohan Oza)</t>
+          <t>Prebiotic soda you can drink daily</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>TikTok creator seeding + 2 Super Bowls (2024 first ad, 2025 return)</t>
+          <t>Prebiotic fiber + ACV; ~2g fiber, 2–5g sugar</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Pink aesthetic, Alix Earle/Emily Mariko seeding, vending-machine stunt (2025, mixed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="66" customHeight="1">
+          <t>ACV “tonic” (Mother Beverage) → 2020 bright “prebiotic soda”</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>$8.9M settlement — 2g fiber too little for claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="64" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
           <t>OLIPOP</t>
@@ -5172,21 +5441,26 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Ben Goodwin (ex-Obi) &amp; David Lester; $100k from Obi sale</t>
+          <t>“New kind of soda”, serious fiber</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>DTC repurchase rates + reactive social</t>
+          <t>Up to 9g fiber (cassava/chicory/artichoke) + botanicals</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>“Soda Stories”; needled Poppi's vending spend during 2025 SB — earned media without paying for the game</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="66" customHeight="1">
+          <t>Stable gut-health since launch; ~4× Poppi fiber</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>No suit found; higher fiber = stronger substantiation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>LMNT</t>
@@ -5194,21 +5468,26 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Robb Wolf (biochemist) + Ketogains (Villaseñor)</t>
+          <t>Zero-sugar, high-sodium for keto/athletes</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Podcast-sponsorship moat (Huberman, Attia)</t>
+          <t>1,000mg sodium, 200mg K, 60mg Mg, 0g sugar</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Host-read trust + free-sample funnel; $54.6M mktg + $7.1M sampling in 2023 (~26.5% of rev)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="66" customHeight="1">
+          <t>Salt-first, science-forward</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Sodium is the polarizing hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="64" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Liquid I.V.</t>
@@ -5216,21 +5495,26 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Brandin Cohen, college brainchild (+2)</t>
+          <t>Hydration Multiplier, 2–3× faster</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>In-store/Costco roadshow sampling + give-back</t>
+          <t>Cellular Transport Tech; 500mg sodium, 11g carbs</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Founder sampled every weekend; POS-data sell-in; Emerson Group for national muscle</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="66" customHeight="1">
+          <t>Added sugar-free line later</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>CTT efficacy is marketing-led; sugar a vulnerability</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="64" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Nuun</t>
@@ -5238,100 +5522,121 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Tim Moxey, British Ironman</t>
+          <t>Carb-free effervescent electrolyte</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Grassroots endurance-community events</t>
+          <t>300mg sodium, 1g sugar, 15 cal, stevia</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Authentic credibility in run/bike/tri before mainstream</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="66" customHeight="1">
+          <t>Endurance carb-free → added powders</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Clean low-sugar story</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>Celsius</t>
+          <t>Vital Proteins Sparkling</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Turnaround 2012; Li Ka-shing $15M (2015)</t>
+          <t>Beauty-from-within + clinical collagen at mass price</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Amazon + fitness influencers/gym sampling</t>
+          <t>VERISOL collagen + 100% DV Vit C; 0g sugar</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Amazon velocity → Target DSD → PepsiCo $550M distribution</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="66" customHeight="1">
+          <t>Extends #1 collagen powder into a can</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Strongest collagen claim, but see 2025 efficacy meta-analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="64" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Vital Proteins Sparkling</t>
+          <t>Recess</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>K. Seidensticker; Nestlé-owned</t>
+          <t>Relaxation — sell the benefit not the molecule</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Big-brand media + retail muscle + collagen loyalty</t>
+          <t>Magnesium L-threonate + adaptogens</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Distribution &amp; #1-collagen halo, not scrappy virality</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="66" customHeight="1">
+          <t>Pivoted CBD → relaxation (CBD &lt;8% of sales)</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>KEY LESSON: lead with felt benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Recess</t>
+          <t>Aura Bora</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Benjamin Witte</t>
+          <t>Herbal/floral, zero everything</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Distinctive pastel brand world + culture-tuned social</t>
+          <t>0 cal/sugar/sodium; herb+fruit+flower</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Owned a vibe + the “relaxation” moment</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52" customHeight="1">
+          <t>Flavor-forward, no health-claim baggage</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Low regulatory risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>READ-ACROSS: The two cheapest high-ROI challenger playbooks are LMNT's trusted-host podcast model and OLIPOP's reactive earned-media social — both winnable without Super Bowl budgets. Pair with Costco-roadshow sampling (Liquid I.V.). Brand tone must evolve with stage (Poppi's vending stunt misfired once mainstream).</t>
+          <t>READ-ACROSS for MUV: “collagen-as-hero” has a graveyard AND a 2025 no-benefit meta-analysis. Winners wrap collagen in a big brand + clinical claim at mass price (Vital Proteins) OR sell a broader felt benefit (Recess). Lead MUV with gut+hydration function + a credible collagen dose under the “Canada's #1 collagen brand” halo — not narrow beauty-from-within.</t>
         </is>
       </c>
       <c r="B12" s="34" t="n"/>
       <c r="C12" s="34" t="n"/>
-      <c r="D12" s="35" t="n"/>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
@@ -5356,20 +5661,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Launch Playbook Teardowns — phased GTM timelines</t>
+          <t>Marketing &amp; Brand Build — the virality engine</t>
         </is>
       </c>
       <c r="N1" s="95" t="inlineStr">
@@ -5386,26 +5690,21 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Phase 0 (pre-launch)</t>
+          <t>Founder story</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>Phase 1 (launch, yr 0–1)</t>
+          <t>Growth engine</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>Phase 2 (scale, yr 1–3)</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Phase 3 (maturity/exit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="92" customHeight="1">
+          <t>What moved the needle</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="66" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Poppi</t>
@@ -5413,26 +5712,21 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>2015–16: gut-health insight; ~$90k self-funded; “Mother Beverage” glass bottles</t>
+          <t>Allison &amp; Stephen Ellsworth; Shark Tank 2018 ($400k/25%, Rohan Oza)</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>Farmers markets → Whole Foods regional; ~$500k in 18 mo; Shark Tank 2018 ($400k/25% Oza)</t>
+          <t>TikTok creator seeding + 2 Super Bowls (2024 first ad, 2025 return)</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>2020 rebrand to cans + national launch (Mar 2020); TikTok creator seeding; #1 Amazon soda 2023</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>2024 first Super Bowl ad; &gt;$500M rev; PepsiCo $1.95B closed May 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="92" customHeight="1">
+          <t>Pink aesthetic, Alix Earle/Emily Mariko seeding, vending-machine stunt (2025, mixed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="66" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
           <t>OLIPOP</t>
@@ -5440,26 +5734,21 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Founders' prior brand Obi; $100k seed; nostalgic-soda + fiber insight</t>
+          <t>Ben Goodwin (ex-Obi) &amp; David Lester; $100k from Obi sale</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Late 2018: 40 NorCal indie grocers; ~$852k yr 1; ~$2.49/can; gut-health science story</t>
+          <t>DTC repurchase rates + reactive social</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Natural → conventional → mass; “astronomical repurchase” sell-in; $73.4M (2022); $39.7M Series B</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>$200M (2023)→$400M+ (2024); 7,000+ grocers; $50M @ $1.85B (Feb 2025); INDEPENDENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="92" customHeight="1">
+          <t>“Soda Stories”; needled Poppi's vending spend during 2025 SB — earned media without paying for the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="66" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>LMNT</t>
@@ -5467,26 +5756,21 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>2018–19: keto-sodium insight; Robb Wolf + Ketogains; high-sodium no-sugar formula</t>
+          <t>Robb Wolf (biochemist) + Ketogains (Villaseñor)</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Late 2019 DTC-only; free Sample Pack (pay ~$5 shipping); profitable yr 1 (claim)</t>
+          <t>Podcast-sponsorship moat (Huberman, Attia)</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Podcast sponsorships (Huberman et al., ~10k episodes); ~$50M run-rate by Q1 2022</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>$206M sales (2023, SEC); private, founder-controlled; selective retail; NO exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="92" customHeight="1">
+          <t>Host-read trust + free-sample funnel; $54.6M mktg + $7.1M sampling in 2023 (~26.5% of rev)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="66" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Liquid I.V.</t>
@@ -5494,67 +5778,122 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>2012: adults using Pedialyte insight; WHO-ORS-based CTT formula</t>
+          <t>Brandin Cohen, college brainchild (+2)</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Whole Foods “Supplier 101”; founder samples weekly → 12 WF by 2015</t>
+          <t>In-store/Costco roadshow sampling + give-back</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Costco roadshow sampling; Emerson Group (2015); ~$100M within 5 yrs</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Unilever Sept 2020 (~$500M est.); 30k→80k stores; $1B+ brand</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="92" customHeight="1">
+          <t>Founder sampled every weekend; POS-data sell-in; Emerson Group for national muscle</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="66" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
+          <t>Nuun</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Tim Moxey, British Ironman</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Grassroots endurance-community events</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Authentic credibility in run/bike/tri before mainstream</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="66" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
           <t>Celsius</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>2004 (Elite FX); near-bankruptcy/delisting ~2010 — over-marketing before PMF</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Turnaround 2012; Li Ka-shing $15M (2015); NASDAQ uplisting 2017 (~$36M rev)</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Amazon ~15–20% of sales (2020); Target DSD; 100k+ doors by 2021</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>PepsiCo $550M/8.5% (2022) → ~#3 energy; bought Alani Nu $1.8B (2025)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>DATE TRAP: Poppi's FIRST Super Bowl ad = 2024 (LVIII); the vending-machine controversy = the 2025 (LIX) return. Many secondary sources conflate them.</t>
-        </is>
-      </c>
-      <c r="B9" s="34" t="n"/>
-      <c r="C9" s="34" t="n"/>
-      <c r="D9" s="34" t="n"/>
-      <c r="E9" s="35" t="n"/>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Turnaround 2012; Li Ka-shing $15M (2015)</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Amazon + fitness influencers/gym sampling</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Amazon velocity → Target DSD → PepsiCo $550M distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="66" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Vital Proteins Sparkling</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>K. Seidensticker; Nestlé-owned</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Big-brand media + retail muscle + collagen loyalty</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Distribution &amp; #1-collagen halo, not scrappy virality</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Recess</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Benjamin Witte</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Distinctive pastel brand world + culture-tuned social</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Owned a vibe + the “relaxation” moment</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>READ-ACROSS: The two cheapest high-ROI challenger playbooks are LMNT's trusted-host podcast model and OLIPOP's reactive earned-media social — both winnable without Super Bowl budgets. Pair with Costco-roadshow sampling (Liquid I.V.). Brand tone must evolve with stage (Poppi's vending stunt misfired once mainstream).</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="n"/>
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A12:D12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
@@ -5579,17 +5918,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="114" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Success Patterns &amp; Failure Modes</t>
+          <t>Launch Playbook Teardowns — phased GTM timelines</t>
         </is>
       </c>
       <c r="N1" s="95" t="inlineStr">
@@ -5599,154 +5941,182 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>SEVEN SUCCESS PATTERNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Founder-authority insight tied to a personal health problem — cheap, durable brand moat (Ellsworth gut health, Wolf sodium, Cohen Pedialyte).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>ONE concentrated trial-generation tactic, executed obsessively, before broad spend.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>Sell-in on DATA (velocity/repurchase), not flavour — the single most repeated lever.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>Sequenced channel ladder — natural/DTC → specialty → grocery → mass → club; never skip rungs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>Strategic-investor signal early (Oza, Li Ka-shing, celebrity rounds) — capital + credibility + distribution.</t>
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Phase 0 (pre-launch)</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1 (launch, yr 0–1)</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Phase 2 (scale, yr 1–3)</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Phase 3 (maturity/exit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="92" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Poppi</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>2015–16: gut-health insight; ~$90k self-funded; “Mother Beverage” glass bottles</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Farmers markets → Whole Foods regional; ~$500k in 18 mo; Shark Tank 2018 ($400k/25% Oza)</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>2020 rebrand to cans + national launch (Mar 2020); TikTok creator seeding; #1 Amazon soda 2023</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>2024 first Super Bowl ad; &gt;$500M rev; PepsiCo $1.95B closed May 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>OLIPOP</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Founders' prior brand Obi; $100k seed; nostalgic-soda + fiber insight</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Late 2018: 40 NorCal indie grocers; ~$852k yr 1; ~$2.49/can; gut-health science story</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Natural → conventional → mass; “astronomical repurchase” sell-in; $73.4M (2022); $39.7M Series B</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>$200M (2023)→$400M+ (2024); 7,000+ grocers; $50M @ $1.85B (Feb 2025); INDEPENDENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="92" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>LMNT</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>2018–19: keto-sodium insight; Robb Wolf + Ketogains; high-sodium no-sugar formula</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Late 2019 DTC-only; free Sample Pack (pay ~$5 shipping); profitable yr 1 (claim)</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Podcast sponsorships (Huberman et al., ~10k episodes); ~$50M run-rate by Q1 2022</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>$206M sales (2023, SEC); private, founder-controlled; selective retail; NO exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="92" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Liquid I.V.</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>2012: adults using Pedialyte insight; WHO-ORS-based CTT formula</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Whole Foods “Supplier 101”; founder samples weekly → 12 WF by 2015</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Costco roadshow sampling; Emerson Group (2015); ~$100M within 5 yrs</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Unilever Sept 2020 (~$500M est.); 30k→80k stores; $1B+ brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="92" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Celsius</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>2004 (Elite FX); near-bankruptcy/delisting ~2010 — over-marketing before PMF</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Turnaround 2012; Li Ka-shing $15M (2015); NASDAQ uplisting 2017 (~$36M rev)</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Amazon ~15–20% of sales (2020); Target DSD; 100k+ doors by 2021</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>PepsiCo $550M/8.5% (2022) → ~#3 energy; bought Alani Nu $1.8B (2025)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>Category-creation language to escape commodity comparison and hold a $2–$3/can premium.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>Endgame split: strategic exit (Poppi/Liquid I.V./Celsius) vs independence (OLIPOP/LMNT) — both valid; scale eventually needs a partner or heavy capital.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>SIX FAILURE MODES</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>Over-distribution before product-market fit — Celsius's own ~2010 near-bankruptcy is the canonical case. Velocity must precede footprint.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>Undercapitalized / capital-intensive DTC — beverages are heavy physical goods; ~90% of beverage startups failed historically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>Premium price with no defensible moat / thin claims — ~32% of consumers cite “too expensive”; premium needs credible function + repeat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>Trial without retention — sampling/virality wasted if repurchase is weak (inverse of the OLIPOP/Liquid I.V. data story).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>Brand/tone missteps at scale — Poppi's 2025 vending stunt; tactics must evolve with brand stage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>Wrong timing / flavour failure — the baseline reasons ~85% of new CPG products fail within 2 years.</t>
-        </is>
-      </c>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>DATE TRAP: Poppi's FIRST Super Bowl ad = 2024 (LVIII); the vending-machine controversy = the 2025 (LIX) return. Many secondary sources conflate them.</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="n"/>
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A12:B12"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
@@ -5771,21 +6141,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="114" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Financial Outcomes &amp; M&amp;A Comps</t>
+          <t>Success Patterns &amp; Failure Modes</t>
         </is>
       </c>
       <c r="N1" s="95" t="inlineStr">
@@ -5795,373 +6161,154 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Revenue trajectory</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Funding / valuation</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Exit / status</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Category share</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>Profitability</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Poppi</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>$13M(20)→$65M(22)→$100M+(23)→~$500M(24)</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>VC-backed pre-exit</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>PepsiCo $1.95B (net ~$1.65B), May 2025</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>~38% modern soda (24)</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>OLIPOP</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>$852k(18)→$200M+(23)→$400M+(24)</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>$50M Series C @ $1.85B (Feb 2025, JPM)</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>~32.7% modern soda (24)</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>Cash-profitable early 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>LMNT</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>$206M sales (2023, SEC)</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Reg CF / Republic</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>~20% net margin (2023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Liquid I.V.</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>~$100M in 5 yrs → ~$200M exit → $1B+ now</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Unilever Sept 2020 (~$500M est.)</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>Unilever +$80M MO plant</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Nuun</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>$10M+ (2013)</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>TSG Consumer (2017)</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Nestlé HS July 2021 (undisclosed)</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>#1 run/bike/outdoor</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Celsius</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>multi-$B (public)</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Li Ka-shing $15M (2015)</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Public; PepsiCo $550M (2022); bought Alani Nu $1.8B</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>~#3 US energy (~11.5%)</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>Profitable</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Health-Ade</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>~$250M/yr retail</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>~$54M raised</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Generous Brands $500M</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Alani Nu</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>~$595M (2024)</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Congo Brands</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Celsius $1.8B (2025)</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Vital Proteins</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>(in Nestlé HS)</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Nestlé (full 2022)</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Aura Bora</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>$12M (2024)</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>~$22M raised</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>Majority to Next In Natural (2025)</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>M&amp;A READ: Strategics now own most winners — PepsiCo (Poppi, Celsius stake), Unilever (Liquid I.V., Olly), Nestlé (Vital Proteins, Nuun), KDP (Ghost). For a challenger the realistic endgame is acquisition, not durable independence — but Coke's organic Simply Pop shows incumbents may CLONE rather than buy, compressing the premium. OLIPOP (independent, $1.85B) is the counter-example.</t>
-        </is>
-      </c>
-      <c r="B14" s="34" t="n"/>
-      <c r="C14" s="34" t="n"/>
-      <c r="D14" s="34" t="n"/>
-      <c r="E14" s="34" t="n"/>
-      <c r="F14" s="35" t="n"/>
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>SEVEN SUCCESS PATTERNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Founder-authority insight tied to a personal health problem — cheap, durable brand moat (Ellsworth gut health, Wolf sodium, Cohen Pedialyte).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>ONE concentrated trial-generation tactic, executed obsessively, before broad spend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Sell-in on DATA (velocity/repurchase), not flavour — the single most repeated lever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Sequenced channel ladder — natural/DTC → specialty → grocery → mass → club; never skip rungs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Strategic-investor signal early (Oza, Li Ka-shing, celebrity rounds) — capital + credibility + distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Category-creation language to escape commodity comparison and hold a $2–$3/can premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Endgame split: strategic exit (Poppi/Liquid I.V./Celsius) vs independence (OLIPOP/LMNT) — both valid; scale eventually needs a partner or heavy capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>SIX FAILURE MODES</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Over-distribution before product-market fit — Celsius's own ~2010 near-bankruptcy is the canonical case. Velocity must precede footprint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Undercapitalized / capital-intensive DTC — beverages are heavy physical goods; ~90% of beverage startups failed historically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Premium price with no defensible moat / thin claims — ~32% of consumers cite “too expensive”; premium needs credible function + repeat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>Trial without retention — sampling/virality wasted if repurchase is weak (inverse of the OLIPOP/Liquid I.V. data story).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>Brand/tone missteps at scale — Poppi's 2025 vending stunt; tactics must evolve with brand stage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Wrong timing / flavour failure — the baseline reasons ~85% of new CPG products fail within 2 years.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
@@ -6186,20 +6333,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Per-Brand SWOT</t>
+          <t>Financial Outcomes &amp; M&amp;A Comps</t>
         </is>
       </c>
       <c r="N1" s="95" t="inlineStr">
@@ -6216,26 +6364,31 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Strengths</t>
+          <t>Revenue trajectory</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>Weaknesses</t>
+          <t>Funding / valuation</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>Opportunities</t>
+          <t>Exit / status</t>
         </is>
       </c>
       <c r="E3" s="11" t="inlineStr">
         <is>
-          <t>Threats</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="58" customHeight="1">
+          <t>Category share</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Poppi</t>
@@ -6243,26 +6396,31 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>Mass brand love, TikTok engine, PepsiCo distribution</t>
+          <t>$13M(20)→$65M(22)→$100M+(23)→~$500M(24)</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>Thin fiber dose, claims litigation history</t>
+          <t>VC-backed pre-exit</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>PepsiCo scale, international</t>
+          <t>PepsiCo $1.95B (net ~$1.65B), May 2025</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Commoditization, Simply Pop, claim scrutiny</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
+          <t>~38% modern soda (24)</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
           <t>OLIPOP</t>
@@ -6270,26 +6428,31 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>9g fiber moat, repeat rate, independence, $1.85B val</t>
+          <t>$852k(18)→$200M+(23)→$400M+(24)</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Premium price, single category</t>
+          <t>$50M Series C @ $1.85B (Feb 2025, JPM)</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Mass expansion, intl, format extensions</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>PepsiCo-backed Poppi, Coke Simply Pop, private label</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
+          <t>~32.7% modern soda (24)</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Cash-profitable early 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>LMNT</t>
@@ -6297,26 +6460,31 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Profitable, capital-light, podcast moat, 20% net margin</t>
+          <t>$206M sales (2023, SEC)</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Polarizing high sodium, niche, DTC-dependent</t>
+          <t>Reg CF / Republic</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Retail expansion, sparkling line, intl</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Electrolyte crowding (Prime, LMNT clones)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>~20% net margin (2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Liquid I.V.</t>
@@ -6324,82 +6492,238 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Unilever scale, Costco engine, $1B+ brand</t>
+          <t>~$100M in 5 yrs → ~$200M exit → $1B+ now</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Sugar content, undifferentiated vs new entrants</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Global expansion, sugar-free line</t>
+          <t>Unilever Sept 2020 (~$500M est.)</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Crowded hydration, Prime, private label</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Unilever +$80M MO plant</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Vital Proteins Sparkling</t>
+          <t>Nuun</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Nestlé muscle, #1 collagen halo, clinical claim, mass price</t>
+          <t>$10M+ (2013)</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>New format unproven, collagen efficacy debate</t>
+          <t>TSG Consumer (2017)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Owns beauty-from-within mainstreaming</t>
+          <t>Nestlé HS July 2021 (undisclosed)</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>2025 no-benefit meta-analysis, claims risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
+          <t>#1 run/bike/outdoor</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>MUV (Organika)</t>
+          <t>Celsius</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Domestic CA producer, #1 CA collagen halo, existing CA shelf, cost edge</t>
+          <t>multi-$B (public)</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Unproven RTD, food-format claim limits, small vs strategics</t>
+          <t>Li Ka-shing $15M (2015)</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Costco CA/Amazon beachhead, gut+beauty stack, Supplemented-Food pathway</t>
+          <t>Public; PepsiCo $550M (2022); bought Alani Nu $1.8B</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>Nestlé/Vital Proteins, collagen efficacy/claims liability, shelf saturation</t>
-        </is>
-      </c>
+          <t>~#3 US energy (~11.5%)</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Profitable</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Health-Ade</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>~$250M/yr retail</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>~$54M raised</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Generous Brands $500M</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Alani Nu</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>~$595M (2024)</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Congo Brands</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Celsius $1.8B (2025)</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Vital Proteins</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>(in Nestlé HS)</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Nestlé (full 2022)</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Aura Bora</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>$12M (2024)</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>~$22M raised</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Majority to Next In Natural (2025)</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>M&amp;A READ: Strategics now own most winners — PepsiCo (Poppi, Celsius stake), Unilever (Liquid I.V., Olly), Nestlé (Vital Proteins, Nuun), KDP (Ghost). For a challenger the realistic endgame is acquisition, not durable independence — but Coke's organic Simply Pop shows incumbents may CLONE rather than buy, compressing the premium. OLIPOP (independent, $1.85B) is the counter-example.</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="n"/>
+      <c r="C14" s="34" t="n"/>
+      <c r="D14" s="34" t="n"/>
+      <c r="E14" s="34" t="n"/>
+      <c r="F14" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
@@ -6424,7 +6748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6843,6 +7167,18 @@
       <c r="B36" s="58" t="inlineStr">
         <is>
           <t>Sport-electrolyte → Supplemented Foods reclassification; claims fork (supersedes Tab 19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="94" t="inlineStr">
+        <is>
+          <t>MÜV Peer Set</t>
+        </is>
+      </c>
+      <c r="B37" s="58" t="inlineStr">
+        <is>
+          <t>MÜV's direct electrolyte/sparkling rivals vs category-adjacent context (reconciliation)</t>
         </is>
       </c>
     </row>
@@ -6884,6 +7220,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -6899,6 +7236,244 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="003E5C76"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Per-Brand SWOT</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Strengths</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Weaknesses</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Opportunities</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Threats</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Poppi</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Mass brand love, TikTok engine, PepsiCo distribution</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Thin fiber dose, claims litigation history</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>PepsiCo scale, international</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Commoditization, Simply Pop, claim scrutiny</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>OLIPOP</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>9g fiber moat, repeat rate, independence, $1.85B val</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Premium price, single category</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Mass expansion, intl, format extensions</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>PepsiCo-backed Poppi, Coke Simply Pop, private label</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>LMNT</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Profitable, capital-light, podcast moat, 20% net margin</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Polarizing high sodium, niche, DTC-dependent</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Retail expansion, sparkling line, intl</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Electrolyte crowding (Prime, LMNT clones)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Liquid I.V.</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Unilever scale, Costco engine, $1B+ brand</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Sugar content, undifferentiated vs new entrants</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Global expansion, sugar-free line</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Crowded hydration, Prime, private label</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Vital Proteins Sparkling</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Nestlé muscle, #1 collagen halo, clinical claim, mass price</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>New format unproven, collagen efficacy debate</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Owns beauty-from-within mainstreaming</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>2025 no-benefit meta-analysis, claims risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>MUV (Organika)</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Domestic CA producer, #1 CA collagen halo, existing CA shelf, cost edge</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Unproven RTD, food-format claim limits, small vs strategics</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Costco CA/Amazon beachhead, gut+beauty stack, Supplemented-Food pathway</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Nestlé/Vital Proteins, collagen efficacy/claims liability, shelf saturation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="003E5C76"/>
@@ -7327,7 +7902,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001E7D32"/>
@@ -7879,7 +8454,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001E7D32"/>
@@ -8409,7 +8984,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001E7D32"/>
@@ -8449,6 +9024,8 @@
           <t>HEADLINE: Health Canada Public Notice (Apr 2026) reclassifies ALL sport-electrolyte products — RTD beverages, powders/concentrates AND effervescent tablets — from Natural Health Products (NHP/NPN) to FOODS / Supplemented Foods. Existing NPN holders transition by Dec 31, 2027; NEW products must comply with the Food &amp; Drug Regulations immediately. Oral Rehydration Solutions (clinical) stay NHP.</t>
         </is>
       </c>
+      <c r="B4" s="34" t="n"/>
+      <c r="C4" s="35" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="42" t="inlineStr">
@@ -8833,6 +9410,8 @@
           <t>OPEN ITEMS ⚠: confirm exact transition date (Dec 31 2027 vs Jan 1 2028) on the canada.ca notice; MÜV's current licensing status (food vs any legacy NPN); verbatim collagen monograph wording; Bill 96 trademark analysis for “MÜV Sparkling Electrolytes”. canada.ca/LNHPD pages block automated fetch (403) — verify on the live primary page before a compliance filing.</t>
         </is>
       </c>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -8853,7 +9432,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E7D8A"/>
@@ -8895,6 +9474,11 @@
           <t>TWO FINDINGS THAT RESHAPE THE READ: (1) MÜV is a ready-to-drink SPARKLING CAN (verified: ingredient list begins “Carbonated water”, SKU 4338, ~$14.99), not a powder. (2) Canada is moving ALL sport-electrolyte products (RTD, powder, effervescent) from NHP to SUPPLEMENTED FOODS by Dec 31, 2027. So MÜV competes in the daily-wellness sparkling lane and is food-regulated; win on format + Canadian-made, not on collagen-beauty claims.</t>
         </is>
       </c>
+      <c r="B4" s="34" t="n"/>
+      <c r="C4" s="34" t="n"/>
+      <c r="D4" s="34" t="n"/>
+      <c r="E4" s="34" t="n"/>
+      <c r="F4" s="35" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="42" t="inlineStr">
@@ -9440,6 +10024,11 @@
           <t>WHITE SPACE ◐: a flavored SPARKLING electrolyte is genuinely rare (LMNT Sparkling can; Nuun tablets fizz). MÜV's carbonation is a real sensory differentiator that aids flavour release → more consumption, no hydration penalty (Beverage Hydration Index).</t>
         </is>
       </c>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="34" t="n"/>
+      <c r="D29" s="34" t="n"/>
+      <c r="E29" s="34" t="n"/>
+      <c r="F29" s="35" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="42" t="inlineStr">
@@ -9618,6 +10207,11 @@
           <t>SOURCES &amp; CONFIDENCE: Circana via CNN (category); Grand View/Mordor (powder market, ◐); organika.com (MÜV SKU 4338, ingredient list); Globe &amp; Mail/CBC/PRNewswire/Coachwood (BioSteel); strategyonline.ca/Unilever (Liquid I.V. Canada); drinklmnt.com/hubermanlab.com (LMNT). Revenue &amp; market-size figures are estimates/projections (⚠). Several canada.ca/retailer pages block automated fetch (403) — confirm load-bearing items on the live page.</t>
         </is>
       </c>
+      <c r="B43" s="34" t="n"/>
+      <c r="C43" s="34" t="n"/>
+      <c r="D43" s="34" t="n"/>
+      <c r="E43" s="34" t="n"/>
+      <c r="F43" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -9640,7 +10234,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B45309"/>
@@ -9791,7 +10385,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C9A227"/>
@@ -10086,7 +10680,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C9A227"/>
@@ -10319,190 +10913,6 @@
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00B45309"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Phased Launch Plan (0–18 months)</t>
-        </is>
-      </c>
-      <c r="N1" s="95" t="inlineStr">
-        <is>
-          <t>↩ Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Phase</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Timing</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Objectives</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Key workstreams</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Success gate</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="80" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Phase 0 — Foundation</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Months 0–3</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Lock product, claims, regulatory pathway, co-pack</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Finalize formula &amp; collagen dose; regulatory-counsel claim opinion (Supplemented Foods); co-packer quote &amp; MOQ; bilingual + Bill 96 artwork; brand/positioning</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory sign-off on claim set + artwork approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="80" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1 — Beachhead</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Months 3–9</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Prove velocity &amp; repeat in a contained beachhead</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Costco CA roadshows + Amazon.ca + Well.ca/Natura + Organika pharmacy/health-food base; podcast + reactive social; sampling</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>Repeat rate + velocity above category benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Phase 2 — Scale</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Months 9–18</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Earn conventional grocery on proven data</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Sell-in to Loblaw/Sobeys/Metro on velocity data; distributor (UNFI CA / Tree of Life); managed trade spend; add SKUs on repeat data</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>National listings won on data, not discounts</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Phase 3 — Defend &amp; extend</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>18 mo+</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Category leadership &amp; optionality</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Format/flavour extensions; deepen moat; evaluate strategic-partner vs independent scale</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Profitable contribution + exit optionality</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
@@ -10527,21 +10937,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Risk Register</t>
+          <t>Phased Launch Plan (0–18 months)</t>
         </is>
       </c>
       <c r="N1" s="95" t="inlineStr">
@@ -10550,409 +10959,144 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Likelihood × Impact (H/M/L). Ranked by exposure</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Likelihood</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Mitigation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Collagen efficacy / claims liability (2025 meta-analysis; Poppi-style dose-insufficiency suit)</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory/Legal</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>Dose to efficacy (2.5g+); structure/function-safe language; substantiation files; lead with gut/hydration not beauty</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Strategic-owned competition (Nestlé owns Vital Proteins; PepsiCo/Unilever firepower)</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E6" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>Compete on Canadian-made + domestic cost edge + Organika collagen credibility; niche beachhead before they react</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Canada claim/label pathway misread (food vs NHP; SFCI; collagen caution)</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory</t>
-        </is>
-      </c>
-      <c r="D7" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory-counsel opinion before artwork; design to Supplemented Foods framework; caffeine-free</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Over-distribution before product-market fit</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>Execution</t>
-        </is>
-      </c>
-      <c r="D8" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E8" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>Prove velocity/repeat in beachhead before national; gate Phase 2 on data</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Slotting / trade-spend cash burn</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E9" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Use free-fill over cash slotting; 35–45% trade-spend budget; Code of Conduct leverage on arbitrary fees</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Thin differentiation / shelf saturation (prebiotic shelf filling fast)</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D10" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E10" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Defensible spec (fiber + collagen dose) + function stacking; Canadian-made story</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Private-label encroachment (~$277B, ~21% share, growing 2×)</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D11" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E11" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Brand equity + clinical-grade ingredients retailers can't easily copy</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>DTC CAC / heavy-ship economics if DTC-led</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D12" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E12" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>Lead retail/beachhead not paid DTC; subscription + sampling only</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Co-packer capacity / collagen sourcing / cost inflation</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="D13" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E13" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>Lock co-pack capacity early; qualify 2nd collagen supplier; hedge raws</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>FX / tariff / freight premium on cross-border inputs</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D14" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E14" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>Domestic CA co-pack; monitor tariff status post-Dec 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>GLP-1 demand shift away from sweet/snack</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Macro</t>
-        </is>
-      </c>
-      <c r="D15" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E15" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Low-cal, fiber, protein, hydration positioning aligns with GLP-1 users</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>Brand/tone misstep at scale</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="D16" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E16" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>Evolve tactics with stage; avoid Poppi-style stunts once mainstream</t>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Objectives</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Key workstreams</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Success gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Phase 0 — Foundation</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Months 0–3</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Lock product, claims, regulatory pathway, co-pack</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Finalize formula &amp; collagen dose; regulatory-counsel claim opinion (Supplemented Foods); co-packer quote &amp; MOQ; bilingual + Bill 96 artwork; brand/positioning</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory sign-off on claim set + artwork approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1 — Beachhead</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Months 3–9</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Prove velocity &amp; repeat in a contained beachhead</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Costco CA roadshows + Amazon.ca + Well.ca/Natura + Organika pharmacy/health-food base; podcast + reactive social; sampling</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Repeat rate + velocity above category benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Phase 2 — Scale</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Months 9–18</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Earn conventional grocery on proven data</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Sell-in to Loblaw/Sobeys/Metro on velocity data; distributor (UNFI CA / Tree of Life); managed trade spend; add SKUs on repeat data</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>National listings won on data, not discounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Phase 3 — Defend &amp; extend</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>18 mo+</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Category leadership &amp; optionality</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Format/flavour extensions; deepen moat; evaluate strategic-partner vs independent scale</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Profitable contribution + exit optionality</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
@@ -11161,6 +11305,456 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Likelihood × Impact (H/M/L). Ranked by exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Likelihood</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Mitigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Collagen efficacy / claims liability (2025 meta-analysis; Poppi-style dose-insufficiency suit)</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory/Legal</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Dose to efficacy (2.5g+); structure/function-safe language; substantiation files; lead with gut/hydration not beauty</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Strategic-owned competition (Nestlé owns Vital Proteins; PepsiCo/Unilever firepower)</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Compete on Canadian-made + domestic cost edge + Organika collagen credibility; niche beachhead before they react</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Canada claim/label pathway misread (food vs NHP; SFCI; collagen caution)</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory-counsel opinion before artwork; design to Supplemented Foods framework; caffeine-free</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Over-distribution before product-market fit</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Prove velocity/repeat in beachhead before national; gate Phase 2 on data</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Slotting / trade-spend cash burn</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Use free-fill over cash slotting; 35–45% trade-spend budget; Code of Conduct leverage on arbitrary fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Thin differentiation / shelf saturation (prebiotic shelf filling fast)</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Defensible spec (fiber + collagen dose) + function stacking; Canadian-made story</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Private-label encroachment (~$277B, ~21% share, growing 2×)</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Brand equity + clinical-grade ingredients retailers can't easily copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>DTC CAC / heavy-ship economics if DTC-led</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Lead retail/beachhead not paid DTC; subscription + sampling only</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Co-packer capacity / collagen sourcing / cost inflation</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Lock co-pack capacity early; qualify 2nd collagen supplier; hedge raws</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>FX / tariff / freight premium on cross-border inputs</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Domestic CA co-pack; monitor tariff status post-Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>GLP-1 demand shift away from sweet/snack</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Low-cal, fiber, protein, hydration positioning aligns with GLP-1 users</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Brand/tone misstep at scale</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Evolve tactics with stage; avoid Poppi-style stunts once mainstream</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00B45309"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -11454,7 +12048,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -11978,7 +12572,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C9A227"/>
@@ -12316,7 +12910,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>

--- a/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
+++ b/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
@@ -12,38 +12,39 @@
     <sheet name="02 Executive Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Dashboard" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Financial Model" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="03 Methodology" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="04 Market Sizing" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="05 Trends &amp; Macro" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="06 Consumer" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="07 Comparison Matrix" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="MÜV Peer Set" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="08 Extended Landscape" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="09 Channel &amp; Retail" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="10 Channel Economics" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="11 Formulation" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="12 Marketing" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="13 Launch Playbooks" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="14 Patterns &amp; Failures" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="15 Outcomes &amp; M&amp;A" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="16 SWOT" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="17 Scoring Model" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="18 Canada Market" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="19 Canada Regulatory" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Canada Regulatory v2" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Electrolyte BFY Deep-Dive" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="20 GTM Recommendation" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Go-NoGo Decision" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Battlecards" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="21 Launch Plan" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="22 Risk Register" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="23 KPI Dashboard" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="24 Sources" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="Verification Log" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="25 Glossary" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="Scenario Comparison" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="03 Methodology" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="04 Market Sizing" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="05 Trends &amp; Macro" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="06 Consumer" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="07 Comparison Matrix" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="MÜV Peer Set" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="08 Extended Landscape" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="09 Channel &amp; Retail" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="10 Channel Economics" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="11 Formulation" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="12 Marketing" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="13 Launch Playbooks" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="14 Patterns &amp; Failures" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="15 Outcomes &amp; M&amp;A" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="16 SWOT" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="17 Scoring Model" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="18 Canada Market" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="19 Canada Regulatory" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="Canada Regulatory v2" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="Electrolyte BFY Deep-Dive" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="20 GTM Recommendation" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Go-NoGo Decision" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Battlecards" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="21 Launch Plan" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="22 Risk Register" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="23 KPI Dashboard" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="24 Sources" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Verification Log" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="25 Glossary" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'07 Comparison Matrix'!$A$3:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'07 Comparison Matrix'!$A$3:$L$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -346,7 +347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -633,6 +634,27 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1157,6 +1179,115 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Year-3 Net Revenue vs EBITDA by Scenario (CAD)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Scenario Comparison'!B18</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Scenario Comparison'!$A$19:$A$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Scenario Comparison'!$B$19:$B$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Scenario Comparison'!C18</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Scenario Comparison'!$A$19:$A$21</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Scenario Comparison'!$C$19:$C$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1264,6 +1395,33 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1872,6 +2030,233 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002E7D8A"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Consumer Segmentation &amp; The Collagen Buyer</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Dimension</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Read</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Detail &amp; evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Demand engine</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Gen Z + Millennials</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>~80% of Gen Z, ~75% of Millennials consume functional beverages regularly; 36% of adults but 41%+ of wellness spend (McKinsey). US wellness market $480B (2024).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Gender skew (category)</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Female-led growth</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Women = fastest-growing segment (~5.3% growth); over-index on probiotic/fortified. Hard female-% split is paywalled — DATA GAP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Collagen / BFW buyer</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Women 25–45</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Women = 68.4% of beauty-from-within drink revenue (2024); buy anti-aging, hydration, hair/nail outcomes; clinically-backed claims drive repeat/subscription.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Efficacy &amp; skepticism</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>RISK</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>2025 AJM systematic review/meta-analysis: NO clinical evidence collagen prevents/treats skin aging; industry-funded trials showed benefit, independent ones did not. Positive studies used 2.5–10g/day, effect at 4–8 wks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Willingness to pay</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Attribute-gated</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Younger consumers are price-conscious AND premium-willing for a named function / clean label / brand-community. Premiumization is real but not blanket.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>RETAILER / CLUB BUYER CRITERIA (what gets a new functional bev listed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Criterion</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>What buyers actually want</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Gating metric — will the SKU turn fast enough to earn its facing</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Repeat rate</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Buyers discount discount-driven velocity; they want durable repeat &amp; customer-level margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Margin / trade support</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Plan 35–45% trade spend in early scale; slotting, promo, free-fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Differentiation + demand-gen</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Category-builder story + brand-funded marketing (the Poppi/OLIPOP social-first benchmark)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>IMPLICATION: MUV should dose collagen to a defensible level (2.5g+), lead with gut/hydration function, and prove repeat rate in a beachhead before pitching national buyers. The collagen efficacy debate makes substantiation files and structure/function-safe language mandatory.</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="35" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A10:C10"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="003E5C76"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -2510,7 +2895,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C9A227"/>
@@ -2554,6 +2939,12 @@
           <t>HOW TO READ THIS WORKBOOK: Tabs 07–17 profile the BROAD functional-beverage market (Poppi/OLIPOP/Vital Proteins). Those are CATEGORY-ADJACENT — they prove the better-for-you thesis and supply the LAUNCH PLAYBOOK, but they are NOT MÜV's direct shelf rivals. MÜV's DIRECT peer set is electrolyte/hydration + sparkling (this tab + ‘Electrolyte BFY Deep-Dive’). Read the two together: borrow the soda brands' go-to-market, but benchmark price/format/claims against the electrolyte brands.</t>
         </is>
       </c>
+      <c r="B4" s="34" t="n"/>
+      <c r="C4" s="34" t="n"/>
+      <c r="D4" s="34" t="n"/>
+      <c r="E4" s="34" t="n"/>
+      <c r="F4" s="34" t="n"/>
+      <c r="G4" s="35" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="102" t="inlineStr">
@@ -3040,6 +3431,12 @@
           <t>RECONCILED THESIS: MÜV should be PRICED &amp; FORMULATED against the DIRECT peers (≤ LMNT/Liquid I.V. per-serving economics, sparkling as the wedge, Supplemented-Food claims) while BORROWING the GTM from the adjacent soda winners (one obsessive trial tactic, sell-in on velocity/repeat, sequenced channel ladder). Win the daily-wellness sparkling occasion, made in Canada — don't fight Poppi for the soda shelf or Vital Proteins for beauty claims.</t>
         </is>
       </c>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="34" t="n"/>
+      <c r="D22" s="34" t="n"/>
+      <c r="E22" s="34" t="n"/>
+      <c r="F22" s="34" t="n"/>
+      <c r="G22" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3058,7 +3455,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="003E5C76"/>
@@ -4481,7 +4878,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="003E5C76"/>
@@ -4776,563 +5173,6 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A13:E13"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="003E5C76"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="68" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Channel Economics &amp; Margin Waterfall</t>
-        </is>
-      </c>
-      <c r="N1" s="95" t="inlineStr">
-        <is>
-          <t>↩ Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Only Amazon fees, Costco margin &amp; DTC CAC are HARD; the rest are operator rules-of-thumb — model as ranges</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>MARGIN WATERFALL — canned functional beverage</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Typical value</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Unit COGS target</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>&lt; $1.00/unit (liquid+can+co-pack at scale)</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>12oz decorated can (component)</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>~$0.15/can at intro minimums</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Co-pack run (10,000 cases)</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>≈ $200,000; MOQ 2,000–5,000 cases/SKU</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Blended gross margin (early)</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>40–50%; aspiration 50–65% at scale</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>GM by channel</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Retail ~35–45%; DTC ~40–50% (before CAC/freight)</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>COGS warning</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Excluding freight/duty/co-pack overstates GM by 3–8 pts — the #1 error</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>CHANNEL TAKE-RATES (who takes margin off the top)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Channel / cost</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Take / value</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Grocery (conventional)</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>~30–50% retailer margin; bev often 30–40%</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Natural/premium (Whole Foods)</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>45%+ (slower turns)</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Club (Costco)</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Max 14% markup (15% Kirkland); FY24 actual GM 10.92% — volume not margin play</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Distributor (general)</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>15–25% markup; UNFI avg ~13–14% (range 6–30%)</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>HARD-ish</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>DSD vs warehouse</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>DSD can save ~5–10% in fees vs UNFI/KeHE routing</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Broker</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>3–5% of net sales + often $5–10k/mo retainer</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>8–45% referral (most 15%) + FBA $3.73–$6.97/unit ($25+ heavy bev)</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>HARD (published)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>DTC CAC (food &amp; bev)</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>~$45–$53 (lowest vertical); supplements ~$89; shipping $8–15/order</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>HARD (benchmark)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>TRADE SPEND &amp; FEES</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Slotting fee</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>$250 → $250,000 by retailer/scope; ~$25,000/item regional cluster</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>Trade spend % of revenue</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>10–20% (emerging brands high end); US trade spend &gt;$200B, ~20% of gross, #2 P&amp;L line</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>HARD (aggregate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Free fill</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>1 free case/SKU/store on first order — cheaper substitute for slotting</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>LMNT subscription model</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>$200M+ rev 2023, ~20% net margin, 250k+ customers; free-8-pack (pay shipping) funnel</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>HARD (company/SEC)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>CANADA COST STACK (additive on US economics)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>Grocery concentration</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>Loblaw+Sobeys+Metro ≈ 80% w/ Walmart+Costco; all signed Grocery Code of Conduct (in force Jan 1, 2025)</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>Listing/slotting fees</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>Charged but NOT publicly disclosed; Code now lets suppliers challenge arbitrary fees — model at ≥ US slotting</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>No public $</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>Bilingual packaging</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>EN+FR mandatory; French ~2× longer; non-compliance fines up to $20,000; Bill 96 adds rules</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>HARD (regulatory)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>Distributors (CA)</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>UNFI Canada, Tree of Life Canada, Purity Life, Ecotrend</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>HARD (existence)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>Freight/FX/duty</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>FX (US$1≈C$1.15+) + cross-border freight + duty; model as premium; local co-pack is the margin fix</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>Qualitative</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="46" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>DTC-for-beverage reality check: heavy to ship, low online AOV, CAC can exceed contribution. Historically ~90% of beverage startups fail; the survivable DTC model (LMNT) is subscription + free-sample acquisition + asset-light profitability — not paid-media scale.</t>
-        </is>
-      </c>
-      <c r="B38" s="34" t="n"/>
-      <c r="C38" s="34" t="n"/>
-      <c r="D38" s="35" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
@@ -5357,20 +5197,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Formulation &amp; Positioning — the claim that won</t>
+          <t>Channel Economics &amp; Margin Waterfall</t>
         </is>
       </c>
       <c r="N1" s="95" t="inlineStr">
@@ -5379,264 +5217,519 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Winning claim</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Hero ingredient &amp; spec</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Positioning evolution</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Claim risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="64" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Poppi</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Prebiotic soda you can drink daily</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Prebiotic fiber + ACV; ~2g fiber, 2–5g sugar</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>ACV “tonic” (Mother Beverage) → 2020 bright “prebiotic soda”</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>$8.9M settlement — 2g fiber too little for claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="64" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>OLIPOP</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>“New kind of soda”, serious fiber</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Up to 9g fiber (cassava/chicory/artichoke) + botanicals</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Stable gut-health since launch; ~4× Poppi fiber</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>No suit found; higher fiber = stronger substantiation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="64" customHeight="1">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Only Amazon fees, Costco margin &amp; DTC CAC are HARD; the rest are operator rules-of-thumb — model as ranges</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>MARGIN WATERFALL — canned functional beverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Typical value</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>LMNT</t>
+          <t>Unit COGS target</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Zero-sugar, high-sodium for keto/athletes</t>
+          <t>&lt; $1.00/unit (liquid+can+co-pack at scale)</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>1,000mg sodium, 200mg K, 60mg Mg, 0g sugar</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Salt-first, science-forward</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>Sodium is the polarizing hook</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="64" customHeight="1">
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Liquid I.V.</t>
+          <t>12oz decorated can (component)</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Hydration Multiplier, 2–3× faster</t>
+          <t>~$0.15/can at intro minimums</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Cellular Transport Tech; 500mg sodium, 11g carbs</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Added sugar-free line later</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>CTT efficacy is marketing-led; sugar a vulnerability</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="64" customHeight="1">
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Nuun</t>
+          <t>Co-pack run (10,000 cases)</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Carb-free effervescent electrolyte</t>
+          <t>≈ $200,000; MOQ 2,000–5,000 cases/SKU</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>300mg sodium, 1g sugar, 15 cal, stevia</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Endurance carb-free → added powders</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Clean low-sugar story</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="64" customHeight="1">
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>Vital Proteins Sparkling</t>
+          <t>Blended gross margin (early)</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Beauty-from-within + clinical collagen at mass price</t>
+          <t>40–50%; aspiration 50–65% at scale</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>VERISOL collagen + 100% DV Vit C; 0g sugar</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Extends #1 collagen powder into a can</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>Strongest collagen claim, but see 2025 efficacy meta-analysis</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="64" customHeight="1">
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Recess</t>
+          <t>GM by channel</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Relaxation — sell the benefit not the molecule</t>
+          <t>Retail ~35–45%; DTC ~40–50% (before CAC/freight)</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Magnesium L-threonate + adaptogens</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Pivoted CBD → relaxation (CBD &lt;8% of sales)</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>KEY LESSON: lead with felt benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="64" customHeight="1">
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Aura Bora</t>
+          <t>COGS warning</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Herbal/floral, zero everything</t>
+          <t>Excluding freight/duty/co-pack overstates GM by 3–8 pts — the #1 error</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>0 cal/sugar/sodium; herb+fruit+flower</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Flavor-forward, no health-claim baggage</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>Low regulatory risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>READ-ACROSS for MUV: “collagen-as-hero” has a graveyard AND a 2025 no-benefit meta-analysis. Winners wrap collagen in a big brand + clinical claim at mass price (Vital Proteins) OR sell a broader felt benefit (Recess). Lead MUV with gut+hydration function + a credible collagen dose under the “Canada's #1 collagen brand” halo — not narrow beauty-from-within.</t>
-        </is>
-      </c>
-      <c r="B12" s="34" t="n"/>
-      <c r="C12" s="34" t="n"/>
-      <c r="D12" s="34" t="n"/>
-      <c r="E12" s="35" t="n"/>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>CHANNEL TAKE-RATES (who takes margin off the top)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Channel / cost</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Take / value</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Grocery (conventional)</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>~30–50% retailer margin; bev often 30–40%</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Natural/premium (Whole Foods)</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>45%+ (slower turns)</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Club (Costco)</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Max 14% markup (15% Kirkland); FY24 actual GM 10.92% — volume not margin play</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Distributor (general)</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>15–25% markup; UNFI avg ~13–14% (range 6–30%)</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>HARD-ish</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>DSD vs warehouse</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>DSD can save ~5–10% in fees vs UNFI/KeHE routing</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>3–5% of net sales + often $5–10k/mo retainer</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>8–45% referral (most 15%) + FBA $3.73–$6.97/unit ($25+ heavy bev)</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>HARD (published)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>DTC CAC (food &amp; bev)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>~$45–$53 (lowest vertical); supplements ~$89; shipping $8–15/order</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>HARD (benchmark)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>TRADE SPEND &amp; FEES</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Slotting fee</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>$250 → $250,000 by retailer/scope; ~$25,000/item regional cluster</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Trade spend % of revenue</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>10–20% (emerging brands high end); US trade spend &gt;$200B, ~20% of gross, #2 P&amp;L line</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>HARD (aggregate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Free fill</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>1 free case/SKU/store on first order — cheaper substitute for slotting</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>LMNT subscription model</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>$200M+ rev 2023, ~20% net margin, 250k+ customers; free-8-pack (pay shipping) funnel</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>HARD (company/SEC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>CANADA COST STACK (additive on US economics)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Grocery concentration</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Loblaw+Sobeys+Metro ≈ 80% w/ Walmart+Costco; all signed Grocery Code of Conduct (in force Jan 1, 2025)</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>Listing/slotting fees</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>Charged but NOT publicly disclosed; Code now lets suppliers challenge arbitrary fees — model at ≥ US slotting</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>No public $</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Bilingual packaging</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>EN+FR mandatory; French ~2× longer; non-compliance fines up to $20,000; Bill 96 adds rules</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>HARD (regulatory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>Distributors (CA)</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>UNFI Canada, Tree of Life Canada, Purity Life, Ecotrend</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>HARD (existence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Freight/FX/duty</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>FX (US$1≈C$1.15+) + cross-border freight + duty; model as premium; local co-pack is the margin fix</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="46" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>DTC-for-beverage reality check: heavy to ship, low online AOV, CAC can exceed contribution. Historically ~90% of beverage startups fail; the survivable DTC model (LMNT) is subscription + free-sample acquisition + asset-light profitability — not paid-media scale.</t>
+        </is>
+      </c>
+      <c r="B38" s="34" t="n"/>
+      <c r="C38" s="34" t="n"/>
+      <c r="D38" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A12:E12"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
@@ -5665,15 +5758,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand Build — the virality engine</t>
+          <t>Formulation &amp; Positioning — the claim that won</t>
         </is>
       </c>
       <c r="N1" s="95" t="inlineStr">
@@ -5690,21 +5784,26 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Founder story</t>
+          <t>Winning claim</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>Growth engine</t>
+          <t>Hero ingredient &amp; spec</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>What moved the needle</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="66" customHeight="1">
+          <t>Positioning evolution</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Claim risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="64" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Poppi</t>
@@ -5712,21 +5811,26 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>Allison &amp; Stephen Ellsworth; Shark Tank 2018 ($400k/25%, Rohan Oza)</t>
+          <t>Prebiotic soda you can drink daily</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>TikTok creator seeding + 2 Super Bowls (2024 first ad, 2025 return)</t>
+          <t>Prebiotic fiber + ACV; ~2g fiber, 2–5g sugar</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Pink aesthetic, Alix Earle/Emily Mariko seeding, vending-machine stunt (2025, mixed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="66" customHeight="1">
+          <t>ACV “tonic” (Mother Beverage) → 2020 bright “prebiotic soda”</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>$8.9M settlement — 2g fiber too little for claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="64" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
           <t>OLIPOP</t>
@@ -5734,21 +5838,26 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Ben Goodwin (ex-Obi) &amp; David Lester; $100k from Obi sale</t>
+          <t>“New kind of soda”, serious fiber</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>DTC repurchase rates + reactive social</t>
+          <t>Up to 9g fiber (cassava/chicory/artichoke) + botanicals</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>“Soda Stories”; needled Poppi's vending spend during 2025 SB — earned media without paying for the game</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="66" customHeight="1">
+          <t>Stable gut-health since launch; ~4× Poppi fiber</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>No suit found; higher fiber = stronger substantiation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>LMNT</t>
@@ -5756,21 +5865,26 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Robb Wolf (biochemist) + Ketogains (Villaseñor)</t>
+          <t>Zero-sugar, high-sodium for keto/athletes</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Podcast-sponsorship moat (Huberman, Attia)</t>
+          <t>1,000mg sodium, 200mg K, 60mg Mg, 0g sugar</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Host-read trust + free-sample funnel; $54.6M mktg + $7.1M sampling in 2023 (~26.5% of rev)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="66" customHeight="1">
+          <t>Salt-first, science-forward</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Sodium is the polarizing hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="64" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Liquid I.V.</t>
@@ -5778,21 +5892,26 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Brandin Cohen, college brainchild (+2)</t>
+          <t>Hydration Multiplier, 2–3× faster</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>In-store/Costco roadshow sampling + give-back</t>
+          <t>Cellular Transport Tech; 500mg sodium, 11g carbs</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Founder sampled every weekend; POS-data sell-in; Emerson Group for national muscle</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="66" customHeight="1">
+          <t>Added sugar-free line later</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>CTT efficacy is marketing-led; sugar a vulnerability</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="64" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Nuun</t>
@@ -5800,100 +5919,121 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Tim Moxey, British Ironman</t>
+          <t>Carb-free effervescent electrolyte</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Grassroots endurance-community events</t>
+          <t>300mg sodium, 1g sugar, 15 cal, stevia</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Authentic credibility in run/bike/tri before mainstream</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="66" customHeight="1">
+          <t>Endurance carb-free → added powders</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Clean low-sugar story</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>Celsius</t>
+          <t>Vital Proteins Sparkling</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Turnaround 2012; Li Ka-shing $15M (2015)</t>
+          <t>Beauty-from-within + clinical collagen at mass price</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Amazon + fitness influencers/gym sampling</t>
+          <t>VERISOL collagen + 100% DV Vit C; 0g sugar</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Amazon velocity → Target DSD → PepsiCo $550M distribution</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="66" customHeight="1">
+          <t>Extends #1 collagen powder into a can</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Strongest collagen claim, but see 2025 efficacy meta-analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="64" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Vital Proteins Sparkling</t>
+          <t>Recess</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>K. Seidensticker; Nestlé-owned</t>
+          <t>Relaxation — sell the benefit not the molecule</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Big-brand media + retail muscle + collagen loyalty</t>
+          <t>Magnesium L-threonate + adaptogens</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Distribution &amp; #1-collagen halo, not scrappy virality</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="66" customHeight="1">
+          <t>Pivoted CBD → relaxation (CBD &lt;8% of sales)</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>KEY LESSON: lead with felt benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Recess</t>
+          <t>Aura Bora</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Benjamin Witte</t>
+          <t>Herbal/floral, zero everything</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Distinctive pastel brand world + culture-tuned social</t>
+          <t>0 cal/sugar/sodium; herb+fruit+flower</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Owned a vibe + the “relaxation” moment</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52" customHeight="1">
+          <t>Flavor-forward, no health-claim baggage</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Low regulatory risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>READ-ACROSS: The two cheapest high-ROI challenger playbooks are LMNT's trusted-host podcast model and OLIPOP's reactive earned-media social — both winnable without Super Bowl budgets. Pair with Costco-roadshow sampling (Liquid I.V.). Brand tone must evolve with stage (Poppi's vending stunt misfired once mainstream).</t>
+          <t>READ-ACROSS for MUV: “collagen-as-hero” has a graveyard AND a 2025 no-benefit meta-analysis. Winners wrap collagen in a big brand + clinical claim at mass price (Vital Proteins) OR sell a broader felt benefit (Recess). Lead MUV with gut+hydration function + a credible collagen dose under the “Canada's #1 collagen brand” halo — not narrow beauty-from-within.</t>
         </is>
       </c>
       <c r="B12" s="34" t="n"/>
       <c r="C12" s="34" t="n"/>
-      <c r="D12" s="35" t="n"/>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
@@ -5918,20 +6058,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Launch Playbook Teardowns — phased GTM timelines</t>
+          <t>Marketing &amp; Brand Build — the virality engine</t>
         </is>
       </c>
       <c r="N1" s="95" t="inlineStr">
@@ -5948,26 +6087,21 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Phase 0 (pre-launch)</t>
+          <t>Founder story</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>Phase 1 (launch, yr 0–1)</t>
+          <t>Growth engine</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>Phase 2 (scale, yr 1–3)</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Phase 3 (maturity/exit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="92" customHeight="1">
+          <t>What moved the needle</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="66" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Poppi</t>
@@ -5975,26 +6109,21 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>2015–16: gut-health insight; ~$90k self-funded; “Mother Beverage” glass bottles</t>
+          <t>Allison &amp; Stephen Ellsworth; Shark Tank 2018 ($400k/25%, Rohan Oza)</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>Farmers markets → Whole Foods regional; ~$500k in 18 mo; Shark Tank 2018 ($400k/25% Oza)</t>
+          <t>TikTok creator seeding + 2 Super Bowls (2024 first ad, 2025 return)</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>2020 rebrand to cans + national launch (Mar 2020); TikTok creator seeding; #1 Amazon soda 2023</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>2024 first Super Bowl ad; &gt;$500M rev; PepsiCo $1.95B closed May 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="92" customHeight="1">
+          <t>Pink aesthetic, Alix Earle/Emily Mariko seeding, vending-machine stunt (2025, mixed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="66" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
           <t>OLIPOP</t>
@@ -6002,26 +6131,21 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Founders' prior brand Obi; $100k seed; nostalgic-soda + fiber insight</t>
+          <t>Ben Goodwin (ex-Obi) &amp; David Lester; $100k from Obi sale</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Late 2018: 40 NorCal indie grocers; ~$852k yr 1; ~$2.49/can; gut-health science story</t>
+          <t>DTC repurchase rates + reactive social</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Natural → conventional → mass; “astronomical repurchase” sell-in; $73.4M (2022); $39.7M Series B</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>$200M (2023)→$400M+ (2024); 7,000+ grocers; $50M @ $1.85B (Feb 2025); INDEPENDENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="92" customHeight="1">
+          <t>“Soda Stories”; needled Poppi's vending spend during 2025 SB — earned media without paying for the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="66" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>LMNT</t>
@@ -6029,26 +6153,21 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>2018–19: keto-sodium insight; Robb Wolf + Ketogains; high-sodium no-sugar formula</t>
+          <t>Robb Wolf (biochemist) + Ketogains (Villaseñor)</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Late 2019 DTC-only; free Sample Pack (pay ~$5 shipping); profitable yr 1 (claim)</t>
+          <t>Podcast-sponsorship moat (Huberman, Attia)</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Podcast sponsorships (Huberman et al., ~10k episodes); ~$50M run-rate by Q1 2022</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>$206M sales (2023, SEC); private, founder-controlled; selective retail; NO exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="92" customHeight="1">
+          <t>Host-read trust + free-sample funnel; $54.6M mktg + $7.1M sampling in 2023 (~26.5% of rev)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="66" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Liquid I.V.</t>
@@ -6056,67 +6175,122 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>2012: adults using Pedialyte insight; WHO-ORS-based CTT formula</t>
+          <t>Brandin Cohen, college brainchild (+2)</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Whole Foods “Supplier 101”; founder samples weekly → 12 WF by 2015</t>
+          <t>In-store/Costco roadshow sampling + give-back</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Costco roadshow sampling; Emerson Group (2015); ~$100M within 5 yrs</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Unilever Sept 2020 (~$500M est.); 30k→80k stores; $1B+ brand</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="92" customHeight="1">
+          <t>Founder sampled every weekend; POS-data sell-in; Emerson Group for national muscle</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="66" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
+          <t>Nuun</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Tim Moxey, British Ironman</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Grassroots endurance-community events</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Authentic credibility in run/bike/tri before mainstream</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="66" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
           <t>Celsius</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>2004 (Elite FX); near-bankruptcy/delisting ~2010 — over-marketing before PMF</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Turnaround 2012; Li Ka-shing $15M (2015); NASDAQ uplisting 2017 (~$36M rev)</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Amazon ~15–20% of sales (2020); Target DSD; 100k+ doors by 2021</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>PepsiCo $550M/8.5% (2022) → ~#3 energy; bought Alani Nu $1.8B (2025)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>DATE TRAP: Poppi's FIRST Super Bowl ad = 2024 (LVIII); the vending-machine controversy = the 2025 (LIX) return. Many secondary sources conflate them.</t>
-        </is>
-      </c>
-      <c r="B9" s="34" t="n"/>
-      <c r="C9" s="34" t="n"/>
-      <c r="D9" s="34" t="n"/>
-      <c r="E9" s="35" t="n"/>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Turnaround 2012; Li Ka-shing $15M (2015)</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Amazon + fitness influencers/gym sampling</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Amazon velocity → Target DSD → PepsiCo $550M distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="66" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Vital Proteins Sparkling</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>K. Seidensticker; Nestlé-owned</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Big-brand media + retail muscle + collagen loyalty</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Distribution &amp; #1-collagen halo, not scrappy virality</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Recess</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Benjamin Witte</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Distinctive pastel brand world + culture-tuned social</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Owned a vibe + the “relaxation” moment</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>READ-ACROSS: The two cheapest high-ROI challenger playbooks are LMNT's trusted-host podcast model and OLIPOP's reactive earned-media social — both winnable without Super Bowl budgets. Pair with Costco-roadshow sampling (Liquid I.V.). Brand tone must evolve with stage (Poppi's vending stunt misfired once mainstream).</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="n"/>
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A12:D12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
@@ -6141,17 +6315,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="114" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Success Patterns &amp; Failure Modes</t>
+          <t>Launch Playbook Teardowns — phased GTM timelines</t>
         </is>
       </c>
       <c r="N1" s="95" t="inlineStr">
@@ -6161,154 +6338,182 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>SEVEN SUCCESS PATTERNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Founder-authority insight tied to a personal health problem — cheap, durable brand moat (Ellsworth gut health, Wolf sodium, Cohen Pedialyte).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>ONE concentrated trial-generation tactic, executed obsessively, before broad spend.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>Sell-in on DATA (velocity/repurchase), not flavour — the single most repeated lever.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>Sequenced channel ladder — natural/DTC → specialty → grocery → mass → club; never skip rungs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>Strategic-investor signal early (Oza, Li Ka-shing, celebrity rounds) — capital + credibility + distribution.</t>
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Phase 0 (pre-launch)</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1 (launch, yr 0–1)</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Phase 2 (scale, yr 1–3)</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Phase 3 (maturity/exit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="92" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Poppi</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>2015–16: gut-health insight; ~$90k self-funded; “Mother Beverage” glass bottles</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Farmers markets → Whole Foods regional; ~$500k in 18 mo; Shark Tank 2018 ($400k/25% Oza)</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>2020 rebrand to cans + national launch (Mar 2020); TikTok creator seeding; #1 Amazon soda 2023</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>2024 first Super Bowl ad; &gt;$500M rev; PepsiCo $1.95B closed May 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>OLIPOP</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Founders' prior brand Obi; $100k seed; nostalgic-soda + fiber insight</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Late 2018: 40 NorCal indie grocers; ~$852k yr 1; ~$2.49/can; gut-health science story</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Natural → conventional → mass; “astronomical repurchase” sell-in; $73.4M (2022); $39.7M Series B</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>$200M (2023)→$400M+ (2024); 7,000+ grocers; $50M @ $1.85B (Feb 2025); INDEPENDENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="92" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>LMNT</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>2018–19: keto-sodium insight; Robb Wolf + Ketogains; high-sodium no-sugar formula</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Late 2019 DTC-only; free Sample Pack (pay ~$5 shipping); profitable yr 1 (claim)</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Podcast sponsorships (Huberman et al., ~10k episodes); ~$50M run-rate by Q1 2022</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>$206M sales (2023, SEC); private, founder-controlled; selective retail; NO exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="92" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Liquid I.V.</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>2012: adults using Pedialyte insight; WHO-ORS-based CTT formula</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Whole Foods “Supplier 101”; founder samples weekly → 12 WF by 2015</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Costco roadshow sampling; Emerson Group (2015); ~$100M within 5 yrs</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Unilever Sept 2020 (~$500M est.); 30k→80k stores; $1B+ brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="92" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Celsius</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>2004 (Elite FX); near-bankruptcy/delisting ~2010 — over-marketing before PMF</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Turnaround 2012; Li Ka-shing $15M (2015); NASDAQ uplisting 2017 (~$36M rev)</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Amazon ~15–20% of sales (2020); Target DSD; 100k+ doors by 2021</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>PepsiCo $550M/8.5% (2022) → ~#3 energy; bought Alani Nu $1.8B (2025)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>Category-creation language to escape commodity comparison and hold a $2–$3/can premium.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>Endgame split: strategic exit (Poppi/Liquid I.V./Celsius) vs independence (OLIPOP/LMNT) — both valid; scale eventually needs a partner or heavy capital.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>SIX FAILURE MODES</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>Over-distribution before product-market fit — Celsius's own ~2010 near-bankruptcy is the canonical case. Velocity must precede footprint.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>Undercapitalized / capital-intensive DTC — beverages are heavy physical goods; ~90% of beverage startups failed historically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>Premium price with no defensible moat / thin claims — ~32% of consumers cite “too expensive”; premium needs credible function + repeat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>Trial without retention — sampling/virality wasted if repurchase is weak (inverse of the OLIPOP/Liquid I.V. data story).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>Brand/tone missteps at scale — Poppi's 2025 vending stunt; tactics must evolve with brand stage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>Wrong timing / flavour failure — the baseline reasons ~85% of new CPG products fail within 2 years.</t>
-        </is>
-      </c>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>DATE TRAP: Poppi's FIRST Super Bowl ad = 2024 (LVIII); the vending-machine controversy = the 2025 (LIX) return. Many secondary sources conflate them.</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="n"/>
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A12:B12"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
@@ -6333,21 +6538,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="114" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Financial Outcomes &amp; M&amp;A Comps</t>
+          <t>Success Patterns &amp; Failure Modes</t>
         </is>
       </c>
       <c r="N1" s="95" t="inlineStr">
@@ -6357,373 +6558,154 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Revenue trajectory</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Funding / valuation</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Exit / status</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Category share</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>Profitability</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Poppi</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>$13M(20)→$65M(22)→$100M+(23)→~$500M(24)</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>VC-backed pre-exit</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>PepsiCo $1.95B (net ~$1.65B), May 2025</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>~38% modern soda (24)</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>OLIPOP</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>$852k(18)→$200M+(23)→$400M+(24)</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>$50M Series C @ $1.85B (Feb 2025, JPM)</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>~32.7% modern soda (24)</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>Cash-profitable early 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>LMNT</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>$206M sales (2023, SEC)</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Reg CF / Republic</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>~20% net margin (2023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Liquid I.V.</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>~$100M in 5 yrs → ~$200M exit → $1B+ now</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Unilever Sept 2020 (~$500M est.)</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>Unilever +$80M MO plant</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Nuun</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>$10M+ (2013)</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>TSG Consumer (2017)</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Nestlé HS July 2021 (undisclosed)</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>#1 run/bike/outdoor</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Celsius</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>multi-$B (public)</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Li Ka-shing $15M (2015)</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Public; PepsiCo $550M (2022); bought Alani Nu $1.8B</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>~#3 US energy (~11.5%)</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>Profitable</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Health-Ade</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>~$250M/yr retail</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>~$54M raised</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Generous Brands $500M</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Alani Nu</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>~$595M (2024)</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Congo Brands</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Celsius $1.8B (2025)</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Vital Proteins</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>(in Nestlé HS)</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Nestlé (full 2022)</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Aura Bora</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>$12M (2024)</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>~$22M raised</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>Majority to Next In Natural (2025)</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>M&amp;A READ: Strategics now own most winners — PepsiCo (Poppi, Celsius stake), Unilever (Liquid I.V., Olly), Nestlé (Vital Proteins, Nuun), KDP (Ghost). For a challenger the realistic endgame is acquisition, not durable independence — but Coke's organic Simply Pop shows incumbents may CLONE rather than buy, compressing the premium. OLIPOP (independent, $1.85B) is the counter-example.</t>
-        </is>
-      </c>
-      <c r="B14" s="34" t="n"/>
-      <c r="C14" s="34" t="n"/>
-      <c r="D14" s="34" t="n"/>
-      <c r="E14" s="34" t="n"/>
-      <c r="F14" s="35" t="n"/>
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>SEVEN SUCCESS PATTERNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Founder-authority insight tied to a personal health problem — cheap, durable brand moat (Ellsworth gut health, Wolf sodium, Cohen Pedialyte).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>ONE concentrated trial-generation tactic, executed obsessively, before broad spend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Sell-in on DATA (velocity/repurchase), not flavour — the single most repeated lever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Sequenced channel ladder — natural/DTC → specialty → grocery → mass → club; never skip rungs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Strategic-investor signal early (Oza, Li Ka-shing, celebrity rounds) — capital + credibility + distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Category-creation language to escape commodity comparison and hold a $2–$3/can premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Endgame split: strategic exit (Poppi/Liquid I.V./Celsius) vs independence (OLIPOP/LMNT) — both valid; scale eventually needs a partner or heavy capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>SIX FAILURE MODES</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Over-distribution before product-market fit — Celsius's own ~2010 near-bankruptcy is the canonical case. Velocity must precede footprint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Undercapitalized / capital-intensive DTC — beverages are heavy physical goods; ~90% of beverage startups failed historically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Premium price with no defensible moat / thin claims — ~32% of consumers cite “too expensive”; premium needs credible function + repeat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>Trial without retention — sampling/virality wasted if repurchase is weak (inverse of the OLIPOP/Liquid I.V. data story).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>Brand/tone missteps at scale — Poppi's 2025 vending stunt; tactics must evolve with brand stage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Wrong timing / flavour failure — the baseline reasons ~85% of new CPG products fail within 2 years.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
@@ -6748,7 +6730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7179,6 +7161,18 @@
       <c r="B37" s="58" t="inlineStr">
         <is>
           <t>MÜV's direct electrolyte/sparkling rivals vs category-adjacent context (reconciliation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="94" t="inlineStr">
+        <is>
+          <t>Scenario Comparison</t>
+        </is>
+      </c>
+      <c r="B38" s="58" t="inlineStr">
+        <is>
+          <t>All 3 scenarios side-by-side (per-can, EBITDA, break-even) + chart</t>
         </is>
       </c>
     </row>
@@ -7221,6 +7215,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -7242,6 +7237,421 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Financial Outcomes &amp; M&amp;A Comps</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Revenue trajectory</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Funding / valuation</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Exit / status</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Category share</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Poppi</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>$13M(20)→$65M(22)→$100M+(23)→~$500M(24)</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>VC-backed pre-exit</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>PepsiCo $1.95B (net ~$1.65B), May 2025</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>~38% modern soda (24)</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>OLIPOP</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>$852k(18)→$200M+(23)→$400M+(24)</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>$50M Series C @ $1.85B (Feb 2025, JPM)</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>~32.7% modern soda (24)</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Cash-profitable early 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>LMNT</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>$206M sales (2023, SEC)</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Reg CF / Republic</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>~20% net margin (2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Liquid I.V.</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>~$100M in 5 yrs → ~$200M exit → $1B+ now</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Unilever Sept 2020 (~$500M est.)</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Unilever +$80M MO plant</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Nuun</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>$10M+ (2013)</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>TSG Consumer (2017)</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Nestlé HS July 2021 (undisclosed)</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>#1 run/bike/outdoor</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Celsius</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>multi-$B (public)</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Li Ka-shing $15M (2015)</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Public; PepsiCo $550M (2022); bought Alani Nu $1.8B</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>~#3 US energy (~11.5%)</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Profitable</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Health-Ade</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>~$250M/yr retail</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>~$54M raised</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Generous Brands $500M</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Alani Nu</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>~$595M (2024)</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Congo Brands</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Celsius $1.8B (2025)</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Vital Proteins</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>(in Nestlé HS)</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Nestlé (full 2022)</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Aura Bora</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>$12M (2024)</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>~$22M raised</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Majority to Next In Natural (2025)</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>M&amp;A READ: Strategics now own most winners — PepsiCo (Poppi, Celsius stake), Unilever (Liquid I.V., Olly), Nestlé (Vital Proteins, Nuun), KDP (Ghost). For a challenger the realistic endgame is acquisition, not durable independence — but Coke's organic Simply Pop shows incumbents may CLONE rather than buy, compressing the premium. OLIPOP (independent, $1.85B) is the counter-example.</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="n"/>
+      <c r="C14" s="34" t="n"/>
+      <c r="D14" s="34" t="n"/>
+      <c r="E14" s="34" t="n"/>
+      <c r="F14" s="35" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="003E5C76"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -7473,7 +7883,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="003E5C76"/>
@@ -7902,7 +8312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001E7D32"/>
@@ -8454,7 +8864,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001E7D32"/>
@@ -8984,7 +9394,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001E7D32"/>
@@ -9432,7 +9842,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E7D8A"/>
@@ -10234,7 +10644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B45309"/>
@@ -10385,7 +10795,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C9A227"/>
@@ -10680,7 +11090,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C9A227"/>
@@ -10913,190 +11323,6 @@
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00B45309"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Phased Launch Plan (0–18 months)</t>
-        </is>
-      </c>
-      <c r="N1" s="95" t="inlineStr">
-        <is>
-          <t>↩ Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Phase</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Timing</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Objectives</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Key workstreams</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Success gate</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="80" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Phase 0 — Foundation</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Months 0–3</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Lock product, claims, regulatory pathway, co-pack</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Finalize formula &amp; collagen dose; regulatory-counsel claim opinion (Supplemented Foods); co-packer quote &amp; MOQ; bilingual + Bill 96 artwork; brand/positioning</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory sign-off on claim set + artwork approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="80" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1 — Beachhead</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Months 3–9</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Prove velocity &amp; repeat in a contained beachhead</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Costco CA roadshows + Amazon.ca + Well.ca/Natura + Organika pharmacy/health-food base; podcast + reactive social; sampling</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>Repeat rate + velocity above category benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Phase 2 — Scale</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Months 9–18</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Earn conventional grocery on proven data</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Sell-in to Loblaw/Sobeys/Metro on velocity data; distributor (UNFI CA / Tree of Life); managed trade spend; add SKUs on repeat data</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>National listings won on data, not discounts</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Phase 3 — Defend &amp; extend</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>18 mo+</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Category leadership &amp; optionality</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Format/flavour extensions; deepen moat; evaluate strategic-partner vs independent scale</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Profitable contribution + exit optionality</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
@@ -11305,21 +11531,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Risk Register</t>
+          <t>Phased Launch Plan (0–18 months)</t>
         </is>
       </c>
       <c r="N1" s="95" t="inlineStr">
@@ -11328,409 +11553,144 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Likelihood × Impact (H/M/L). Ranked by exposure</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Likelihood</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Mitigation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Collagen efficacy / claims liability (2025 meta-analysis; Poppi-style dose-insufficiency suit)</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory/Legal</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>Dose to efficacy (2.5g+); structure/function-safe language; substantiation files; lead with gut/hydration not beauty</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Strategic-owned competition (Nestlé owns Vital Proteins; PepsiCo/Unilever firepower)</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E6" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>Compete on Canadian-made + domestic cost edge + Organika collagen credibility; niche beachhead before they react</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Canada claim/label pathway misread (food vs NHP; SFCI; collagen caution)</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory</t>
-        </is>
-      </c>
-      <c r="D7" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory-counsel opinion before artwork; design to Supplemented Foods framework; caffeine-free</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Over-distribution before product-market fit</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>Execution</t>
-        </is>
-      </c>
-      <c r="D8" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E8" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>Prove velocity/repeat in beachhead before national; gate Phase 2 on data</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Slotting / trade-spend cash burn</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E9" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Use free-fill over cash slotting; 35–45% trade-spend budget; Code of Conduct leverage on arbitrary fees</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Thin differentiation / shelf saturation (prebiotic shelf filling fast)</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D10" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E10" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Defensible spec (fiber + collagen dose) + function stacking; Canadian-made story</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Private-label encroachment (~$277B, ~21% share, growing 2×)</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D11" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E11" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Brand equity + clinical-grade ingredients retailers can't easily copy</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>DTC CAC / heavy-ship economics if DTC-led</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D12" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E12" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>Lead retail/beachhead not paid DTC; subscription + sampling only</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Co-packer capacity / collagen sourcing / cost inflation</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="D13" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E13" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>Lock co-pack capacity early; qualify 2nd collagen supplier; hedge raws</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>FX / tariff / freight premium on cross-border inputs</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D14" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E14" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>Domestic CA co-pack; monitor tariff status post-Dec 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>GLP-1 demand shift away from sweet/snack</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Macro</t>
-        </is>
-      </c>
-      <c r="D15" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E15" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Low-cal, fiber, protein, hydration positioning aligns with GLP-1 users</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>Brand/tone misstep at scale</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="D16" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E16" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>Evolve tactics with stage; avoid Poppi-style stunts once mainstream</t>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Objectives</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Key workstreams</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Success gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Phase 0 — Foundation</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Months 0–3</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Lock product, claims, regulatory pathway, co-pack</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Finalize formula &amp; collagen dose; regulatory-counsel claim opinion (Supplemented Foods); co-packer quote &amp; MOQ; bilingual + Bill 96 artwork; brand/positioning</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory sign-off on claim set + artwork approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1 — Beachhead</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Months 3–9</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Prove velocity &amp; repeat in a contained beachhead</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Costco CA roadshows + Amazon.ca + Well.ca/Natura + Organika pharmacy/health-food base; podcast + reactive social; sampling</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Repeat rate + velocity above category benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Phase 2 — Scale</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Months 9–18</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Earn conventional grocery on proven data</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Sell-in to Loblaw/Sobeys/Metro on velocity data; distributor (UNFI CA / Tree of Life); managed trade spend; add SKUs on repeat data</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>National listings won on data, not discounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Phase 3 — Defend &amp; extend</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>18 mo+</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Category leadership &amp; optionality</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Format/flavour extensions; deepen moat; evaluate strategic-partner vs independent scale</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Profitable contribution + exit optionality</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
@@ -11755,6 +11715,456 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Likelihood × Impact (H/M/L). Ranked by exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Likelihood</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Mitigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Collagen efficacy / claims liability (2025 meta-analysis; Poppi-style dose-insufficiency suit)</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory/Legal</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Dose to efficacy (2.5g+); structure/function-safe language; substantiation files; lead with gut/hydration not beauty</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Strategic-owned competition (Nestlé owns Vital Proteins; PepsiCo/Unilever firepower)</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Compete on Canadian-made + domestic cost edge + Organika collagen credibility; niche beachhead before they react</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Canada claim/label pathway misread (food vs NHP; SFCI; collagen caution)</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory-counsel opinion before artwork; design to Supplemented Foods framework; caffeine-free</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Over-distribution before product-market fit</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Prove velocity/repeat in beachhead before national; gate Phase 2 on data</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Slotting / trade-spend cash burn</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Use free-fill over cash slotting; 35–45% trade-spend budget; Code of Conduct leverage on arbitrary fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Thin differentiation / shelf saturation (prebiotic shelf filling fast)</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Defensible spec (fiber + collagen dose) + function stacking; Canadian-made story</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Private-label encroachment (~$277B, ~21% share, growing 2×)</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Brand equity + clinical-grade ingredients retailers can't easily copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>DTC CAC / heavy-ship economics if DTC-led</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Lead retail/beachhead not paid DTC; subscription + sampling only</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Co-packer capacity / collagen sourcing / cost inflation</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Lock co-pack capacity early; qualify 2nd collagen supplier; hedge raws</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>FX / tariff / freight premium on cross-border inputs</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Domestic CA co-pack; monitor tariff status post-Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>GLP-1 demand shift away from sweet/snack</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Low-cal, fiber, protein, hydration positioning aligns with GLP-1 users</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Brand/tone misstep at scale</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Evolve tactics with stage; avoid Poppi-style stunts once mainstream</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00B45309"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12048,7 +12458,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -12572,7 +12982,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C9A227"/>
@@ -12910,7 +13320,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -14718,6 +15128,309 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Scenario Comparison — Conservative · Base · Aggressive</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Full envelope of the Financial Model, computed for all three scenarios (edit source assumptions on ‘Financial Model’)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="74" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="74" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="C4" s="74" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D4" s="74" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="103" t="inlineStr">
+        <is>
+          <t>List price / can</t>
+        </is>
+      </c>
+      <c r="B5" s="80" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="C5" s="80" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="D5" s="80" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="103" t="inlineStr">
+        <is>
+          <t>COGS / can</t>
+        </is>
+      </c>
+      <c r="B6" s="80" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C6" s="80" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="D6" s="80" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="103" t="inlineStr">
+        <is>
+          <t>Net revenue / can</t>
+        </is>
+      </c>
+      <c r="B7" s="80" t="n">
+        <v>1.672636</v>
+      </c>
+      <c r="C7" s="80" t="n">
+        <v>1.928225</v>
+      </c>
+      <c r="D7" s="80" t="n">
+        <v>2.234584</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="103" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B8" s="104" t="n">
+        <v>0.2825695489036468</v>
+      </c>
+      <c r="C8" s="104" t="n">
+        <v>0.4554577396310078</v>
+      </c>
+      <c r="D8" s="104" t="n">
+        <v>0.5748649413045113</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="59" t="inlineStr">
+        <is>
+          <t>Contribution / can</t>
+        </is>
+      </c>
+      <c r="B9" s="105" t="n">
+        <v>0.05447700000000022</v>
+      </c>
+      <c r="C9" s="105" t="n">
+        <v>0.4925800000000002</v>
+      </c>
+      <c r="D9" s="105" t="n">
+        <v>0.9493963999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="103" t="inlineStr">
+        <is>
+          <t>Break-even units (Yr-1 load)</t>
+        </is>
+      </c>
+      <c r="B10" s="106" t="n">
+        <v>8260366.760284123</v>
+      </c>
+      <c r="C10" s="106" t="n">
+        <v>1522595.314466685</v>
+      </c>
+      <c r="D10" s="106" t="n">
+        <v>1369291.056928381</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="103" t="inlineStr">
+        <is>
+          <t>Year-1 units</t>
+        </is>
+      </c>
+      <c r="B11" s="106" t="n">
+        <v>31200</v>
+      </c>
+      <c r="C11" s="106" t="n">
+        <v>78000</v>
+      </c>
+      <c r="D11" s="106" t="n">
+        <v>210600</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="57" t="inlineStr">
+        <is>
+          <t>Year-1 EBITDA</t>
+        </is>
+      </c>
+      <c r="B12" s="107" t="n">
+        <v>-448300.3176</v>
+      </c>
+      <c r="C12" s="107" t="n">
+        <v>-711578.76</v>
+      </c>
+      <c r="D12" s="107" t="n">
+        <v>-1100057.11816</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="103" t="inlineStr">
+        <is>
+          <t>Year-3 net revenue</t>
+        </is>
+      </c>
+      <c r="B13" s="108" t="n">
+        <v>1065469.132</v>
+      </c>
+      <c r="C13" s="108" t="n">
+        <v>3008031</v>
+      </c>
+      <c r="D13" s="108" t="n">
+        <v>9586365.359999999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="109" t="inlineStr">
+        <is>
+          <t>Year-3 EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="73" t="n">
+        <v>-365298.1509999998</v>
+      </c>
+      <c r="C14" s="73" t="n">
+        <v>118424.8000000004</v>
+      </c>
+      <c r="D14" s="73" t="n">
+        <v>2972910.555999999</v>
+      </c>
+    </row>
+    <row r="17" hidden="1">
+      <c r="A17" s="41" t="inlineStr">
+        <is>
+          <t>(chart data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" hidden="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Y3 Net Rev</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Y3 EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" hidden="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1065469</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-365298</v>
+      </c>
+    </row>
+    <row r="20" hidden="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3008031</v>
+      </c>
+      <c r="C20" t="n">
+        <v>118425</v>
+      </c>
+    </row>
+    <row r="21" hidden="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>9586365</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2972911</v>
+      </c>
+    </row>
+    <row r="34" ht="52" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>Read: the Base case is the planning anchor; Conservative shows the downside if velocity/doors lag and costs run high; Aggressive shows the ceiling if the sparkling wedge + Costco beachhead over-deliver. All figures are illustrative — edit the yellow inputs on ‘Financial Model’ (the active scenario there drives the interactive P&amp;L; this tab always shows all three).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="0014304F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -14833,7 +15546,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E7D8A"/>
@@ -15585,7 +16298,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E7D8A"/>
@@ -15837,231 +16550,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="002E7D8A"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
-    <col width="74" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Consumer Segmentation &amp; The Collagen Buyer</t>
-        </is>
-      </c>
-      <c r="N1" s="95" t="inlineStr">
-        <is>
-          <t>↩ Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Dimension</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Detail &amp; evidence</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Demand engine</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Gen Z + Millennials</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>~80% of Gen Z, ~75% of Millennials consume functional beverages regularly; 36% of adults but 41%+ of wellness spend (McKinsey). US wellness market $480B (2024).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Gender skew (category)</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Female-led growth</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Women = fastest-growing segment (~5.3% growth); over-index on probiotic/fortified. Hard female-% split is paywalled — DATA GAP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Collagen / BFW buyer</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Women 25–45</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Women = 68.4% of beauty-from-within drink revenue (2024); buy anti-aging, hydration, hair/nail outcomes; clinically-backed claims drive repeat/subscription.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Efficacy &amp; skepticism</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>RISK</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>2025 AJM systematic review/meta-analysis: NO clinical evidence collagen prevents/treats skin aging; industry-funded trials showed benefit, independent ones did not. Positive studies used 2.5–10g/day, effect at 4–8 wks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Willingness to pay</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Attribute-gated</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Younger consumers are price-conscious AND premium-willing for a named function / clean label / brand-community. Premiumization is real but not blanket.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>RETAILER / CLUB BUYER CRITERIA (what gets a new functional bev listed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>Criterion</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>What buyers actually want</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Velocity</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Gating metric — will the SKU turn fast enough to earn its facing</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Repeat rate</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>Buyers discount discount-driven velocity; they want durable repeat &amp; customer-level margin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Margin / trade support</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Plan 35–45% trade spend in early scale; slotting, promo, free-fill</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>Differentiation + demand-gen</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>Category-builder story + brand-funded marketing (the Poppi/OLIPOP social-first benchmark)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>IMPLICATION: MUV should dose collagen to a defensible level (2.5g+), lead with gut/hydration function, and prove repeat rate in a beachhead before pitching national buyers. The collagen efficacy debate makes substantiation files and structure/function-safe language mandatory.</t>
-        </is>
-      </c>
-      <c r="B16" s="34" t="n"/>
-      <c r="C16" s="35" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A10:C10"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
 </file>
--- a/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
+++ b/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
@@ -59,7 +59,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -227,6 +227,32 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0014304F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001155CC"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="16">
     <fill>
@@ -306,7 +332,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -386,11 +412,44 @@
         <color rgb="00FFFFFF"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00FFFFFF"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00FFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="00FFFFFF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00FFFFFF"/>
+      </left>
+      <right style="medium">
+        <color rgb="00FFFFFF"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00FFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -731,6 +790,51 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="14" fillId="13" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="14" fillId="13" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="13" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="14" fillId="13" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="13" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="13" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1364,6 +1468,247 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Electrolyte positioning — Sodium (mg) vs Price/serving</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <scatterChart>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>LMNT</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="9"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'MÜV Peer Set'!$B$27</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'MÜV Peer Set'!$C$27</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Liquid I.V.</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="9"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'MÜV Peer Set'!$B$28</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'MÜV Peer Set'!$C$28</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Nuun</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="9"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'MÜV Peer Set'!$B$29</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'MÜV Peer Set'!$C$29</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <v>Organika sachets</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:noFill/>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="9"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <xVal>
+            <numRef>
+              <f>'MÜV Peer Set'!$B$30</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'MÜV Peer Set'!$C$30</f>
+            </numRef>
+          </yVal>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </scatterChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Sodium mg/serving</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Price/serving ($)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>MÜV model</author>
+  </authors>
+  <commentList>
+    <comment ref="C4" authorId="0" shapeId="0">
+      <text>
+        <t>Pick Conservative / Base / Aggressive. The whole P&amp;L, break-even and sensitivity recompute from this one cell.</t>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0">
+      <text>
+        <t>Shelf price per can. Edit per scenario in cols C/D/E.</t>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0" shapeId="0">
+      <text>
+        <t>All-in cost/can (liquid+can+co-pack). Remember freight/duty are extra.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1489,6 +1834,33 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="3060000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1847,7 +2219,11 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="22" customHeight="1"/>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="121" t="n"/>
+      <c r="C7" s="121" t="n"/>
+      <c r="D7" s="121" t="n"/>
+    </row>
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="112" t="inlineStr">
         <is>
@@ -1872,7 +2248,11 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="22" customHeight="1"/>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="121" t="n"/>
+      <c r="C11" s="121" t="n"/>
+      <c r="D11" s="121" t="n"/>
+    </row>
     <row r="13" ht="22" customHeight="1">
       <c r="B13" s="112" t="inlineStr">
         <is>
@@ -1897,7 +2277,11 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1"/>
+    <row r="15" ht="22" customHeight="1">
+      <c r="B15" s="121" t="n"/>
+      <c r="C15" s="121" t="n"/>
+      <c r="D15" s="121" t="n"/>
+    </row>
     <row r="17" ht="22" customHeight="1">
       <c r="B17" s="112" t="inlineStr">
         <is>
@@ -1922,7 +2306,11 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1"/>
+    <row r="19" ht="22" customHeight="1">
+      <c r="B19" s="121" t="n"/>
+      <c r="C19" s="121" t="n"/>
+      <c r="D19" s="121" t="n"/>
+    </row>
     <row r="21" ht="22" customHeight="1">
       <c r="B21" s="112" t="inlineStr">
         <is>
@@ -1947,13 +2335,20 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="22" customHeight="1"/>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="121" t="n"/>
+      <c r="C23" s="121" t="n"/>
+      <c r="D23" s="121" t="n"/>
+    </row>
     <row r="25" ht="34" customHeight="1">
       <c r="B25" s="119" t="inlineStr">
         <is>
           <t>Verified anchor: MÜV Sparkling Electrolytes is a ready-to-drink sparkling CAN (SKU 4338), food-regulated in Canada. Gold tabs are interactive. Every tab has a “↩ Home” link (top-right) back to this page.</t>
         </is>
       </c>
+      <c r="C25" s="34" t="n"/>
+      <c r="D25" s="34" t="n"/>
+      <c r="E25" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -3150,7 +3545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3690,6 +4085,90 @@
       <c r="E22" s="34" t="n"/>
       <c r="F22" s="34" t="n"/>
       <c r="G22" s="35" t="n"/>
+    </row>
+    <row r="25" hidden="1">
+      <c r="A25" s="41" t="inlineStr">
+        <is>
+          <t>Positioning: sodium (mg) vs price/serving — data</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" hidden="1">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sodium</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" hidden="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LMNT</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="28" hidden="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Liquid I.V.</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>500</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="29" hidden="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Nuun</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>300</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="30" hidden="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Organika sachets</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>440</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" hidden="1"/>
+    <row r="32" hidden="1">
+      <c r="A32" s="133" t="inlineStr">
+        <is>
+          <t>MÜV sodium/serving TBD (confirm on-can) — plot when known. Aim: daily-wellness zone (moderate sodium, mid price).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3706,6 +4185,7 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -13028,6 +13508,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -13051,7 +13532,7 @@
           <t>PepsiCo — Poppi acquisition ($1.95B, closed May 2025)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="134" t="inlineStr">
         <is>
           <t>pepsico.com/newsroom</t>
         </is>
@@ -13068,7 +13549,7 @@
           <t>Poppi $8.9M gut-health class-action settlement (final approval Apr 2026)</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="135" t="inlineStr">
         <is>
           <t>classaction.org; bevnet.com; axios.com</t>
         </is>
@@ -13085,7 +13566,7 @@
           <t>OLIPOP $50M Series C @ $1.85B; revenue; profitability</t>
         </is>
       </c>
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="134" t="inlineStr">
         <is>
           <t>cnbc.com; fooddive.com; bevindustry.com</t>
         </is>
@@ -13153,7 +13634,7 @@
           <t>Liquid I.V. Costco national launch (2019, ~516 whs); Unilever acq. Sept 2020</t>
         </is>
       </c>
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="134" t="inlineStr">
         <is>
           <t>liquid-iv.com; unilever.com; bevnet.com</t>
         </is>
@@ -13170,7 +13651,7 @@
           <t>Nuun — Nestlé Health Science acquisition (July 2021)</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="135" t="inlineStr">
         <is>
           <t>nestle.com; businesswire.com</t>
         </is>
@@ -13187,7 +13668,7 @@
           <t>Vital Proteins sparkling ($2.50/can, VERISOL); Nestlé ownership</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
+      <c r="B13" s="134" t="inlineStr">
         <is>
           <t>fooddive.com; wwd.com; foodbusinessnews.net</t>
         </is>
@@ -13204,7 +13685,7 @@
           <t>Celsius — PepsiCo $550M/8.5% (2022); Alani Nu $1.8B (2025)</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="135" t="inlineStr">
         <is>
           <t>bevnet.com; bloomberg.com; businesswire.com</t>
         </is>
@@ -13221,7 +13702,7 @@
           <t>Health-Ade — Generous Brands $500M; $4M kombucha settlement</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
+      <c r="B15" s="134" t="inlineStr">
         <is>
           <t>fooddive.com; bursor.com</t>
         </is>
@@ -13238,7 +13719,7 @@
           <t>Collagen efficacy — 2025 systematic review/meta-analysis (no proven skin benefit; funding bias)</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="135" t="inlineStr">
         <is>
           <t>Am. Journal of Medicine; nutraingredients.com</t>
         </is>
@@ -13289,7 +13770,7 @@
           <t>Channel economics (Amazon fees, Costco margin, DTC CAC, slotting, distributor)</t>
         </is>
       </c>
-      <c r="B19" s="12" t="inlineStr">
+      <c r="B19" s="134" t="inlineStr">
         <is>
           <t>sellingpartners.aboutamazon.com; massivemoats; eightx.co; balancedbusinessgroup.com</t>
         </is>
@@ -13306,7 +13787,7 @@
           <t>Canada — NHP vs Food classification (food-format guidance)</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="135" t="inlineStr">
         <is>
           <t>canada.ca Health Canada guidance</t>
         </is>
@@ -13323,7 +13804,7 @@
           <t>Canada — Supplemented Foods Regulations (in force Jul 2022; SFCI; Jan 2026)</t>
         </is>
       </c>
-      <c r="B21" s="12" t="inlineStr">
+      <c r="B21" s="134" t="inlineStr">
         <is>
           <t>canada.ca; inspection.canada.ca; fasken.com</t>
         </is>
@@ -13340,7 +13821,7 @@
           <t>Canada — collagen caution statement (FDR C.R.C. c.870)</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="135" t="inlineStr">
         <is>
           <t>laws.justice.gc.ca</t>
         </is>
@@ -13357,7 +13838,7 @@
           <t>Canada — caffeine 180mg cap (Prime Energy blocked)</t>
         </is>
       </c>
-      <c r="B23" s="12" t="inlineStr">
+      <c r="B23" s="134" t="inlineStr">
         <is>
           <t>canada.ca; stack3d.com</t>
         </is>
@@ -13374,7 +13855,7 @@
           <t>Canada — Bill 96 / OQLF packaging (Jun 2025)</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="135" t="inlineStr">
         <is>
           <t>mltaikins.com; stikeman.com</t>
         </is>
@@ -13408,7 +13889,7 @@
           <t>US brand Canada entry (Liquid I.V. 2023, Poppi Aug 2024, Celsius Jan 2024)</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="135" t="inlineStr">
         <is>
           <t>foodincanada.com; newswire.ca; prnewswire.com</t>
         </is>
@@ -13425,7 +13906,7 @@
           <t>Launch playbooks (Poppi/OLIPOP/LMNT/Liquid I.V./Celsius timelines)</t>
         </is>
       </c>
-      <c r="B27" s="12" t="inlineStr">
+      <c r="B27" s="134" t="inlineStr">
         <is>
           <t>fortune.com; entrepreneur.com; cnbc.com; inc.com; hubermanlab.com</t>
         </is>
@@ -13442,7 +13923,7 @@
           <t>Extended landscape (Culture Pop, Spindrift, Prime, Cure, etc.)</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="135" t="inlineStr">
         <is>
           <t>bevnet.com; techcrunch.com; prnewswire.com; wikipedia</t>
         </is>
@@ -13459,7 +13940,7 @@
           <t>Private label ~$277B, ~21% share</t>
         </is>
       </c>
-      <c r="B29" s="12" t="inlineStr">
+      <c r="B29" s="134" t="inlineStr">
         <is>
           <t>grocerydive.com; nielseniq.com</t>
         </is>
@@ -13476,7 +13957,7 @@
           <t>CPG failure rate ~85% in 2 years</t>
         </is>
       </c>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="B30" s="135" t="inlineStr">
         <is>
           <t>foodnavigator-usa.com; eightx.co</t>
         </is>
@@ -13487,6 +13968,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
@@ -13505,6 +13987,26 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -14910,13 +15412,14 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="62" t="inlineStr">
         <is>
           <t>Scenario (pick):</t>
         </is>
       </c>
-      <c r="C4" s="63" t="inlineStr">
+      <c r="C4" s="122" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
@@ -14938,6 +15441,13 @@
         <v/>
       </c>
     </row>
+    <row r="6">
+      <c r="F6" s="123" t="inlineStr">
+        <is>
+          <t>LEGEND</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="B7" s="11" t="inlineStr">
         <is>
@@ -14959,10 +15469,14 @@
           <t>Aggressive</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
+      <c r="F7" s="124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  edit me  </t>
+        </is>
+      </c>
+      <c r="G7" s="125">
+        <f> yellow input cell</f>
+        <v/>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
@@ -14971,17 +15485,22 @@
           <t>List price / can (CAD)</t>
         </is>
       </c>
-      <c r="C8" s="44" t="n">
+      <c r="C8" s="126" t="n">
         <v>3.29</v>
       </c>
-      <c r="D8" s="44" t="n">
+      <c r="D8" s="126" t="n">
         <v>3.49</v>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="126" t="n">
         <v>3.79</v>
       </c>
-      <c r="F8" s="67">
-        <f>CHOOSE($C$5,C8,D8,E8)</f>
+      <c r="F8" s="127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  formula  </t>
+        </is>
+      </c>
+      <c r="G8" s="125">
+        <f> calculated (locked)</f>
         <v/>
       </c>
     </row>
@@ -14991,13 +15510,13 @@
           <t>COGS / can (CAD)</t>
         </is>
       </c>
-      <c r="C9" s="44" t="n">
+      <c r="C9" s="126" t="n">
         <v>1.2</v>
       </c>
-      <c r="D9" s="44" t="n">
+      <c r="D9" s="126" t="n">
         <v>1.05</v>
       </c>
-      <c r="E9" s="44" t="n">
+      <c r="E9" s="126" t="n">
         <v>0.95</v>
       </c>
       <c r="F9" s="67">
@@ -15011,13 +15530,13 @@
           <t>Retailer margin %</t>
         </is>
       </c>
-      <c r="C10" s="45" t="n">
+      <c r="C10" s="128" t="n">
         <v>0.38</v>
       </c>
-      <c r="D10" s="45" t="n">
+      <c r="D10" s="128" t="n">
         <v>0.35</v>
       </c>
-      <c r="E10" s="45" t="n">
+      <c r="E10" s="128" t="n">
         <v>0.33</v>
       </c>
       <c r="F10" s="68">
@@ -15031,13 +15550,13 @@
           <t>Distributor margin %</t>
         </is>
       </c>
-      <c r="C11" s="45" t="n">
+      <c r="C11" s="128" t="n">
         <v>0.18</v>
       </c>
-      <c r="D11" s="45" t="n">
+      <c r="D11" s="128" t="n">
         <v>0.15</v>
       </c>
-      <c r="E11" s="45" t="n">
+      <c r="E11" s="128" t="n">
         <v>0.12</v>
       </c>
       <c r="F11" s="68">
@@ -15051,13 +15570,13 @@
           <t>Trade spend % of net</t>
         </is>
       </c>
-      <c r="C12" s="45" t="n">
+      <c r="C12" s="128" t="n">
         <v>0.25</v>
       </c>
-      <c r="D12" s="45" t="n">
+      <c r="D12" s="128" t="n">
         <v>0.2</v>
       </c>
-      <c r="E12" s="45" t="n">
+      <c r="E12" s="128" t="n">
         <v>0.15</v>
       </c>
       <c r="F12" s="68">
@@ -15071,13 +15590,13 @@
           <t>Cans per case</t>
         </is>
       </c>
-      <c r="C13" s="46" t="n">
+      <c r="C13" s="129" t="n">
         <v>12</v>
       </c>
-      <c r="D13" s="46" t="n">
+      <c r="D13" s="129" t="n">
         <v>12</v>
       </c>
-      <c r="E13" s="46" t="n">
+      <c r="E13" s="129" t="n">
         <v>12</v>
       </c>
       <c r="F13" s="69">
@@ -15091,13 +15610,13 @@
           <t>Doors — Year 1</t>
         </is>
       </c>
-      <c r="C14" s="51" t="n">
+      <c r="C14" s="130" t="n">
         <v>300</v>
       </c>
-      <c r="D14" s="51" t="n">
+      <c r="D14" s="130" t="n">
         <v>500</v>
       </c>
-      <c r="E14" s="51" t="n">
+      <c r="E14" s="130" t="n">
         <v>900</v>
       </c>
       <c r="F14" s="70">
@@ -15111,13 +15630,13 @@
           <t>Doors — Year 2</t>
         </is>
       </c>
-      <c r="C15" s="51" t="n">
+      <c r="C15" s="130" t="n">
         <v>1200</v>
       </c>
-      <c r="D15" s="51" t="n">
+      <c r="D15" s="130" t="n">
         <v>2000</v>
       </c>
-      <c r="E15" s="51" t="n">
+      <c r="E15" s="130" t="n">
         <v>3500</v>
       </c>
       <c r="F15" s="70">
@@ -15131,13 +15650,13 @@
           <t>Doors — Year 3</t>
         </is>
       </c>
-      <c r="C16" s="51" t="n">
+      <c r="C16" s="130" t="n">
         <v>3500</v>
       </c>
-      <c r="D16" s="51" t="n">
+      <c r="D16" s="130" t="n">
         <v>6000</v>
       </c>
-      <c r="E16" s="51" t="n">
+      <c r="E16" s="130" t="n">
         <v>11000</v>
       </c>
       <c r="F16" s="70">
@@ -15151,13 +15670,13 @@
           <t>Velocity Y1 (u/store/wk)</t>
         </is>
       </c>
-      <c r="C17" s="52" t="n">
+      <c r="C17" s="131" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="52" t="n">
+      <c r="D17" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="52" t="n">
+      <c r="E17" s="131" t="n">
         <v>4.5</v>
       </c>
       <c r="F17" s="71">
@@ -15171,13 +15690,13 @@
           <t>Velocity Y2 (u/store/wk)</t>
         </is>
       </c>
-      <c r="C18" s="52" t="n">
+      <c r="C18" s="131" t="n">
         <v>3</v>
       </c>
-      <c r="D18" s="52" t="n">
+      <c r="D18" s="131" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="52" t="n">
+      <c r="E18" s="131" t="n">
         <v>6</v>
       </c>
       <c r="F18" s="71">
@@ -15191,13 +15710,13 @@
           <t>Velocity Y3 (u/store/wk)</t>
         </is>
       </c>
-      <c r="C19" s="52" t="n">
+      <c r="C19" s="131" t="n">
         <v>3.5</v>
       </c>
-      <c r="D19" s="52" t="n">
+      <c r="D19" s="131" t="n">
         <v>5</v>
       </c>
-      <c r="E19" s="52" t="n">
+      <c r="E19" s="131" t="n">
         <v>7.5</v>
       </c>
       <c r="F19" s="71">
@@ -15211,13 +15730,13 @@
           <t>Marketing / year (CAD)</t>
         </is>
       </c>
-      <c r="C20" s="72" t="n">
+      <c r="C20" s="132" t="n">
         <v>150000</v>
       </c>
-      <c r="D20" s="72" t="n">
+      <c r="D20" s="132" t="n">
         <v>300000</v>
       </c>
-      <c r="E20" s="72" t="n">
+      <c r="E20" s="132" t="n">
         <v>600000</v>
       </c>
       <c r="F20" s="73">
@@ -15231,13 +15750,13 @@
           <t>Fixed overhead / year (CAD)</t>
         </is>
       </c>
-      <c r="C21" s="72" t="n">
+      <c r="C21" s="132" t="n">
         <v>250000</v>
       </c>
-      <c r="D21" s="72" t="n">
+      <c r="D21" s="132" t="n">
         <v>350000</v>
       </c>
-      <c r="E21" s="72" t="n">
+      <c r="E21" s="132" t="n">
         <v>500000</v>
       </c>
       <c r="F21" s="73">
@@ -15251,13 +15770,13 @@
           <t>Slotting (Year 1 one-time)</t>
         </is>
       </c>
-      <c r="C22" s="72" t="n">
+      <c r="C22" s="132" t="n">
         <v>50000</v>
       </c>
-      <c r="D22" s="72" t="n">
+      <c r="D22" s="132" t="n">
         <v>100000</v>
       </c>
-      <c r="E22" s="72" t="n">
+      <c r="E22" s="132" t="n">
         <v>200000</v>
       </c>
       <c r="F22" s="73">
@@ -15265,6 +15784,7 @@
         <v/>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="42" t="inlineStr">
         <is>
@@ -15327,6 +15847,7 @@
         <v/>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="42" t="inlineStr">
         <is>
@@ -15584,6 +16105,7 @@
         <v/>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="42" t="inlineStr">
         <is>
@@ -15646,6 +16168,7 @@
         <v/>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="42" t="inlineStr">
         <is>
@@ -15800,6 +16323,7 @@
         <v/>
       </c>
     </row>
+    <row r="60"/>
     <row r="61" ht="58" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
@@ -15815,6 +16339,7 @@
       <c r="H61" s="35" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="0"/>
   <mergeCells count="7">
     <mergeCell ref="A53:H53"/>
     <mergeCell ref="A24:H24"/>
@@ -15873,6 +16398,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
+++ b/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
@@ -1550,6 +1550,88 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>Break-even units by scenario (Yr-1 cost load ÷ contribution/can)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Scenario Comparison'!B38</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Scenario Comparison'!$A$39:$A$41</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Scenario Comparison'!$B$39:$B$41</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Electrolyte positioning — Sodium (mg) vs Price/serving</a:t>
             </a:r>
           </a:p>
@@ -1917,6 +1999,28 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -2237,7 +2341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:E25"/>
+  <dimension ref="B2:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2250,7 +2354,6 @@
     <col width="3" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="44" customHeight="1">
       <c r="B2" s="110" t="inlineStr">
         <is>
@@ -14875,7 +14978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -15187,9 +15290,137 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="42" t="inlineStr">
+        <is>
+          <t>REGULATORY &amp; FORMAT TERMS (Canada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="87" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="B29" s="58" t="inlineStr">
+        <is>
+          <t>Ready-to-drink — a finished beverage (e.g., a can), vs a powder/tablet to reconstitute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="89" t="inlineStr">
+        <is>
+          <t>NHP</t>
+        </is>
+      </c>
+      <c r="B30" s="60" t="inlineStr">
+        <is>
+          <t>Natural Health Product — Canadian licensed supplement category; bears an NPN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="87" t="inlineStr">
+        <is>
+          <t>NPN</t>
+        </is>
+      </c>
+      <c r="B31" s="58" t="inlineStr">
+        <is>
+          <t>Natural Product Number — 8-digit licence number on an NHP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="89" t="inlineStr">
+        <is>
+          <t>Supplemented Food</t>
+        </is>
+      </c>
+      <c r="B32" s="60" t="inlineStr">
+        <is>
+          <t>A food with added vitamins/minerals/amino acids beyond normal fortification, under the Supplemented Foods Regulations (in force 2022-07-21).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="87" t="inlineStr">
+        <is>
+          <t>SFFt</t>
+        </is>
+      </c>
+      <c r="B33" s="58" t="inlineStr">
+        <is>
+          <t>Supplemented Food Facts table — modified Nutrition Facts table with a 'Supplemented with' line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="89" t="inlineStr">
+        <is>
+          <t>SFCI</t>
+        </is>
+      </c>
+      <c r="B34" s="60" t="inlineStr">
+        <is>
+          <t>Supplemented Food Caution Identifier — the black-&amp;-white '!' identifier required when cautionary statements apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="87" t="inlineStr">
+        <is>
+          <t>ORS</t>
+        </is>
+      </c>
+      <c r="B35" s="58" t="inlineStr">
+        <is>
+          <t>Oral Rehydration Solution — clinical rehydration product; stays regulated as an NHP (carve-out from the electrolyte→food shift).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="89" t="inlineStr">
+        <is>
+          <t>Food–NHP interface</t>
+        </is>
+      </c>
+      <c r="B36" s="60" t="inlineStr">
+        <is>
+          <t>Health Canada guidance that classifies food-format products; format is not decisive — representation + claims are.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="87" t="inlineStr">
+        <is>
+          <t>Fibersol</t>
+        </is>
+      </c>
+      <c r="B37" s="58" t="inlineStr">
+        <is>
+          <t>A soluble prebiotic dietary fibre used in MÜV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="89" t="inlineStr">
+        <is>
+          <t>Bill 96 / OQLF</t>
+        </is>
+      </c>
+      <c r="B38" s="60" t="inlineStr">
+        <is>
+          <t>Quebec French-language packaging rules; generic/descriptive trademark terms need French.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A28:B28"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
@@ -17445,7 +17676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -17734,6 +17965,55 @@
       <c r="C34" s="34" t="n"/>
       <c r="D34" s="34" t="n"/>
       <c r="E34" s="35" t="n"/>
+    </row>
+    <row r="37" hidden="1">
+      <c r="A37" s="41" t="inlineStr">
+        <is>
+          <t>(break-even chart data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" hidden="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Break-even units</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" hidden="1">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>8260367</v>
+      </c>
+    </row>
+    <row r="40" hidden="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1522595</v>
+      </c>
+    </row>
+    <row r="41" hidden="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1369291</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
+++ b/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
@@ -14,36 +14,37 @@
     <sheet name="02 Executive Summary" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Dashboard" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Financial Model" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Scenario Comparison" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="03 Methodology" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="04 Market Sizing" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="05 Trends &amp; Macro" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="06 Consumer" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="07 Comparison Matrix" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="MÜV Peer Set" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="08 Extended Landscape" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="09 Channel &amp; Retail" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="10 Channel Economics" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="11 Formulation" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="12 Marketing" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="13 Launch Playbooks" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="14 Patterns &amp; Failures" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="15 Outcomes &amp; M&amp;A" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="16 SWOT" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="17 Scoring Model" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="18 Canada Market" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="19 Canada Regulatory" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Canada Regulatory v2" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Electrolyte BFY Deep-Dive" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="20 GTM Recommendation" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Go-NoGo Decision" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="Battlecards" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="21 Launch Plan" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="22 Risk Register" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="23 KPI Dashboard" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="24 Sources" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="Verification Log" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="25 Glossary" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="Assumptions Audit" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Scenario Comparison" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="03 Methodology" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="04 Market Sizing" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="05 Trends &amp; Macro" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="06 Consumer" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="07 Comparison Matrix" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="MÜV Peer Set" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="08 Extended Landscape" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="09 Channel &amp; Retail" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="10 Channel Economics" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="11 Formulation" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="12 Marketing" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="13 Launch Playbooks" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="14 Patterns &amp; Failures" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="15 Outcomes &amp; M&amp;A" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="16 SWOT" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="17 Scoring Model" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="18 Canada Market" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="19 Canada Regulatory" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Canada Regulatory v2" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="Electrolyte BFY Deep-Dive" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="20 GTM Recommendation" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Go-NoGo Decision" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Battlecards" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="21 Launch Plan" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="22 Risk Register" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="23 KPI Dashboard" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="24 Sources" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="Verification Log" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="25 Glossary" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'🏠 Start Here'!$A$1:$E$25</definedName>
@@ -53,37 +54,37 @@
     <definedName name="_xlnm.Print_Area" localSheetId="4">'02 Executive Summary'!$A$1:$N$17</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Dashboard'!$A$1:$N$78</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Financial Model'!$A$1:$N$61</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Scenario Comparison'!$A$1:$N$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="8">'03 Methodology'!$A$1:$N$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="9">'04 Market Sizing'!$A$1:$N$27</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'05 Trends &amp; Macro'!$A$1:$N$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'06 Consumer'!$A$1:$N$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'07 Comparison Matrix'!$A$3:$L$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'07 Comparison Matrix'!$A$1:$N$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="13">'MÜV Peer Set'!$A$1:$N$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="14">'08 Extended Landscape'!$A$1:$N$50</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'09 Channel &amp; Retail'!$A$1:$N$13</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="16">'10 Channel Economics'!$A$1:$N$38</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="17">'11 Formulation'!$A$1:$N$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="18">'12 Marketing'!$A$1:$N$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="19">'13 Launch Playbooks'!$A$1:$N$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="20">'14 Patterns &amp; Failures'!$A$1:$N$18</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="21">'15 Outcomes &amp; M&amp;A'!$A$1:$N$14</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="22">'16 SWOT'!$A$1:$N$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="23">'17 Scoring Model'!$A$1:$N$14</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="24">'18 Canada Market'!$A$1:$N$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="25">'19 Canada Regulatory'!$A$1:$N$38</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="26">'Canada Regulatory v2'!$A$1:$N$31</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="27">'Electrolyte BFY Deep-Dive'!$A$1:$N$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="28">'20 GTM Recommendation'!$A$1:$N$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="29">'Go-NoGo Decision'!$A$1:$N$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="30">'Battlecards'!$A$1:$N$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="31">'21 Launch Plan'!$A$1:$N$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="32">'22 Risk Register'!$A$1:$N$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="33">'23 KPI Dashboard'!$A$1:$N$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="34">'24 Sources'!$A$1:$N$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="35">'Verification Log'!$A$1:$N$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="36">'25 Glossary'!$A$1:$N$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Scenario Comparison'!$A$1:$N$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'03 Methodology'!$A$1:$N$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'04 Market Sizing'!$A$1:$N$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'05 Trends &amp; Macro'!$A$1:$N$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'06 Consumer'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'07 Comparison Matrix'!$A$3:$L$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'07 Comparison Matrix'!$A$1:$N$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'MÜV Peer Set'!$A$1:$N$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'08 Extended Landscape'!$A$1:$N$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'09 Channel &amp; Retail'!$A$1:$N$13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'10 Channel Economics'!$A$1:$N$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="18">'11 Formulation'!$A$1:$N$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="19">'12 Marketing'!$A$1:$N$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="20">'13 Launch Playbooks'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="21">'14 Patterns &amp; Failures'!$A$1:$N$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="22">'15 Outcomes &amp; M&amp;A'!$A$1:$N$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="23">'16 SWOT'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="24">'17 Scoring Model'!$A$1:$N$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="25">'18 Canada Market'!$A$1:$N$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="26">'19 Canada Regulatory'!$A$1:$N$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="27">'Canada Regulatory v2'!$A$1:$N$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="28">'Electrolyte BFY Deep-Dive'!$A$1:$N$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="29">'20 GTM Recommendation'!$A$1:$N$11</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="30">'Go-NoGo Decision'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="31">'Battlecards'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="32">'21 Launch Plan'!$A$1:$N$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="33">'22 Risk Register'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="34">'23 KPI Dashboard'!$A$1:$N$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="35">'24 Sources'!$A$1:$N$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="36">'Verification Log'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="37">'25 Glossary'!$A$1:$N$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -97,7 +98,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -296,6 +297,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="17">
@@ -498,7 +505,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -905,6 +912,34 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2574,6 +2609,130 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0014304F"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="88" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Methodology &amp; Confidence Framework</t>
+        </is>
+      </c>
+      <c r="M1" s="95" t="inlineStr">
+        <is>
+          <t>🏠 Home</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="92" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Research design</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Six parallel research streams: (1) market sizing, (2) channel economics, (3) extended competitor sweep, (4) Canada market + regulatory, (5) launch-playbook teardowns, (6) consumer trends + risk. Each ran independent multi-source web research with per-claim citation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Source hierarchy</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Decision-grade → scanner data (Circana/SPINS), company/SEC filings (LMNT Reg CF), regulatory primary (Health Canada, CFIA, FDR), transaction/press releases. Directional → syndicated research-firm market sizes (Grand View, FMI, Mordor) which vary widely by category definition. Lowest → single secondary sources / social estimates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="92" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Confidence tagging</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Every load-bearing figure is tagged HARD / DIRECTIONAL / FLAG. Where sources conflict (collagen market size; prebiotic soda; adaptogen market) both figures are shown and the conflict flagged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="92" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Known limitations</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>(a) Many primary publisher pages (CNBC, Entrepreneur, Circana, canada.ca) block automated fetch (HTTP 403); figures were captured via search extracts of those same pages plus corroborating sources — re-verify load-bearing numbers from the cited URLs before external use. (b) Private-company margins and Canadian per-SKU listing fees are confidential; ranges are industry rules-of-thumb. (c) Female-skew % and licensed Circana/Mintel splits sit behind paywalls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="92" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>What would strengthen this</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Licensed Circana/SPINS pull for Canada; a regulatory-counsel opinion on the Supplemented-Foods claim set; primary interviews with 2–3 Canadian distributors (UNFI Canada, Tree of Life, Purity Life); a co-packer capacity/quote for a Canadian RTD line.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="002E7D8A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -3329,7 +3488,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E7D8A"/>
@@ -3589,7 +3748,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E7D8A"/>
@@ -3822,7 +3981,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="003E5C76"/>
@@ -4469,7 +4628,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C9A227"/>
@@ -5120,7 +5279,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="003E5C76"/>
@@ -6549,7 +6708,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="003E5C76"/>
@@ -6849,569 +7008,6 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A13:E13"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="003E5C76"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="68" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Channel Economics &amp; Margin Waterfall</t>
-        </is>
-      </c>
-      <c r="M1" s="95" t="inlineStr">
-        <is>
-          <t>🏠 Home</t>
-        </is>
-      </c>
-      <c r="N1" s="95" t="inlineStr">
-        <is>
-          <t>↩ Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Only Amazon fees, Costco margin &amp; DTC CAC are HARD; the rest are operator rules-of-thumb — model as ranges</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>MARGIN WATERFALL — canned functional beverage</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Line</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Typical value</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Unit COGS target</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>&lt; $1.00/unit (liquid+can+co-pack at scale)</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>12oz decorated can (component)</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>~$0.15/can at intro minimums</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Co-pack run (10,000 cases)</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>≈ $200,000; MOQ 2,000–5,000 cases/SKU</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Blended gross margin (early)</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>40–50%; aspiration 50–65% at scale</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>GM by channel</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Retail ~35–45%; DTC ~40–50% (before CAC/freight)</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>COGS warning</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Excluding freight/duty/co-pack overstates GM by 3–8 pts — the #1 error</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>CHANNEL TAKE-RATES (who takes margin off the top)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>Channel / cost</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Take / value</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Grocery (conventional)</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>~30–50% retailer margin; bev often 30–40%</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Natural/premium (Whole Foods)</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>45%+ (slower turns)</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Club (Costco)</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Max 14% markup (15% Kirkland); FY24 actual GM 10.92% — volume not margin play</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Distributor (general)</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>15–25% markup; UNFI avg ~13–14% (range 6–30%)</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>HARD-ish</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>DSD vs warehouse</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>DSD can save ~5–10% in fees vs UNFI/KeHE routing</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Broker</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>3–5% of net sales + often $5–10k/mo retainer</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>8–45% referral (most 15%) + FBA $3.73–$6.97/unit ($25+ heavy bev)</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>HARD (published)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>DTC CAC (food &amp; bev)</t>
-        </is>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>~$45–$53 (lowest vertical); supplements ~$89; shipping $8–15/order</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>HARD (benchmark)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>TRADE SPEND &amp; FEES</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Slotting fee</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>$250 → $250,000 by retailer/scope; ~$25,000/item regional cluster</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>Trade spend % of revenue</t>
-        </is>
-      </c>
-      <c r="B27" s="13" t="inlineStr">
-        <is>
-          <t>10–20% (emerging brands high end); US trade spend &gt;$200B, ~20% of gross, #2 P&amp;L line</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>HARD (aggregate)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>Free fill</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="inlineStr">
-        <is>
-          <t>1 free case/SKU/store on first order — cheaper substitute for slotting</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>RULE OF THUMB</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>LMNT subscription model</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>$200M+ rev 2023, ~20% net margin, 250k+ customers; free-8-pack (pay shipping) funnel</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>HARD (company/SEC)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>CANADA COST STACK (additive on US economics)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Item</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>Grocery concentration</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="inlineStr">
-        <is>
-          <t>Loblaw+Sobeys+Metro ≈ 80% w/ Walmart+Costco; all signed Grocery Code of Conduct (in force Jan 1, 2025)</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>Listing/slotting fees</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="inlineStr">
-        <is>
-          <t>Charged but NOT publicly disclosed; Code now lets suppliers challenge arbitrary fees — model at ≥ US slotting</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>No public $</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>Bilingual packaging</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="inlineStr">
-        <is>
-          <t>EN+FR mandatory; French ~2× longer; non-compliance fines up to $20,000; Bill 96 adds rules</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>HARD (regulatory)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>Distributors (CA)</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>UNFI Canada, Tree of Life Canada, Purity Life, Ecotrend</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
-        <is>
-          <t>HARD (existence)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>Freight/FX/duty</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="inlineStr">
-        <is>
-          <t>FX (US$1≈C$1.15+) + cross-border freight + duty; model as premium; local co-pack is the margin fix</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>Qualitative</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="46" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>DTC-for-beverage reality check: heavy to ship, low online AOV, CAC can exceed contribution. Historically ~90% of beverage startups fail; the survivable DTC model (LMNT) is subscription + free-sample acquisition + asset-light profitability — not paid-media scale.</t>
-        </is>
-      </c>
-      <c r="B38" s="34" t="n"/>
-      <c r="C38" s="34" t="n"/>
-      <c r="D38" s="35" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
@@ -7437,20 +7033,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Formulation &amp; Positioning — the claim that won</t>
+          <t>Channel Economics &amp; Margin Waterfall</t>
         </is>
       </c>
       <c r="M1" s="95" t="inlineStr">
@@ -7464,264 +7058,519 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Winning claim</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Hero ingredient &amp; spec</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Positioning evolution</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Claim risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="64" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Poppi</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Prebiotic soda you can drink daily</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Prebiotic fiber + ACV; ~2g fiber, 2–5g sugar</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>ACV “tonic” (Mother Beverage) → 2020 bright “prebiotic soda”</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>$8.9M settlement — 2g fiber too little for claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="64" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>OLIPOP</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>“New kind of soda”, serious fiber</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Up to 9g fiber (cassava/chicory/artichoke) + botanicals</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Stable gut-health since launch; ~4× Poppi fiber</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>No suit found; higher fiber = stronger substantiation</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="64" customHeight="1">
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Only Amazon fees, Costco margin &amp; DTC CAC are HARD; the rest are operator rules-of-thumb — model as ranges</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>MARGIN WATERFALL — canned functional beverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Typical value</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>LMNT</t>
+          <t>Unit COGS target</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Zero-sugar, high-sodium for keto/athletes</t>
+          <t>&lt; $1.00/unit (liquid+can+co-pack at scale)</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>1,000mg sodium, 200mg K, 60mg Mg, 0g sugar</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Salt-first, science-forward</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>Sodium is the polarizing hook</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="64" customHeight="1">
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Liquid I.V.</t>
+          <t>12oz decorated can (component)</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Hydration Multiplier, 2–3× faster</t>
+          <t>~$0.15/can at intro minimums</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Cellular Transport Tech; 500mg sodium, 11g carbs</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Added sugar-free line later</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>CTT efficacy is marketing-led; sugar a vulnerability</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="64" customHeight="1">
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Nuun</t>
+          <t>Co-pack run (10,000 cases)</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Carb-free effervescent electrolyte</t>
+          <t>≈ $200,000; MOQ 2,000–5,000 cases/SKU</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>300mg sodium, 1g sugar, 15 cal, stevia</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Endurance carb-free → added powders</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Clean low-sugar story</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="64" customHeight="1">
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>Vital Proteins Sparkling</t>
+          <t>Blended gross margin (early)</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Beauty-from-within + clinical collagen at mass price</t>
+          <t>40–50%; aspiration 50–65% at scale</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>VERISOL collagen + 100% DV Vit C; 0g sugar</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Extends #1 collagen powder into a can</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>Strongest collagen claim, but see 2025 efficacy meta-analysis</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="64" customHeight="1">
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Recess</t>
+          <t>GM by channel</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Relaxation — sell the benefit not the molecule</t>
+          <t>Retail ~35–45%; DTC ~40–50% (before CAC/freight)</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Magnesium L-threonate + adaptogens</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Pivoted CBD → relaxation (CBD &lt;8% of sales)</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>KEY LESSON: lead with felt benefit</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="64" customHeight="1">
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Aura Bora</t>
+          <t>COGS warning</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Herbal/floral, zero everything</t>
+          <t>Excluding freight/duty/co-pack overstates GM by 3–8 pts — the #1 error</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>0 cal/sugar/sodium; herb+fruit+flower</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Flavor-forward, no health-claim baggage</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>Low regulatory risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>READ-ACROSS for MUV: “collagen-as-hero” has a graveyard AND a 2025 no-benefit meta-analysis. Winners wrap collagen in a big brand + clinical claim at mass price (Vital Proteins) OR sell a broader felt benefit (Recess). Lead MUV with gut+hydration function + a credible collagen dose under the “Canada's #1 collagen brand” halo — not narrow beauty-from-within.</t>
-        </is>
-      </c>
-      <c r="B12" s="34" t="n"/>
-      <c r="C12" s="34" t="n"/>
-      <c r="D12" s="34" t="n"/>
-      <c r="E12" s="35" t="n"/>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>CHANNEL TAKE-RATES (who takes margin off the top)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Channel / cost</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Take / value</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Grocery (conventional)</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>~30–50% retailer margin; bev often 30–40%</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Natural/premium (Whole Foods)</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>45%+ (slower turns)</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Club (Costco)</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Max 14% markup (15% Kirkland); FY24 actual GM 10.92% — volume not margin play</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Distributor (general)</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>15–25% markup; UNFI avg ~13–14% (range 6–30%)</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>HARD-ish</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>DSD vs warehouse</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>DSD can save ~5–10% in fees vs UNFI/KeHE routing</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>3–5% of net sales + often $5–10k/mo retainer</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>8–45% referral (most 15%) + FBA $3.73–$6.97/unit ($25+ heavy bev)</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>HARD (published)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>DTC CAC (food &amp; bev)</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>~$45–$53 (lowest vertical); supplements ~$89; shipping $8–15/order</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>HARD (benchmark)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>TRADE SPEND &amp; FEES</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Slotting fee</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>$250 → $250,000 by retailer/scope; ~$25,000/item regional cluster</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Trade spend % of revenue</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
+        <is>
+          <t>10–20% (emerging brands high end); US trade spend &gt;$200B, ~20% of gross, #2 P&amp;L line</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>HARD (aggregate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Free fill</t>
+        </is>
+      </c>
+      <c r="B28" s="12" t="inlineStr">
+        <is>
+          <t>1 free case/SKU/store on first order — cheaper substitute for slotting</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>RULE OF THUMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>LMNT subscription model</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
+        <is>
+          <t>$200M+ rev 2023, ~20% net margin, 250k+ customers; free-8-pack (pay shipping) funnel</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>HARD (company/SEC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>CANADA COST STACK (additive on US economics)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Grocery concentration</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Loblaw+Sobeys+Metro ≈ 80% w/ Walmart+Costco; all signed Grocery Code of Conduct (in force Jan 1, 2025)</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>HARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>Listing/slotting fees</t>
+        </is>
+      </c>
+      <c r="B34" s="13" t="inlineStr">
+        <is>
+          <t>Charged but NOT publicly disclosed; Code now lets suppliers challenge arbitrary fees — model at ≥ US slotting</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>No public $</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Bilingual packaging</t>
+        </is>
+      </c>
+      <c r="B35" s="12" t="inlineStr">
+        <is>
+          <t>EN+FR mandatory; French ~2× longer; non-compliance fines up to $20,000; Bill 96 adds rules</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>HARD (regulatory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>Distributors (CA)</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="inlineStr">
+        <is>
+          <t>UNFI Canada, Tree of Life Canada, Purity Life, Ecotrend</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>HARD (existence)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>Freight/FX/duty</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="inlineStr">
+        <is>
+          <t>FX (US$1≈C$1.15+) + cross-border freight + duty; model as premium; local co-pack is the margin fix</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>Qualitative</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="46" customHeight="1">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>DTC-for-beverage reality check: heavy to ship, low online AOV, CAC can exceed contribution. Historically ~90% of beverage startups fail; the survivable DTC model (LMNT) is subscription + free-sample acquisition + asset-light profitability — not paid-media scale.</t>
+        </is>
+      </c>
+      <c r="B38" s="34" t="n"/>
+      <c r="C38" s="34" t="n"/>
+      <c r="D38" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A12:E12"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
@@ -7751,15 +7600,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Marketing &amp; Brand Build — the virality engine</t>
+          <t>Formulation &amp; Positioning — the claim that won</t>
         </is>
       </c>
       <c r="M1" s="95" t="inlineStr">
@@ -7781,21 +7631,26 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Founder story</t>
+          <t>Winning claim</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>Growth engine</t>
+          <t>Hero ingredient &amp; spec</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>What moved the needle</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="66" customHeight="1">
+          <t>Positioning evolution</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Claim risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="64" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Poppi</t>
@@ -7803,21 +7658,26 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>Allison &amp; Stephen Ellsworth; Shark Tank 2018 ($400k/25%, Rohan Oza)</t>
+          <t>Prebiotic soda you can drink daily</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>TikTok creator seeding + 2 Super Bowls (2024 first ad, 2025 return)</t>
+          <t>Prebiotic fiber + ACV; ~2g fiber, 2–5g sugar</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Pink aesthetic, Alix Earle/Emily Mariko seeding, vending-machine stunt (2025, mixed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="66" customHeight="1">
+          <t>ACV “tonic” (Mother Beverage) → 2020 bright “prebiotic soda”</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>$8.9M settlement — 2g fiber too little for claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="64" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
           <t>OLIPOP</t>
@@ -7825,21 +7685,26 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Ben Goodwin (ex-Obi) &amp; David Lester; $100k from Obi sale</t>
+          <t>“New kind of soda”, serious fiber</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>DTC repurchase rates + reactive social</t>
+          <t>Up to 9g fiber (cassava/chicory/artichoke) + botanicals</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>“Soda Stories”; needled Poppi's vending spend during 2025 SB — earned media without paying for the game</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="66" customHeight="1">
+          <t>Stable gut-health since launch; ~4× Poppi fiber</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>No suit found; higher fiber = stronger substantiation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="64" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>LMNT</t>
@@ -7847,21 +7712,26 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Robb Wolf (biochemist) + Ketogains (Villaseñor)</t>
+          <t>Zero-sugar, high-sodium for keto/athletes</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Podcast-sponsorship moat (Huberman, Attia)</t>
+          <t>1,000mg sodium, 200mg K, 60mg Mg, 0g sugar</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Host-read trust + free-sample funnel; $54.6M mktg + $7.1M sampling in 2023 (~26.5% of rev)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="66" customHeight="1">
+          <t>Salt-first, science-forward</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Sodium is the polarizing hook</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="64" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Liquid I.V.</t>
@@ -7869,21 +7739,26 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>Brandin Cohen, college brainchild (+2)</t>
+          <t>Hydration Multiplier, 2–3× faster</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>In-store/Costco roadshow sampling + give-back</t>
+          <t>Cellular Transport Tech; 500mg sodium, 11g carbs</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Founder sampled every weekend; POS-data sell-in; Emerson Group for national muscle</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="66" customHeight="1">
+          <t>Added sugar-free line later</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>CTT efficacy is marketing-led; sugar a vulnerability</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="64" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Nuun</t>
@@ -7891,100 +7766,121 @@
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>Tim Moxey, British Ironman</t>
+          <t>Carb-free effervescent electrolyte</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Grassroots endurance-community events</t>
+          <t>300mg sodium, 1g sugar, 15 cal, stevia</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Authentic credibility in run/bike/tri before mainstream</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="66" customHeight="1">
+          <t>Endurance carb-free → added powders</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Clean low-sugar story</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="64" customHeight="1">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>Celsius</t>
+          <t>Vital Proteins Sparkling</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>Turnaround 2012; Li Ka-shing $15M (2015)</t>
+          <t>Beauty-from-within + clinical collagen at mass price</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Amazon + fitness influencers/gym sampling</t>
+          <t>VERISOL collagen + 100% DV Vit C; 0g sugar</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Amazon velocity → Target DSD → PepsiCo $550M distribution</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="66" customHeight="1">
+          <t>Extends #1 collagen powder into a can</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>Strongest collagen claim, but see 2025 efficacy meta-analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="64" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Vital Proteins Sparkling</t>
+          <t>Recess</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>K. Seidensticker; Nestlé-owned</t>
+          <t>Relaxation — sell the benefit not the molecule</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>Big-brand media + retail muscle + collagen loyalty</t>
+          <t>Magnesium L-threonate + adaptogens</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Distribution &amp; #1-collagen halo, not scrappy virality</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="66" customHeight="1">
+          <t>Pivoted CBD → relaxation (CBD &lt;8% of sales)</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>KEY LESSON: lead with felt benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="64" customHeight="1">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Recess</t>
+          <t>Aura Bora</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>Benjamin Witte</t>
+          <t>Herbal/floral, zero everything</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Distinctive pastel brand world + culture-tuned social</t>
+          <t>0 cal/sugar/sodium; herb+fruit+flower</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Owned a vibe + the “relaxation” moment</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52" customHeight="1">
+          <t>Flavor-forward, no health-claim baggage</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>Low regulatory risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>READ-ACROSS: The two cheapest high-ROI challenger playbooks are LMNT's trusted-host podcast model and OLIPOP's reactive earned-media social — both winnable without Super Bowl budgets. Pair with Costco-roadshow sampling (Liquid I.V.). Brand tone must evolve with stage (Poppi's vending stunt misfired once mainstream).</t>
+          <t>READ-ACROSS for MUV: “collagen-as-hero” has a graveyard AND a 2025 no-benefit meta-analysis. Winners wrap collagen in a big brand + clinical claim at mass price (Vital Proteins) OR sell a broader felt benefit (Recess). Lead MUV with gut+hydration function + a credible collagen dose under the “Canada's #1 collagen brand” halo — not narrow beauty-from-within.</t>
         </is>
       </c>
       <c r="B12" s="34" t="n"/>
       <c r="C12" s="34" t="n"/>
-      <c r="D12" s="35" t="n"/>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
@@ -8213,20 +8109,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Launch Playbook Teardowns — phased GTM timelines</t>
+          <t>Marketing &amp; Brand Build — the virality engine</t>
         </is>
       </c>
       <c r="M1" s="95" t="inlineStr">
@@ -8248,26 +8143,21 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Phase 0 (pre-launch)</t>
+          <t>Founder story</t>
         </is>
       </c>
       <c r="C3" s="11" t="inlineStr">
         <is>
-          <t>Phase 1 (launch, yr 0–1)</t>
+          <t>Growth engine</t>
         </is>
       </c>
       <c r="D3" s="11" t="inlineStr">
         <is>
-          <t>Phase 2 (scale, yr 1–3)</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Phase 3 (maturity/exit)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="92" customHeight="1">
+          <t>What moved the needle</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="66" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Poppi</t>
@@ -8275,26 +8165,21 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>2015–16: gut-health insight; ~$90k self-funded; “Mother Beverage” glass bottles</t>
+          <t>Allison &amp; Stephen Ellsworth; Shark Tank 2018 ($400k/25%, Rohan Oza)</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>Farmers markets → Whole Foods regional; ~$500k in 18 mo; Shark Tank 2018 ($400k/25% Oza)</t>
+          <t>TikTok creator seeding + 2 Super Bowls (2024 first ad, 2025 return)</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>2020 rebrand to cans + national launch (Mar 2020); TikTok creator seeding; #1 Amazon soda 2023</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>2024 first Super Bowl ad; &gt;$500M rev; PepsiCo $1.95B closed May 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="92" customHeight="1">
+          <t>Pink aesthetic, Alix Earle/Emily Mariko seeding, vending-machine stunt (2025, mixed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="66" customHeight="1">
       <c r="A5" s="13" t="inlineStr">
         <is>
           <t>OLIPOP</t>
@@ -8302,26 +8187,21 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Founders' prior brand Obi; $100k seed; nostalgic-soda + fiber insight</t>
+          <t>Ben Goodwin (ex-Obi) &amp; David Lester; $100k from Obi sale</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Late 2018: 40 NorCal indie grocers; ~$852k yr 1; ~$2.49/can; gut-health science story</t>
+          <t>DTC repurchase rates + reactive social</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Natural → conventional → mass; “astronomical repurchase” sell-in; $73.4M (2022); $39.7M Series B</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>$200M (2023)→$400M+ (2024); 7,000+ grocers; $50M @ $1.85B (Feb 2025); INDEPENDENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="92" customHeight="1">
+          <t>“Soda Stories”; needled Poppi's vending spend during 2025 SB — earned media without paying for the game</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="66" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>LMNT</t>
@@ -8329,26 +8209,21 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>2018–19: keto-sodium insight; Robb Wolf + Ketogains; high-sodium no-sugar formula</t>
+          <t>Robb Wolf (biochemist) + Ketogains (Villaseñor)</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Late 2019 DTC-only; free Sample Pack (pay ~$5 shipping); profitable yr 1 (claim)</t>
+          <t>Podcast-sponsorship moat (Huberman, Attia)</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Podcast sponsorships (Huberman et al., ~10k episodes); ~$50M run-rate by Q1 2022</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>$206M sales (2023, SEC); private, founder-controlled; selective retail; NO exit</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="92" customHeight="1">
+          <t>Host-read trust + free-sample funnel; $54.6M mktg + $7.1M sampling in 2023 (~26.5% of rev)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="66" customHeight="1">
       <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Liquid I.V.</t>
@@ -8356,67 +8231,122 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>2012: adults using Pedialyte insight; WHO-ORS-based CTT formula</t>
+          <t>Brandin Cohen, college brainchild (+2)</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Whole Foods “Supplier 101”; founder samples weekly → 12 WF by 2015</t>
+          <t>In-store/Costco roadshow sampling + give-back</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Costco roadshow sampling; Emerson Group (2015); ~$100M within 5 yrs</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Unilever Sept 2020 (~$500M est.); 30k→80k stores; $1B+ brand</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="92" customHeight="1">
+          <t>Founder sampled every weekend; POS-data sell-in; Emerson Group for national muscle</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="66" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
+          <t>Nuun</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Tim Moxey, British Ironman</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Grassroots endurance-community events</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Authentic credibility in run/bike/tri before mainstream</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="66" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
           <t>Celsius</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>2004 (Elite FX); near-bankruptcy/delisting ~2010 — over-marketing before PMF</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>Turnaround 2012; Li Ka-shing $15M (2015); NASDAQ uplisting 2017 (~$36M rev)</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Amazon ~15–20% of sales (2020); Target DSD; 100k+ doors by 2021</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>PepsiCo $550M/8.5% (2022) → ~#3 energy; bought Alani Nu $1.8B (2025)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>DATE TRAP: Poppi's FIRST Super Bowl ad = 2024 (LVIII); the vending-machine controversy = the 2025 (LIX) return. Many secondary sources conflate them.</t>
-        </is>
-      </c>
-      <c r="B9" s="34" t="n"/>
-      <c r="C9" s="34" t="n"/>
-      <c r="D9" s="34" t="n"/>
-      <c r="E9" s="35" t="n"/>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Turnaround 2012; Li Ka-shing $15M (2015)</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Amazon + fitness influencers/gym sampling</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Amazon velocity → Target DSD → PepsiCo $550M distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="66" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Vital Proteins Sparkling</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>K. Seidensticker; Nestlé-owned</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Big-brand media + retail muscle + collagen loyalty</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Distribution &amp; #1-collagen halo, not scrappy virality</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Recess</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Benjamin Witte</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Distinctive pastel brand world + culture-tuned social</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Owned a vibe + the “relaxation” moment</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>READ-ACROSS: The two cheapest high-ROI challenger playbooks are LMNT's trusted-host podcast model and OLIPOP's reactive earned-media social — both winnable without Super Bowl budgets. Pair with Costco-roadshow sampling (Liquid I.V.). Brand tone must evolve with stage (Poppi's vending stunt misfired once mainstream).</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="n"/>
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A12:D12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
@@ -8442,17 +8372,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="114" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Success Patterns &amp; Failure Modes</t>
+          <t>Launch Playbook Teardowns — phased GTM timelines</t>
         </is>
       </c>
       <c r="M1" s="95" t="inlineStr">
@@ -8467,154 +8400,182 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>SEVEN SUCCESS PATTERNS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>Founder-authority insight tied to a personal health problem — cheap, durable brand moat (Ellsworth gut health, Wolf sodium, Cohen Pedialyte).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>ONE concentrated trial-generation tactic, executed obsessively, before broad spend.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>Sell-in on DATA (velocity/repurchase), not flavour — the single most repeated lever.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>Sequenced channel ladder — natural/DTC → specialty → grocery → mass → club; never skip rungs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>Strategic-investor signal early (Oza, Li Ka-shing, celebrity rounds) — capital + credibility + distribution.</t>
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Phase 0 (pre-launch)</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Phase 1 (launch, yr 0–1)</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Phase 2 (scale, yr 1–3)</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Phase 3 (maturity/exit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="92" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Poppi</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>2015–16: gut-health insight; ~$90k self-funded; “Mother Beverage” glass bottles</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Farmers markets → Whole Foods regional; ~$500k in 18 mo; Shark Tank 2018 ($400k/25% Oza)</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>2020 rebrand to cans + national launch (Mar 2020); TikTok creator seeding; #1 Amazon soda 2023</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>2024 first Super Bowl ad; &gt;$500M rev; PepsiCo $1.95B closed May 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="92" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>OLIPOP</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Founders' prior brand Obi; $100k seed; nostalgic-soda + fiber insight</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Late 2018: 40 NorCal indie grocers; ~$852k yr 1; ~$2.49/can; gut-health science story</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Natural → conventional → mass; “astronomical repurchase” sell-in; $73.4M (2022); $39.7M Series B</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>$200M (2023)→$400M+ (2024); 7,000+ grocers; $50M @ $1.85B (Feb 2025); INDEPENDENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="92" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>LMNT</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>2018–19: keto-sodium insight; Robb Wolf + Ketogains; high-sodium no-sugar formula</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Late 2019 DTC-only; free Sample Pack (pay ~$5 shipping); profitable yr 1 (claim)</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Podcast sponsorships (Huberman et al., ~10k episodes); ~$50M run-rate by Q1 2022</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>$206M sales (2023, SEC); private, founder-controlled; selective retail; NO exit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="92" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Liquid I.V.</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>2012: adults using Pedialyte insight; WHO-ORS-based CTT formula</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Whole Foods “Supplier 101”; founder samples weekly → 12 WF by 2015</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Costco roadshow sampling; Emerson Group (2015); ~$100M within 5 yrs</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Unilever Sept 2020 (~$500M est.); 30k→80k stores; $1B+ brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="92" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Celsius</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>2004 (Elite FX); near-bankruptcy/delisting ~2010 — over-marketing before PMF</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Turnaround 2012; Li Ka-shing $15M (2015); NASDAQ uplisting 2017 (~$36M rev)</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Amazon ~15–20% of sales (2020); Target DSD; 100k+ doors by 2021</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>PepsiCo $550M/8.5% (2022) → ~#3 energy; bought Alani Nu $1.8B (2025)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>Category-creation language to escape commodity comparison and hold a $2–$3/can premium.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>Endgame split: strategic exit (Poppi/Liquid I.V./Celsius) vs independence (OLIPOP/LMNT) — both valid; scale eventually needs a partner or heavy capital.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="21" t="inlineStr">
-        <is>
-          <t>SIX FAILURE MODES</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>Over-distribution before product-market fit — Celsius's own ~2010 near-bankruptcy is the canonical case. Velocity must precede footprint.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>Undercapitalized / capital-intensive DTC — beverages are heavy physical goods; ~90% of beverage startups failed historically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>Premium price with no defensible moat / thin claims — ~32% of consumers cite “too expensive”; premium needs credible function + repeat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>Trial without retention — sampling/virality wasted if repurchase is weak (inverse of the OLIPOP/Liquid I.V. data story).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>Brand/tone missteps at scale — Poppi's 2025 vending stunt; tactics must evolve with brand stage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>Wrong timing / flavour failure — the baseline reasons ~85% of new CPG products fail within 2 years.</t>
-        </is>
-      </c>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>DATE TRAP: Poppi's FIRST Super Bowl ad = 2024 (LVIII); the vending-machine controversy = the 2025 (LIX) return. Many secondary sources conflate them.</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="n"/>
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A12:B12"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
@@ -8640,21 +8601,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="114" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Financial Outcomes &amp; M&amp;A Comps</t>
+          <t>Success Patterns &amp; Failure Modes</t>
         </is>
       </c>
       <c r="M1" s="95" t="inlineStr">
@@ -8669,373 +8626,154 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Revenue trajectory</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Funding / valuation</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Exit / status</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Category share</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>Profitability</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Poppi</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>$13M(20)→$65M(22)→$100M+(23)→~$500M(24)</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>VC-backed pre-exit</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>PepsiCo $1.95B (net ~$1.65B), May 2025</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>~38% modern soda (24)</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>OLIPOP</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>$852k(18)→$200M+(23)→$400M+(24)</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>$50M Series C @ $1.85B (Feb 2025, JPM)</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>~32.7% modern soda (24)</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>Cash-profitable early 2024</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>LMNT</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>$206M sales (2023, SEC)</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Reg CF / Republic</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Independent</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>~20% net margin (2023)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Liquid I.V.</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>~$100M in 5 yrs → ~$200M exit → $1B+ now</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Unilever Sept 2020 (~$500M est.)</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>Unilever +$80M MO plant</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Nuun</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>$10M+ (2013)</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>TSG Consumer (2017)</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Nestlé HS July 2021 (undisclosed)</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>#1 run/bike/outdoor</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Celsius</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>multi-$B (public)</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Li Ka-shing $15M (2015)</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Public; PepsiCo $550M (2022); bought Alani Nu $1.8B</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>~#3 US energy (~11.5%)</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>Profitable</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Health-Ade</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>~$250M/yr retail</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>~$54M raised</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Generous Brands $500M</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Alani Nu</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>~$595M (2024)</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Congo Brands</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Celsius $1.8B (2025)</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Vital Proteins</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>(in Nestlé HS)</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>Nestlé (full 2022)</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Aura Bora</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>$12M (2024)</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>~$22M raised</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>Majority to Next In Natural (2025)</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>M&amp;A READ: Strategics now own most winners — PepsiCo (Poppi, Celsius stake), Unilever (Liquid I.V., Olly), Nestlé (Vital Proteins, Nuun), KDP (Ghost). For a challenger the realistic endgame is acquisition, not durable independence — but Coke's organic Simply Pop shows incumbents may CLONE rather than buy, compressing the premium. OLIPOP (independent, $1.85B) is the counter-example.</t>
-        </is>
-      </c>
-      <c r="B14" s="34" t="n"/>
-      <c r="C14" s="34" t="n"/>
-      <c r="D14" s="34" t="n"/>
-      <c r="E14" s="34" t="n"/>
-      <c r="F14" s="35" t="n"/>
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>SEVEN SUCCESS PATTERNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Founder-authority insight tied to a personal health problem — cheap, durable brand moat (Ellsworth gut health, Wolf sodium, Cohen Pedialyte).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>ONE concentrated trial-generation tactic, executed obsessively, before broad spend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Sell-in on DATA (velocity/repurchase), not flavour — the single most repeated lever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Sequenced channel ladder — natural/DTC → specialty → grocery → mass → club; never skip rungs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Strategic-investor signal early (Oza, Li Ka-shing, celebrity rounds) — capital + credibility + distribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Category-creation language to escape commodity comparison and hold a $2–$3/can premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Endgame split: strategic exit (Poppi/Liquid I.V./Celsius) vs independence (OLIPOP/LMNT) — both valid; scale eventually needs a partner or heavy capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>SIX FAILURE MODES</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Over-distribution before product-market fit — Celsius's own ~2010 near-bankruptcy is the canonical case. Velocity must precede footprint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Undercapitalized / capital-intensive DTC — beverages are heavy physical goods; ~90% of beverage startups failed historically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Premium price with no defensible moat / thin claims — ~32% of consumers cite “too expensive”; premium needs credible function + repeat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>Trial without retention — sampling/virality wasted if repurchase is weak (inverse of the OLIPOP/Liquid I.V. data story).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>Brand/tone missteps at scale — Poppi's 2025 vending stunt; tactics must evolve with brand stage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Wrong timing / flavour failure — the baseline reasons ~85% of new CPG products fail within 2 years.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
@@ -9061,6 +8799,427 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Financial Outcomes &amp; M&amp;A Comps</t>
+        </is>
+      </c>
+      <c r="M1" s="95" t="inlineStr">
+        <is>
+          <t>🏠 Home</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Revenue trajectory</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Funding / valuation</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Exit / status</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Category share</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
+          <t>Profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Poppi</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>$13M(20)→$65M(22)→$100M+(23)→~$500M(24)</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>VC-backed pre-exit</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>PepsiCo $1.95B (net ~$1.65B), May 2025</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>~38% modern soda (24)</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>OLIPOP</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>$852k(18)→$200M+(23)→$400M+(24)</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>$50M Series C @ $1.85B (Feb 2025, JPM)</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>~32.7% modern soda (24)</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Cash-profitable early 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>LMNT</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>$206M sales (2023, SEC)</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Reg CF / Republic</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Independent</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>~20% net margin (2023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Liquid I.V.</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>~$100M in 5 yrs → ~$200M exit → $1B+ now</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Unilever Sept 2020 (~$500M est.)</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Unilever +$80M MO plant</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Nuun</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>$10M+ (2013)</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>TSG Consumer (2017)</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Nestlé HS July 2021 (undisclosed)</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>#1 run/bike/outdoor</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Celsius</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>multi-$B (public)</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Li Ka-shing $15M (2015)</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Public; PepsiCo $550M (2022); bought Alani Nu $1.8B</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>~#3 US energy (~11.5%)</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Profitable</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Health-Ade</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>~$250M/yr retail</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>~$54M raised</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Generous Brands $500M</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Alani Nu</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>~$595M (2024)</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Congo Brands</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Celsius $1.8B (2025)</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Vital Proteins</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>(in Nestlé HS)</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Nestlé (full 2022)</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Aura Bora</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>$12M (2024)</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>~$22M raised</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Majority to Next In Natural (2025)</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>M&amp;A READ: Strategics now own most winners — PepsiCo (Poppi, Celsius stake), Unilever (Liquid I.V., Olly), Nestlé (Vital Proteins, Nuun), KDP (Ghost). For a challenger the realistic endgame is acquisition, not durable independence — but Coke's organic Simply Pop shows incumbents may CLONE rather than buy, compressing the premium. OLIPOP (independent, $1.85B) is the counter-example.</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="n"/>
+      <c r="C14" s="34" t="n"/>
+      <c r="D14" s="34" t="n"/>
+      <c r="E14" s="34" t="n"/>
+      <c r="F14" s="35" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="003E5C76"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9298,7 +9457,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="003E5C76"/>
@@ -9733,7 +9892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001E7D32"/>
@@ -10291,7 +10450,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001E7D32"/>
@@ -10827,7 +10986,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001E7D32"/>
@@ -11281,7 +11440,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E7D8A"/>
@@ -12086,163 +12245,6 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00B45309"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="92" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>MUV Go-to-Market Recommendation</t>
-        </is>
-      </c>
-      <c r="M1" s="95" t="inlineStr">
-        <is>
-          <t>🏠 Home</t>
-        </is>
-      </c>
-      <c r="N1" s="95" t="inlineStr">
-        <is>
-          <t>↩ Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="52" customHeight="1">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>VERDICT: GO — conditional on resolving the Supplemented-Foods claim/label pathway and dosing collagen to a defensible level. The tailwinds are real and Organika has a genuine structural edge in Canada; the risks (collagen efficacy/claims, strategic competition) are manageable with discipline.</t>
-        </is>
-      </c>
-      <c r="B3" s="35" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Decision</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Recommendation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="78" customHeight="1">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>1. Positioning</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Lead with a FUNCTIONAL benefit stack (gut/prebiotic + hydration + a credible collagen dose) under a “by Canada's #1 collagen brand” halo. Avoid narrow beauty-from-within hero claims — the graveyard + 2025 efficacy meta-analysis make it the riskiest lane. Function-stacking also hedges single-fad risk.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="78" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>2. Formulation</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Dose collagen to a substantiable level (2.5g+; positive studies used 2.5–10g/day). Zero/low sugar is table stakes. Add prebiotic fiber for a defensible gut hook (OLIPOP's 9g beat Poppi's 2g in court). Caffeine-free to avoid the 180mg energy-drink caution regime.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="78" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>3. Channel beachhead</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Costco Canada + Amazon.ca + natural channel (Whole Foods CA, Healthy Planet) + Organika's existing pharmacy/health-food/Well.ca base. This mirrors Liquid I.V./Poppi's Canada entry — and Organika already holds the relationships. Do NOT chase national grocery before proving velocity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="78" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>4. Pricing</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Anchor at/below the ~$3.49 CAD premium-functional shelf norm. Domestic production lets MUV protect margin where imported US brands cannot — a durable advantage. Plan 35–45% trade spend in early scale; use free-fill over cash slotting where possible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="78" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>5. Marketing</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Run the cheap challenger playbooks: trusted-host podcast sponsorship (LMNT model) + reactive earned-media social (OLIPOP model) + Costco roadshow sampling (Liquid I.V. model). Skip Super Bowl-tier spend. Sell-in to buyers on velocity/repeat data, not taste.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="78" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>6. Claims &amp; legal</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Engage Canadian regulatory counsel on the Supplemented-Foods claim set BEFORE artwork. Build substantiation files. Include the mandatory collagen “do not use as sole source of nutrition” caution. Dose-to-claim discipline is existential (Poppi paid $8.9M).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="78" customHeight="1">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>7. Moat &amp; exit</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Differentiate on a real, defensible spec + Canadian-made authenticity + Organika's collagen credibility. Plan for an acquisition-oriented endgame (strategics own the category) while building OLIPOP-style independence optionality through profitability and repeat rate.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -12571,6 +12573,163 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00B45309"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MUV Go-to-Market Recommendation</t>
+        </is>
+      </c>
+      <c r="M1" s="95" t="inlineStr">
+        <is>
+          <t>🏠 Home</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="52" customHeight="1">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>VERDICT: GO — conditional on resolving the Supplemented-Foods claim/label pathway and dosing collagen to a defensible level. The tailwinds are real and Organika has a genuine structural edge in Canada; the risks (collagen efficacy/claims, strategic competition) are manageable with discipline.</t>
+        </is>
+      </c>
+      <c r="B3" s="35" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Decision</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="78" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>1. Positioning</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Lead with a FUNCTIONAL benefit stack (gut/prebiotic + hydration + a credible collagen dose) under a “by Canada's #1 collagen brand” halo. Avoid narrow beauty-from-within hero claims — the graveyard + 2025 efficacy meta-analysis make it the riskiest lane. Function-stacking also hedges single-fad risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="78" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>2. Formulation</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Dose collagen to a substantiable level (2.5g+; positive studies used 2.5–10g/day). Zero/low sugar is table stakes. Add prebiotic fiber for a defensible gut hook (OLIPOP's 9g beat Poppi's 2g in court). Caffeine-free to avoid the 180mg energy-drink caution regime.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="78" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>3. Channel beachhead</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Costco Canada + Amazon.ca + natural channel (Whole Foods CA, Healthy Planet) + Organika's existing pharmacy/health-food/Well.ca base. This mirrors Liquid I.V./Poppi's Canada entry — and Organika already holds the relationships. Do NOT chase national grocery before proving velocity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="78" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>4. Pricing</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Anchor at/below the ~$3.49 CAD premium-functional shelf norm. Domestic production lets MUV protect margin where imported US brands cannot — a durable advantage. Plan 35–45% trade spend in early scale; use free-fill over cash slotting where possible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="78" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>5. Marketing</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Run the cheap challenger playbooks: trusted-host podcast sponsorship (LMNT model) + reactive earned-media social (OLIPOP model) + Costco roadshow sampling (Liquid I.V. model). Skip Super Bowl-tier spend. Sell-in to buyers on velocity/repeat data, not taste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="78" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>6. Claims &amp; legal</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Engage Canadian regulatory counsel on the Supplemented-Foods claim set BEFORE artwork. Build substantiation files. Include the mandatory collagen “do not use as sole source of nutrition” caution. Dose-to-claim discipline is existential (Poppi paid $8.9M).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="78" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>7. Moat &amp; exit</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Differentiate on a real, defensible spec + Canadian-made authenticity + Organika's collagen credibility. Plan for an acquisition-oriented endgame (strategics own the category) while building OLIPOP-style independence optionality through profitability and repeat rate.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00C9A227"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
@@ -12869,7 +13028,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C9A227"/>
@@ -13107,196 +13266,6 @@
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00B45309"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Phased Launch Plan (0–18 months)</t>
-        </is>
-      </c>
-      <c r="M1" s="95" t="inlineStr">
-        <is>
-          <t>🏠 Home</t>
-        </is>
-      </c>
-      <c r="N1" s="95" t="inlineStr">
-        <is>
-          <t>↩ Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Phase</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Timing</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Objectives</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Key workstreams</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Success gate</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="80" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Phase 0 — Foundation</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Months 0–3</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Lock product, claims, regulatory pathway, co-pack</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Finalize formula &amp; collagen dose; regulatory-counsel claim opinion (Supplemented Foods); co-packer quote &amp; MOQ; bilingual + Bill 96 artwork; brand/positioning</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory sign-off on claim set + artwork approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="80" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1 — Beachhead</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Months 3–9</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Prove velocity &amp; repeat in a contained beachhead</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Costco CA roadshows + Amazon.ca + Well.ca/Natura + Organika pharmacy/health-food base; podcast + reactive social; sampling</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>Repeat rate + velocity above category benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Phase 2 — Scale</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Months 9–18</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Earn conventional grocery on proven data</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Sell-in to Loblaw/Sobeys/Metro on velocity data; distributor (UNFI CA / Tree of Life); managed trade spend; add SKUs on repeat data</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>National listings won on data, not discounts</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Phase 3 — Defend &amp; extend</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>18 mo+</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Category leadership &amp; optionality</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Format/flavour extensions; deepen moat; evaluate strategic-partner vs independent scale</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Profitable contribution + exit optionality</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
@@ -13322,21 +13291,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Risk Register</t>
+          <t>Phased Launch Plan (0–18 months)</t>
         </is>
       </c>
       <c r="M1" s="95" t="inlineStr">
@@ -13350,409 +13318,144 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Likelihood × Impact (H/M/L). Ranked by exposure</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Likelihood</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Mitigation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Collagen efficacy / claims liability (2025 meta-analysis; Poppi-style dose-insufficiency suit)</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory/Legal</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>Dose to efficacy (2.5g+); structure/function-safe language; substantiation files; lead with gut/hydration not beauty</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Strategic-owned competition (Nestlé owns Vital Proteins; PepsiCo/Unilever firepower)</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E6" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>Compete on Canadian-made + domestic cost edge + Organika collagen credibility; niche beachhead before they react</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Canada claim/label pathway misread (food vs NHP; SFCI; collagen caution)</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory</t>
-        </is>
-      </c>
-      <c r="D7" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory-counsel opinion before artwork; design to Supplemented Foods framework; caffeine-free</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Over-distribution before product-market fit</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>Execution</t>
-        </is>
-      </c>
-      <c r="D8" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E8" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>Prove velocity/repeat in beachhead before national; gate Phase 2 on data</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Slotting / trade-spend cash burn</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E9" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Use free-fill over cash slotting; 35–45% trade-spend budget; Code of Conduct leverage on arbitrary fees</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Thin differentiation / shelf saturation (prebiotic shelf filling fast)</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D10" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E10" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Defensible spec (fiber + collagen dose) + function stacking; Canadian-made story</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Private-label encroachment (~$277B, ~21% share, growing 2×)</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D11" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E11" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Brand equity + clinical-grade ingredients retailers can't easily copy</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>DTC CAC / heavy-ship economics if DTC-led</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D12" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E12" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>Lead retail/beachhead not paid DTC; subscription + sampling only</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Co-packer capacity / collagen sourcing / cost inflation</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="D13" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E13" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>Lock co-pack capacity early; qualify 2nd collagen supplier; hedge raws</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>FX / tariff / freight premium on cross-border inputs</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D14" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E14" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>Domestic CA co-pack; monitor tariff status post-Dec 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>GLP-1 demand shift away from sweet/snack</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Macro</t>
-        </is>
-      </c>
-      <c r="D15" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E15" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Low-cal, fiber, protein, hydration positioning aligns with GLP-1 users</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>Brand/tone misstep at scale</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="D16" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E16" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>Evolve tactics with stage; avoid Poppi-style stunts once mainstream</t>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Objectives</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Key workstreams</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Success gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Phase 0 — Foundation</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Months 0–3</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Lock product, claims, regulatory pathway, co-pack</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Finalize formula &amp; collagen dose; regulatory-counsel claim opinion (Supplemented Foods); co-packer quote &amp; MOQ; bilingual + Bill 96 artwork; brand/positioning</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory sign-off on claim set + artwork approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1 — Beachhead</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Months 3–9</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Prove velocity &amp; repeat in a contained beachhead</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Costco CA roadshows + Amazon.ca + Well.ca/Natura + Organika pharmacy/health-food base; podcast + reactive social; sampling</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Repeat rate + velocity above category benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Phase 2 — Scale</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Months 9–18</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Earn conventional grocery on proven data</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Sell-in to Loblaw/Sobeys/Metro on velocity data; distributor (UNFI CA / Tree of Life); managed trade spend; add SKUs on repeat data</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>National listings won on data, not discounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Phase 3 — Defend &amp; extend</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>18 mo+</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Category leadership &amp; optionality</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Format/flavour extensions; deepen moat; evaluate strategic-partner vs independent scale</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Profitable contribution + exit optionality</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
@@ -13778,6 +13481,566 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:N24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="M1" s="95" t="inlineStr">
+        <is>
+          <t>🏠 Home</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Likelihood × Impact (H/M/L). Ranked by exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Likelihood</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Mitigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Collagen efficacy / claims liability (2025 meta-analysis; Poppi-style dose-insufficiency suit)</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory/Legal</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Dose to efficacy (2.5g+); structure/function-safe language; substantiation files; lead with gut/hydration not beauty</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Strategic-owned competition (Nestlé owns Vital Proteins; PepsiCo/Unilever firepower)</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Compete on Canadian-made + domestic cost edge + Organika collagen credibility; niche beachhead before they react</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Canada claim/label pathway misread (food vs NHP; SFCI; collagen caution)</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory-counsel opinion before artwork; design to Supplemented Foods framework; caffeine-free</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Over-distribution before product-market fit</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Prove velocity/repeat in beachhead before national; gate Phase 2 on data</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Slotting / trade-spend cash burn</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Use free-fill over cash slotting; 35–45% trade-spend budget; Code of Conduct leverage on arbitrary fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Thin differentiation / shelf saturation (prebiotic shelf filling fast)</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Defensible spec (fiber + collagen dose) + function stacking; Canadian-made story</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Private-label encroachment (~$277B, ~21% share, growing 2×)</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Brand equity + clinical-grade ingredients retailers can't easily copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>DTC CAC / heavy-ship economics if DTC-led</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Lead retail/beachhead not paid DTC; subscription + sampling only</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Co-packer capacity / collagen sourcing / cost inflation</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Lock co-pack capacity early; qualify 2nd collagen supplier; hedge raws</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>FX / tariff / freight premium on cross-border inputs</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Domestic CA co-pack; monitor tariff status post-Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>GLP-1 demand shift away from sweet/snack</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Low-cal, fiber, protein, hydration positioning aligns with GLP-1 users</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Brand/tone misstep at scale</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Evolve tactics with stage; avoid Poppi-style stunts once mainstream</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="138" t="inlineStr">
+        <is>
+          <t>LIKELIHOOD × IMPACT HEATMAP (risk #s placed by rating)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="148" t="inlineStr">
+        <is>
+          <t>Impact ↓ / Likelihood →</t>
+        </is>
+      </c>
+      <c r="B20" s="149" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C20" s="149" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="D20" s="149" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="149" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B21" s="150" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" s="151" t="inlineStr">
+        <is>
+          <t>3, 4, 5</t>
+        </is>
+      </c>
+      <c r="D21" s="151" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="149" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="B22" s="152" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C22" s="150" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="D22" s="151" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="149" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B23" s="152" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C23" s="152" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D23" s="150" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="133" t="inlineStr">
+        <is>
+          <t>Red = act now · Amber = manage · Green = monitor. Numbers refer to the risk # in the table above.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A24:F24"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00B45309"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -14077,7 +14340,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -14627,7 +14890,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C9A227"/>
@@ -14971,7 +15234,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -15446,7 +15709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -15918,6 +16181,18 @@
       <c r="B40" s="103" t="inlineStr">
         <is>
           <t>One printable page: verdict, numbers, 5 moves, risks</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="120" t="inlineStr">
+        <is>
+          <t>Assumptions Audit</t>
+        </is>
+      </c>
+      <c r="B41" s="103" t="inlineStr">
+        <is>
+          <t>Every model input with its source &amp; confidence tag</t>
         </is>
       </c>
     </row>
@@ -15964,6 +16239,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -17676,6 +17952,352 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="143" t="inlineStr">
+        <is>
+          <t>Assumptions Audit — every model input, with source &amp; confidence</t>
+        </is>
+      </c>
+      <c r="M1" s="95" t="inlineStr">
+        <is>
+          <t>🏠 Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="74" t="inlineStr">
+        <is>
+          <t>Input</t>
+        </is>
+      </c>
+      <c r="B3" s="74" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="C3" s="74" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="D3" s="74" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="E3" s="74" t="inlineStr">
+        <is>
+          <t>Source / confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="57" t="inlineStr">
+        <is>
+          <t>List price / can (CAD)</t>
+        </is>
+      </c>
+      <c r="B4" s="144" t="inlineStr">
+        <is>
+          <t>$3.29</t>
+        </is>
+      </c>
+      <c r="C4" s="144" t="inlineStr">
+        <is>
+          <t>$3.49</t>
+        </is>
+      </c>
+      <c r="D4" s="144" t="inlineStr">
+        <is>
+          <t>$3.79</t>
+        </is>
+      </c>
+      <c r="E4" s="103" t="inlineStr">
+        <is>
+          <t>MÜV SRP ~$14.99/pack; per-can set vs ~$3.49 CAD premium shelf norm ◐</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="59" t="inlineStr">
+        <is>
+          <t>COGS / can (CAD)</t>
+        </is>
+      </c>
+      <c r="B5" s="145" t="inlineStr">
+        <is>
+          <t>$1.20</t>
+        </is>
+      </c>
+      <c r="C5" s="145" t="inlineStr">
+        <is>
+          <t>$1.05</t>
+        </is>
+      </c>
+      <c r="D5" s="145" t="inlineStr">
+        <is>
+          <t>$0.95</t>
+        </is>
+      </c>
+      <c r="E5" s="146" t="inlineStr">
+        <is>
+          <t>Industry rule-of-thumb &lt;$1 target at scale; excludes freight/duty ⚠</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="57" t="inlineStr">
+        <is>
+          <t>Retailer margin %</t>
+        </is>
+      </c>
+      <c r="B6" s="144" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="C6" s="144" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="D6" s="144" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="E6" s="103" t="inlineStr">
+        <is>
+          <t>Grocery bev 30–40% rule-of-thumb ◐</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="59" t="inlineStr">
+        <is>
+          <t>Distributor margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="145" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="C7" s="145" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="D7" s="145" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="E7" s="146" t="inlineStr">
+        <is>
+          <t>UNFI/KeHE ~13–25% range ◐</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="57" t="inlineStr">
+        <is>
+          <t>Trade spend % of net</t>
+        </is>
+      </c>
+      <c r="B8" s="144" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="C8" s="144" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="D8" s="144" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="E8" s="103" t="inlineStr">
+        <is>
+          <t>Emerging-brand 10–20%+ ◐</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="59" t="inlineStr">
+        <is>
+          <t>Doors Y1 / Y2 / Y3</t>
+        </is>
+      </c>
+      <c r="B9" s="145" t="inlineStr">
+        <is>
+          <t>300/1.2k/3.5k</t>
+        </is>
+      </c>
+      <c r="C9" s="145" t="inlineStr">
+        <is>
+          <t>500/2k/6k</t>
+        </is>
+      </c>
+      <c r="D9" s="145" t="inlineStr">
+        <is>
+          <t>900/3.5k/11k</t>
+        </is>
+      </c>
+      <c r="E9" s="146" t="inlineStr">
+        <is>
+          <t>Illustrative beachhead→scale ramp ⚠</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="57" t="inlineStr">
+        <is>
+          <t>Velocity (u/store/wk)</t>
+        </is>
+      </c>
+      <c r="B10" s="144" t="inlineStr">
+        <is>
+          <t>2 / 3 / 3.5</t>
+        </is>
+      </c>
+      <c r="C10" s="144" t="inlineStr">
+        <is>
+          <t>3 / 4 / 5</t>
+        </is>
+      </c>
+      <c r="D10" s="144" t="inlineStr">
+        <is>
+          <t>4.5 / 6 / 7.5</t>
+        </is>
+      </c>
+      <c r="E10" s="103" t="inlineStr">
+        <is>
+          <t>Illustrative; buyers reward velocity ⚠</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="59" t="inlineStr">
+        <is>
+          <t>Marketing / yr</t>
+        </is>
+      </c>
+      <c r="B11" s="145" t="inlineStr">
+        <is>
+          <t>$150k</t>
+        </is>
+      </c>
+      <c r="C11" s="145" t="inlineStr">
+        <is>
+          <t>$300k</t>
+        </is>
+      </c>
+      <c r="D11" s="145" t="inlineStr">
+        <is>
+          <t>$600k</t>
+        </is>
+      </c>
+      <c r="E11" s="146" t="inlineStr">
+        <is>
+          <t>Illustrative challenger budget ⚠</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="57" t="inlineStr">
+        <is>
+          <t>Fixed overhead / yr</t>
+        </is>
+      </c>
+      <c r="B12" s="144" t="inlineStr">
+        <is>
+          <t>$250k</t>
+        </is>
+      </c>
+      <c r="C12" s="144" t="inlineStr">
+        <is>
+          <t>$350k</t>
+        </is>
+      </c>
+      <c r="D12" s="144" t="inlineStr">
+        <is>
+          <t>$500k</t>
+        </is>
+      </c>
+      <c r="E12" s="103" t="inlineStr">
+        <is>
+          <t>Illustrative ⚠</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="59" t="inlineStr">
+        <is>
+          <t>Slotting (Y1 one-time)</t>
+        </is>
+      </c>
+      <c r="B13" s="145" t="inlineStr">
+        <is>
+          <t>$50k</t>
+        </is>
+      </c>
+      <c r="C13" s="145" t="inlineStr">
+        <is>
+          <t>$100k</t>
+        </is>
+      </c>
+      <c r="D13" s="145" t="inlineStr">
+        <is>
+          <t>$200k</t>
+        </is>
+      </c>
+      <c r="E13" s="146" t="inlineStr">
+        <is>
+          <t>Slotting $250–$250k/SKU range ◐</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="147" t="inlineStr">
+        <is>
+          <t>All financial inputs are ILLUSTRATIVE planning scaffolding, not a forecast. Replace each with real co-packer, distributor and buyer numbers. ◐ rule-of-thumb · ⚠ estimate/illustrative.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -18029,128 +18651,4 @@
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="0014304F"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="88" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Methodology &amp; Confidence Framework</t>
-        </is>
-      </c>
-      <c r="M1" s="95" t="inlineStr">
-        <is>
-          <t>🏠 Home</t>
-        </is>
-      </c>
-      <c r="N1" s="95" t="inlineStr">
-        <is>
-          <t>↩ Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Element</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="92" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Research design</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Six parallel research streams: (1) market sizing, (2) channel economics, (3) extended competitor sweep, (4) Canada market + regulatory, (5) launch-playbook teardowns, (6) consumer trends + risk. Each ran independent multi-source web research with per-claim citation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="92" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Source hierarchy</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Decision-grade → scanner data (Circana/SPINS), company/SEC filings (LMNT Reg CF), regulatory primary (Health Canada, CFIA, FDR), transaction/press releases. Directional → syndicated research-firm market sizes (Grand View, FMI, Mordor) which vary widely by category definition. Lowest → single secondary sources / social estimates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="92" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Confidence tagging</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Every load-bearing figure is tagged HARD / DIRECTIONAL / FLAG. Where sources conflict (collagen market size; prebiotic soda; adaptogen market) both figures are shown and the conflict flagged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="92" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Known limitations</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>(a) Many primary publisher pages (CNBC, Entrepreneur, Circana, canada.ca) block automated fetch (HTTP 403); figures were captured via search extracts of those same pages plus corroborating sources — re-verify load-bearing numbers from the cited URLs before external use. (b) Private-company margins and Canadian per-SKU listing fees are confidential; ranges are industry rules-of-thumb. (c) Female-skew % and licensed Circana/Mintel splits sit behind paywalls.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="92" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>What would strengthen this</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Licensed Circana/SPINS pull for Canada; a regulatory-counsel opinion on the Supplemented-Foods claim set; primary interviews with 2–3 Canadian distributors (UNFI Canada, Tree of Life, Purity Life); a co-packer capacity/quote for a Canadian RTD line.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
 </file>
--- a/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
+++ b/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
@@ -43,8 +43,9 @@
     <sheet name="22 Risk Register" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="23 KPI Dashboard" sheetId="35" state="visible" r:id="rId35"/>
     <sheet name="24 Sources" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="Verification Log" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="25 Glossary" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Data Confidence" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="Verification Log" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="25 Glossary" sheetId="39" state="visible" r:id="rId39"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'🏠 Start Here'!$A$1:$E$25</definedName>
@@ -83,8 +84,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="33">'22 Risk Register'!$A$1:$N$16</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="34">'23 KPI Dashboard'!$A$1:$N$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="35">'24 Sources'!$A$1:$N$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="36">'Verification Log'!$A$1:$N$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="37">'25 Glossary'!$A$1:$N$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="37">'Verification Log'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="38">'25 Glossary'!$A$1:$N$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -98,7 +99,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -304,6 +305,27 @@
       <color rgb="00FFFFFF"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -505,7 +527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -939,6 +961,25 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1870,6 +1911,88 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Confidence tag distribution</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Data Confidence'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Data Confidence'!$B$5:$B$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data Confidence'!$C$5:$C$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
@@ -2069,6 +2192,33 @@
       <rowOff>0</rowOff>
     </from>
     <ext cx="5760000" cy="3060000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4680000" cy="2520000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -2376,7 +2526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2389,6 +2539,7 @@
     <col width="3" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="44" customHeight="1">
       <c r="B2" s="110" t="inlineStr">
         <is>
@@ -2403,6 +2554,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="112" t="inlineStr">
         <is>
@@ -2432,6 +2584,7 @@
       <c r="C7" s="121" t="n"/>
       <c r="D7" s="121" t="n"/>
     </row>
+    <row r="8"/>
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="112" t="inlineStr">
         <is>
@@ -2461,6 +2614,7 @@
       <c r="C11" s="121" t="n"/>
       <c r="D11" s="121" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13" ht="22" customHeight="1">
       <c r="B13" s="112" t="inlineStr">
         <is>
@@ -2490,6 +2644,7 @@
       <c r="C15" s="121" t="n"/>
       <c r="D15" s="121" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="B17" s="112" t="inlineStr">
         <is>
@@ -2519,6 +2674,7 @@
       <c r="C19" s="121" t="n"/>
       <c r="D19" s="121" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21" ht="22" customHeight="1">
       <c r="B21" s="112" t="inlineStr">
         <is>
@@ -2548,6 +2704,7 @@
       <c r="C23" s="121" t="n"/>
       <c r="D23" s="121" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25" ht="34" customHeight="1">
       <c r="B25" s="119" t="inlineStr">
         <is>
@@ -2637,6 +2794,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -2773,6 +2931,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -3180,6 +3339,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
@@ -3335,6 +3495,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
@@ -3521,6 +3682,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -3780,6 +3942,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -3882,6 +4045,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
@@ -4671,6 +4835,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="64" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -5176,6 +5341,8 @@
       <c r="F22" s="34" t="n"/>
       <c r="G22" s="35" t="n"/>
     </row>
+    <row r="23"/>
+    <row r="24"/>
     <row r="25" hidden="1">
       <c r="A25" s="41" t="inlineStr">
         <is>
@@ -5314,6 +5481,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
@@ -6749,6 +6917,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -7065,6 +7234,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -7191,6 +7361,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
@@ -7351,6 +7522,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
@@ -7443,6 +7615,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
@@ -7623,6 +7796,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -7906,7 +8080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:M24"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7937,6 +8111,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="138" t="inlineStr">
         <is>
@@ -8063,6 +8238,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="B24" s="142" t="inlineStr">
         <is>
@@ -8135,6 +8311,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -8399,6 +8576,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -8625,6 +8803,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
         <is>
@@ -8702,6 +8881,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
         <is>
@@ -8827,6 +9007,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -9247,6 +9428,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -9503,6 +9685,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -9832,6 +10015,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -9925,6 +10109,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
@@ -10086,6 +10271,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -10212,6 +10398,7 @@
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
@@ -10321,6 +10508,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
@@ -10489,6 +10677,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -10615,6 +10804,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
@@ -10690,6 +10880,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
@@ -10765,6 +10956,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
@@ -10883,6 +11075,7 @@
       <c r="B32" s="34" t="n"/>
       <c r="C32" s="35" t="n"/>
     </row>
+    <row r="33"/>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="96" t="inlineStr">
         <is>
@@ -11025,6 +11218,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -11481,6 +11675,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -12297,6 +12492,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="28" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -12329,7 +12525,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Whether/how to launch a Canadian functional collagen sparkling beverage (“MUV”)</t>
+          <t>Whether/how to launch MÜV — a Canadian sparkling electrolyte RTD (can) — in Canada</t>
         </is>
       </c>
     </row>
@@ -12377,7 +12573,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -12389,10 +12585,11 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Draft for internal review — verify amber-flagged items before external circulation</t>
-        </is>
-      </c>
-    </row>
+          <t>Working draft — 38+ tabs. Start on 🏠 Start Here; one-page summary on Executive Brief 1-page. Interactive: Financial Model · Scenario Comparison · Go-NoGo. Verify amber-flagged items before external use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15" ht="96" customHeight="1">
       <c r="A15" s="17" t="inlineStr">
         <is>
@@ -12406,6 +12603,7 @@
       <c r="F15" s="34" t="n"/>
       <c r="G15" s="35" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -12452,6 +12650,7 @@
       <c r="G20" s="34" t="n"/>
       <c r="H20" s="35" t="n"/>
     </row>
+    <row r="21"/>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="6" t="inlineStr">
         <is>
@@ -12601,6 +12800,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
         <is>
@@ -12768,6 +12968,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -12969,6 +13170,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="40" t="inlineStr">
         <is>
@@ -12982,6 +13184,7 @@
       <c r="D14" s="34" t="n"/>
       <c r="E14" s="35" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
         <is>
@@ -13070,6 +13273,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -13318,6 +13522,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -13516,6 +13721,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -13908,6 +14114,8 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="138" t="inlineStr">
         <is>
@@ -14075,6 +14283,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -14379,6 +14588,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -14838,6 +15048,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
@@ -14895,6 +15106,149 @@
   <sheetPr>
     <tabColor rgb="00C9A227"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="153" t="inlineStr">
+        <is>
+          <t>Data Confidence Scoreboard</t>
+        </is>
+      </c>
+      <c r="M1" s="95" t="inlineStr">
+        <is>
+          <t>🏠 Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="154" t="inlineStr">
+        <is>
+          <t>Tally of confidence tags across the whole dossier — how much rests on hard evidence vs estimates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="74" t="inlineStr">
+        <is>
+          <t>Confidence tier</t>
+        </is>
+      </c>
+      <c r="B4" s="74" t="inlineStr">
+        <is>
+          <t>Marker</t>
+        </is>
+      </c>
+      <c r="C4" s="74" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="D4" s="74" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="109" t="inlineStr">
+        <is>
+          <t>Hard (primary/scanner/regulatory)</t>
+        </is>
+      </c>
+      <c r="B5" s="144" t="inlineStr">
+        <is>
+          <t>✅ HARD</t>
+        </is>
+      </c>
+      <c r="C5" s="155" t="n">
+        <v>48</v>
+      </c>
+      <c r="D5" s="156" t="n">
+        <v>0.4403669724770642</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="59" t="inlineStr">
+        <is>
+          <t>Directional (research-firm/single-source)</t>
+        </is>
+      </c>
+      <c r="B6" s="144" t="inlineStr">
+        <is>
+          <t>◐ DIRECTIONAL</t>
+        </is>
+      </c>
+      <c r="C6" s="155" t="n">
+        <v>28</v>
+      </c>
+      <c r="D6" s="156" t="n">
+        <v>0.2568807339449541</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="157" t="inlineStr">
+        <is>
+          <t>Flag (estimate/verify/contested)</t>
+        </is>
+      </c>
+      <c r="B7" s="144" t="inlineStr">
+        <is>
+          <t>⚠ FLAG</t>
+        </is>
+      </c>
+      <c r="C7" s="155" t="n">
+        <v>33</v>
+      </c>
+      <c r="D7" s="156" t="n">
+        <v>0.3027522935779817</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="158" t="inlineStr">
+        <is>
+          <t>TOTAL tags</t>
+        </is>
+      </c>
+      <c r="C8" s="159" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="119" t="inlineStr">
+        <is>
+          <t>Read: a healthy dossier leans on hard/primary evidence for its load-bearing claims (verified on the Verification Log) while transparently flagging estimates. Market-size projections and all financial inputs are ◐/⚠ by nature — never quote them as fact.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N16"/>
@@ -14931,6 +15285,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -15208,6 +15563,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="56" t="inlineStr">
         <is>
@@ -15234,7 +15590,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -15265,6 +15621,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -15553,6 +15910,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="42" t="inlineStr">
         <is>
@@ -15709,7 +16067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -15728,6 +16086,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -16193,6 +16552,18 @@
       <c r="B41" s="103" t="inlineStr">
         <is>
           <t>Every model input with its source &amp; confidence tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="120" t="inlineStr">
+        <is>
+          <t>Data Confidence</t>
+        </is>
+      </c>
+      <c r="B42" s="103" t="inlineStr">
+        <is>
+          <t>Scoreboard: ✅/◐/⚠ tag counts across the dossier</t>
         </is>
       </c>
     </row>
@@ -16240,6 +16611,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -16292,6 +16664,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -16307,6 +16680,7 @@
       </c>
       <c r="B5" s="35" t="n"/>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
@@ -16410,6 +16784,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="92" customHeight="1">
       <c r="A17" s="17" t="inlineStr">
         <is>
@@ -16492,6 +16867,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="36" t="inlineStr">
         <is>
@@ -16588,6 +16964,38 @@
       </c>
       <c r="J6" s="35" t="n"/>
     </row>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="41" t="inlineStr">
         <is>
@@ -16595,6 +17003,36 @@
         </is>
       </c>
     </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
     <row r="70" hidden="1">
       <c r="A70" s="40" t="inlineStr">
         <is>
@@ -16961,6 +17399,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="62" t="inlineStr">
         <is>
@@ -17332,6 +17771,7 @@
         <v/>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="42" t="inlineStr">
         <is>
@@ -17394,6 +17834,7 @@
         <v/>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="42" t="inlineStr">
         <is>
@@ -17651,6 +18092,7 @@
         <v/>
       </c>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="42" t="inlineStr">
         <is>
@@ -17713,6 +18155,7 @@
         <v/>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="42" t="inlineStr">
         <is>
@@ -17867,6 +18310,7 @@
         <v/>
       </c>
     </row>
+    <row r="60"/>
     <row r="61" ht="58" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
@@ -17974,6 +18418,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="74" t="inlineStr">
         <is>
@@ -18271,12 +18716,17 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="147" t="inlineStr">
         <is>
           <t>All financial inputs are ILLUSTRATIVE planning scaffolding, not a forecast. Replace each with real co-packer, distributor and buyer numbers. ◐ rule-of-thumb · ⚠ estimate/illustrative.</t>
         </is>
       </c>
+      <c r="B15" s="34" t="n"/>
+      <c r="C15" s="34" t="n"/>
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -18332,6 +18782,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="74" t="inlineStr">
         <is>
@@ -18514,6 +18965,8 @@
         <v>2972910.555999999</v>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17" hidden="1">
       <c r="A17" s="41" t="inlineStr">
         <is>
@@ -18577,6 +19030,18 @@
         <v>2972911</v>
       </c>
     </row>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
     <row r="34" ht="52" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
@@ -18588,6 +19053,8 @@
       <c r="D34" s="34" t="n"/>
       <c r="E34" s="35" t="n"/>
     </row>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37" hidden="1">
       <c r="A37" s="41" t="inlineStr">
         <is>

--- a/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
+++ b/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
@@ -527,7 +527,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -981,6 +981,21 @@
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2526,7 +2541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="B2:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2539,7 +2554,6 @@
     <col width="3" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="44" customHeight="1">
       <c r="B2" s="110" t="inlineStr">
         <is>
@@ -2554,7 +2568,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="112" t="inlineStr">
         <is>
@@ -2584,7 +2597,6 @@
       <c r="C7" s="121" t="n"/>
       <c r="D7" s="121" t="n"/>
     </row>
-    <row r="8"/>
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="112" t="inlineStr">
         <is>
@@ -2614,7 +2626,6 @@
       <c r="C11" s="121" t="n"/>
       <c r="D11" s="121" t="n"/>
     </row>
-    <row r="12"/>
     <row r="13" ht="22" customHeight="1">
       <c r="B13" s="112" t="inlineStr">
         <is>
@@ -2644,7 +2655,6 @@
       <c r="C15" s="121" t="n"/>
       <c r="D15" s="121" t="n"/>
     </row>
-    <row r="16"/>
     <row r="17" ht="22" customHeight="1">
       <c r="B17" s="112" t="inlineStr">
         <is>
@@ -2674,7 +2684,6 @@
       <c r="C19" s="121" t="n"/>
       <c r="D19" s="121" t="n"/>
     </row>
-    <row r="20"/>
     <row r="21" ht="22" customHeight="1">
       <c r="B21" s="112" t="inlineStr">
         <is>
@@ -2704,7 +2713,6 @@
       <c r="C23" s="121" t="n"/>
       <c r="D23" s="121" t="n"/>
     </row>
-    <row r="24"/>
     <row r="25" ht="34" customHeight="1">
       <c r="B25" s="119" t="inlineStr">
         <is>
@@ -2794,7 +2802,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -2931,7 +2938,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -3339,7 +3345,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
@@ -3495,7 +3500,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="15" t="inlineStr">
         <is>
@@ -3682,7 +3686,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -3942,7 +3945,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -4045,7 +4047,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
@@ -4835,7 +4836,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="64" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -5341,8 +5341,6 @@
       <c r="F22" s="34" t="n"/>
       <c r="G22" s="35" t="n"/>
     </row>
-    <row r="23"/>
-    <row r="24"/>
     <row r="25" hidden="1">
       <c r="A25" s="41" t="inlineStr">
         <is>
@@ -5481,7 +5479,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
@@ -6917,7 +6914,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -7234,7 +7230,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -7361,7 +7356,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
@@ -7522,7 +7516,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
@@ -7615,7 +7608,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
@@ -7796,7 +7788,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -8080,7 +8071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="B1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -8111,7 +8102,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5" ht="18" customHeight="1">
       <c r="B5" s="138" t="inlineStr">
         <is>
@@ -8238,7 +8228,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="B24" s="142" t="inlineStr">
         <is>
@@ -8311,7 +8300,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -8576,7 +8564,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -8803,7 +8790,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
         <is>
@@ -8881,7 +8867,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
         <is>
@@ -9007,7 +8992,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -9428,7 +9412,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -9685,7 +9668,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
@@ -10015,7 +9997,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="58" customHeight="1">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -10109,7 +10090,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
@@ -10271,7 +10251,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -10398,7 +10377,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
@@ -10508,7 +10486,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
@@ -10677,7 +10654,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -10804,7 +10780,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
@@ -10880,7 +10855,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="18" t="inlineStr">
         <is>
@@ -10956,7 +10930,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" s="15" t="inlineStr">
         <is>
@@ -11075,7 +11048,6 @@
       <c r="B32" s="34" t="n"/>
       <c r="C32" s="35" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="96" t="inlineStr">
         <is>
@@ -11218,7 +11190,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="58" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -11675,7 +11646,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="60" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -12492,7 +12462,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6" ht="28" customHeight="1">
       <c r="B6" s="4" t="inlineStr">
         <is>
@@ -12589,7 +12558,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="96" customHeight="1">
       <c r="A15" s="17" t="inlineStr">
         <is>
@@ -12603,7 +12571,6 @@
       <c r="F15" s="34" t="n"/>
       <c r="G15" s="35" t="n"/>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -12650,7 +12617,6 @@
       <c r="G20" s="34" t="n"/>
       <c r="H20" s="35" t="n"/>
     </row>
-    <row r="21"/>
     <row r="22" ht="18" customHeight="1">
       <c r="B22" s="6" t="inlineStr">
         <is>
@@ -12800,7 +12766,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="52" customHeight="1">
       <c r="A3" s="17" t="inlineStr">
         <is>
@@ -12968,7 +12933,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -13170,7 +13134,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="40" t="inlineStr">
         <is>
@@ -13184,7 +13147,6 @@
       <c r="D14" s="34" t="n"/>
       <c r="E14" s="35" t="n"/>
     </row>
-    <row r="15"/>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="17" t="inlineStr">
         <is>
@@ -13273,7 +13235,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -13522,7 +13483,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -13721,7 +13681,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -14114,8 +14073,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="138" t="inlineStr">
         <is>
@@ -14283,7 +14240,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -14588,7 +14544,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -15048,7 +15003,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
@@ -15228,6 +15182,9 @@
           <t>Read: a healthy dossier leans on hard/primary evidence for its load-bearing claims (verified on the Verification Log) while transparently flagging estimates. Market-size projections and all financial inputs are ◐/⚠ by nature — never quote them as fact.</t>
         </is>
       </c>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="34" t="n"/>
+      <c r="D24" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -15285,7 +15242,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -15563,7 +15519,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="56" t="inlineStr">
         <is>
@@ -15621,7 +15576,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -15910,7 +15864,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
     <row r="28">
       <c r="A28" s="42" t="inlineStr">
         <is>
@@ -16067,7 +16020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -16086,7 +16039,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -16567,8 +16519,88 @@
         </is>
       </c>
     </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="160" t="inlineStr">
+        <is>
+          <t>HOW TO NAVIGATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="161" t="inlineStr">
+        <is>
+          <t>Click any tab name above</t>
+        </is>
+      </c>
+      <c r="B45" s="162" t="inlineStr">
+        <is>
+          <t>jumps straight to that tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="163" t="inlineStr">
+        <is>
+          <t>🏠 Start Here</t>
+        </is>
+      </c>
+      <c r="B46" s="164" t="inlineStr">
+        <is>
+          <t>the front door — grouped cards to every section (workbook opens here)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="161" t="inlineStr">
+        <is>
+          <t>🏠 Home (top-right of every tab)</t>
+        </is>
+      </c>
+      <c r="B47" s="162" t="inlineStr">
+        <is>
+          <t>returns to Start Here</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="163" t="inlineStr">
+        <is>
+          <t>Gold tab</t>
+        </is>
+      </c>
+      <c r="B48" s="164" t="inlineStr">
+        <is>
+          <t>interactive: Financial Model, Scenario Comparison, Go-NoGo, Peer Set, Data Confidence, etc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="161" t="inlineStr">
+        <is>
+          <t>Executive Brief 1-page</t>
+        </is>
+      </c>
+      <c r="B49" s="162" t="inlineStr">
+        <is>
+          <t>the whole recommendation on one printable page</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="163" t="inlineStr">
+        <is>
+          <t>Confidence tags ✅ / ◐ / ⚠</t>
+        </is>
+      </c>
+      <c r="B50" s="164" t="inlineStr">
+        <is>
+          <t>hard evidence / directional / estimate-or-flag (see Data Confidence scoreboard)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A44:B44"/>
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <hyperlinks>
@@ -16664,7 +16696,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
@@ -16680,7 +16711,6 @@
       </c>
       <c r="B5" s="35" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
@@ -16784,7 +16814,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="92" customHeight="1">
       <c r="A17" s="17" t="inlineStr">
         <is>
@@ -16867,7 +16896,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="36" t="inlineStr">
         <is>
@@ -16964,38 +16992,6 @@
       </c>
       <c r="J6" s="35" t="n"/>
     </row>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="41" t="inlineStr">
         <is>
@@ -17003,36 +16999,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
-    <row r="63"/>
-    <row r="64"/>
-    <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
-    <row r="69"/>
     <row r="70" hidden="1">
       <c r="A70" s="40" t="inlineStr">
         <is>
@@ -17399,7 +17365,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="62" t="inlineStr">
         <is>
@@ -17771,7 +17736,6 @@
         <v/>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="42" t="inlineStr">
         <is>
@@ -17834,7 +17798,6 @@
         <v/>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="42" t="inlineStr">
         <is>
@@ -18092,7 +18055,6 @@
         <v/>
       </c>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="42" t="inlineStr">
         <is>
@@ -18155,7 +18117,6 @@
         <v/>
       </c>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="42" t="inlineStr">
         <is>
@@ -18310,7 +18271,6 @@
         <v/>
       </c>
     </row>
-    <row r="60"/>
     <row r="61" ht="58" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
@@ -18418,7 +18378,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="74" t="inlineStr">
         <is>
@@ -18716,7 +18675,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="147" t="inlineStr">
         <is>
@@ -18782,7 +18740,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="74" t="inlineStr">
         <is>
@@ -18965,8 +18922,6 @@
         <v>2972910.555999999</v>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
     <row r="17" hidden="1">
       <c r="A17" s="41" t="inlineStr">
         <is>
@@ -19030,18 +18985,6 @@
         <v>2972911</v>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
     <row r="34" ht="52" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
@@ -19053,8 +18996,6 @@
       <c r="D34" s="34" t="n"/>
       <c r="E34" s="35" t="n"/>
     </row>
-    <row r="35"/>
-    <row r="36"/>
     <row r="37" hidden="1">
       <c r="A37" s="41" t="inlineStr">
         <is>

--- a/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
+++ b/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
@@ -37,15 +37,17 @@
     <sheet name="Canada Regulatory v2" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="Electrolyte BFY Deep-Dive" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="20 GTM Recommendation" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="Go-NoGo Decision" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="Battlecards" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="21 Launch Plan" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="22 Risk Register" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="23 KPI Dashboard" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="24 Sources" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="Data Confidence" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="Verification Log" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="25 Glossary" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="How to Present" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="Next Steps &amp; Gates" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Go-NoGo Decision" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Battlecards" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="21 Launch Plan" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="22 Risk Register" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="23 KPI Dashboard" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="24 Sources" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Data Confidence" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="Verification Log" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="25 Glossary" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'🏠 Start Here'!$A$1:$E$25</definedName>
@@ -78,14 +80,14 @@
     <definedName name="_xlnm.Print_Area" localSheetId="27">'Canada Regulatory v2'!$A$1:$N$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="28">'Electrolyte BFY Deep-Dive'!$A$1:$N$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="29">'20 GTM Recommendation'!$A$1:$N$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="30">'Go-NoGo Decision'!$A$1:$N$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="31">'Battlecards'!$A$1:$N$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="32">'21 Launch Plan'!$A$1:$N$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="33">'22 Risk Register'!$A$1:$N$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="34">'23 KPI Dashboard'!$A$1:$N$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="35">'24 Sources'!$A$1:$N$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="37">'Verification Log'!$A$1:$N$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="38">'25 Glossary'!$A$1:$N$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="32">'Go-NoGo Decision'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="33">'Battlecards'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="34">'21 Launch Plan'!$A$1:$N$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="35">'22 Risk Register'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="36">'23 KPI Dashboard'!$A$1:$N$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="37">'24 Sources'!$A$1:$N$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="39">'Verification Log'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="40">'25 Glossary'!$A$1:$N$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -527,7 +529,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -996,6 +998,10 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12899,6 +12905,553 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:M14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="153" t="inlineStr">
+        <is>
+          <t>How to Present — leadership readout</t>
+        </is>
+      </c>
+      <c r="M1" s="95" t="inlineStr">
+        <is>
+          <t>🏠 Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="154" t="inlineStr">
+        <is>
+          <t>One line to say on each key tab. Lead with the decision; let the tabs back it up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="74" t="inlineStr">
+        <is>
+          <t>Tab</t>
+        </is>
+      </c>
+      <c r="B4" s="74" t="inlineStr">
+        <is>
+          <t>Say this</t>
+        </is>
+      </c>
+      <c r="C4" s="74" t="inlineStr">
+        <is>
+          <t>Then show</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="57" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="B5" s="103" t="inlineStr">
+        <is>
+          <t>“One decision: GO — conditional. Launch MÜV as daily-wellness sparkling hydration, made in Canada.”</t>
+        </is>
+      </c>
+      <c r="C5" s="103" t="inlineStr">
+        <is>
+          <t>Executive Brief 1-page</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="59" t="inlineStr">
+        <is>
+          <t>Executive Brief</t>
+        </is>
+      </c>
+      <c r="B6" s="146" t="inlineStr">
+        <is>
+          <t>“Here's the whole case on one page — verdict, numbers, five moves, risks.”</t>
+        </is>
+      </c>
+      <c r="C6" s="146" t="inlineStr">
+        <is>
+          <t>Executive Brief 1-page</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="57" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="B7" s="103" t="inlineStr">
+        <is>
+          <t>“The category is real: modern soda $1.8B (+83%), hydration powders $1.5B (+20%).”</t>
+        </is>
+      </c>
+      <c r="C7" s="103" t="inlineStr">
+        <is>
+          <t>Dashboard charts</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="59" t="inlineStr">
+        <is>
+          <t>MÜV Peer Set</t>
+        </is>
+      </c>
+      <c r="B8" s="146" t="inlineStr">
+        <is>
+          <t>“We compete with LMNT, Liquid I.V., Nuun — not Poppi. Sparkling is our wedge.”</t>
+        </is>
+      </c>
+      <c r="C8" s="146" t="inlineStr">
+        <is>
+          <t>peer ladder + scatter</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="57" t="inlineStr">
+        <is>
+          <t>Financial Model</t>
+        </is>
+      </c>
+      <c r="B9" s="103" t="inlineStr">
+        <is>
+          <t>“Flip the scenario. Even Conservative has a defined break-even; Base is healthy.”</t>
+        </is>
+      </c>
+      <c r="C9" s="103" t="inlineStr">
+        <is>
+          <t>scenario dropdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="59" t="inlineStr">
+        <is>
+          <t>Canada Regulatory v2</t>
+        </is>
+      </c>
+      <c r="B10" s="146" t="inlineStr">
+        <is>
+          <t>“It's a food, not an NHP. We label to Supplemented Foods now; collagen claims stay on the powder.”</t>
+        </is>
+      </c>
+      <c r="C10" s="146" t="inlineStr">
+        <is>
+          <t>claims fork table</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="57" t="inlineStr">
+        <is>
+          <t>Go-No-Go</t>
+        </is>
+      </c>
+      <c r="B11" s="103" t="inlineStr">
+        <is>
+          <t>“The weighted gates say GO — conditional. The conditions are dose/claims and regulatory sign-off.”</t>
+        </is>
+      </c>
+      <c r="C11" s="103" t="inlineStr">
+        <is>
+          <t>auto-verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="59" t="inlineStr">
+        <is>
+          <t>Data Confidence / Verification Log</t>
+        </is>
+      </c>
+      <c r="B12" s="146" t="inlineStr">
+        <is>
+          <t>“Every load-bearing number is primary-sourced; estimates are flagged, not hidden.”</t>
+        </is>
+      </c>
+      <c r="C12" s="146" t="inlineStr">
+        <is>
+          <t>scoreboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="57" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="B13" s="103" t="inlineStr">
+        <is>
+          <t>“Top three risks — claims liability, big-CPG rivals, over-distribution — all mitigable.”</t>
+        </is>
+      </c>
+      <c r="C13" s="103" t="inlineStr">
+        <is>
+          <t>heatmap</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="32" customHeight="1">
+      <c r="A14" s="59" t="inlineStr">
+        <is>
+          <t>The ask</t>
+        </is>
+      </c>
+      <c r="B14" s="146" t="inlineStr">
+        <is>
+          <t>“Approve Phase 0: confirm MÜV specs, regulatory sign-off, co-packer quote, Costco beachhead.”</t>
+        </is>
+      </c>
+      <c r="C14" s="146" t="inlineStr">
+        <is>
+          <t>Next Steps &amp; Gates</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="153" t="inlineStr">
+        <is>
+          <t>Next Steps &amp; Decision Gates</t>
+        </is>
+      </c>
+      <c r="M1" s="95" t="inlineStr">
+        <is>
+          <t>🏠 Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="154" t="inlineStr">
+        <is>
+          <t>Immediate actions to move MÜV forward. Status is illustrative — set owners/dates with the team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="74" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="74" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C4" s="74" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D4" s="74" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="E4" s="74" t="inlineStr">
+        <is>
+          <t>Why it's a gate</t>
+        </is>
+      </c>
+      <c r="F4" s="74" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="103" t="inlineStr">
+        <is>
+          <t>Confirm MÜV on-can specs (sodium mg, pack size, any collagen variant)</t>
+        </is>
+      </c>
+      <c r="C5" s="103" t="inlineStr">
+        <is>
+          <t>Brand / R&amp;D</t>
+        </is>
+      </c>
+      <c r="D5" s="103" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E5" s="103" t="inlineStr">
+        <is>
+          <t>Unblocks claims + fills the last model input</t>
+        </is>
+      </c>
+      <c r="F5" s="166" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="146" t="inlineStr">
+        <is>
+          <t>Regulatory counsel sign-off on the claim set (Supplemented Food)</t>
+        </is>
+      </c>
+      <c r="C6" s="146" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="D6" s="146" t="inlineStr">
+        <is>
+          <t>Wk 1–3</t>
+        </is>
+      </c>
+      <c r="E6" s="146" t="inlineStr">
+        <is>
+          <t>De-risks the label; must precede artwork</t>
+        </is>
+      </c>
+      <c r="F6" s="166" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="57" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="103" t="inlineStr">
+        <is>
+          <t>Canadian co-packer quote + capacity</t>
+        </is>
+      </c>
+      <c r="C7" s="103" t="inlineStr">
+        <is>
+          <t>Ops</t>
+        </is>
+      </c>
+      <c r="D7" s="103" t="inlineStr">
+        <is>
+          <t>Wk 1–4</t>
+        </is>
+      </c>
+      <c r="E7" s="103" t="inlineStr">
+        <is>
+          <t>Real COGS replaces the illustrative model input</t>
+        </is>
+      </c>
+      <c r="F7" s="166" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="59" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="146" t="inlineStr">
+        <is>
+          <t>Bilingual + Quebec Bill 96 artwork</t>
+        </is>
+      </c>
+      <c r="C8" s="146" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D8" s="146" t="inlineStr">
+        <is>
+          <t>Wk 3–6</t>
+        </is>
+      </c>
+      <c r="E8" s="146" t="inlineStr">
+        <is>
+          <t>Compliance; long-lead for print</t>
+        </is>
+      </c>
+      <c r="F8" s="166" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="103" t="inlineStr">
+        <is>
+          <t>Costco Canada roadshow slot + Amazon.ca / Well.ca listings</t>
+        </is>
+      </c>
+      <c r="C9" s="103" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D9" s="103" t="inlineStr">
+        <is>
+          <t>Wk 4–9</t>
+        </is>
+      </c>
+      <c r="E9" s="103" t="inlineStr">
+        <is>
+          <t>The beachhead trial engine</t>
+        </is>
+      </c>
+      <c r="F9" s="166" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="146" t="inlineStr">
+        <is>
+          <t>Define velocity + repeat-rate targets (KPIs)</t>
+        </is>
+      </c>
+      <c r="C10" s="146" t="inlineStr">
+        <is>
+          <t>Sales / Finance</t>
+        </is>
+      </c>
+      <c r="D10" s="146" t="inlineStr">
+        <is>
+          <t>Wk 2</t>
+        </is>
+      </c>
+      <c r="E10" s="146" t="inlineStr">
+        <is>
+          <t>Gates Phase 2 national sell-in</t>
+        </is>
+      </c>
+      <c r="F10" s="166" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="103" t="inlineStr">
+        <is>
+          <t>Board approval of Phase 0 budget</t>
+        </is>
+      </c>
+      <c r="C11" s="103" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
+      </c>
+      <c r="D11" s="103" t="inlineStr">
+        <is>
+          <t>Wk 1</t>
+        </is>
+      </c>
+      <c r="E11" s="103" t="inlineStr">
+        <is>
+          <t>Greenlights the above</t>
+        </is>
+      </c>
+      <c r="F11" s="166" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>Sequenced to the Launch Plan (Tab 21): #1–4 = Phase 0 foundation, #5–6 = Phase 1 beachhead.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13193,7 +13746,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C9A227"/>
@@ -13431,756 +13984,6 @@
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00B45309"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Phased Launch Plan (0–18 months)</t>
-        </is>
-      </c>
-      <c r="M1" s="95" t="inlineStr">
-        <is>
-          <t>🏠 Home</t>
-        </is>
-      </c>
-      <c r="N1" s="95" t="inlineStr">
-        <is>
-          <t>↩ Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Phase</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Timing</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Objectives</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Key workstreams</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Success gate</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="80" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Phase 0 — Foundation</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Months 0–3</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Lock product, claims, regulatory pathway, co-pack</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Finalize formula &amp; collagen dose; regulatory-counsel claim opinion (Supplemented Foods); co-packer quote &amp; MOQ; bilingual + Bill 96 artwork; brand/positioning</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory sign-off on claim set + artwork approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="80" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1 — Beachhead</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Months 3–9</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Prove velocity &amp; repeat in a contained beachhead</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Costco CA roadshows + Amazon.ca + Well.ca/Natura + Organika pharmacy/health-food base; podcast + reactive social; sampling</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>Repeat rate + velocity above category benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Phase 2 — Scale</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Months 9–18</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Earn conventional grocery on proven data</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Sell-in to Loblaw/Sobeys/Metro on velocity data; distributor (UNFI CA / Tree of Life); managed trade spend; add SKUs on repeat data</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>National listings won on data, not discounts</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Phase 3 — Defend &amp; extend</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>18 mo+</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Category leadership &amp; optionality</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Format/flavour extensions; deepen moat; evaluate strategic-partner vs independent scale</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Profitable contribution + exit optionality</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00B45309"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Register</t>
-        </is>
-      </c>
-      <c r="M1" s="95" t="inlineStr">
-        <is>
-          <t>🏠 Home</t>
-        </is>
-      </c>
-      <c r="N1" s="95" t="inlineStr">
-        <is>
-          <t>↩ Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Likelihood × Impact (H/M/L). Ranked by exposure</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Likelihood</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Mitigation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Collagen efficacy / claims liability (2025 meta-analysis; Poppi-style dose-insufficiency suit)</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory/Legal</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>Dose to efficacy (2.5g+); structure/function-safe language; substantiation files; lead with gut/hydration not beauty</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Strategic-owned competition (Nestlé owns Vital Proteins; PepsiCo/Unilever firepower)</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E6" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>Compete on Canadian-made + domestic cost edge + Organika collagen credibility; niche beachhead before they react</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Canada claim/label pathway misread (food vs NHP; SFCI; collagen caution)</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory</t>
-        </is>
-      </c>
-      <c r="D7" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory-counsel opinion before artwork; design to Supplemented Foods framework; caffeine-free</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Over-distribution before product-market fit</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>Execution</t>
-        </is>
-      </c>
-      <c r="D8" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E8" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>Prove velocity/repeat in beachhead before national; gate Phase 2 on data</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Slotting / trade-spend cash burn</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E9" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Use free-fill over cash slotting; 35–45% trade-spend budget; Code of Conduct leverage on arbitrary fees</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Thin differentiation / shelf saturation (prebiotic shelf filling fast)</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D10" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E10" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Defensible spec (fiber + collagen dose) + function stacking; Canadian-made story</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Private-label encroachment (~$277B, ~21% share, growing 2×)</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D11" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E11" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Brand equity + clinical-grade ingredients retailers can't easily copy</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>DTC CAC / heavy-ship economics if DTC-led</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D12" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E12" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>Lead retail/beachhead not paid DTC; subscription + sampling only</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Co-packer capacity / collagen sourcing / cost inflation</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="D13" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E13" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>Lock co-pack capacity early; qualify 2nd collagen supplier; hedge raws</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>FX / tariff / freight premium on cross-border inputs</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D14" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E14" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>Domestic CA co-pack; monitor tariff status post-Dec 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>GLP-1 demand shift away from sweet/snack</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Macro</t>
-        </is>
-      </c>
-      <c r="D15" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E15" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Low-cal, fiber, protein, hydration positioning aligns with GLP-1 users</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>Brand/tone misstep at scale</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="D16" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E16" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>Evolve tactics with stage; avoid Poppi-style stunts once mainstream</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="138" t="inlineStr">
-        <is>
-          <t>LIKELIHOOD × IMPACT HEATMAP (risk #s placed by rating)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="148" t="inlineStr">
-        <is>
-          <t>Impact ↓ / Likelihood →</t>
-        </is>
-      </c>
-      <c r="B20" s="149" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C20" s="149" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="D20" s="149" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="149" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B21" s="150" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C21" s="151" t="inlineStr">
-        <is>
-          <t>3, 4, 5</t>
-        </is>
-      </c>
-      <c r="D21" s="151" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="149" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="B22" s="152" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C22" s="150" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10</t>
-        </is>
-      </c>
-      <c r="D22" s="151" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="149" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B23" s="152" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C23" s="152" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D23" s="150" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="133" t="inlineStr">
-        <is>
-          <t>Red = act now · Amber = manage · Green = monitor. Numbers refer to the risk # in the table above.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A24:F24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
@@ -14206,6 +14009,756 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Phased Launch Plan (0–18 months)</t>
+        </is>
+      </c>
+      <c r="M1" s="95" t="inlineStr">
+        <is>
+          <t>🏠 Home</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Objectives</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Key workstreams</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Success gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Phase 0 — Foundation</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Months 0–3</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Lock product, claims, regulatory pathway, co-pack</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Finalize formula &amp; collagen dose; regulatory-counsel claim opinion (Supplemented Foods); co-packer quote &amp; MOQ; bilingual + Bill 96 artwork; brand/positioning</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory sign-off on claim set + artwork approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1 — Beachhead</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Months 3–9</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Prove velocity &amp; repeat in a contained beachhead</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Costco CA roadshows + Amazon.ca + Well.ca/Natura + Organika pharmacy/health-food base; podcast + reactive social; sampling</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Repeat rate + velocity above category benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Phase 2 — Scale</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Months 9–18</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Earn conventional grocery on proven data</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Sell-in to Loblaw/Sobeys/Metro on velocity data; distributor (UNFI CA / Tree of Life); managed trade spend; add SKUs on repeat data</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>National listings won on data, not discounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Phase 3 — Defend &amp; extend</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>18 mo+</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Category leadership &amp; optionality</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Format/flavour extensions; deepen moat; evaluate strategic-partner vs independent scale</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Profitable contribution + exit optionality</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00B45309"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="M1" s="95" t="inlineStr">
+        <is>
+          <t>🏠 Home</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Likelihood × Impact (H/M/L). Ranked by exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Likelihood</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Mitigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Collagen efficacy / claims liability (2025 meta-analysis; Poppi-style dose-insufficiency suit)</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory/Legal</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Dose to efficacy (2.5g+); structure/function-safe language; substantiation files; lead with gut/hydration not beauty</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Strategic-owned competition (Nestlé owns Vital Proteins; PepsiCo/Unilever firepower)</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Compete on Canadian-made + domestic cost edge + Organika collagen credibility; niche beachhead before they react</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Canada claim/label pathway misread (food vs NHP; SFCI; collagen caution)</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory-counsel opinion before artwork; design to Supplemented Foods framework; caffeine-free</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Over-distribution before product-market fit</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Prove velocity/repeat in beachhead before national; gate Phase 2 on data</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Slotting / trade-spend cash burn</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Use free-fill over cash slotting; 35–45% trade-spend budget; Code of Conduct leverage on arbitrary fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Thin differentiation / shelf saturation (prebiotic shelf filling fast)</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Defensible spec (fiber + collagen dose) + function stacking; Canadian-made story</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Private-label encroachment (~$277B, ~21% share, growing 2×)</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Brand equity + clinical-grade ingredients retailers can't easily copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>DTC CAC / heavy-ship economics if DTC-led</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Lead retail/beachhead not paid DTC; subscription + sampling only</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Co-packer capacity / collagen sourcing / cost inflation</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Lock co-pack capacity early; qualify 2nd collagen supplier; hedge raws</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>FX / tariff / freight premium on cross-border inputs</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Domestic CA co-pack; monitor tariff status post-Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>GLP-1 demand shift away from sweet/snack</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Low-cal, fiber, protein, hydration positioning aligns with GLP-1 users</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Brand/tone misstep at scale</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Evolve tactics with stage; avoid Poppi-style stunts once mainstream</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="138" t="inlineStr">
+        <is>
+          <t>LIKELIHOOD × IMPACT HEATMAP (risk #s placed by rating)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="148" t="inlineStr">
+        <is>
+          <t>Impact ↓ / Likelihood →</t>
+        </is>
+      </c>
+      <c r="B20" s="149" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C20" s="149" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="D20" s="149" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="149" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B21" s="150" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" s="151" t="inlineStr">
+        <is>
+          <t>3, 4, 5</t>
+        </is>
+      </c>
+      <c r="D21" s="151" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="149" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="B22" s="152" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C22" s="150" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="D22" s="151" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="149" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B23" s="152" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C23" s="152" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D23" s="150" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="133" t="inlineStr">
+        <is>
+          <t>Red = act now · Amber = manage · Green = monitor. Numbers refer to the risk # in the table above.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A24:F24"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00B45309"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -14505,7 +15058,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -15055,7 +15608,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C9A227"/>
@@ -15201,818 +15754,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00C9A227"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Verification Log</t>
-        </is>
-      </c>
-      <c r="M1" s="95" t="inlineStr">
-        <is>
-          <t>🏠 Home</t>
-        </is>
-      </c>
-      <c r="N1" s="95" t="inlineStr">
-        <is>
-          <t>↩ Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>What was checked against sources on 2026-06-13, and what changed. Honesty over false precision.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Claim checked</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Finding / corrected value</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="97" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="58" t="inlineStr">
-        <is>
-          <t>What is MÜV — and is it a can or a powder?</t>
-        </is>
-      </c>
-      <c r="C5" s="98" t="inlineStr">
-        <is>
-          <t>CONFIRMED + CORRECTED (2x)</t>
-        </is>
-      </c>
-      <c r="D5" s="58" t="inlineStr">
-        <is>
-          <t>“MÜV Sparkling Electrolytes” is a real Organika SKU and is a ready-to-drink SPARKLING CAN (SKU 4338, ~$14.99; ingredient list begins “Carbonated water” + Fibersol, magnesium glycinate, stevia; 0 sugar, caffeine-free). NOTE: an interim round-5 finding called it a powder — that was WRONG (it described Organika's separate electrolyte sachets / Electrolytes+Collagen powder) and is retracted.</t>
-        </is>
-      </c>
-      <c r="E5" s="58" t="inlineStr">
-        <is>
-          <t>organika.com (SKU 4338, ingredient list); retailer listings</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="99" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="60" t="inlineStr">
-        <is>
-          <t>Canada regulatory pathway for MÜV</t>
-        </is>
-      </c>
-      <c r="C6" s="98" t="inlineStr">
-        <is>
-          <t>CORRECTED (primary)</t>
-        </is>
-      </c>
-      <c r="D6" s="60" t="inlineStr">
-        <is>
-          <t>Format is NOT the decider. Health Canada is reclassifying ALL sport-electrolyte products (RTD/powder/effervescent) from NHP to SUPPLEMENTED FOODS — NPN holders by Dec 31, 2027; new products comply with FDR now. So MÜV (a can) is a Supplemented Food; collagen beauty claims remain NHP-only. ORS stays NHP. See ‘Canada Regulatory v2’.</t>
-        </is>
-      </c>
-      <c r="E6" s="60" t="inlineStr">
-        <is>
-          <t>canada.ca Public Notice (Apr 2026); Gowling; dicentra; CHFA</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="97" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="58" t="inlineStr">
-        <is>
-          <t>Poppi → PepsiCo $1.95B</t>
-        </is>
-      </c>
-      <c r="C7" s="98" t="inlineStr">
-        <is>
-          <t>CONFIRMED (primary)</t>
-        </is>
-      </c>
-      <c r="D7" s="58" t="inlineStr">
-        <is>
-          <t>$1.95B incl. $300M anticipated cash tax benefits → net $1.65B, plus a performance earnout. Closed/announced May 19, 2025.</t>
-        </is>
-      </c>
-      <c r="E7" s="58" t="inlineStr">
-        <is>
-          <t>PepsiCo newsroom PR (2025-05-19)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="99" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="60" t="inlineStr">
-        <is>
-          <t>OLIPOP $50M Series C @ $1.85B</t>
-        </is>
-      </c>
-      <c r="C8" s="98" t="inlineStr">
-        <is>
-          <t>CONFIRMED (primary)</t>
-        </is>
-      </c>
-      <c r="D8" s="60" t="inlineStr">
-        <is>
-          <t>$50M led by JP Morgan Private Capital at $1.85B valuation (Feb 12, 2025); company states fully profitable, &gt;$400M 2024 sales; described as final anticipated equity round.</t>
-        </is>
-      </c>
-      <c r="E8" s="60" t="inlineStr">
-        <is>
-          <t>Bloomberg; CNBC (2025-02-12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="97" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="58" t="inlineStr">
-        <is>
-          <t>LMNT FY2023 $206M sales, ~20% net</t>
-        </is>
-      </c>
-      <c r="C9" s="98" t="inlineStr">
-        <is>
-          <t>CONFIRMED (primary)</t>
-        </is>
-      </c>
-      <c r="D9" s="58" t="inlineStr">
-        <is>
-          <t>$206M sales, ~20% net income margin, $54.6M marketing (~26.5% of revenue) — LMNT's own SEC Form C-AR, CIK 1871551, FY ended 12/31/2023.</t>
-        </is>
-      </c>
-      <c r="E9" s="58" t="inlineStr">
-        <is>
-          <t>sec.gov EDGAR (lmnt.pdf, CIK 1871551)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="99" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="60" t="inlineStr">
-        <is>
-          <t>Modern soda $1.8B 2024, +83% YoY</t>
-        </is>
-      </c>
-      <c r="C10" s="98" t="inlineStr">
-        <is>
-          <t>CONFIRMED (scanner)</t>
-        </is>
-      </c>
-      <c r="D10" s="60" t="inlineStr">
-        <is>
-          <t>$1.8B in 2024, up 83% from $983M (2023). Shares: Poppi 38%, OLIPOP 32.7%, Zevia 12.1%, Jarritos 10.3%, Fever-Tree 4%, other 2.9%.</t>
-        </is>
-      </c>
-      <c r="E10" s="60" t="inlineStr">
-        <is>
-          <t>Circana via Beverage Industry / CNN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="97" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="58" t="inlineStr">
-        <is>
-          <t>Poppi $8.9M gut-health settlement</t>
-        </is>
-      </c>
-      <c r="C11" s="98" t="inlineStr">
-        <is>
-          <t>CONFIRMED (primary)</t>
-        </is>
-      </c>
-      <c r="D11" s="58" t="inlineStr">
-        <is>
-          <t>$8.9M settlement; suit (June 2024) alleged 2g fiber too low (need &gt;4 cans/day). Class period from Jan 23, 2020. Preliminary approval May 23, 2025; FINAL approval April 14, 2026.</t>
-        </is>
-      </c>
-      <c r="E11" s="58" t="inlineStr">
-        <is>
-          <t>classaction.org; BevNET; Today</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="99" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="60" t="inlineStr">
-        <is>
-          <t>Liquid I.V. Costco 2019; Unilever 2020</t>
-        </is>
-      </c>
-      <c r="C12" s="98" t="inlineStr">
-        <is>
-          <t>CONFIRMED (primary)</t>
-        </is>
-      </c>
-      <c r="D12" s="60" t="inlineStr">
-        <is>
-          <t>National Costco launch Jan 8, 2019 → 516 warehouses. Unilever agreed to acquire Sept 1, 2020 (~$500M / ~5x reported; terms officially undisclosed).</t>
-        </is>
-      </c>
-      <c r="E12" s="60" t="inlineStr">
-        <is>
-          <t>liquid-iv.com; Unilever PR; BevNET</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="97" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="58" t="inlineStr">
-        <is>
-          <t>Canada Supplemented Foods Reg; 180mg caffeine cap</t>
-        </is>
-      </c>
-      <c r="C13" s="98" t="inlineStr">
-        <is>
-          <t>CONFIRMED (primary)</t>
-        </is>
-      </c>
-      <c r="D13" s="58" t="inlineStr">
-        <is>
-          <t>Amendments in force July 21, 2022. 180mg caffeine cap per single-serve container; Prime Energy (200mg) violated it and was recalled in Canada (July 2023), alongside others.</t>
-        </is>
-      </c>
-      <c r="E13" s="58" t="inlineStr">
-        <is>
-          <t>Health Canada (canada.ca); CNN; Fasken</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="99" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="60" t="inlineStr">
-        <is>
-          <t>Celsius–PepsiCo $550M; Celsius buys Alani Nu $1.8B</t>
-        </is>
-      </c>
-      <c r="C14" s="98" t="inlineStr">
-        <is>
-          <t>CONFIRMED (primary)</t>
-        </is>
-      </c>
-      <c r="D14" s="60" t="inlineStr">
-        <is>
-          <t>PepsiCo $550M convertible pref @ $75/sh (~8.5%), Aug 2022, global distribution. Celsius acquired Alani Nu for $1.8B (incl. $150M tax assets → net $1.65B); announced Feb 2025, CLOSED April 1, 2025.</t>
-        </is>
-      </c>
-      <c r="E14" s="60" t="inlineStr">
-        <is>
-          <t>SEC 8-K; BevNET; Food Dive</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="56" t="inlineStr">
-        <is>
-          <t>Method note: All 10 items were re-verified on 2026-06-13. Items 1–2 confirmed against Organika's site + Canadian retailer listings (storefront blocks automated fetch, so confirmed via search-indexed product/retailer pages). Items 3–10 were re-pulled and CONFIRMED against primary sources (PepsiCo, SEC EDGAR, Circana via trade press, Health Canada, classaction.org, Unilever, Celsius SEC 8-Ks), several with added precision (net purchase prices, exact close dates). No competitor figure required downward correction. The material corrections were on MÜV (items 1–2): verified as an RTD sparkling CAN (not a powder), and the Canada sport-electrolyte → Supplemented-Food reclassification (deep-research pass). Direct primary-PDF re-read still advised for any figure quoted verbatim in board materials.</t>
-        </is>
-      </c>
-      <c r="B16" s="34" t="n"/>
-      <c r="C16" s="34" t="n"/>
-      <c r="D16" s="34" t="n"/>
-      <c r="E16" s="35" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00595959"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N38"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Glossary &amp; Abbreviations</t>
-        </is>
-      </c>
-      <c r="M1" s="95" t="inlineStr">
-        <is>
-          <t>🏠 Home</t>
-        </is>
-      </c>
-      <c r="N1" s="95" t="inlineStr">
-        <is>
-          <t>↩ Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Term</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>ACV</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Apple cider vinegar (Poppi's original hero ingredient)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>ACV (retail)</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Also: All-Commodity Volume — a retail distribution/weighting metric (context-dependent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>CFIA</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Canadian Food Inspection Agency — regulates food-format products in Canada</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>CTT</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Cellular Transport Technology — Liquid I.V.'s hydration claim</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>DSD</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="inlineStr">
-        <is>
-          <t>Direct Store Delivery — brand/bottler delivers &amp; merchandises in-store (Coca-Cola model)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>DTC</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Direct-to-consumer (e-commerce / subscription)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Fulfillment by Amazon</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>FDR</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Food and Drug Regulations (Canada)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>GLP-1</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Glucagon-like peptide-1 agonists (Ozempic/Wegovy) — weight-loss drugs reshaping food demand</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>GM / COGS</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>Gross margin / Cost of goods sold</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>MOQ</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Minimum order quantity (co-packer runs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>MULO</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>Multi-Outlet (SPINS/Circana retail measurement universe)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>NHP / NPN</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>Natural Health Product / Natural Product Number (Canada licensing for supplements)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>PMF</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>Product-market fit</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>Ready-to-drink (a finished beverage, vs powder/tablet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>SAM/SOM/TAM</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>Serviceable available / obtainable / total addressable market</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>SFCI</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>Supplemented Food Caution Identifier — Canada's ‘!’ caution box for supplemented foods</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>SFR</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>Supplemented Foods Regulations (Canada, in force Jul 21 2022)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>SPINS / Circana</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>Syndicated retail scanner-data providers (point-of-sale sales &amp; velocity)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>Slotting fee</t>
-        </is>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>Payment to a retailer to list a new SKU / secure shelf space</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Trade spend</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Promotional/discount spend to retailers — typically the #2 P&amp;L line after COGS</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>UNFI / KeHE</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>Major North American natural/specialty food distributors</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>VERISOL</t>
-        </is>
-      </c>
-      <c r="B26" s="12" t="inlineStr">
-        <is>
-          <t>A clinically-studied collagen peptide (Vital Proteins sparkling)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="42" t="inlineStr">
-        <is>
-          <t>REGULATORY &amp; FORMAT TERMS (Canada)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="87" t="inlineStr">
-        <is>
-          <t>RTD</t>
-        </is>
-      </c>
-      <c r="B29" s="58" t="inlineStr">
-        <is>
-          <t>Ready-to-drink — a finished beverage (e.g., a can), vs a powder/tablet to reconstitute.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="89" t="inlineStr">
-        <is>
-          <t>NHP</t>
-        </is>
-      </c>
-      <c r="B30" s="60" t="inlineStr">
-        <is>
-          <t>Natural Health Product — Canadian licensed supplement category; bears an NPN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="87" t="inlineStr">
-        <is>
-          <t>NPN</t>
-        </is>
-      </c>
-      <c r="B31" s="58" t="inlineStr">
-        <is>
-          <t>Natural Product Number — 8-digit licence number on an NHP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="89" t="inlineStr">
-        <is>
-          <t>Supplemented Food</t>
-        </is>
-      </c>
-      <c r="B32" s="60" t="inlineStr">
-        <is>
-          <t>A food with added vitamins/minerals/amino acids beyond normal fortification, under the Supplemented Foods Regulations (in force 2022-07-21).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="87" t="inlineStr">
-        <is>
-          <t>SFFt</t>
-        </is>
-      </c>
-      <c r="B33" s="58" t="inlineStr">
-        <is>
-          <t>Supplemented Food Facts table — modified Nutrition Facts table with a 'Supplemented with' line.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="89" t="inlineStr">
-        <is>
-          <t>SFCI</t>
-        </is>
-      </c>
-      <c r="B34" s="60" t="inlineStr">
-        <is>
-          <t>Supplemented Food Caution Identifier — the black-&amp;-white '!' identifier required when cautionary statements apply.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="87" t="inlineStr">
-        <is>
-          <t>ORS</t>
-        </is>
-      </c>
-      <c r="B35" s="58" t="inlineStr">
-        <is>
-          <t>Oral Rehydration Solution — clinical rehydration product; stays regulated as an NHP (carve-out from the electrolyte→food shift).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="89" t="inlineStr">
-        <is>
-          <t>Food–NHP interface</t>
-        </is>
-      </c>
-      <c r="B36" s="60" t="inlineStr">
-        <is>
-          <t>Health Canada guidance that classifies food-format products; format is not decisive — representation + claims are.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="87" t="inlineStr">
-        <is>
-          <t>Fibersol</t>
-        </is>
-      </c>
-      <c r="B37" s="58" t="inlineStr">
-        <is>
-          <t>A soluble prebiotic dietary fibre used in MÜV.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="89" t="inlineStr">
-        <is>
-          <t>Bill 96 / OQLF</t>
-        </is>
-      </c>
-      <c r="B38" s="60" t="inlineStr">
-        <is>
-          <t>Quebec French-language packaging rules; generic/descriptive trademark terms need French.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A28:B28"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -16020,7 +15761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -16595,6 +16336,30 @@
       <c r="B50" s="164" t="inlineStr">
         <is>
           <t>hard evidence / directional / estimate-or-flag (see Data Confidence scoreboard)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="120" t="inlineStr">
+        <is>
+          <t>How to Present</t>
+        </is>
+      </c>
+      <c r="B51" s="103" t="inlineStr">
+        <is>
+          <t>Leadership readout — one talking point per key tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="120" t="inlineStr">
+        <is>
+          <t>Next Steps &amp; Gates</t>
+        </is>
+      </c>
+      <c r="B52" s="103" t="inlineStr">
+        <is>
+          <t>Immediate actions &amp; decision gates with status</t>
         </is>
       </c>
     </row>
@@ -16644,6 +16409,820 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId42"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Verification Log</t>
+        </is>
+      </c>
+      <c r="M1" s="95" t="inlineStr">
+        <is>
+          <t>🏠 Home</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>What was checked against sources on 2026-06-13, and what changed. Honesty over false precision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Claim checked</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Finding / corrected value</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="97" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="58" t="inlineStr">
+        <is>
+          <t>What is MÜV — and is it a can or a powder?</t>
+        </is>
+      </c>
+      <c r="C5" s="98" t="inlineStr">
+        <is>
+          <t>CONFIRMED + CORRECTED (2x)</t>
+        </is>
+      </c>
+      <c r="D5" s="58" t="inlineStr">
+        <is>
+          <t>“MÜV Sparkling Electrolytes” is a real Organika SKU and is a ready-to-drink SPARKLING CAN (SKU 4338, ~$14.99; ingredient list begins “Carbonated water” + Fibersol, magnesium glycinate, stevia; 0 sugar, caffeine-free). NOTE: an interim round-5 finding called it a powder — that was WRONG (it described Organika's separate electrolyte sachets / Electrolytes+Collagen powder) and is retracted.</t>
+        </is>
+      </c>
+      <c r="E5" s="58" t="inlineStr">
+        <is>
+          <t>organika.com (SKU 4338, ingredient list); retailer listings</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="99" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="60" t="inlineStr">
+        <is>
+          <t>Canada regulatory pathway for MÜV</t>
+        </is>
+      </c>
+      <c r="C6" s="98" t="inlineStr">
+        <is>
+          <t>CORRECTED (primary)</t>
+        </is>
+      </c>
+      <c r="D6" s="60" t="inlineStr">
+        <is>
+          <t>Format is NOT the decider. Health Canada is reclassifying ALL sport-electrolyte products (RTD/powder/effervescent) from NHP to SUPPLEMENTED FOODS — NPN holders by Dec 31, 2027; new products comply with FDR now. So MÜV (a can) is a Supplemented Food; collagen beauty claims remain NHP-only. ORS stays NHP. See ‘Canada Regulatory v2’.</t>
+        </is>
+      </c>
+      <c r="E6" s="60" t="inlineStr">
+        <is>
+          <t>canada.ca Public Notice (Apr 2026); Gowling; dicentra; CHFA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="97" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="58" t="inlineStr">
+        <is>
+          <t>Poppi → PepsiCo $1.95B</t>
+        </is>
+      </c>
+      <c r="C7" s="98" t="inlineStr">
+        <is>
+          <t>CONFIRMED (primary)</t>
+        </is>
+      </c>
+      <c r="D7" s="58" t="inlineStr">
+        <is>
+          <t>$1.95B incl. $300M anticipated cash tax benefits → net $1.65B, plus a performance earnout. Closed/announced May 19, 2025.</t>
+        </is>
+      </c>
+      <c r="E7" s="58" t="inlineStr">
+        <is>
+          <t>PepsiCo newsroom PR (2025-05-19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="99" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>OLIPOP $50M Series C @ $1.85B</t>
+        </is>
+      </c>
+      <c r="C8" s="98" t="inlineStr">
+        <is>
+          <t>CONFIRMED (primary)</t>
+        </is>
+      </c>
+      <c r="D8" s="60" t="inlineStr">
+        <is>
+          <t>$50M led by JP Morgan Private Capital at $1.85B valuation (Feb 12, 2025); company states fully profitable, &gt;$400M 2024 sales; described as final anticipated equity round.</t>
+        </is>
+      </c>
+      <c r="E8" s="60" t="inlineStr">
+        <is>
+          <t>Bloomberg; CNBC (2025-02-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="97" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="58" t="inlineStr">
+        <is>
+          <t>LMNT FY2023 $206M sales, ~20% net</t>
+        </is>
+      </c>
+      <c r="C9" s="98" t="inlineStr">
+        <is>
+          <t>CONFIRMED (primary)</t>
+        </is>
+      </c>
+      <c r="D9" s="58" t="inlineStr">
+        <is>
+          <t>$206M sales, ~20% net income margin, $54.6M marketing (~26.5% of revenue) — LMNT's own SEC Form C-AR, CIK 1871551, FY ended 12/31/2023.</t>
+        </is>
+      </c>
+      <c r="E9" s="58" t="inlineStr">
+        <is>
+          <t>sec.gov EDGAR (lmnt.pdf, CIK 1871551)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="99" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="60" t="inlineStr">
+        <is>
+          <t>Modern soda $1.8B 2024, +83% YoY</t>
+        </is>
+      </c>
+      <c r="C10" s="98" t="inlineStr">
+        <is>
+          <t>CONFIRMED (scanner)</t>
+        </is>
+      </c>
+      <c r="D10" s="60" t="inlineStr">
+        <is>
+          <t>$1.8B in 2024, up 83% from $983M (2023). Shares: Poppi 38%, OLIPOP 32.7%, Zevia 12.1%, Jarritos 10.3%, Fever-Tree 4%, other 2.9%.</t>
+        </is>
+      </c>
+      <c r="E10" s="60" t="inlineStr">
+        <is>
+          <t>Circana via Beverage Industry / CNN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="97" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="58" t="inlineStr">
+        <is>
+          <t>Poppi $8.9M gut-health settlement</t>
+        </is>
+      </c>
+      <c r="C11" s="98" t="inlineStr">
+        <is>
+          <t>CONFIRMED (primary)</t>
+        </is>
+      </c>
+      <c r="D11" s="58" t="inlineStr">
+        <is>
+          <t>$8.9M settlement; suit (June 2024) alleged 2g fiber too low (need &gt;4 cans/day). Class period from Jan 23, 2020. Preliminary approval May 23, 2025; FINAL approval April 14, 2026.</t>
+        </is>
+      </c>
+      <c r="E11" s="58" t="inlineStr">
+        <is>
+          <t>classaction.org; BevNET; Today</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="99" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="60" t="inlineStr">
+        <is>
+          <t>Liquid I.V. Costco 2019; Unilever 2020</t>
+        </is>
+      </c>
+      <c r="C12" s="98" t="inlineStr">
+        <is>
+          <t>CONFIRMED (primary)</t>
+        </is>
+      </c>
+      <c r="D12" s="60" t="inlineStr">
+        <is>
+          <t>National Costco launch Jan 8, 2019 → 516 warehouses. Unilever agreed to acquire Sept 1, 2020 (~$500M / ~5x reported; terms officially undisclosed).</t>
+        </is>
+      </c>
+      <c r="E12" s="60" t="inlineStr">
+        <is>
+          <t>liquid-iv.com; Unilever PR; BevNET</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="97" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="58" t="inlineStr">
+        <is>
+          <t>Canada Supplemented Foods Reg; 180mg caffeine cap</t>
+        </is>
+      </c>
+      <c r="C13" s="98" t="inlineStr">
+        <is>
+          <t>CONFIRMED (primary)</t>
+        </is>
+      </c>
+      <c r="D13" s="58" t="inlineStr">
+        <is>
+          <t>Amendments in force July 21, 2022. 180mg caffeine cap per single-serve container; Prime Energy (200mg) violated it and was recalled in Canada (July 2023), alongside others.</t>
+        </is>
+      </c>
+      <c r="E13" s="58" t="inlineStr">
+        <is>
+          <t>Health Canada (canada.ca); CNN; Fasken</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="99" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="60" t="inlineStr">
+        <is>
+          <t>Celsius–PepsiCo $550M; Celsius buys Alani Nu $1.8B</t>
+        </is>
+      </c>
+      <c r="C14" s="98" t="inlineStr">
+        <is>
+          <t>CONFIRMED (primary)</t>
+        </is>
+      </c>
+      <c r="D14" s="60" t="inlineStr">
+        <is>
+          <t>PepsiCo $550M convertible pref @ $75/sh (~8.5%), Aug 2022, global distribution. Celsius acquired Alani Nu for $1.8B (incl. $150M tax assets → net $1.65B); announced Feb 2025, CLOSED April 1, 2025.</t>
+        </is>
+      </c>
+      <c r="E14" s="60" t="inlineStr">
+        <is>
+          <t>SEC 8-K; BevNET; Food Dive</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="56" t="inlineStr">
+        <is>
+          <t>Method note: All 10 items were re-verified on 2026-06-13. Items 1–2 confirmed against Organika's site + Canadian retailer listings (storefront blocks automated fetch, so confirmed via search-indexed product/retailer pages). Items 3–10 were re-pulled and CONFIRMED against primary sources (PepsiCo, SEC EDGAR, Circana via trade press, Health Canada, classaction.org, Unilever, Celsius SEC 8-Ks), several with added precision (net purchase prices, exact close dates). No competitor figure required downward correction. The material corrections were on MÜV (items 1–2): verified as an RTD sparkling CAN (not a powder), and the Canada sport-electrolyte → Supplemented-Food reclassification (deep-research pass). Direct primary-PDF re-read still advised for any figure quoted verbatim in board materials.</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="35" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00595959"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:N38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Glossary &amp; Abbreviations</t>
+        </is>
+      </c>
+      <c r="M1" s="95" t="inlineStr">
+        <is>
+          <t>🏠 Home</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Term</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>ACV</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Apple cider vinegar (Poppi's original hero ingredient)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>ACV (retail)</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Also: All-Commodity Volume — a retail distribution/weighting metric (context-dependent)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>CFIA</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Canadian Food Inspection Agency — regulates food-format products in Canada</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>CTT</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Cellular Transport Technology — Liquid I.V.'s hydration claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>DSD</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Direct Store Delivery — brand/bottler delivers &amp; merchandises in-store (Coca-Cola model)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>DTC</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Direct-to-consumer (e-commerce / subscription)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>FDR</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Food and Drug Regulations (Canada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>GLP-1</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Glucagon-like peptide-1 agonists (Ozempic/Wegovy) — weight-loss drugs reshaping food demand</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>GM / COGS</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Gross margin / Cost of goods sold</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>MOQ</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Minimum order quantity (co-packer runs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>MULO</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Multi-Outlet (SPINS/Circana retail measurement universe)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>NHP / NPN</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Natural Health Product / Natural Product Number (Canada licensing for supplements)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>PMF</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Product-market fit</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Ready-to-drink (a finished beverage, vs powder/tablet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>SAM/SOM/TAM</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Serviceable available / obtainable / total addressable market</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>SFCI</t>
+        </is>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>Supplemented Food Caution Identifier — Canada's ‘!’ caution box for supplemented foods</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>SFR</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>Supplemented Foods Regulations (Canada, in force Jul 21 2022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>SPINS / Circana</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Syndicated retail scanner-data providers (point-of-sale sales &amp; velocity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Slotting fee</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Payment to a retailer to list a new SKU / secure shelf space</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Trade spend</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Promotional/discount spend to retailers — typically the #2 P&amp;L line after COGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>UNFI / KeHE</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>Major North American natural/specialty food distributors</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>VERISOL</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>A clinically-studied collagen peptide (Vital Proteins sparkling)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="42" t="inlineStr">
+        <is>
+          <t>REGULATORY &amp; FORMAT TERMS (Canada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="87" t="inlineStr">
+        <is>
+          <t>RTD</t>
+        </is>
+      </c>
+      <c r="B29" s="58" t="inlineStr">
+        <is>
+          <t>Ready-to-drink — a finished beverage (e.g., a can), vs a powder/tablet to reconstitute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="89" t="inlineStr">
+        <is>
+          <t>NHP</t>
+        </is>
+      </c>
+      <c r="B30" s="60" t="inlineStr">
+        <is>
+          <t>Natural Health Product — Canadian licensed supplement category; bears an NPN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="87" t="inlineStr">
+        <is>
+          <t>NPN</t>
+        </is>
+      </c>
+      <c r="B31" s="58" t="inlineStr">
+        <is>
+          <t>Natural Product Number — 8-digit licence number on an NHP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="89" t="inlineStr">
+        <is>
+          <t>Supplemented Food</t>
+        </is>
+      </c>
+      <c r="B32" s="60" t="inlineStr">
+        <is>
+          <t>A food with added vitamins/minerals/amino acids beyond normal fortification, under the Supplemented Foods Regulations (in force 2022-07-21).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="87" t="inlineStr">
+        <is>
+          <t>SFFt</t>
+        </is>
+      </c>
+      <c r="B33" s="58" t="inlineStr">
+        <is>
+          <t>Supplemented Food Facts table — modified Nutrition Facts table with a 'Supplemented with' line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="89" t="inlineStr">
+        <is>
+          <t>SFCI</t>
+        </is>
+      </c>
+      <c r="B34" s="60" t="inlineStr">
+        <is>
+          <t>Supplemented Food Caution Identifier — the black-&amp;-white '!' identifier required when cautionary statements apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="87" t="inlineStr">
+        <is>
+          <t>ORS</t>
+        </is>
+      </c>
+      <c r="B35" s="58" t="inlineStr">
+        <is>
+          <t>Oral Rehydration Solution — clinical rehydration product; stays regulated as an NHP (carve-out from the electrolyte→food shift).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="89" t="inlineStr">
+        <is>
+          <t>Food–NHP interface</t>
+        </is>
+      </c>
+      <c r="B36" s="60" t="inlineStr">
+        <is>
+          <t>Health Canada guidance that classifies food-format products; format is not decisive — representation + claims are.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="87" t="inlineStr">
+        <is>
+          <t>Fibersol</t>
+        </is>
+      </c>
+      <c r="B37" s="58" t="inlineStr">
+        <is>
+          <t>A soluble prebiotic dietary fibre used in MÜV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="89" t="inlineStr">
+        <is>
+          <t>Bill 96 / OQLF</t>
+        </is>
+      </c>
+      <c r="B38" s="60" t="inlineStr">
+        <is>
+          <t>Quebec French-language packaging rules; generic/descriptive trademark terms need French.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A28:B28"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -18740,6 +19319,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="74" t="inlineStr">
         <is>
@@ -18922,6 +19502,8 @@
         <v>2972910.555999999</v>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17" hidden="1">
       <c r="A17" s="41" t="inlineStr">
         <is>
@@ -18952,10 +19534,10 @@
           <t>Conservative</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="165" t="n">
         <v>1065469</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="165" t="n">
         <v>-365298</v>
       </c>
     </row>
@@ -18965,10 +19547,10 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="165" t="n">
         <v>3008031</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="165" t="n">
         <v>118425</v>
       </c>
     </row>
@@ -18978,13 +19560,25 @@
           <t>Aggressive</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="165" t="n">
         <v>9586365</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="165" t="n">
         <v>2972911</v>
       </c>
     </row>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
     <row r="34" ht="52" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
@@ -18996,6 +19590,8 @@
       <c r="D34" s="34" t="n"/>
       <c r="E34" s="35" t="n"/>
     </row>
+    <row r="35"/>
+    <row r="36"/>
     <row r="37" hidden="1">
       <c r="A37" s="41" t="inlineStr">
         <is>
@@ -19021,7 +19617,7 @@
           <t>Conservative</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="165" t="n">
         <v>8260367</v>
       </c>
     </row>
@@ -19031,7 +19627,7 @@
           <t>Base</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" s="165" t="n">
         <v>1522595</v>
       </c>
     </row>
@@ -19041,7 +19637,7 @@
           <t>Aggressive</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="165" t="n">
         <v>1369291</v>
       </c>
     </row>

--- a/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
+++ b/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
@@ -101,7 +101,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="40">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -328,6 +328,12 @@
       <name val="Calibri"/>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="001E7D32"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -529,7 +535,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="172">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1002,6 +1008,21 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -16776,7 +16797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17215,8 +17236,16 @@
         </is>
       </c>
     </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="171" t="inlineStr">
+        <is>
+          <t>→ For full detail on the Supplemented-Foods pathway, SFFt, SFCI and the electrolyte→food reclassification, see the ‘Canada Regulatory v2’ tab.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A40:B40"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A28:B28"/>
   </mergeCells>
@@ -17475,6 +17504,13 @@
         </is>
       </c>
     </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="167" t="inlineStr">
+        <is>
+          <t>THESIS: MÜV wins the daily-wellness SPARKLING electrolyte lane, made in Canada — food-regulated, priced with the electrolyte peers, GTM borrowed from the soda winners.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="36" t="inlineStr">
         <is>
@@ -17862,25 +17898,26 @@
     <row r="80" hidden="1"/>
     <row r="81" hidden="1"/>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="A39:L39"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C6:D6"/>
     <mergeCell ref="I4:J4"/>
-    <mergeCell ref="I6:J6"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A39:L39"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
@@ -19285,7 +19322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -19319,7 +19356,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="74" t="inlineStr">
         <is>
@@ -19502,8 +19538,6 @@
         <v>2972910.555999999</v>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16"/>
     <row r="17" hidden="1">
       <c r="A17" s="41" t="inlineStr">
         <is>
@@ -19567,18 +19601,6 @@
         <v>2972911</v>
       </c>
     </row>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
     <row r="34" ht="52" customHeight="1">
       <c r="A34" s="17" t="inlineStr">
         <is>
@@ -19590,8 +19612,6 @@
       <c r="D34" s="34" t="n"/>
       <c r="E34" s="35" t="n"/>
     </row>
-    <row r="35"/>
-    <row r="36"/>
     <row r="37" hidden="1">
       <c r="A37" s="41" t="inlineStr">
         <is>
@@ -19641,11 +19661,58 @@
         <v>1369291</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="42" t="inlineStr">
+        <is>
+          <t>TAKEAWAY BY SCENARIO</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="168" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="B44" s="58" t="inlineStr">
+        <is>
+          <t>Downside case — thin margins, later break-even. Validates the floor: even here MÜV has a defined path, not a hole.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="169" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="B45" s="58" t="inlineStr">
+        <is>
+          <t>Planning anchor — healthy contribution and break-even within the Year-1 door plan. The realistic case to underwrite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="170" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="B46" s="58" t="inlineStr">
+        <is>
+          <t>Upside — if the sparkling wedge + Costco beachhead over-deliver on velocity. Treat as ceiling, not plan.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="7">
+    <mergeCell ref="A34:E34"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B46:D46"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="B44:D44"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>

--- a/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
+++ b/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
@@ -101,7 +101,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="42">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -334,6 +334,18 @@
       <color rgb="001E7D32"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="001E7D32"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -535,7 +547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="175">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1022,6 +1034,15 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2805,7 +2826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2901,8 +2922,76 @@
         </is>
       </c>
     </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="42" t="inlineStr">
+        <is>
+          <t>WHAT WOULD STRENGTHEN THIS FURTHER (priority order)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="87" t="inlineStr">
+        <is>
+          <t>1. Confirm MÜV on-can specs</t>
+        </is>
+      </c>
+      <c r="B11" s="58" t="inlineStr">
+        <is>
+          <t>Sodium mg, pack size, and whether a collagen variant exists — the last open input on the model and claims.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="89" t="inlineStr">
+        <is>
+          <t>2. Licensed Canadian scanner data</t>
+        </is>
+      </c>
+      <c r="B12" s="60" t="inlineStr">
+        <is>
+          <t>NielsenIQ/Circana Canada pull for the sparkling-electrolyte sub-segment to replace US-proxy sizing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="87" t="inlineStr">
+        <is>
+          <t>3. Regulatory-counsel opinion</t>
+        </is>
+      </c>
+      <c r="B13" s="58" t="inlineStr">
+        <is>
+          <t>Written classification + permissible claim set under the Supplemented Foods framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="89" t="inlineStr">
+        <is>
+          <t>4. Real cost inputs</t>
+        </is>
+      </c>
+      <c r="B14" s="60" t="inlineStr">
+        <is>
+          <t>Co-packer COGS quote + distributor terms to replace the illustrative model assumptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="87" t="inlineStr">
+        <is>
+          <t>5. Distributor interviews</t>
+        </is>
+      </c>
+      <c r="B15" s="58" t="inlineStr">
+        <is>
+          <t>UNFI Canada / Tree of Life / Purity Life on listing terms and velocity expectations.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <hyperlinks>
@@ -4180,7 +4269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4796,6 +4885,75 @@
       <c r="J12" s="34" t="n"/>
       <c r="K12" s="34" t="n"/>
       <c r="L12" s="35" t="n"/>
+    </row>
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="172" t="inlineStr">
+        <is>
+          <t>MÜV (Organika) — SUBJECT</t>
+        </is>
+      </c>
+      <c r="B13" s="173" t="inlineStr">
+        <is>
+          <t>Sparkling electrolyte (RTD)</t>
+        </is>
+      </c>
+      <c r="C13" s="173" t="inlineStr">
+        <is>
+          <t>Organika est. 1990</t>
+        </is>
+      </c>
+      <c r="D13" s="173" t="inlineStr">
+        <is>
+          <t>Organika (BC, Canada)</t>
+        </is>
+      </c>
+      <c r="E13" s="173" t="inlineStr">
+        <is>
+          <t>Costco CA / Amazon.ca / Well.ca (planned)</t>
+        </is>
+      </c>
+      <c r="F13" s="173" t="inlineStr">
+        <is>
+          <t>Daily-wellness sparkling hydration + prebiotic fibre</t>
+        </is>
+      </c>
+      <c r="G13" s="173" t="inlineStr">
+        <is>
+          <t>RTD sparkling CAN (SKU 4338)</t>
+        </is>
+      </c>
+      <c r="H13" s="173" t="inlineStr">
+        <is>
+          <t>0 sugar, caffeine-free, magnesium glycinate, Fibersol; sodium TBD</t>
+        </is>
+      </c>
+      <c r="I13" s="173" t="inlineStr">
+        <is>
+          <t>$14.99 / pack</t>
+        </is>
+      </c>
+      <c r="J13" s="173" t="inlineStr">
+        <is>
+          <t>Canadian beachhead (planned)</t>
+        </is>
+      </c>
+      <c r="K13" s="173" t="inlineStr">
+        <is>
+          <t>n/a (pre-launch)</t>
+        </is>
+      </c>
+      <c r="L13" s="173" t="inlineStr">
+        <is>
+          <t>Food-regulated (Supplemented Food)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="133" t="inlineStr">
+        <is>
+          <t>↑ MÜV shown for benchmarking; its direct rivals (LMNT/Liquid I.V./Nuun) are on the ‘MÜV Peer Set’ tab.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:L11"/>
@@ -13473,7 +13631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -13733,13 +13891,21 @@
       <c r="E16" s="34" t="n"/>
       <c r="F16" s="35" t="n"/>
     </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="174" t="inlineStr">
+        <is>
+          <t>HOW TO USE: edit the yellow Weight and Score (1–5) cells; the weighted total and the GO / GO-conditional / NO-GO verdict recompute automatically.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="C14:E14"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:E11">
     <cfRule type="dataBar" priority="1">
@@ -17242,6 +17408,7 @@
           <t>→ For full detail on the Supplemented-Foods pathway, SFFt, SFCI and the electrolyte→food reclassification, see the ‘Canada Regulatory v2’ tab.</t>
         </is>
       </c>
+      <c r="B40" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -19679,6 +19846,8 @@
           <t>Downside case — thin margins, later break-even. Validates the floor: even here MÜV has a defined path, not a hole.</t>
         </is>
       </c>
+      <c r="C44" s="34" t="n"/>
+      <c r="D44" s="35" t="n"/>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="169" t="inlineStr">
@@ -19691,6 +19860,8 @@
           <t>Planning anchor — healthy contribution and break-even within the Year-1 door plan. The realistic case to underwrite.</t>
         </is>
       </c>
+      <c r="C45" s="34" t="n"/>
+      <c r="D45" s="35" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="170" t="inlineStr">
@@ -19703,13 +19874,15 @@
           <t>Upside — if the sparkling wedge + Costco beachhead over-deliver on velocity. Treat as ceiling, not plan.</t>
         </is>
       </c>
+      <c r="C46" s="34" t="n"/>
+      <c r="D46" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A34:E34"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="B46:D46"/>
     <mergeCell ref="B45:D45"/>
-    <mergeCell ref="B46:D46"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="B44:D44"/>

--- a/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
+++ b/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
@@ -101,7 +101,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="43">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -346,6 +346,12 @@
       <color rgb="001E7D32"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="003E5C76"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -547,7 +553,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1045,6 +1051,9 @@
     <xf numFmtId="0" fontId="41" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="42" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1167,6 +1176,88 @@
             </numRef>
           </val>
         </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Confidence tag distribution</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Data Confidence'!C4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Data Confidence'!$B$5:$B$7</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data Confidence'!$C$5:$C$7</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showVal val="1"/>
+        </dLbls>
         <gapWidth val="150"/>
         <axId val="10"/>
         <axId val="100"/>
@@ -1986,7 +2077,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Confidence tag distribution</a:t>
+              <a:t>Peer price per serving ($) — where to anchor MÜV</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1994,14 +2085,14 @@
     </title>
     <plotArea>
       <barChart>
-        <barDir val="col"/>
+        <barDir val="bar"/>
         <grouping val="clustered"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Data Confidence'!C4</f>
+              <f>'23 KPI Dashboard'!B16</f>
             </strRef>
           </tx>
           <spPr>
@@ -2011,12 +2102,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Data Confidence'!$B$5:$B$7</f>
+              <f>'23 KPI Dashboard'!$A$17:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Data Confidence'!$C$5:$C$7</f>
+              <f>'23 KPI Dashboard'!$B$17:$B$20</f>
             </numRef>
           </val>
         </ser>
@@ -2273,6 +2364,33 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4680000" cy="2340000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -2616,6 +2734,13 @@
         </is>
       </c>
     </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="B4" s="98" t="inlineStr">
+        <is>
+          <t>US hydration powders $1.5B (+20%)  ·  sparkling electrolyte = white space  ·  MÜV = food-regulated RTD can  ·  Verdict: GO — conditional</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="112" t="inlineStr">
         <is>
@@ -2772,13 +2897,14 @@
       <c r="E25" s="35" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B4:E4"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B10:B11"/>
@@ -13897,6 +14023,11 @@
           <t>HOW TO USE: edit the yellow Weight and Score (1–5) cells; the weighted total and the GO / GO-conditional / NO-GO verdict recompute automatically.</t>
         </is>
       </c>
+      <c r="B18" s="34" t="n"/>
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="34" t="n"/>
+      <c r="E18" s="34" t="n"/>
+      <c r="F18" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -14946,7 +15077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -15221,6 +15352,65 @@
         <is>
           <t>Phase 1+</t>
         </is>
+      </c>
+    </row>
+    <row r="15" hidden="1">
+      <c r="A15" s="41" t="inlineStr">
+        <is>
+          <t>(peer price/serving benchmark data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" hidden="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Price/serving</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" hidden="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LMNT</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="18" hidden="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Liquid I.V.</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="19" hidden="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Nuun</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="20" hidden="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Organika sachet</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -15242,6 +15432,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -15252,7 +15443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -15284,6 +15475,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -15743,6 +15935,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
@@ -15752,11 +15945,19 @@
       <c r="B32" s="34" t="n"/>
       <c r="C32" s="35" t="n"/>
     </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="175" t="inlineStr">
+        <is>
+          <t>SOURCE MIX: Primary 15 · Trade 6 · Other 3 · Scanner 2  (total 26 rows; load-bearing claims lean primary/regulatory).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A32:C32"/>
     <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A34:C34"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>

--- a/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
+++ b/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
@@ -101,7 +101,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="44">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -352,6 +352,12 @@
       <color rgb="003E5C76"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -553,7 +559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="177">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1054,6 +1060,7 @@
     <xf numFmtId="0" fontId="42" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2740,6 +2747,9 @@
           <t>US hydration powders $1.5B (+20%)  ·  sparkling electrolyte = white space  ·  MÜV = food-regulated RTD can  ·  Verdict: GO — conditional</t>
         </is>
       </c>
+      <c r="C4" s="34" t="n"/>
+      <c r="D4" s="34" t="n"/>
+      <c r="E4" s="35" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="B5" s="112" t="inlineStr">
@@ -5762,7 +5772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5790,6 +5800,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
@@ -5872,7 +5883,7 @@
           <t>Kombucha 2012; Pop 2020</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>Prebiotic soda; flagship kombucha</t>
         </is>
@@ -5978,7 +5989,7 @@
           <t>~2,500 stores</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Undisclosed (FLAG)</t>
         </is>
@@ -6376,7 +6387,7 @@
           <t>Mass</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>~$1.2–1.3B peak 2023, then down ~75% (FLAG)</t>
         </is>
@@ -6504,7 +6515,7 @@
           <t>Retail</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>Undisclosed (FLAG)</t>
         </is>
@@ -6742,7 +6753,7 @@
           <t>DTC + retail</t>
         </is>
       </c>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>Undisclosed (FLAG)</t>
         </is>
@@ -6774,7 +6785,7 @@
           <t>Anthropologie, UO</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>Undisclosed (FLAG)</t>
         </is>
@@ -6823,7 +6834,7 @@
           <t>Halo</t>
         </is>
       </c>
-      <c r="B39" s="12" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>Ambiguous</t>
         </is>
@@ -6870,7 +6881,7 @@
           <t>DTC-led</t>
         </is>
       </c>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>~$1M seed; later FLAG</t>
         </is>
@@ -7005,7 +7016,7 @@
           <t>Regional</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>Undisclosed (FLAG)</t>
         </is>
@@ -7155,6 +7166,13 @@
       <c r="D50" s="34" t="n"/>
       <c r="E50" s="34" t="n"/>
       <c r="F50" s="35" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="176" t="inlineStr">
+        <is>
+          <t>Amber cells = FLAG / unverified / could-not-confirm (10 tagged). Re-verify before external use.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -15475,7 +15493,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -15935,7 +15952,6 @@
         </is>
       </c>
     </row>
-    <row r="31"/>
     <row r="32" ht="58" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
@@ -15951,6 +15967,8 @@
           <t>SOURCE MIX: Primary 15 · Trade 6 · Other 3 · Scanner 2  (total 26 rows; load-bearing claims lean primary/regulatory).</t>
         </is>
       </c>
+      <c r="B34" s="34" t="n"/>
+      <c r="C34" s="35" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
+++ b/Organika_Sparkling_Competitor_Intelligence_ENTERPRISE.xlsx
@@ -38,16 +38,17 @@
     <sheet name="Electrolyte BFY Deep-Dive" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="20 GTM Recommendation" sheetId="30" state="visible" r:id="rId30"/>
     <sheet name="How to Present" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="Next Steps &amp; Gates" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="Go-NoGo Decision" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="Battlecards" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="21 Launch Plan" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="22 Risk Register" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="23 KPI Dashboard" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="24 Sources" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="Data Confidence" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="Verification Log" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="25 Glossary" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="FAQ &amp; Objections" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="Next Steps &amp; Gates" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="Go-NoGo Decision" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="Battlecards" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="21 Launch Plan" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="22 Risk Register" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="23 KPI Dashboard" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="24 Sources" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="Data Confidence" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="Verification Log" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="25 Glossary" sheetId="42" state="visible" r:id="rId42"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'🏠 Start Here'!$A$1:$E$25</definedName>
@@ -80,14 +81,14 @@
     <definedName name="_xlnm.Print_Area" localSheetId="27">'Canada Regulatory v2'!$A$1:$N$31</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="28">'Electrolyte BFY Deep-Dive'!$A$1:$N$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="29">'20 GTM Recommendation'!$A$1:$N$11</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="32">'Go-NoGo Decision'!$A$1:$N$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="33">'Battlecards'!$A$1:$N$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="34">'21 Launch Plan'!$A$1:$N$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="35">'22 Risk Register'!$A$1:$N$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="36">'23 KPI Dashboard'!$A$1:$N$12</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="37">'24 Sources'!$A$1:$N$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="39">'Verification Log'!$A$1:$N$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="40">'25 Glossary'!$A$1:$N$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="33">'Go-NoGo Decision'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="34">'Battlecards'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="35">'21 Launch Plan'!$A$1:$N$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="36">'22 Risk Register'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="37">'23 KPI Dashboard'!$A$1:$N$12</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="38">'24 Sources'!$A$1:$N$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="40">'Verification Log'!$A$1:$N$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="41">'25 Glossary'!$A$1:$N$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -559,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="177">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1061,6 +1062,27 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5800,7 +5822,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
@@ -13462,6 +13483,206 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="64" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="179" t="inlineStr">
+        <is>
+          <t>FAQ &amp; Objections — answers for the leadership room</t>
+        </is>
+      </c>
+      <c r="M1" s="95" t="inlineStr">
+        <is>
+          <t>🏠 Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="180" t="inlineStr">
+        <is>
+          <t>Anticipated pushback and the one-line answer. Back each with the named tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="181" t="inlineStr">
+        <is>
+          <t>Objection</t>
+        </is>
+      </c>
+      <c r="B4" s="181" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+      <c r="C4" s="181" t="inlineStr">
+        <is>
+          <t>Proof tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="87" t="inlineStr">
+        <is>
+          <t>“Isn't this just another me-too electrolyte?”</t>
+        </is>
+      </c>
+      <c r="B5" s="58" t="inlineStr">
+        <is>
+          <t>A flavored SPARKLING electrolyte is genuine white space; we own the daily-wellness sparkling occasion, made in Canada.</t>
+        </is>
+      </c>
+      <c r="C5" s="182" t="inlineStr">
+        <is>
+          <t>MÜV Peer Set / Deep-Dive</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="89" t="inlineStr">
+        <is>
+          <t>“Nestlé owns Vital Proteins, PepsiCo owns Poppi — can we even compete?”</t>
+        </is>
+      </c>
+      <c r="B6" s="60" t="inlineStr">
+        <is>
+          <t>We don't fight them on their shelf. We win the sparkling daily-wellness occasion in Canada where we already hold distribution + a collagen-brand halo.</t>
+        </is>
+      </c>
+      <c r="C6" s="183" t="inlineStr">
+        <is>
+          <t>15 Outcomes &amp; M&amp;A / GTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="87" t="inlineStr">
+        <is>
+          <t>“Collagen efficacy is contested — what's the legal exposure?”</t>
+        </is>
+      </c>
+      <c r="B7" s="58" t="inlineStr">
+        <is>
+          <t>Exactly why the CAN sells hydration/electrolyte (food claims). Collagen beauty claims stay on the NHP powder line, not the can.</t>
+        </is>
+      </c>
+      <c r="C7" s="182" t="inlineStr">
+        <is>
+          <t>Canada Regulatory v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="89" t="inlineStr">
+        <is>
+          <t>“Why a can, not a powder — powders ship cheaper?”</t>
+        </is>
+      </c>
+      <c r="B8" s="60" t="inlineStr">
+        <is>
+          <t>Sparkling is the wedge and the sensory differentiator; BC manufacturing protects margin. Regulatorily both are food now, so it's a commercial choice.</t>
+        </is>
+      </c>
+      <c r="C8" s="183" t="inlineStr">
+        <is>
+          <t>Electrolyte BFY Deep-Dive</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="87" t="inlineStr">
+        <is>
+          <t>“What's the regulatory risk in Canada?”</t>
+        </is>
+      </c>
+      <c r="B9" s="58" t="inlineStr">
+        <is>
+          <t>It's a Supplemented Food — design to that framework from day one (SFFt, cautions). ORS carve-out doesn't apply. Confirm the claim set with counsel.</t>
+        </is>
+      </c>
+      <c r="C9" s="182" t="inlineStr">
+        <is>
+          <t>Canada Regulatory v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="89" t="inlineStr">
+        <is>
+          <t>“Is the financial model real?”</t>
+        </is>
+      </c>
+      <c r="B10" s="60" t="inlineStr">
+        <is>
+          <t>It's illustrative scaffolding — every input is flagged. Replace with co-packer/distributor quotes. Even the Conservative case has a defined break-even.</t>
+        </is>
+      </c>
+      <c r="C10" s="183" t="inlineStr">
+        <is>
+          <t>Financial Model / Assumptions Audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="87" t="inlineStr">
+        <is>
+          <t>“Why not just extend the existing powder line?”</t>
+        </is>
+      </c>
+      <c r="B11" s="58" t="inlineStr">
+        <is>
+          <t>The powder line stays (and keeps its collagen claims). MÜV captures the sparkling RTD occasion the powder can't.</t>
+        </is>
+      </c>
+      <c r="C11" s="182" t="inlineStr">
+        <is>
+          <t>MÜV Peer Set</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="89" t="inlineStr">
+        <is>
+          <t>“What exactly do you need from us?”</t>
+        </is>
+      </c>
+      <c r="B12" s="60" t="inlineStr">
+        <is>
+          <t>Approve Phase 0: confirm MÜV specs, regulatory sign-off, co-packer quote, and the Costco Canada beachhead.</t>
+        </is>
+      </c>
+      <c r="C12" s="183" t="inlineStr">
+        <is>
+          <t>Next Steps &amp; Gates</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -13768,7 +13989,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C9A227"/>
@@ -14082,7 +14303,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C9A227"/>
@@ -14320,196 +14541,6 @@
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00B45309"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:N7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Phased Launch Plan (0–18 months)</t>
-        </is>
-      </c>
-      <c r="M1" s="95" t="inlineStr">
-        <is>
-          <t>🏠 Home</t>
-        </is>
-      </c>
-      <c r="N1" s="95" t="inlineStr">
-        <is>
-          <t>↩ Contents</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Phase</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Timing</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Objectives</t>
-        </is>
-      </c>
-      <c r="D3" s="11" t="inlineStr">
-        <is>
-          <t>Key workstreams</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="inlineStr">
-        <is>
-          <t>Success gate</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="80" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Phase 0 — Foundation</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="inlineStr">
-        <is>
-          <t>Months 0–3</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>Lock product, claims, regulatory pathway, co-pack</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Finalize formula &amp; collagen dose; regulatory-counsel claim opinion (Supplemented Foods); co-packer quote &amp; MOQ; bilingual + Bill 96 artwork; brand/positioning</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory sign-off on claim set + artwork approved</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="80" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Phase 1 — Beachhead</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Months 3–9</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Prove velocity &amp; repeat in a contained beachhead</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Costco CA roadshows + Amazon.ca + Well.ca/Natura + Organika pharmacy/health-food base; podcast + reactive social; sampling</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>Repeat rate + velocity above category benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="80" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Phase 2 — Scale</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="inlineStr">
-        <is>
-          <t>Months 9–18</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>Earn conventional grocery on proven data</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Sell-in to Loblaw/Sobeys/Metro on velocity data; distributor (UNFI CA / Tree of Life); managed trade spend; add SKUs on repeat data</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>National listings won on data, not discounts</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Phase 3 — Defend &amp; extend</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>18 mo+</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Category leadership &amp; optionality</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Format/flavour extensions; deepen moat; evaluate strategic-partner vs independent scale</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>Profitable contribution + exit optionality</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
@@ -14535,21 +14566,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Risk Register</t>
+          <t>Phased Launch Plan (0–18 months)</t>
         </is>
       </c>
       <c r="M1" s="95" t="inlineStr">
@@ -14563,513 +14593,144 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Likelihood × Impact (H/M/L). Ranked by exposure</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
-        <is>
-          <t>Risk</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Likelihood</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Impact</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
-        <is>
-          <t>Mitigation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="46" customHeight="1">
-      <c r="A5" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Collagen efficacy / claims liability (2025 meta-analysis; Poppi-style dose-insufficiency suit)</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory/Legal</t>
-        </is>
-      </c>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>Dose to efficacy (2.5g+); structure/function-safe language; substantiation files; lead with gut/hydration not beauty</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Strategic-owned competition (Nestlé owns Vital Proteins; PepsiCo/Unilever firepower)</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Competitive</t>
-        </is>
-      </c>
-      <c r="D6" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="E6" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="inlineStr">
-        <is>
-          <t>Compete on Canadian-made + domestic cost edge + Organika collagen credibility; niche beachhead before they react</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Canada claim/label pathway misread (food vs NHP; SFCI; collagen caution)</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory</t>
-        </is>
-      </c>
-      <c r="D7" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E7" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Regulatory-counsel opinion before artwork; design to Supplemented Foods framework; caffeine-free</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>Over-distribution before product-market fit</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>Execution</t>
-        </is>
-      </c>
-      <c r="D8" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E8" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F8" s="13" t="inlineStr">
-        <is>
-          <t>Prove velocity/repeat in beachhead before national; gate Phase 2 on data</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Slotting / trade-spend cash burn</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D9" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E9" s="31" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Use free-fill over cash slotting; 35–45% trade-spend budget; Code of Conduct leverage on arbitrary fees</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="46" customHeight="1">
-      <c r="A10" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>Thin differentiation / shelf saturation (prebiotic shelf filling fast)</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D10" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E10" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="inlineStr">
-        <is>
-          <t>Defensible spec (fiber + collagen dose) + function stacking; Canadian-made story</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="46" customHeight="1">
-      <c r="A11" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Private-label encroachment (~$277B, ~21% share, growing 2×)</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D11" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E11" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Brand equity + clinical-grade ingredients retailers can't easily copy</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="46" customHeight="1">
-      <c r="A12" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>DTC CAC / heavy-ship economics if DTC-led</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D12" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E12" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>Lead retail/beachhead not paid DTC; subscription + sampling only</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="46" customHeight="1">
-      <c r="A13" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Co-packer capacity / collagen sourcing / cost inflation</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>Operations</t>
-        </is>
-      </c>
-      <c r="D13" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E13" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>Lock co-pack capacity early; qualify 2nd collagen supplier; hedge raws</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="46" customHeight="1">
-      <c r="A14" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>FX / tariff / freight premium on cross-border inputs</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
-      <c r="D14" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E14" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>Domestic CA co-pack; monitor tariff status post-Dec 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="46" customHeight="1">
-      <c r="A15" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>GLP-1 demand shift away from sweet/snack</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>Macro</t>
-        </is>
-      </c>
-      <c r="D15" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="E15" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Low-cal, fiber, protein, hydration positioning aligns with GLP-1 users</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="46" customHeight="1">
-      <c r="A16" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>Brand/tone misstep at scale</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>Brand</t>
-        </is>
-      </c>
-      <c r="D16" s="33" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E16" s="32" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>Evolve tactics with stage; avoid Poppi-style stunts once mainstream</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="138" t="inlineStr">
-        <is>
-          <t>LIKELIHOOD × IMPACT HEATMAP (risk #s placed by rating)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="148" t="inlineStr">
-        <is>
-          <t>Impact ↓ / Likelihood →</t>
-        </is>
-      </c>
-      <c r="B20" s="149" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="C20" s="149" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="D20" s="149" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="149" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="B21" s="150" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C21" s="151" t="inlineStr">
-        <is>
-          <t>3, 4, 5</t>
-        </is>
-      </c>
-      <c r="D21" s="151" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="149" t="inlineStr">
-        <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="B22" s="152" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C22" s="150" t="inlineStr">
-        <is>
-          <t>6,7,8,9,10</t>
-        </is>
-      </c>
-      <c r="D22" s="151" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="149" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="B23" s="152" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C23" s="152" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="D23" s="150" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="133" t="inlineStr">
-        <is>
-          <t>Red = act now · Amber = manage · Green = monitor. Numbers refer to the risk # in the table above.</t>
+    <row r="3">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Timing</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Objectives</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>Key workstreams</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="inlineStr">
+        <is>
+          <t>Success gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="80" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Phase 0 — Foundation</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>Months 0–3</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>Lock product, claims, regulatory pathway, co-pack</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Finalize formula &amp; collagen dose; regulatory-counsel claim opinion (Supplemented Foods); co-packer quote &amp; MOQ; bilingual + Bill 96 artwork; brand/positioning</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory sign-off on claim set + artwork approved</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="80" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Phase 1 — Beachhead</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Months 3–9</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Prove velocity &amp; repeat in a contained beachhead</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Costco CA roadshows + Amazon.ca + Well.ca/Natura + Organika pharmacy/health-food base; podcast + reactive social; sampling</t>
+        </is>
+      </c>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>Repeat rate + velocity above category benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Phase 2 — Scale</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Months 9–18</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Earn conventional grocery on proven data</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Sell-in to Loblaw/Sobeys/Metro on velocity data; distributor (UNFI CA / Tree of Life); managed trade spend; add SKUs on repeat data</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>National listings won on data, not discounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="80" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Phase 3 — Defend &amp; extend</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>18 mo+</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Category leadership &amp; optionality</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Format/flavour extensions; deepen moat; evaluate strategic-partner vs independent scale</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>Profitable contribution + exit optionality</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A24:F24"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
@@ -15095,6 +14756,566 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:N24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Risk Register</t>
+        </is>
+      </c>
+      <c r="M1" s="95" t="inlineStr">
+        <is>
+          <t>🏠 Home</t>
+        </is>
+      </c>
+      <c r="N1" s="95" t="inlineStr">
+        <is>
+          <t>↩ Contents</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Likelihood × Impact (H/M/L). Ranked by exposure</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>Likelihood</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Mitigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>Collagen efficacy / claims liability (2025 meta-analysis; Poppi-style dose-insufficiency suit)</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory/Legal</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>Dose to efficacy (2.5g+); structure/function-safe language; substantiation files; lead with gut/hydration not beauty</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Strategic-owned competition (Nestlé owns Vital Proteins; PepsiCo/Unilever firepower)</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Competitive</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Compete on Canadian-made + domestic cost edge + Organika collagen credibility; niche beachhead before they react</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Canada claim/label pathway misread (food vs NHP; SFCI; collagen caution)</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Regulatory-counsel opinion before artwork; design to Supplemented Foods framework; caffeine-free</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Over-distribution before product-market fit</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Prove velocity/repeat in beachhead before national; gate Phase 2 on data</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Slotting / trade-spend cash burn</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Use free-fill over cash slotting; 35–45% trade-spend budget; Code of Conduct leverage on arbitrary fees</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Thin differentiation / shelf saturation (prebiotic shelf filling fast)</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Defensible spec (fiber + collagen dose) + function stacking; Canadian-made story</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Private-label encroachment (~$277B, ~21% share, growing 2×)</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Brand equity + clinical-grade ingredients retailers can't easily copy</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>DTC CAC / heavy-ship economics if DTC-led</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>Lead retail/beachhead not paid DTC; subscription + sampling only</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Co-packer capacity / collagen sourcing / cost inflation</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Lock co-pack capacity early; qualify 2nd collagen supplier; hedge raws</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>FX / tariff / freight premium on cross-border inputs</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>Domestic CA co-pack; monitor tariff status post-Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>GLP-1 demand shift away from sweet/snack</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>Macro</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>Low-cal, fiber, protein, hydration positioning aligns with GLP-1 users</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Brand/tone misstep at scale</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="D16" s="33" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Evolve tactics with stage; avoid Poppi-style stunts once mainstream</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="138" t="inlineStr">
+        <is>
+          <t>LIKELIHOOD × IMPACT HEATMAP (risk #s placed by rating)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="148" t="inlineStr">
+        <is>
+          <t>Impact ↓ / Likelihood →</t>
+        </is>
+      </c>
+      <c r="B20" s="149" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C20" s="149" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="D20" s="149" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="149" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="B21" s="150" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" s="151" t="inlineStr">
+        <is>
+          <t>3, 4, 5</t>
+        </is>
+      </c>
+      <c r="D21" s="151" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="149" t="inlineStr">
+        <is>
+          <t>Med</t>
+        </is>
+      </c>
+      <c r="B22" s="152" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C22" s="150" t="inlineStr">
+        <is>
+          <t>6,7,8,9,10</t>
+        </is>
+      </c>
+      <c r="D22" s="151" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="149" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="B23" s="152" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C23" s="152" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D23" s="150" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="133" t="inlineStr">
+        <is>
+          <t>Red = act now · Amber = manage · Green = monitor. Numbers refer to the risk # in the table above.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A24:F24"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;LOrganika MUV — Competitor Intelligence (confidential draft)&amp;R&amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00B45309"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -15454,7 +15675,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
@@ -16014,152 +16235,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00C9A227"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:M24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="153" t="inlineStr">
-        <is>
-          <t>Data Confidence Scoreboard</t>
-        </is>
-      </c>
-      <c r="M1" s="95" t="inlineStr">
-        <is>
-          <t>🏠 Home</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="154" t="inlineStr">
-        <is>
-          <t>Tally of confidence tags across the whole dossier — how much rests on hard evidence vs estimates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="74" t="inlineStr">
-        <is>
-          <t>Confidence tier</t>
-        </is>
-      </c>
-      <c r="B4" s="74" t="inlineStr">
-        <is>
-          <t>Marker</t>
-        </is>
-      </c>
-      <c r="C4" s="74" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="D4" s="74" t="inlineStr">
-        <is>
-          <t>Share</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="109" t="inlineStr">
-        <is>
-          <t>Hard (primary/scanner/regulatory)</t>
-        </is>
-      </c>
-      <c r="B5" s="144" t="inlineStr">
-        <is>
-          <t>✅ HARD</t>
-        </is>
-      </c>
-      <c r="C5" s="155" t="n">
-        <v>48</v>
-      </c>
-      <c r="D5" s="156" t="n">
-        <v>0.4403669724770642</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="59" t="inlineStr">
-        <is>
-          <t>Directional (research-firm/single-source)</t>
-        </is>
-      </c>
-      <c r="B6" s="144" t="inlineStr">
-        <is>
-          <t>◐ DIRECTIONAL</t>
-        </is>
-      </c>
-      <c r="C6" s="155" t="n">
-        <v>28</v>
-      </c>
-      <c r="D6" s="156" t="n">
-        <v>0.2568807339449541</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="157" t="inlineStr">
-        <is>
-          <t>Flag (estimate/verify/contested)</t>
-        </is>
-      </c>
-      <c r="B7" s="144" t="inlineStr">
-        <is>
-          <t>⚠ FLAG</t>
-        </is>
-      </c>
-      <c r="C7" s="155" t="n">
-        <v>33</v>
-      </c>
-      <c r="D7" s="156" t="n">
-        <v>0.3027522935779817</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="158" t="inlineStr">
-        <is>
-          <t>TOTAL tags</t>
-        </is>
-      </c>
-      <c r="C8" s="159" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="24" ht="44" customHeight="1">
-      <c r="A24" s="119" t="inlineStr">
-        <is>
-          <t>Read: a healthy dossier leans on hard/primary evidence for its load-bearing claims (verified on the Verification Log) while transparently flagging estimates. Market-size projections and all financial inputs are ◐/⚠ by nature — never quote them as fact.</t>
-        </is>
-      </c>
-      <c r="B24" s="34" t="n"/>
-      <c r="C24" s="34" t="n"/>
-      <c r="D24" s="35" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -16167,7 +16242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -16766,6 +16841,18 @@
       <c r="B52" s="103" t="inlineStr">
         <is>
           <t>Immediate actions &amp; decision gates with status</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="177" t="inlineStr">
+        <is>
+          <t>FAQ &amp; Objections</t>
+        </is>
+      </c>
+      <c r="B53" s="178" t="inlineStr">
+        <is>
+          <t>Anticipated leadership pushback + crisp answers, with proof tabs</t>
         </is>
       </c>
     </row>
@@ -16817,6 +16904,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -16836,6 +16924,152 @@
   <sheetPr>
     <tabColor rgb="00C9A227"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="153" t="inlineStr">
+        <is>
+          <t>Data Confidence Scoreboard</t>
+        </is>
+      </c>
+      <c r="M1" s="95" t="inlineStr">
+        <is>
+          <t>🏠 Home</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="154" t="inlineStr">
+        <is>
+          <t>Tally of confidence tags across the whole dossier — how much rests on hard evidence vs estimates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="74" t="inlineStr">
+        <is>
+          <t>Confidence tier</t>
+        </is>
+      </c>
+      <c r="B4" s="74" t="inlineStr">
+        <is>
+          <t>Marker</t>
+        </is>
+      </c>
+      <c r="C4" s="74" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="D4" s="74" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="109" t="inlineStr">
+        <is>
+          <t>Hard (primary/scanner/regulatory)</t>
+        </is>
+      </c>
+      <c r="B5" s="144" t="inlineStr">
+        <is>
+          <t>✅ HARD</t>
+        </is>
+      </c>
+      <c r="C5" s="155" t="n">
+        <v>48</v>
+      </c>
+      <c r="D5" s="156" t="n">
+        <v>0.4403669724770642</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="59" t="inlineStr">
+        <is>
+          <t>Directional (research-firm/single-source)</t>
+        </is>
+      </c>
+      <c r="B6" s="144" t="inlineStr">
+        <is>
+          <t>◐ DIRECTIONAL</t>
+        </is>
+      </c>
+      <c r="C6" s="155" t="n">
+        <v>28</v>
+      </c>
+      <c r="D6" s="156" t="n">
+        <v>0.2568807339449541</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="157" t="inlineStr">
+        <is>
+          <t>Flag (estimate/verify/contested)</t>
+        </is>
+      </c>
+      <c r="B7" s="144" t="inlineStr">
+        <is>
+          <t>⚠ FLAG</t>
+        </is>
+      </c>
+      <c r="C7" s="155" t="n">
+        <v>33</v>
+      </c>
+      <c r="D7" s="156" t="n">
+        <v>0.3027522935779817</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="158" t="inlineStr">
+        <is>
+          <t>TOTAL tags</t>
+        </is>
+      </c>
+      <c r="C8" s="159" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="119" t="inlineStr">
+        <is>
+          <t>Read: a healthy dossier leans on hard/primary evidence for its load-bearing claims (verified on the Verification Log) while transparently flagging estimates. Market-size projections and all financial inputs are ◐/⚠ by nature — never quote them as fact.</t>
+        </is>
+      </c>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="34" t="n"/>
+      <c r="D24" s="35" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N16"/>
@@ -17175,7 +17409,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00595959"/>
